--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
   <si>
     <t>Параметры:</t>
   </si>
@@ -78,31 +78,628 @@
     <t>ЛГУП-6441  </t>
   </si>
   <si>
-    <t>Втулка НТ.002.009.003 (долбежка паза)</t>
+    <t>Масло индустриальное YMOIL HC-68 (200л)</t>
+  </si>
+  <si>
+    <t>ЛГУП-6488  </t>
+  </si>
+  <si>
+    <t>УЗНО Счетчик Тор-50 Ха 2.833.034 1ExdIICT4 X, IP65</t>
+  </si>
+  <si>
+    <t>ЛГУП-6489  </t>
+  </si>
+  <si>
+    <t>Крышка ПСМНТ.001.000.007 (литье из стали 20Л)</t>
+  </si>
+  <si>
+    <t>ЛГУП-6499  </t>
+  </si>
+  <si>
+    <t>Хомуты НТ.010.000.000 СБ (Корпус) (литье из стали 20Л)</t>
+  </si>
+  <si>
+    <t>Угольник ПСМНТ.001.029.000 СБ (Корпус) (литье из стали 20Л)</t>
+  </si>
+  <si>
+    <t>Клапан предохранительный НТ.3.02.00.00.000 СБ (Корпус) (литье из стали 20Л)</t>
+  </si>
+  <si>
+    <t>Удостоверение </t>
   </si>
   <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>ЛГУП-6469  </t>
-  </si>
-  <si>
-    <t>УЗНО Пила ленточная 4080х34х1,1 Z3/4 R MASTER M51</t>
-  </si>
-  <si>
-    <t>ЛГУП-6487  </t>
-  </si>
-  <si>
-    <t>Масло индустриальное YMOIL HC-68 (200л)</t>
-  </si>
-  <si>
-    <t>ЛГУП-6488  </t>
-  </si>
-  <si>
-    <t>УЗНО Счетчик Тор-50 Ха 2.833.034 1ExdIICT4 X, IP65</t>
-  </si>
-  <si>
-    <t>ЛГУП-6489  </t>
+    <t>НТ00-000048</t>
+  </si>
+  <si>
+    <t>УЗНО Дверь левая с доводчиком2000х1000 мм (ВхШ) полотно RAL 9003 (белый)/ коробка (RAL 9003) (белый)</t>
+  </si>
+  <si>
+    <t>ЛГУП-6522  </t>
+  </si>
+  <si>
+    <t>УЗНО Дверь левая с доводчиком1900х1000 мм (ВхШ) полотно RAL 9003 (белый)/ коробка (RAL 9003) (белый)</t>
+  </si>
+  <si>
+    <t>Окно 1200х1100 мм / ПВХ-профили морозост. исп, RAL 7036 серый</t>
+  </si>
+  <si>
+    <t>УЗНО Лист S=16 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>кг</t>
+  </si>
+  <si>
+    <t>ЛГУП-6524  </t>
+  </si>
+  <si>
+    <t>УЗНО Лист S=14 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>УЗНО Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>УЗНО Лист 6,0 ГОСТ 19903-2015/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>УЗНО Лист чечевица В-К-ПУ-3,0 Ст3сп ГОСТ 8568-77</t>
+  </si>
+  <si>
+    <t>УЗНО Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
+  </si>
+  <si>
+    <t>УЗНО Лист ромб. О-ПН-4,0 Ст.09Г2С ГОСТ 8568-77</t>
+  </si>
+  <si>
+    <t>УЗНО Лист Б-ПН-4 ГОСТ 19903-2015/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>УЗНО Лист алюм. анод. сатин (черн/бел) 1,0</t>
+  </si>
+  <si>
+    <t>УЗНО Лист S=5 ГОСТ 19903-74 09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>УЗНО Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
+  </si>
+  <si>
+    <t>ЛГУП-6525  </t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М20 ГОСТ 9064 -75</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М20-6Н ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М20х1,5.6.019 ГОСТ 15522-73</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М24 оцинк. ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М24-7Н ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М27.7Н.09Г2С ОСТ 26-2041-96</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М6-6Н.5.019 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М8-6Н.016 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>УЗНО Гвозди П1,6х25 ГОСТ 4028-63</t>
+  </si>
+  <si>
+    <t>УЗНО Заклепка 4,8х8 оцинкованная</t>
+  </si>
+  <si>
+    <t>УЗНО Заклепка 4х8.31 ГОСТ 10299-80</t>
+  </si>
+  <si>
+    <t>УЗНО Заклепка вытяжная Al 4,0х8 din 7337</t>
+  </si>
+  <si>
+    <t>УЗНО Саморез для сэндвич панелей 5,5х100</t>
+  </si>
+  <si>
+    <t>УЗНО Саморез для сэндвич панелей 5,5х130</t>
+  </si>
+  <si>
+    <t>УЗНО Саморез для сэндвич панелей 5,5х25</t>
+  </si>
+  <si>
+    <t>УЗНО Саморез для сэндвич-панели 5,5х180</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М8-6Н ГОСТ 15521-70</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М10-6gх150.019 ГОСТ 7798-70 (DIN 933)</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М10х30 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М16-6gх110.58 ГОСТ 7805-70</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М20х50 ГОСТ15591-70</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М24-6gх70.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М6-6gх12.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М8-6gх120.58.019 ГОСТ 7801-81</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М8-6gх16 56.35.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М8-6gх40.58 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>УЗНО Болт М8-6gх45.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька М24х180 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М16 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М10.5 019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка АМ36-6Н.20lll.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>УЗНО Гайка АМ30-6Н.20.III.4.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>УЗНО Винт М6-6gх16.58.019 ГОСТ 17475-80</t>
+  </si>
+  <si>
+    <t>УЗНО Винт М4-6gх16.58.019 ГОСТ 17473-80</t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька М27х150.09Г2С ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька М20х110 ГОСТ 9066-75 </t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька М16х90 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька АМ16-6gx80 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька А1М36-6gx220.09Г2С ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька А1М30-6gx180.09Г2С ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>УЗНО Шпилька А1М20-6gх120.48.40Х.IV.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба С.20 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба С 10.019 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба М27 оцинк. ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба А.8.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба А 16.37 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба 8 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба 6.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба 36 ГОСТ 9065-75 (шт.)</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба 30.4.019 ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба 24 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба 12 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба 10.65Г.019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>УЗНО Шайба 10.02.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>УЗНО Саморез кровельный 5,5х25 RAL9003 (белый)</t>
+  </si>
+  <si>
+    <t>УЗНО Саморез кровельный 5,5х25 RAL1021 (желт)</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 4,8х19 с шайбой </t>
+  </si>
+  <si>
+    <t>Заклепка резьбовая Сварком М 5 НЕРЖ цб А2</t>
+  </si>
+  <si>
+    <t>УЗНО Эмаль алкидная 7040 (серая глянцевая) 3ton спрей 520мл</t>
+  </si>
+  <si>
+    <t>ЛГУП-6527  </t>
+  </si>
+  <si>
+    <t>УЗНО Растворитель 646 (0,5л)</t>
+  </si>
+  <si>
+    <t>УЗНО Краска-спрей SABOTAGE 39(черный)</t>
+  </si>
+  <si>
+    <t>УЗНО Краска-спрей SABOTAGE (красная)</t>
+  </si>
+  <si>
+    <t>УЗНО Краска-спрей SABOTAGE (желтая)</t>
+  </si>
+  <si>
+    <t>УЗНО Краска флуоресцентная красная (1 баллончик = 0,4кг)</t>
+  </si>
+  <si>
+    <t>УЗНО Растворитель Р-4 ГОСТ 7827-74</t>
+  </si>
+  <si>
+    <t>л (дм3)</t>
+  </si>
+  <si>
+    <t>УЗНО Грунт-эмаль 2К ПУ, RAL 9003 (белый)</t>
+  </si>
+  <si>
+    <t>УЗНО Разбавитель Procore Universal Thinner</t>
+  </si>
+  <si>
+    <t>УЗНО Грунт-эмаль 2К ПУ, RAL 8007 (коричневый)</t>
+  </si>
+  <si>
+    <t>УЗНО Грунт-эмаль 2КПУ THORAL RAL 9005</t>
+  </si>
+  <si>
+    <t>УЗНО Эмаль ПФ-115 (зеленая0,4кг)</t>
+  </si>
+  <si>
+    <t>УЗНО Грунт-эмаль 2К ПУ, RAL 7036 (серый)</t>
+  </si>
+  <si>
+    <t>УЗНО Грунт-эмаль 2К ПУ, RAL 3020 (красный)</t>
+  </si>
+  <si>
+    <t>УЗНО Грунт-эмаль 2К ПУ, RAL 1021 (желтый)</t>
+  </si>
+  <si>
+    <t>УЗНО разбавитель СОЛЬВ-УР </t>
+  </si>
+  <si>
+    <t>УЗНО Краска Эмаль ПФ-115-серая</t>
+  </si>
+  <si>
+    <t>УЗНО Краска порошковая RAL 9005 (черный) гладкая</t>
+  </si>
+  <si>
+    <t>УЗНО Краска порошковая RAL 7040 (серый) гладкая</t>
+  </si>
+  <si>
+    <t>УЗНО Краска оранж ПФ-115</t>
+  </si>
+  <si>
+    <t>УЗНО Грунт-эмаль Дюропокс ДТМ 80 (внутрянка)</t>
+  </si>
+  <si>
+    <t>УЗНО Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
+  </si>
+  <si>
+    <t>УЗНО Панель стеновая ПТСМ 3100х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>ЛГУП-6528  </t>
+  </si>
+  <si>
+    <t>УЗНО Панель стеновая ПТСМ 3100х1000х100 9003/9003</t>
+  </si>
+  <si>
+    <t>УЗНО Панель стеновая ПТСМ 2900х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>УЗНО Панель стеновая ПТСМ 2500х1000х80 RAL 1021 (желт) снаружи/ RAL 9003 (белый) внутри</t>
+  </si>
+  <si>
+    <t>УЗНО Панель стеновая ПТСМ 2300х1000х80,  снаружи RAL 1021 / внутри RAL 9003</t>
+  </si>
+  <si>
+    <t>УЗНО Лист профилированный С21-1000-0,7 L=1660мм RAL 1021 (желтый)</t>
+  </si>
+  <si>
+    <t>УЗНО Лист профилированный С21-1000-0,7 L=1600мм RAL 1021 (желтый)</t>
+  </si>
+  <si>
+    <t>УЗНО Лист профилированный С21-1000-0,7 L=1015мм RAL 1021 (желт)</t>
+  </si>
+  <si>
+    <t>УЗНО Лист гладкий 0,5 1250х2500мм (для доборных элементов)</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2920х1000х150 RAL 9003 (белый)</t>
+  </si>
+  <si>
+    <t>УЗНО Уплотнитель профнастила С-21 на клейкой основе</t>
+  </si>
+  <si>
+    <t>пог. м</t>
+  </si>
+  <si>
+    <t>УЗНО Паронит ПМБ 2 ГОСТ 481-80</t>
+  </si>
+  <si>
+    <t>ЛГУП-6531  </t>
+  </si>
+  <si>
+    <t>УЗНО Паронит ПОН 2,0 ГОСТ 481-80 (кг)</t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D30 П-15Б-20  ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D40 П-15Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>УЗНО 2-х вентильный клапанный блок КБ-2х40.01(M20x1,5Н,M20x1,5B; M14x1,5B) </t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D70 П-12Б-20 ТУ 6-05-898-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 014-018-25 ГОСТ 9833-73 (фторкаучук)</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 018-021-19-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 020-025-30-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 028-032-25-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 055-060-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 060-065-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 062-068-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 070-076-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 080-085-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 080-086-36-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D80 П-12Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное НТ.202.003.004.0</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо А18х1,2 ГОСТ 13942-86</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 200-210-46-1-1 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо А20х1,2 ГОСТ 13940-86</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо А75 ГОСТ 13943-86 (с пазами)</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо А75х1,7 ГОСТ 13943-86_УЗНО</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 100-106-36-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 096-102-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо уплотнительное НТ.300.000.010.0</t>
+  </si>
+  <si>
+    <t>УЗНО Магнит D4х5 неодимовый</t>
+  </si>
+  <si>
+    <t>УЗНО Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
+  </si>
+  <si>
+    <t>УЗНО Пружина №442 НТ.110.000.007.0 </t>
+  </si>
+  <si>
+    <t>УЗНО Пружина №467 НТ.200.000.029.0</t>
+  </si>
+  <si>
+    <t>УЗНО Пружина крышки НТ.200.004.003.0</t>
+  </si>
+  <si>
+    <t>Шибер НТ.530.000.005.0 (лазер)</t>
+  </si>
+  <si>
+    <t>ЛГУП-6533  </t>
+  </si>
+  <si>
+    <t>УЗНО Рычаг НТ.510.000.003.0 (лазер)</t>
+  </si>
+  <si>
+    <t>Шибер НТ.530.000.005.0 (шлифовка)</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D159х25 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>ЛГУП-6534  </t>
+  </si>
+  <si>
+    <t>УЗНО Труба D20х6 09Г2С</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D219х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D85х10 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D22х4 09Г2С</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D720х14 Ст.09Г2С-К50 ГОСТ 20295-85</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D159х14 ГОСТ 8732-78/ Ст.09Г2С-3 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D152х5 09Г2С ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D14х2 09Г2С ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D133х32 Ст.20 ГОСТ 8372-78</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D133х28 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D133х25 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D273х16 Ст.09Г2С-3 ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D32х4 Ст.09Г2С ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D480х16 10Г2 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D57х6 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D83х12 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>УЗНО Труба 108х8 ст.09Г2С ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D1020х16 ст.09Г2С ГОСТ 20295-85</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D108х19 ГОСТ 8732-78/ Ст.09Г2С ГОСТ 19281-14</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D108х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D89х8 Ст.35 ГОСТ 1050-80</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>УЗНО Задвижка клиновая стальная ЗКС Ду25 Ру160 УХЛ1, класс герметичности "А"</t>
+  </si>
+  <si>
+    <t>ЛГУП-6535  </t>
+  </si>
+  <si>
+    <t>УЗНО Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+  </si>
+  <si>
+    <t>УЗНО Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
+  </si>
+  <si>
+    <t>УЗНО Задвижка ЗКЛ 50-40 ХЛ1 30лс15нж класс герм. А, исп.F ХЛ1 L=216 без КОФ</t>
+  </si>
+  <si>
+    <t>Клапан предохранительный СППК4р 17с25нж Ду80 Ру40</t>
+  </si>
+  <si>
+    <t>ЛГУП-6540  </t>
+  </si>
+  <si>
+    <t>УЗНО Труба D85х15 БрКМц 3-1 ГОСТ 1628-78</t>
+  </si>
+  <si>
+    <t>ЛГУП-6542  </t>
+  </si>
+  <si>
+    <t>УЗНО Труба D75х10 БрКМц 3-1 ГОСТ 1628-78</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D20х5 БрКМц 3-1 ГОСТ 1208-2014</t>
+  </si>
+  <si>
+    <t>УЗНО Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
+  </si>
+  <si>
+    <t>ЛГУП-6544  </t>
   </si>
   <si>
     <t>Сапоги рабочие </t>
@@ -111,148 +708,289 @@
     <t>пар</t>
   </si>
   <si>
-    <t>НТУП-017669</t>
+    <t>НТУП-017680</t>
+  </si>
+  <si>
+    <t>спец одежда летняя</t>
+  </si>
+  <si>
+    <t>Шапка ВЕСНА флисовая </t>
   </si>
   <si>
     <t>Костюм утепленный Метель</t>
   </si>
   <si>
-    <t>Шапка трикотажная зимняя </t>
-  </si>
-  <si>
-    <t>Перчатки зимние</t>
-  </si>
-  <si>
-    <t>Хомуты НТ.010.000.000 СБ (Корпус) (литье из стали 20Л)</t>
-  </si>
-  <si>
-    <t>ЛГУП-6499  </t>
-  </si>
-  <si>
-    <t>Клапан предохранительный НТ.3.02.00.00.000 СБ (Корпус) (литье из стали 20Л)</t>
-  </si>
-  <si>
-    <t>Угольник ПСМНТ.001.029.000 СБ (Корпус) (литье из стали 20Л)</t>
-  </si>
-  <si>
-    <t>Крышка ПСМНТ.001.000.007 (литье из стали 20Л)</t>
-  </si>
-  <si>
-    <t>Пружина №16</t>
-  </si>
-  <si>
-    <t>ЛГУП-6503  </t>
-  </si>
-  <si>
-    <t>Веник сорго /шт/</t>
-  </si>
-  <si>
-    <t>ЛГУП-6512  </t>
-  </si>
-  <si>
-    <t>Линейка 30 см прозрачная</t>
-  </si>
-  <si>
-    <t>Корректирующая ручка</t>
-  </si>
-  <si>
-    <t>Ручка шариковая (набор)</t>
-  </si>
-  <si>
-    <t>Скобы для степлера 24/6</t>
-  </si>
-  <si>
-    <t>Скрепки канцелярские</t>
-  </si>
-  <si>
-    <t>Степлер №24</t>
-  </si>
-  <si>
-    <t>Бумага для заметок</t>
-  </si>
-  <si>
-    <t>Салфетки для экранов всех типов и пластика (запасной блок) BRAUBERG,пакет 100шт,влажные</t>
-  </si>
-  <si>
-    <t>Точилка для карандаша 2 в1 /5/2880</t>
-  </si>
-  <si>
-    <t>УЗНО Нож канцелярский 25мм двухкомпонентный корпус</t>
-  </si>
-  <si>
-    <t>УЗНО Файловый вкладыш А4 /упак/</t>
-  </si>
-  <si>
-    <t>Бумага А4 500л.</t>
-  </si>
-  <si>
-    <t>Карандаш чернографитный, шестигранный, с ластиком (12шт в пакете) /12/2880</t>
-  </si>
-  <si>
-    <t>Клей карандаш</t>
-  </si>
-  <si>
-    <t>Корректирующая жидкость (штрих) с 15-20 мл</t>
-  </si>
-  <si>
-    <t>Бумага с клеевым краем (стикер) 80х80</t>
-  </si>
-  <si>
-    <t>УЗНО Решетка наружная нерегулируемая ВРН 200x200</t>
-  </si>
-  <si>
-    <t>ЛГУП-6514  </t>
-  </si>
-  <si>
-    <t>Вентилятор осевой накладной Ровен VC-125  IP54 0,15 кВт, 220V, 50Гц</t>
-  </si>
-  <si>
-    <t>Воздуховод (проходка) круглый D125 110 мм, оц.-0,5, фланец - нипель</t>
-  </si>
-  <si>
-    <t>Хомут соединительный 125</t>
-  </si>
-  <si>
-    <t>УЗНО смазка Русма-1</t>
-  </si>
-  <si>
-    <t>л.</t>
-  </si>
-  <si>
-    <t>ЛГУП-6516  </t>
-  </si>
-  <si>
-    <t>Лист S=40 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>кг</t>
-  </si>
-  <si>
-    <t>ЛГУП-6517  </t>
-  </si>
-  <si>
-    <t>УЗНО Труба D426х50 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>ЛГУП-6518  </t>
-  </si>
-  <si>
-    <t>УЗНО Круг D370 Ст.20 ГОСТ1050-88</t>
-  </si>
-  <si>
-    <t>ЛГУП-6519  </t>
-  </si>
-  <si>
-    <t>Удостоверение </t>
-  </si>
-  <si>
-    <t>НТ00-000048</t>
-  </si>
-  <si>
-    <t>Стропа 10 тонн 6 метров</t>
-  </si>
-  <si>
-    <t>ЛГУП-6520  </t>
+    <t>УЗНО Разъем: вилка на панель, крепление гайкой Weipu SF1012/P2 и розетка кабельная Weipu SF1010/S2I</t>
+  </si>
+  <si>
+    <t>ЛГУП-6554  </t>
+  </si>
+  <si>
+    <t>УЗНО Геркон КЭМ-2а</t>
+  </si>
+  <si>
+    <t>УЗНО металлорукав D20</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>УЗНО Блок электронный BP15C</t>
+  </si>
+  <si>
+    <t>УЗНО Провод ПУВ 1х0,75 ТУ16-705.501-2010</t>
+  </si>
+  <si>
+    <t>УЗНО Муфта вводная для труб гофрированных D=16 мм ТУ 2248-007-57453845-2009</t>
+  </si>
+  <si>
+    <t>УЗНО Вентиль манометрический ВПЭМ 5х35 1/2-В М20х1,5-В</t>
+  </si>
+  <si>
+    <t>ЛГУП-6555  </t>
+  </si>
+  <si>
+    <t>УЗНО Уплотнение ПСМНТ.001.022.002</t>
+  </si>
+  <si>
+    <t>УЗНО Манометр МП4 P=0..6МПа, ХЛ1 ст.защиты корпуса IP54, кл.точн. 1,0. Присоед-е: М20х1,5 - наружн</t>
+  </si>
+  <si>
+    <t>УЗНО Манометр МП2-УУ2-6,0 МРа</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 016-020-25-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 018-021-19 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 038-042-25 ГОСТ 9833-70</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 040-048-46-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 048-054-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 055-060-30-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 065-075-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 067-075-46-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 070-080-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 075-080-30-2-2 ГОСТ 9833-77</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 080-085-30-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 080-086-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D130 П-12Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D20 П-12Б-20  ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D40 ПА-6-210КС ОСТ6-11-498-79</t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D50 П-12Б-20 ТУ 6-05-898-73</t>
+  </si>
+  <si>
+    <t>УЗНО Полиамид D80 П-12Б-20 ТУ  6-05-988-87</t>
+  </si>
+  <si>
+    <t>УЗНО Фторопласт Ф-4 ПН 1 ГОСТ 24222-80</t>
+  </si>
+  <si>
+    <t>УЗНО Фторопласт Ф-4 пластина 2,0мм</t>
+  </si>
+  <si>
+    <t>УЗНО Пружина ПСМНТ.001.000.030</t>
+  </si>
+  <si>
+    <t>УЗНО Пружина ПСМНТ.001.000.013 (покупная)</t>
+  </si>
+  <si>
+    <t>УЗНО Пружина ПСМНТ.001.000.012</t>
+  </si>
+  <si>
+    <t>УЗНО Пружина НТ.3.02.00.00.002-01</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо уплотнительное ПСМНТ.001.000.025</t>
+  </si>
+  <si>
+    <t>Не исп. УЗНО Кольцо уплотнительное НТ.202.003.004.0</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 350-360-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 210-220-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 130-140-58 ГОСТ 9833-70</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 118-124-36-2-2 ГОСТ 9833-85</t>
+  </si>
+  <si>
+    <t>УЗНО Кольцо 112-118-36 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>УЗНО Отвод 90-57х5-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>ЛГУП-6564  </t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-16 ПМБ-1 ГОСТ15180-86</t>
+  </si>
+  <si>
+    <t>ЛГУП-6567  </t>
+  </si>
+  <si>
+    <t>Прокладка Б-32-16 ПМБ-1 ГОСТ15180-86</t>
+  </si>
+  <si>
+    <t>ТОР 50</t>
+  </si>
+  <si>
+    <t>НТУП-017684</t>
+  </si>
+  <si>
+    <t>Телефон Yealink SIP-T19 1502SN00631</t>
+  </si>
+  <si>
+    <t>ЛГУП-6570  </t>
+  </si>
+  <si>
+    <t>Комбинезон пескоструйщика Вектор с перчатками size:56-58/170-176 арт.25658176</t>
+  </si>
+  <si>
+    <t>ЛГУП-6573  </t>
+  </si>
+  <si>
+    <t>Комбинезон пескоструйщика CONTRACTOR ХL-56</t>
+  </si>
+  <si>
+    <t>Комбинезон пескоструйщика CONTRACTOR L-54</t>
+  </si>
+  <si>
+    <t>Комбинезон химзащиты Jeta Safety 65г/м^2 Size:XL-52-54 JPC-60-XL</t>
+  </si>
+  <si>
+    <t>Коническая фильтрующая полумаска ЗУБР FFP3 с клапаном</t>
+  </si>
+  <si>
+    <t>уп.</t>
+  </si>
+  <si>
+    <t>Костюм рабочий Size: 56-58/170-176</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 42</t>
+  </si>
+  <si>
+    <t>Внутреннее стекло 180х125х2 для шлема пескострущика Vector арт.52009</t>
+  </si>
+  <si>
+    <t>Краги сварочные спилковые пятипалые усиленные (желтый/красный) Артикул 113916</t>
+  </si>
+  <si>
+    <t>Стекло наружное для шлема пескоструйщика Vector арт.52010 180х125х4</t>
+  </si>
+  <si>
+    <t>Тумба выкатная на 3 ящика Т-3,вишня,45*45*62</t>
+  </si>
+  <si>
+    <t>ЛГУП-6574  </t>
+  </si>
+  <si>
+    <t>Модуль аналогового ввода (Ai) (16 каналов) версия 1 АВПЮ.426439.001-04-01</t>
+  </si>
+  <si>
+    <t>ЛГУП-6575  </t>
+  </si>
+  <si>
+    <t>Модуль дискретного ввода-вывода (16 каналов) АВПЮ.426441.360-04-01 исполнение 4.1-1</t>
+  </si>
+  <si>
+    <t>Панель оператора Weintek cMT2158X, 15″</t>
+  </si>
+  <si>
+    <t>Контролер Ария ver.4.5 (4 AI, 4 DI/DO, 4 порта RS485) АВПЮ.426441.358-10-02</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>Онлайн ИБП ST1101 SL (1000 ВА / 900 Вт) Штиль</t>
+  </si>
+  <si>
+    <t>ЛГУП-6576  </t>
+  </si>
+  <si>
+    <t>Блок питания AC-DC 100Вт вх.85-264V AC 47-63Гц 120-370В вых.24В кожух DIN-рейки MDR-100-24 Mean Well</t>
+  </si>
+  <si>
+    <t>ЛГУП-6577  </t>
+  </si>
+  <si>
+    <t>Блок питания AC-DC, 120Вт, вход 90-264V AC, 47-63Гц,127-370В DC, выход 24В,5A, рег. вых 24-28В, в ко</t>
+  </si>
+  <si>
+    <t>ЛГУП-6578  </t>
+  </si>
+  <si>
+    <t>Фланец 50-16-01-1-B-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>ЛГУП-6579  </t>
+  </si>
+  <si>
+    <t>Фланец 32-16-11-1-В-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Инвентарь:щётка жёсткая</t>
+  </si>
+  <si>
+    <t>ЛГУП-6581  </t>
+  </si>
+  <si>
+    <t>Инвентарь:щётка мягкая</t>
+  </si>
+  <si>
+    <t>Сопло 8х150 карбид бора (В4С)</t>
+  </si>
+  <si>
+    <t>Сопло для пескоструйного аппарата , вход 32мм РТС 8мм арт.10112063</t>
+  </si>
+  <si>
+    <t>Сопло пескоструйного цилиндрическое 8х125  Карбид Бора , алюминий </t>
+  </si>
+  <si>
+    <t>Соплодержатель нейлоновый для рукава 25х39</t>
+  </si>
+  <si>
+    <t>Шланг пескоструйный Диаметр 25х39, 20 метров XSTRA SANDBLAST 12BAR-B.P.36BAR</t>
+  </si>
+  <si>
+    <t>Шланг пескоструйный Диаметр 25х39, 40 метров, байонетное сцепление </t>
   </si>
 </sst>
 </file>
@@ -435,7 +1173,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="true"/>
   </sheetPr>
-  <dimension ref="I50"/>
+  <dimension ref="I318"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="5.16796875" style="1" customWidth="true"/>
@@ -554,13 +1292,13 @@
       </c>
       <c r="F11" s="9" t="e"/>
       <c r="G11" s="10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -571,17 +1309,17 @@
       <c r="C12" s="7" t="e"/>
       <c r="D12" s="8" t="e"/>
       <c r="E12" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="9" t="e"/>
       <c r="G12" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true">
@@ -592,17 +1330,17 @@
       <c r="C13" s="7" t="e"/>
       <c r="D13" s="8" t="e"/>
       <c r="E13" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="9" t="e"/>
       <c r="G13" s="10" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true">
@@ -613,17 +1351,17 @@
       <c r="C14" s="7" t="e"/>
       <c r="D14" s="8" t="e"/>
       <c r="E14" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" s="9" t="e"/>
       <c r="G14" s="10" t="n">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="11" customHeight="true">
@@ -634,17 +1372,17 @@
       <c r="C15" s="7" t="e"/>
       <c r="D15" s="8" t="e"/>
       <c r="E15" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F15" s="9" t="e"/>
       <c r="G15" s="10" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="11" customHeight="true">
@@ -655,17 +1393,17 @@
       <c r="C16" s="7" t="e"/>
       <c r="D16" s="8" t="e"/>
       <c r="E16" s="9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F16" s="9" t="e"/>
       <c r="G16" s="10" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" ht="11" customHeight="true">
@@ -676,20 +1414,20 @@
       <c r="C17" s="7" t="e"/>
       <c r="D17" s="8" t="e"/>
       <c r="E17" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F17" s="9" t="e"/>
       <c r="G17" s="10" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" ht="11" customHeight="true">
+    <row r="18" ht="23" customHeight="true">
       <c r="A18" s="5" t="n">
         <v>9</v>
       </c>
@@ -697,20 +1435,20 @@
       <c r="C18" s="7" t="e"/>
       <c r="D18" s="8" t="e"/>
       <c r="E18" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F18" s="9" t="e"/>
       <c r="G18" s="10" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" ht="11" customHeight="true">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="23" customHeight="true">
       <c r="A19" s="5" t="n">
         <v>10</v>
       </c>
@@ -718,17 +1456,17 @@
       <c r="C19" s="7" t="e"/>
       <c r="D19" s="8" t="e"/>
       <c r="E19" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19" s="9" t="e"/>
       <c r="G19" s="10" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H19" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true">
@@ -739,17 +1477,17 @@
       <c r="C20" s="7" t="e"/>
       <c r="D20" s="8" t="e"/>
       <c r="E20" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F20" s="9" t="e"/>
       <c r="G20" s="10" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true">
@@ -760,17 +1498,17 @@
       <c r="C21" s="7" t="e"/>
       <c r="D21" s="8" t="e"/>
       <c r="E21" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F21" s="9" t="e"/>
       <c r="G21" s="10" t="n">
-        <v>300</v>
+        <v>40.86</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true">
@@ -785,13 +1523,13 @@
       </c>
       <c r="F22" s="9" t="e"/>
       <c r="G22" s="10" t="n">
-        <v>300</v>
+        <v>399.96</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true">
@@ -806,13 +1544,13 @@
       </c>
       <c r="F23" s="9" t="e"/>
       <c r="G23" s="10" t="n">
-        <v>4</v>
+        <v>181.92</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true">
@@ -823,17 +1561,17 @@
       <c r="C24" s="7" t="e"/>
       <c r="D24" s="8" t="e"/>
       <c r="E24" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F24" s="9" t="e"/>
       <c r="G24" s="10" t="n">
-        <v>5</v>
+        <v>16.57</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true">
@@ -844,17 +1582,17 @@
       <c r="C25" s="7" t="e"/>
       <c r="D25" s="8" t="e"/>
       <c r="E25" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F25" s="9" t="e"/>
       <c r="G25" s="10" t="n">
-        <v>3</v>
+        <v>11.47</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true">
@@ -865,17 +1603,17 @@
       <c r="C26" s="7" t="e"/>
       <c r="D26" s="8" t="e"/>
       <c r="E26" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F26" s="9" t="e"/>
       <c r="G26" s="10" t="n">
-        <v>4</v>
+        <v>411</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true">
@@ -886,17 +1624,17 @@
       <c r="C27" s="7" t="e"/>
       <c r="D27" s="8" t="e"/>
       <c r="E27" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F27" s="9" t="e"/>
       <c r="G27" s="10" t="n">
-        <v>1</v>
+        <v>668.19</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true">
@@ -907,17 +1645,17 @@
       <c r="C28" s="7" t="e"/>
       <c r="D28" s="8" t="e"/>
       <c r="E28" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F28" s="9" t="e"/>
       <c r="G28" s="10" t="n">
-        <v>6</v>
+        <v>151.53</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" ht="11" customHeight="true">
@@ -928,17 +1666,17 @@
       <c r="C29" s="7" t="e"/>
       <c r="D29" s="8" t="e"/>
       <c r="E29" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F29" s="9" t="e"/>
       <c r="G29" s="10" t="n">
-        <v>5</v>
+        <v>0.865</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true">
@@ -949,17 +1687,17 @@
       <c r="C30" s="7" t="e"/>
       <c r="D30" s="8" t="e"/>
       <c r="E30" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F30" s="9" t="e"/>
       <c r="G30" s="10" t="n">
-        <v>2</v>
+        <v>14.89</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true">
@@ -970,20 +1708,20 @@
       <c r="C31" s="7" t="e"/>
       <c r="D31" s="8" t="e"/>
       <c r="E31" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F31" s="9" t="e"/>
       <c r="G31" s="10" t="n">
-        <v>3</v>
+        <v>622.03</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" ht="23" customHeight="true">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" ht="11" customHeight="true">
       <c r="A32" s="5" t="n">
         <v>23</v>
       </c>
@@ -991,17 +1729,17 @@
       <c r="C32" s="7" t="e"/>
       <c r="D32" s="8" t="e"/>
       <c r="E32" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F32" s="9" t="e"/>
       <c r="G32" s="10" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true">
@@ -1012,17 +1750,17 @@
       <c r="C33" s="7" t="e"/>
       <c r="D33" s="8" t="e"/>
       <c r="E33" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F33" s="9" t="e"/>
       <c r="G33" s="10" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true">
@@ -1033,17 +1771,17 @@
       <c r="C34" s="7" t="e"/>
       <c r="D34" s="8" t="e"/>
       <c r="E34" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F34" s="9" t="e"/>
       <c r="G34" s="10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true">
@@ -1054,17 +1792,17 @@
       <c r="C35" s="7" t="e"/>
       <c r="D35" s="8" t="e"/>
       <c r="E35" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F35" s="9" t="e"/>
       <c r="G35" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true">
@@ -1075,17 +1813,17 @@
       <c r="C36" s="7" t="e"/>
       <c r="D36" s="8" t="e"/>
       <c r="E36" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F36" s="9" t="e"/>
       <c r="G36" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" ht="11" customHeight="true">
@@ -1096,17 +1834,17 @@
       <c r="C37" s="7" t="e"/>
       <c r="D37" s="8" t="e"/>
       <c r="E37" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F37" s="9" t="e"/>
       <c r="G37" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true">
@@ -1117,17 +1855,17 @@
       <c r="C38" s="7" t="e"/>
       <c r="D38" s="8" t="e"/>
       <c r="E38" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F38" s="9" t="e"/>
       <c r="G38" s="10" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true">
@@ -1138,7 +1876,7 @@
       <c r="C39" s="7" t="e"/>
       <c r="D39" s="8" t="e"/>
       <c r="E39" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F39" s="9" t="e"/>
       <c r="G39" s="10" t="n">
@@ -1148,7 +1886,7 @@
         <v>15</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true">
@@ -1159,17 +1897,17 @@
       <c r="C40" s="7" t="e"/>
       <c r="D40" s="8" t="e"/>
       <c r="E40" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F40" s="9" t="e"/>
       <c r="G40" s="10" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true">
@@ -1180,17 +1918,17 @@
       <c r="C41" s="7" t="e"/>
       <c r="D41" s="8" t="e"/>
       <c r="E41" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F41" s="9" t="e"/>
       <c r="G41" s="10" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true">
@@ -1201,17 +1939,17 @@
       <c r="C42" s="7" t="e"/>
       <c r="D42" s="8" t="e"/>
       <c r="E42" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F42" s="9" t="e"/>
       <c r="G42" s="10" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="H42" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" ht="11" customHeight="true">
@@ -1222,7 +1960,7 @@
       <c r="C43" s="7" t="e"/>
       <c r="D43" s="8" t="e"/>
       <c r="E43" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F43" s="9" t="e"/>
       <c r="G43" s="10" t="n">
@@ -1232,7 +1970,7 @@
         <v>15</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true">
@@ -1243,17 +1981,17 @@
       <c r="C44" s="7" t="e"/>
       <c r="D44" s="8" t="e"/>
       <c r="E44" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F44" s="9" t="e"/>
       <c r="G44" s="10" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true">
@@ -1264,17 +2002,17 @@
       <c r="C45" s="7" t="e"/>
       <c r="D45" s="8" t="e"/>
       <c r="E45" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F45" s="9" t="e"/>
       <c r="G45" s="10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true">
@@ -1285,17 +2023,17 @@
       <c r="C46" s="7" t="e"/>
       <c r="D46" s="8" t="e"/>
       <c r="E46" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F46" s="9" t="e"/>
-      <c r="G46" s="12" t="n">
-        <v>2808</v>
+      <c r="G46" s="10" t="n">
+        <v>180</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true">
@@ -1306,17 +2044,17 @@
       <c r="C47" s="7" t="e"/>
       <c r="D47" s="8" t="e"/>
       <c r="E47" s="9" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F47" s="9" t="e"/>
-      <c r="G47" s="12" t="n">
-        <v>5200</v>
+      <c r="G47" s="10" t="n">
+        <v>220</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true">
@@ -1327,17 +2065,17 @@
       <c r="C48" s="7" t="e"/>
       <c r="D48" s="8" t="e"/>
       <c r="E48" s="9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F48" s="9" t="e"/>
-      <c r="G48" s="12" t="n">
-        <v>2500</v>
+      <c r="G48" s="10" t="n">
+        <v>100</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" ht="11" customHeight="true">
@@ -1348,17 +2086,17 @@
       <c r="C49" s="7" t="e"/>
       <c r="D49" s="8" t="e"/>
       <c r="E49" s="9" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F49" s="9" t="e"/>
       <c r="G49" s="10" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true">
@@ -1369,21 +2107,5649 @@
       <c r="C50" s="7" t="e"/>
       <c r="D50" s="8" t="e"/>
       <c r="E50" s="9" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F50" s="9" t="e"/>
       <c r="G50" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" ht="11" customHeight="true">
+      <c r="A51" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B51" s="6" t="e"/>
+      <c r="C51" s="7" t="e"/>
+      <c r="D51" s="8" t="e"/>
+      <c r="E51" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51" s="9" t="e"/>
+      <c r="G51" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" ht="11" customHeight="true">
+      <c r="A52" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="e"/>
+      <c r="C52" s="7" t="e"/>
+      <c r="D52" s="8" t="e"/>
+      <c r="E52" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F52" s="9" t="e"/>
+      <c r="G52" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" ht="11" customHeight="true">
+      <c r="A53" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B53" s="6" t="e"/>
+      <c r="C53" s="7" t="e"/>
+      <c r="D53" s="8" t="e"/>
+      <c r="E53" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F53" s="9" t="e"/>
+      <c r="G53" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H50" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" s="9" t="s">
+      <c r="H53" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" ht="11" customHeight="true">
+      <c r="A54" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="6" t="e"/>
+      <c r="C54" s="7" t="e"/>
+      <c r="D54" s="8" t="e"/>
+      <c r="E54" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54" s="9" t="e"/>
+      <c r="G54" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" ht="11" customHeight="true">
+      <c r="A55" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B55" s="6" t="e"/>
+      <c r="C55" s="7" t="e"/>
+      <c r="D55" s="8" t="e"/>
+      <c r="E55" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F55" s="9" t="e"/>
+      <c r="G55" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" ht="11" customHeight="true">
+      <c r="A56" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B56" s="6" t="e"/>
+      <c r="C56" s="7" t="e"/>
+      <c r="D56" s="8" t="e"/>
+      <c r="E56" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" s="9" t="e"/>
+      <c r="G56" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" ht="11" customHeight="true">
+      <c r="A57" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="6" t="e"/>
+      <c r="C57" s="7" t="e"/>
+      <c r="D57" s="8" t="e"/>
+      <c r="E57" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" s="9" t="e"/>
+      <c r="G57" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" ht="11" customHeight="true">
+      <c r="A58" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B58" s="6" t="e"/>
+      <c r="C58" s="7" t="e"/>
+      <c r="D58" s="8" t="e"/>
+      <c r="E58" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F58" s="9" t="e"/>
+      <c r="G58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" ht="11" customHeight="true">
+      <c r="A59" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B59" s="6" t="e"/>
+      <c r="C59" s="7" t="e"/>
+      <c r="D59" s="8" t="e"/>
+      <c r="E59" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="9" t="e"/>
+      <c r="G59" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" ht="11" customHeight="true">
+      <c r="A60" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B60" s="6" t="e"/>
+      <c r="C60" s="7" t="e"/>
+      <c r="D60" s="8" t="e"/>
+      <c r="E60" s="9" t="s">
         <v>75</v>
       </c>
+      <c r="F60" s="9" t="e"/>
+      <c r="G60" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" ht="11" customHeight="true">
+      <c r="A61" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B61" s="6" t="e"/>
+      <c r="C61" s="7" t="e"/>
+      <c r="D61" s="8" t="e"/>
+      <c r="E61" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="9" t="e"/>
+      <c r="G61" s="10" t="n">
+        <v>448</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" ht="11" customHeight="true">
+      <c r="A62" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B62" s="6" t="e"/>
+      <c r="C62" s="7" t="e"/>
+      <c r="D62" s="8" t="e"/>
+      <c r="E62" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F62" s="9" t="e"/>
+      <c r="G62" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" ht="11" customHeight="true">
+      <c r="A63" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B63" s="6" t="e"/>
+      <c r="C63" s="7" t="e"/>
+      <c r="D63" s="8" t="e"/>
+      <c r="E63" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F63" s="9" t="e"/>
+      <c r="G63" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" ht="11" customHeight="true">
+      <c r="A64" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B64" s="6" t="e"/>
+      <c r="C64" s="7" t="e"/>
+      <c r="D64" s="8" t="e"/>
+      <c r="E64" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F64" s="9" t="e"/>
+      <c r="G64" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" ht="11" customHeight="true">
+      <c r="A65" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B65" s="6" t="e"/>
+      <c r="C65" s="7" t="e"/>
+      <c r="D65" s="8" t="e"/>
+      <c r="E65" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F65" s="9" t="e"/>
+      <c r="G65" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" ht="11" customHeight="true">
+      <c r="A66" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B66" s="6" t="e"/>
+      <c r="C66" s="7" t="e"/>
+      <c r="D66" s="8" t="e"/>
+      <c r="E66" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F66" s="9" t="e"/>
+      <c r="G66" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" ht="11" customHeight="true">
+      <c r="A67" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B67" s="6" t="e"/>
+      <c r="C67" s="7" t="e"/>
+      <c r="D67" s="8" t="e"/>
+      <c r="E67" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F67" s="9" t="e"/>
+      <c r="G67" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true">
+      <c r="A68" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B68" s="6" t="e"/>
+      <c r="C68" s="7" t="e"/>
+      <c r="D68" s="8" t="e"/>
+      <c r="E68" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F68" s="9" t="e"/>
+      <c r="G68" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true">
+      <c r="A69" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B69" s="6" t="e"/>
+      <c r="C69" s="7" t="e"/>
+      <c r="D69" s="8" t="e"/>
+      <c r="E69" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F69" s="9" t="e"/>
+      <c r="G69" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" ht="11" customHeight="true">
+      <c r="A70" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B70" s="6" t="e"/>
+      <c r="C70" s="7" t="e"/>
+      <c r="D70" s="8" t="e"/>
+      <c r="E70" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F70" s="9" t="e"/>
+      <c r="G70" s="10" t="n">
+        <v>176</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="71" ht="11" customHeight="true">
+      <c r="A71" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" s="6" t="e"/>
+      <c r="C71" s="7" t="e"/>
+      <c r="D71" s="8" t="e"/>
+      <c r="E71" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F71" s="9" t="e"/>
+      <c r="G71" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" ht="11" customHeight="true">
+      <c r="A72" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="6" t="e"/>
+      <c r="C72" s="7" t="e"/>
+      <c r="D72" s="8" t="e"/>
+      <c r="E72" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F72" s="9" t="e"/>
+      <c r="G72" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" ht="11" customHeight="true">
+      <c r="A73" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="6" t="e"/>
+      <c r="C73" s="7" t="e"/>
+      <c r="D73" s="8" t="e"/>
+      <c r="E73" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F73" s="9" t="e"/>
+      <c r="G73" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" ht="11" customHeight="true">
+      <c r="A74" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="6" t="e"/>
+      <c r="C74" s="7" t="e"/>
+      <c r="D74" s="8" t="e"/>
+      <c r="E74" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F74" s="9" t="e"/>
+      <c r="G74" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" ht="11" customHeight="true">
+      <c r="A75" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="6" t="e"/>
+      <c r="C75" s="7" t="e"/>
+      <c r="D75" s="8" t="e"/>
+      <c r="E75" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F75" s="9" t="e"/>
+      <c r="G75" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" ht="11" customHeight="true">
+      <c r="A76" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="6" t="e"/>
+      <c r="C76" s="7" t="e"/>
+      <c r="D76" s="8" t="e"/>
+      <c r="E76" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" s="9" t="e"/>
+      <c r="G76" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" ht="11" customHeight="true">
+      <c r="A77" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="6" t="e"/>
+      <c r="C77" s="7" t="e"/>
+      <c r="D77" s="8" t="e"/>
+      <c r="E77" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F77" s="9" t="e"/>
+      <c r="G77" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true">
+      <c r="A78" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="6" t="e"/>
+      <c r="C78" s="7" t="e"/>
+      <c r="D78" s="8" t="e"/>
+      <c r="E78" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F78" s="9" t="e"/>
+      <c r="G78" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" ht="11" customHeight="true">
+      <c r="A79" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="6" t="e"/>
+      <c r="C79" s="7" t="e"/>
+      <c r="D79" s="8" t="e"/>
+      <c r="E79" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F79" s="9" t="e"/>
+      <c r="G79" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" ht="11" customHeight="true">
+      <c r="A80" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="6" t="e"/>
+      <c r="C80" s="7" t="e"/>
+      <c r="D80" s="8" t="e"/>
+      <c r="E80" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F80" s="9" t="e"/>
+      <c r="G80" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="81" ht="11" customHeight="true">
+      <c r="A81" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B81" s="6" t="e"/>
+      <c r="C81" s="7" t="e"/>
+      <c r="D81" s="8" t="e"/>
+      <c r="E81" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F81" s="9" t="e"/>
+      <c r="G81" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" ht="11" customHeight="true">
+      <c r="A82" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B82" s="6" t="e"/>
+      <c r="C82" s="7" t="e"/>
+      <c r="D82" s="8" t="e"/>
+      <c r="E82" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F82" s="9" t="e"/>
+      <c r="G82" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" ht="11" customHeight="true">
+      <c r="A83" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B83" s="6" t="e"/>
+      <c r="C83" s="7" t="e"/>
+      <c r="D83" s="8" t="e"/>
+      <c r="E83" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F83" s="9" t="e"/>
+      <c r="G83" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true">
+      <c r="A84" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="6" t="e"/>
+      <c r="C84" s="7" t="e"/>
+      <c r="D84" s="8" t="e"/>
+      <c r="E84" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F84" s="9" t="e"/>
+      <c r="G84" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" ht="11" customHeight="true">
+      <c r="A85" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B85" s="6" t="e"/>
+      <c r="C85" s="7" t="e"/>
+      <c r="D85" s="8" t="e"/>
+      <c r="E85" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F85" s="9" t="e"/>
+      <c r="G85" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" ht="11" customHeight="true">
+      <c r="A86" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" s="6" t="e"/>
+      <c r="C86" s="7" t="e"/>
+      <c r="D86" s="8" t="e"/>
+      <c r="E86" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F86" s="9" t="e"/>
+      <c r="G86" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" ht="11" customHeight="true">
+      <c r="A87" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B87" s="6" t="e"/>
+      <c r="C87" s="7" t="e"/>
+      <c r="D87" s="8" t="e"/>
+      <c r="E87" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F87" s="9" t="e"/>
+      <c r="G87" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="H87" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="88" ht="11" customHeight="true">
+      <c r="A88" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B88" s="6" t="e"/>
+      <c r="C88" s="7" t="e"/>
+      <c r="D88" s="8" t="e"/>
+      <c r="E88" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F88" s="9" t="e"/>
+      <c r="G88" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="H88" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="89" ht="11" customHeight="true">
+      <c r="A89" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B89" s="6" t="e"/>
+      <c r="C89" s="7" t="e"/>
+      <c r="D89" s="8" t="e"/>
+      <c r="E89" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F89" s="9" t="e"/>
+      <c r="G89" s="10" t="n">
+        <v>750</v>
+      </c>
+      <c r="H89" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" ht="11" customHeight="true">
+      <c r="A90" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B90" s="6" t="e"/>
+      <c r="C90" s="7" t="e"/>
+      <c r="D90" s="8" t="e"/>
+      <c r="E90" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F90" s="9" t="e"/>
+      <c r="G90" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H90" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91" ht="11" customHeight="true">
+      <c r="A91" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B91" s="6" t="e"/>
+      <c r="C91" s="7" t="e"/>
+      <c r="D91" s="8" t="e"/>
+      <c r="E91" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F91" s="9" t="e"/>
+      <c r="G91" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H91" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" ht="11" customHeight="true">
+      <c r="A92" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B92" s="6" t="e"/>
+      <c r="C92" s="7" t="e"/>
+      <c r="D92" s="8" t="e"/>
+      <c r="E92" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F92" s="9" t="e"/>
+      <c r="G92" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H92" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="93" ht="11" customHeight="true">
+      <c r="A93" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B93" s="6" t="e"/>
+      <c r="C93" s="7" t="e"/>
+      <c r="D93" s="8" t="e"/>
+      <c r="E93" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F93" s="9" t="e"/>
+      <c r="G93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" ht="11" customHeight="true">
+      <c r="A94" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B94" s="6" t="e"/>
+      <c r="C94" s="7" t="e"/>
+      <c r="D94" s="8" t="e"/>
+      <c r="E94" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F94" s="9" t="e"/>
+      <c r="G94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="95" ht="11" customHeight="true">
+      <c r="A95" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B95" s="6" t="e"/>
+      <c r="C95" s="7" t="e"/>
+      <c r="D95" s="8" t="e"/>
+      <c r="E95" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F95" s="9" t="e"/>
+      <c r="G95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="96" ht="11" customHeight="true">
+      <c r="A96" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B96" s="6" t="e"/>
+      <c r="C96" s="7" t="e"/>
+      <c r="D96" s="8" t="e"/>
+      <c r="E96" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F96" s="9" t="e"/>
+      <c r="G96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="97" ht="11" customHeight="true">
+      <c r="A97" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B97" s="6" t="e"/>
+      <c r="C97" s="7" t="e"/>
+      <c r="D97" s="8" t="e"/>
+      <c r="E97" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F97" s="9" t="e"/>
+      <c r="G97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="98" ht="11" customHeight="true">
+      <c r="A98" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B98" s="6" t="e"/>
+      <c r="C98" s="7" t="e"/>
+      <c r="D98" s="8" t="e"/>
+      <c r="E98" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F98" s="9" t="e"/>
+      <c r="G98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true">
+      <c r="A99" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B99" s="6" t="e"/>
+      <c r="C99" s="7" t="e"/>
+      <c r="D99" s="8" t="e"/>
+      <c r="E99" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F99" s="9" t="e"/>
+      <c r="G99" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H99" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true">
+      <c r="A100" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B100" s="6" t="e"/>
+      <c r="C100" s="7" t="e"/>
+      <c r="D100" s="8" t="e"/>
+      <c r="E100" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F100" s="9" t="e"/>
+      <c r="G100" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H100" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" ht="11" customHeight="true">
+      <c r="A101" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B101" s="6" t="e"/>
+      <c r="C101" s="7" t="e"/>
+      <c r="D101" s="8" t="e"/>
+      <c r="E101" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F101" s="9" t="e"/>
+      <c r="G101" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H101" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true">
+      <c r="A102" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B102" s="6" t="e"/>
+      <c r="C102" s="7" t="e"/>
+      <c r="D102" s="8" t="e"/>
+      <c r="E102" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F102" s="9" t="e"/>
+      <c r="G102" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H102" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" ht="11" customHeight="true">
+      <c r="A103" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B103" s="6" t="e"/>
+      <c r="C103" s="7" t="e"/>
+      <c r="D103" s="8" t="e"/>
+      <c r="E103" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F103" s="9" t="e"/>
+      <c r="G103" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" ht="11" customHeight="true">
+      <c r="A104" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B104" s="6" t="e"/>
+      <c r="C104" s="7" t="e"/>
+      <c r="D104" s="8" t="e"/>
+      <c r="E104" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F104" s="9" t="e"/>
+      <c r="G104" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H104" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="105" ht="11" customHeight="true">
+      <c r="A105" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B105" s="6" t="e"/>
+      <c r="C105" s="7" t="e"/>
+      <c r="D105" s="8" t="e"/>
+      <c r="E105" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F105" s="9" t="e"/>
+      <c r="G105" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I105" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="106" ht="11" customHeight="true">
+      <c r="A106" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B106" s="6" t="e"/>
+      <c r="C106" s="7" t="e"/>
+      <c r="D106" s="8" t="e"/>
+      <c r="E106" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F106" s="9" t="e"/>
+      <c r="G106" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H106" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="107" ht="11" customHeight="true">
+      <c r="A107" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B107" s="6" t="e"/>
+      <c r="C107" s="7" t="e"/>
+      <c r="D107" s="8" t="e"/>
+      <c r="E107" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F107" s="9" t="e"/>
+      <c r="G107" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I107" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true">
+      <c r="A108" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B108" s="6" t="e"/>
+      <c r="C108" s="7" t="e"/>
+      <c r="D108" s="8" t="e"/>
+      <c r="E108" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F108" s="9" t="e"/>
+      <c r="G108" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H108" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I108" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true">
+      <c r="A109" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B109" s="6" t="e"/>
+      <c r="C109" s="7" t="e"/>
+      <c r="D109" s="8" t="e"/>
+      <c r="E109" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F109" s="9" t="e"/>
+      <c r="G109" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I109" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" ht="11" customHeight="true">
+      <c r="A110" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B110" s="6" t="e"/>
+      <c r="C110" s="7" t="e"/>
+      <c r="D110" s="8" t="e"/>
+      <c r="E110" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F110" s="9" t="e"/>
+      <c r="G110" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I110" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" ht="11" customHeight="true">
+      <c r="A111" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B111" s="6" t="e"/>
+      <c r="C111" s="7" t="e"/>
+      <c r="D111" s="8" t="e"/>
+      <c r="E111" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F111" s="9" t="e"/>
+      <c r="G111" s="10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H111" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I111" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" ht="11" customHeight="true">
+      <c r="A112" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B112" s="6" t="e"/>
+      <c r="C112" s="7" t="e"/>
+      <c r="D112" s="8" t="e"/>
+      <c r="E112" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F112" s="9" t="e"/>
+      <c r="G112" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H112" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="113" ht="11" customHeight="true">
+      <c r="A113" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B113" s="6" t="e"/>
+      <c r="C113" s="7" t="e"/>
+      <c r="D113" s="8" t="e"/>
+      <c r="E113" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F113" s="9" t="e"/>
+      <c r="G113" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H113" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I113" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="114" ht="11" customHeight="true">
+      <c r="A114" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B114" s="6" t="e"/>
+      <c r="C114" s="7" t="e"/>
+      <c r="D114" s="8" t="e"/>
+      <c r="E114" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F114" s="9" t="e"/>
+      <c r="G114" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H114" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I114" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="115" ht="23" customHeight="true">
+      <c r="A115" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B115" s="6" t="e"/>
+      <c r="C115" s="7" t="e"/>
+      <c r="D115" s="8" t="e"/>
+      <c r="E115" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F115" s="9" t="e"/>
+      <c r="G115" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I115" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="116" ht="11" customHeight="true">
+      <c r="A116" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B116" s="6" t="e"/>
+      <c r="C116" s="7" t="e"/>
+      <c r="D116" s="8" t="e"/>
+      <c r="E116" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F116" s="9" t="e"/>
+      <c r="G116" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H116" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="117" ht="23" customHeight="true">
+      <c r="A117" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B117" s="6" t="e"/>
+      <c r="C117" s="7" t="e"/>
+      <c r="D117" s="8" t="e"/>
+      <c r="E117" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F117" s="9" t="e"/>
+      <c r="G117" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H117" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118" ht="23" customHeight="true">
+      <c r="A118" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B118" s="6" t="e"/>
+      <c r="C118" s="7" t="e"/>
+      <c r="D118" s="8" t="e"/>
+      <c r="E118" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F118" s="9" t="e"/>
+      <c r="G118" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H118" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119" ht="11" customHeight="true">
+      <c r="A119" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B119" s="6" t="e"/>
+      <c r="C119" s="7" t="e"/>
+      <c r="D119" s="8" t="e"/>
+      <c r="E119" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F119" s="9" t="e"/>
+      <c r="G119" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I119" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="120" ht="11" customHeight="true">
+      <c r="A120" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B120" s="6" t="e"/>
+      <c r="C120" s="7" t="e"/>
+      <c r="D120" s="8" t="e"/>
+      <c r="E120" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F120" s="9" t="e"/>
+      <c r="G120" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H120" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="121" ht="11" customHeight="true">
+      <c r="A121" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B121" s="6" t="e"/>
+      <c r="C121" s="7" t="e"/>
+      <c r="D121" s="8" t="e"/>
+      <c r="E121" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F121" s="9" t="e"/>
+      <c r="G121" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I121" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="122" ht="11" customHeight="true">
+      <c r="A122" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B122" s="6" t="e"/>
+      <c r="C122" s="7" t="e"/>
+      <c r="D122" s="8" t="e"/>
+      <c r="E122" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F122" s="9" t="e"/>
+      <c r="G122" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I122" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="123" ht="11" customHeight="true">
+      <c r="A123" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B123" s="6" t="e"/>
+      <c r="C123" s="7" t="e"/>
+      <c r="D123" s="8" t="e"/>
+      <c r="E123" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F123" s="9" t="e"/>
+      <c r="G123" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I123" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true">
+      <c r="A124" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B124" s="6" t="e"/>
+      <c r="C124" s="7" t="e"/>
+      <c r="D124" s="8" t="e"/>
+      <c r="E124" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F124" s="9" t="e"/>
+      <c r="G124" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H124" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I124" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" ht="11" customHeight="true">
+      <c r="A125" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B125" s="6" t="e"/>
+      <c r="C125" s="7" t="e"/>
+      <c r="D125" s="8" t="e"/>
+      <c r="E125" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F125" s="9" t="e"/>
+      <c r="G125" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="I125" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="126" ht="11" customHeight="true">
+      <c r="A126" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B126" s="6" t="e"/>
+      <c r="C126" s="7" t="e"/>
+      <c r="D126" s="8" t="e"/>
+      <c r="E126" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F126" s="9" t="e"/>
+      <c r="G126" s="10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H126" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I126" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="127" ht="11" customHeight="true">
+      <c r="A127" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B127" s="6" t="e"/>
+      <c r="C127" s="7" t="e"/>
+      <c r="D127" s="8" t="e"/>
+      <c r="E127" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F127" s="9" t="e"/>
+      <c r="G127" s="10" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="128" ht="11" customHeight="true">
+      <c r="A128" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B128" s="6" t="e"/>
+      <c r="C128" s="7" t="e"/>
+      <c r="D128" s="8" t="e"/>
+      <c r="E128" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F128" s="9" t="e"/>
+      <c r="G128" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H128" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I128" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="129" ht="11" customHeight="true">
+      <c r="A129" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B129" s="6" t="e"/>
+      <c r="C129" s="7" t="e"/>
+      <c r="D129" s="8" t="e"/>
+      <c r="E129" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F129" s="9" t="e"/>
+      <c r="G129" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H129" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I129" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="130" ht="11" customHeight="true">
+      <c r="A130" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B130" s="6" t="e"/>
+      <c r="C130" s="7" t="e"/>
+      <c r="D130" s="8" t="e"/>
+      <c r="E130" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F130" s="9" t="e"/>
+      <c r="G130" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H130" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I130" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="131" ht="11" customHeight="true">
+      <c r="A131" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B131" s="6" t="e"/>
+      <c r="C131" s="7" t="e"/>
+      <c r="D131" s="8" t="e"/>
+      <c r="E131" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F131" s="9" t="e"/>
+      <c r="G131" s="10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H131" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I131" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="132" ht="11" customHeight="true">
+      <c r="A132" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B132" s="6" t="e"/>
+      <c r="C132" s="7" t="e"/>
+      <c r="D132" s="8" t="e"/>
+      <c r="E132" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F132" s="9" t="e"/>
+      <c r="G132" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I132" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="133" ht="11" customHeight="true">
+      <c r="A133" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B133" s="6" t="e"/>
+      <c r="C133" s="7" t="e"/>
+      <c r="D133" s="8" t="e"/>
+      <c r="E133" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F133" s="9" t="e"/>
+      <c r="G133" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I133" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="134" ht="11" customHeight="true">
+      <c r="A134" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B134" s="6" t="e"/>
+      <c r="C134" s="7" t="e"/>
+      <c r="D134" s="8" t="e"/>
+      <c r="E134" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F134" s="9" t="e"/>
+      <c r="G134" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H134" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I134" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="135" ht="11" customHeight="true">
+      <c r="A135" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B135" s="6" t="e"/>
+      <c r="C135" s="7" t="e"/>
+      <c r="D135" s="8" t="e"/>
+      <c r="E135" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F135" s="9" t="e"/>
+      <c r="G135" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I135" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="136" ht="11" customHeight="true">
+      <c r="A136" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B136" s="6" t="e"/>
+      <c r="C136" s="7" t="e"/>
+      <c r="D136" s="8" t="e"/>
+      <c r="E136" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F136" s="9" t="e"/>
+      <c r="G136" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="137" ht="11" customHeight="true">
+      <c r="A137" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B137" s="6" t="e"/>
+      <c r="C137" s="7" t="e"/>
+      <c r="D137" s="8" t="e"/>
+      <c r="E137" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F137" s="9" t="e"/>
+      <c r="G137" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I137" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="138" ht="11" customHeight="true">
+      <c r="A138" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B138" s="6" t="e"/>
+      <c r="C138" s="7" t="e"/>
+      <c r="D138" s="8" t="e"/>
+      <c r="E138" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F138" s="9" t="e"/>
+      <c r="G138" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I138" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="139" ht="11" customHeight="true">
+      <c r="A139" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B139" s="6" t="e"/>
+      <c r="C139" s="7" t="e"/>
+      <c r="D139" s="8" t="e"/>
+      <c r="E139" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F139" s="9" t="e"/>
+      <c r="G139" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H139" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="140" ht="11" customHeight="true">
+      <c r="A140" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B140" s="6" t="e"/>
+      <c r="C140" s="7" t="e"/>
+      <c r="D140" s="8" t="e"/>
+      <c r="E140" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F140" s="9" t="e"/>
+      <c r="G140" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="141" ht="11" customHeight="true">
+      <c r="A141" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B141" s="6" t="e"/>
+      <c r="C141" s="7" t="e"/>
+      <c r="D141" s="8" t="e"/>
+      <c r="E141" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F141" s="9" t="e"/>
+      <c r="G141" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="142" ht="11" customHeight="true">
+      <c r="A142" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B142" s="6" t="e"/>
+      <c r="C142" s="7" t="e"/>
+      <c r="D142" s="8" t="e"/>
+      <c r="E142" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F142" s="9" t="e"/>
+      <c r="G142" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I142" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="143" ht="11" customHeight="true">
+      <c r="A143" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B143" s="6" t="e"/>
+      <c r="C143" s="7" t="e"/>
+      <c r="D143" s="8" t="e"/>
+      <c r="E143" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F143" s="9" t="e"/>
+      <c r="G143" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I143" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="144" ht="11" customHeight="true">
+      <c r="A144" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B144" s="6" t="e"/>
+      <c r="C144" s="7" t="e"/>
+      <c r="D144" s="8" t="e"/>
+      <c r="E144" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F144" s="9" t="e"/>
+      <c r="G144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I144" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="145" ht="11" customHeight="true">
+      <c r="A145" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B145" s="6" t="e"/>
+      <c r="C145" s="7" t="e"/>
+      <c r="D145" s="8" t="e"/>
+      <c r="E145" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F145" s="9" t="e"/>
+      <c r="G145" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I145" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="146" ht="11" customHeight="true">
+      <c r="A146" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B146" s="6" t="e"/>
+      <c r="C146" s="7" t="e"/>
+      <c r="D146" s="8" t="e"/>
+      <c r="E146" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F146" s="9" t="e"/>
+      <c r="G146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I146" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" ht="11" customHeight="true">
+      <c r="A147" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B147" s="6" t="e"/>
+      <c r="C147" s="7" t="e"/>
+      <c r="D147" s="8" t="e"/>
+      <c r="E147" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F147" s="9" t="e"/>
+      <c r="G147" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" ht="11" customHeight="true">
+      <c r="A148" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B148" s="6" t="e"/>
+      <c r="C148" s="7" t="e"/>
+      <c r="D148" s="8" t="e"/>
+      <c r="E148" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F148" s="9" t="e"/>
+      <c r="G148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I148" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" ht="11" customHeight="true">
+      <c r="A149" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B149" s="6" t="e"/>
+      <c r="C149" s="7" t="e"/>
+      <c r="D149" s="8" t="e"/>
+      <c r="E149" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F149" s="9" t="e"/>
+      <c r="G149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I149" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="150" ht="11" customHeight="true">
+      <c r="A150" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B150" s="6" t="e"/>
+      <c r="C150" s="7" t="e"/>
+      <c r="D150" s="8" t="e"/>
+      <c r="E150" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F150" s="9" t="e"/>
+      <c r="G150" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H150" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I150" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="151" ht="11" customHeight="true">
+      <c r="A151" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B151" s="6" t="e"/>
+      <c r="C151" s="7" t="e"/>
+      <c r="D151" s="8" t="e"/>
+      <c r="E151" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F151" s="9" t="e"/>
+      <c r="G151" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H151" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I151" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="152" ht="11" customHeight="true">
+      <c r="A152" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B152" s="6" t="e"/>
+      <c r="C152" s="7" t="e"/>
+      <c r="D152" s="8" t="e"/>
+      <c r="E152" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F152" s="9" t="e"/>
+      <c r="G152" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="153" ht="11" customHeight="true">
+      <c r="A153" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B153" s="6" t="e"/>
+      <c r="C153" s="7" t="e"/>
+      <c r="D153" s="8" t="e"/>
+      <c r="E153" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F153" s="9" t="e"/>
+      <c r="G153" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H153" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I153" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="154" ht="11" customHeight="true">
+      <c r="A154" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B154" s="6" t="e"/>
+      <c r="C154" s="7" t="e"/>
+      <c r="D154" s="8" t="e"/>
+      <c r="E154" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F154" s="9" t="e"/>
+      <c r="G154" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H154" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I154" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="155" ht="11" customHeight="true">
+      <c r="A155" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B155" s="6" t="e"/>
+      <c r="C155" s="7" t="e"/>
+      <c r="D155" s="8" t="e"/>
+      <c r="E155" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F155" s="9" t="e"/>
+      <c r="G155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I155" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="156" ht="11" customHeight="true">
+      <c r="A156" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B156" s="6" t="e"/>
+      <c r="C156" s="7" t="e"/>
+      <c r="D156" s="8" t="e"/>
+      <c r="E156" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F156" s="9" t="e"/>
+      <c r="G156" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I156" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="157" ht="11" customHeight="true">
+      <c r="A157" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B157" s="6" t="e"/>
+      <c r="C157" s="7" t="e"/>
+      <c r="D157" s="8" t="e"/>
+      <c r="E157" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F157" s="9" t="e"/>
+      <c r="G157" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I157" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="158" ht="11" customHeight="true">
+      <c r="A158" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B158" s="6" t="e"/>
+      <c r="C158" s="7" t="e"/>
+      <c r="D158" s="8" t="e"/>
+      <c r="E158" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F158" s="9" t="e"/>
+      <c r="G158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I158" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="159" ht="11" customHeight="true">
+      <c r="A159" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B159" s="6" t="e"/>
+      <c r="C159" s="7" t="e"/>
+      <c r="D159" s="8" t="e"/>
+      <c r="E159" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F159" s="9" t="e"/>
+      <c r="G159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I159" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="160" ht="11" customHeight="true">
+      <c r="A160" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B160" s="6" t="e"/>
+      <c r="C160" s="7" t="e"/>
+      <c r="D160" s="8" t="e"/>
+      <c r="E160" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F160" s="9" t="e"/>
+      <c r="G160" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I160" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="161" ht="11" customHeight="true">
+      <c r="A161" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B161" s="6" t="e"/>
+      <c r="C161" s="7" t="e"/>
+      <c r="D161" s="8" t="e"/>
+      <c r="E161" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F161" s="9" t="e"/>
+      <c r="G161" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H161" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I161" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="162" ht="11" customHeight="true">
+      <c r="A162" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B162" s="6" t="e"/>
+      <c r="C162" s="7" t="e"/>
+      <c r="D162" s="8" t="e"/>
+      <c r="E162" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F162" s="9" t="e"/>
+      <c r="G162" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H162" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I162" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="163" ht="11" customHeight="true">
+      <c r="A163" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B163" s="6" t="e"/>
+      <c r="C163" s="7" t="e"/>
+      <c r="D163" s="8" t="e"/>
+      <c r="E163" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F163" s="9" t="e"/>
+      <c r="G163" s="10" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="H163" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I163" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="164" ht="11" customHeight="true">
+      <c r="A164" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B164" s="6" t="e"/>
+      <c r="C164" s="7" t="e"/>
+      <c r="D164" s="8" t="e"/>
+      <c r="E164" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F164" s="9" t="e"/>
+      <c r="G164" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H164" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="165" ht="11" customHeight="true">
+      <c r="A165" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B165" s="6" t="e"/>
+      <c r="C165" s="7" t="e"/>
+      <c r="D165" s="8" t="e"/>
+      <c r="E165" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F165" s="9" t="e"/>
+      <c r="G165" s="10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H165" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="166" ht="11" customHeight="true">
+      <c r="A166" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B166" s="6" t="e"/>
+      <c r="C166" s="7" t="e"/>
+      <c r="D166" s="8" t="e"/>
+      <c r="E166" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="F166" s="9" t="e"/>
+      <c r="G166" s="10" t="n">
+        <v>617.3</v>
+      </c>
+      <c r="H166" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I166" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="167" ht="11" customHeight="true">
+      <c r="A167" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B167" s="6" t="e"/>
+      <c r="C167" s="7" t="e"/>
+      <c r="D167" s="8" t="e"/>
+      <c r="E167" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F167" s="9" t="e"/>
+      <c r="G167" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H167" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="168" ht="11" customHeight="true">
+      <c r="A168" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B168" s="6" t="e"/>
+      <c r="C168" s="7" t="e"/>
+      <c r="D168" s="8" t="e"/>
+      <c r="E168" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F168" s="9" t="e"/>
+      <c r="G168" s="10" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="H168" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="169" ht="11" customHeight="true">
+      <c r="A169" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B169" s="6" t="e"/>
+      <c r="C169" s="7" t="e"/>
+      <c r="D169" s="8" t="e"/>
+      <c r="E169" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F169" s="9" t="e"/>
+      <c r="G169" s="10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H169" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="170" ht="11" customHeight="true">
+      <c r="A170" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B170" s="6" t="e"/>
+      <c r="C170" s="7" t="e"/>
+      <c r="D170" s="8" t="e"/>
+      <c r="E170" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F170" s="9" t="e"/>
+      <c r="G170" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H170" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="171" ht="11" customHeight="true">
+      <c r="A171" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B171" s="6" t="e"/>
+      <c r="C171" s="7" t="e"/>
+      <c r="D171" s="8" t="e"/>
+      <c r="E171" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F171" s="9" t="e"/>
+      <c r="G171" s="10" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="H171" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="172" ht="11" customHeight="true">
+      <c r="A172" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B172" s="6" t="e"/>
+      <c r="C172" s="7" t="e"/>
+      <c r="D172" s="8" t="e"/>
+      <c r="E172" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F172" s="9" t="e"/>
+      <c r="G172" s="10" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="H172" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I172" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="173" ht="11" customHeight="true">
+      <c r="A173" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B173" s="6" t="e"/>
+      <c r="C173" s="7" t="e"/>
+      <c r="D173" s="8" t="e"/>
+      <c r="E173" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F173" s="9" t="e"/>
+      <c r="G173" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H173" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="174" ht="11" customHeight="true">
+      <c r="A174" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B174" s="6" t="e"/>
+      <c r="C174" s="7" t="e"/>
+      <c r="D174" s="8" t="e"/>
+      <c r="E174" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F174" s="9" t="e"/>
+      <c r="G174" s="10" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H174" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="175" ht="11" customHeight="true">
+      <c r="A175" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B175" s="6" t="e"/>
+      <c r="C175" s="7" t="e"/>
+      <c r="D175" s="8" t="e"/>
+      <c r="E175" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="F175" s="9" t="e"/>
+      <c r="G175" s="10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H175" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="176" ht="11" customHeight="true">
+      <c r="A176" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="B176" s="6" t="e"/>
+      <c r="C176" s="7" t="e"/>
+      <c r="D176" s="8" t="e"/>
+      <c r="E176" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F176" s="9" t="e"/>
+      <c r="G176" s="10" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="H176" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I176" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="177" ht="11" customHeight="true">
+      <c r="A177" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B177" s="6" t="e"/>
+      <c r="C177" s="7" t="e"/>
+      <c r="D177" s="8" t="e"/>
+      <c r="E177" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F177" s="9" t="e"/>
+      <c r="G177" s="10" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="H177" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="178" ht="11" customHeight="true">
+      <c r="A178" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="B178" s="6" t="e"/>
+      <c r="C178" s="7" t="e"/>
+      <c r="D178" s="8" t="e"/>
+      <c r="E178" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F178" s="9" t="e"/>
+      <c r="G178" s="10" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="H178" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="179" ht="11" customHeight="true">
+      <c r="A179" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B179" s="6" t="e"/>
+      <c r="C179" s="7" t="e"/>
+      <c r="D179" s="8" t="e"/>
+      <c r="E179" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F179" s="9" t="e"/>
+      <c r="G179" s="10" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H179" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="180" ht="11" customHeight="true">
+      <c r="A180" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B180" s="6" t="e"/>
+      <c r="C180" s="7" t="e"/>
+      <c r="D180" s="8" t="e"/>
+      <c r="E180" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F180" s="9" t="e"/>
+      <c r="G180" s="10" t="n">
+        <v>66.96</v>
+      </c>
+      <c r="H180" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="181" ht="11" customHeight="true">
+      <c r="A181" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B181" s="6" t="e"/>
+      <c r="C181" s="7" t="e"/>
+      <c r="D181" s="8" t="e"/>
+      <c r="E181" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F181" s="9" t="e"/>
+      <c r="G181" s="10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H181" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I181" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="182" ht="11" customHeight="true">
+      <c r="A182" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="B182" s="6" t="e"/>
+      <c r="C182" s="7" t="e"/>
+      <c r="D182" s="8" t="e"/>
+      <c r="E182" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F182" s="9" t="e"/>
+      <c r="G182" s="10" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="H182" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I182" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="183" ht="11" customHeight="true">
+      <c r="A183" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B183" s="6" t="e"/>
+      <c r="C183" s="7" t="e"/>
+      <c r="D183" s="8" t="e"/>
+      <c r="E183" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F183" s="9" t="e"/>
+      <c r="G183" s="10" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="H183" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I183" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="184" ht="11" customHeight="true">
+      <c r="A184" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="B184" s="6" t="e"/>
+      <c r="C184" s="7" t="e"/>
+      <c r="D184" s="8" t="e"/>
+      <c r="E184" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F184" s="9" t="e"/>
+      <c r="G184" s="12" t="n">
+        <v>1144.91</v>
+      </c>
+      <c r="H184" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I184" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" ht="11" customHeight="true">
+      <c r="A185" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="B185" s="6" t="e"/>
+      <c r="C185" s="7" t="e"/>
+      <c r="D185" s="8" t="e"/>
+      <c r="E185" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="F185" s="9" t="e"/>
+      <c r="G185" s="10" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H185" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I185" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186" ht="11" customHeight="true">
+      <c r="A186" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="B186" s="6" t="e"/>
+      <c r="C186" s="7" t="e"/>
+      <c r="D186" s="8" t="e"/>
+      <c r="E186" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F186" s="9" t="e"/>
+      <c r="G186" s="10" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="H186" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I186" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="187" ht="11" customHeight="true">
+      <c r="A187" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="B187" s="6" t="e"/>
+      <c r="C187" s="7" t="e"/>
+      <c r="D187" s="8" t="e"/>
+      <c r="E187" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F187" s="9" t="e"/>
+      <c r="G187" s="10" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="H187" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I187" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="188" ht="11" customHeight="true">
+      <c r="A188" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="B188" s="6" t="e"/>
+      <c r="C188" s="7" t="e"/>
+      <c r="D188" s="8" t="e"/>
+      <c r="E188" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F188" s="9" t="e"/>
+      <c r="G188" s="10" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="H188" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I188" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="189" ht="11" customHeight="true">
+      <c r="A189" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="B189" s="6" t="e"/>
+      <c r="C189" s="7" t="e"/>
+      <c r="D189" s="8" t="e"/>
+      <c r="E189" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F189" s="9" t="e"/>
+      <c r="G189" s="10" t="n">
+        <v>167.75</v>
+      </c>
+      <c r="H189" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I189" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="190" ht="11" customHeight="true">
+      <c r="A190" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B190" s="6" t="e"/>
+      <c r="C190" s="7" t="e"/>
+      <c r="D190" s="8" t="e"/>
+      <c r="E190" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F190" s="9" t="e"/>
+      <c r="G190" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I190" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="191" ht="23" customHeight="true">
+      <c r="A191" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="B191" s="6" t="e"/>
+      <c r="C191" s="7" t="e"/>
+      <c r="D191" s="8" t="e"/>
+      <c r="E191" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="F191" s="9" t="e"/>
+      <c r="G191" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H191" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I191" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="192" ht="11" customHeight="true">
+      <c r="A192" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="B192" s="6" t="e"/>
+      <c r="C192" s="7" t="e"/>
+      <c r="D192" s="8" t="e"/>
+      <c r="E192" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F192" s="9" t="e"/>
+      <c r="G192" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I192" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="193" ht="11" customHeight="true">
+      <c r="A193" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="B193" s="6" t="e"/>
+      <c r="C193" s="7" t="e"/>
+      <c r="D193" s="8" t="e"/>
+      <c r="E193" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F193" s="9" t="e"/>
+      <c r="G193" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H193" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I193" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="194" ht="11" customHeight="true">
+      <c r="A194" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="B194" s="6" t="e"/>
+      <c r="C194" s="7" t="e"/>
+      <c r="D194" s="8" t="e"/>
+      <c r="E194" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F194" s="9" t="e"/>
+      <c r="G194" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="195" ht="11" customHeight="true">
+      <c r="A195" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="B195" s="6" t="e"/>
+      <c r="C195" s="7" t="e"/>
+      <c r="D195" s="8" t="e"/>
+      <c r="E195" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F195" s="9" t="e"/>
+      <c r="G195" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H195" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I195" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="196" ht="11" customHeight="true">
+      <c r="A196" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="B196" s="6" t="e"/>
+      <c r="C196" s="7" t="e"/>
+      <c r="D196" s="8" t="e"/>
+      <c r="E196" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F196" s="9" t="e"/>
+      <c r="G196" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H196" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I196" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="197" ht="11" customHeight="true">
+      <c r="A197" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="B197" s="6" t="e"/>
+      <c r="C197" s="7" t="e"/>
+      <c r="D197" s="8" t="e"/>
+      <c r="E197" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F197" s="9" t="e"/>
+      <c r="G197" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H197" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I197" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="198" ht="11" customHeight="true">
+      <c r="A198" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="B198" s="6" t="e"/>
+      <c r="C198" s="7" t="e"/>
+      <c r="D198" s="8" t="e"/>
+      <c r="E198" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="F198" s="9" t="e"/>
+      <c r="G198" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H198" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I198" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="199" ht="11" customHeight="true">
+      <c r="A199" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="B199" s="6" t="e"/>
+      <c r="C199" s="7" t="e"/>
+      <c r="D199" s="8" t="e"/>
+      <c r="E199" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F199" s="9" t="e"/>
+      <c r="G199" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H199" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I199" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="200" ht="11" customHeight="true">
+      <c r="A200" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B200" s="6" t="e"/>
+      <c r="C200" s="7" t="e"/>
+      <c r="D200" s="8" t="e"/>
+      <c r="E200" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F200" s="9" t="e"/>
+      <c r="G200" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H200" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="I200" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="201" ht="11" customHeight="true">
+      <c r="A201" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B201" s="6" t="e"/>
+      <c r="C201" s="7" t="e"/>
+      <c r="D201" s="8" t="e"/>
+      <c r="E201" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F201" s="9" t="e"/>
+      <c r="G201" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H201" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I201" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="202" ht="11" customHeight="true">
+      <c r="A202" s="5" t="n">
+        <v>193</v>
+      </c>
+      <c r="B202" s="6" t="e"/>
+      <c r="C202" s="7" t="e"/>
+      <c r="D202" s="8" t="e"/>
+      <c r="E202" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F202" s="9" t="e"/>
+      <c r="G202" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H202" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I202" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="203" ht="11" customHeight="true">
+      <c r="A203" s="5" t="n">
+        <v>194</v>
+      </c>
+      <c r="B203" s="6" t="e"/>
+      <c r="C203" s="7" t="e"/>
+      <c r="D203" s="8" t="e"/>
+      <c r="E203" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F203" s="9" t="e"/>
+      <c r="G203" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H203" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I203" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="204" ht="23" customHeight="true">
+      <c r="A204" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="B204" s="6" t="e"/>
+      <c r="C204" s="7" t="e"/>
+      <c r="D204" s="8" t="e"/>
+      <c r="E204" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="F204" s="9" t="e"/>
+      <c r="G204" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H204" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I204" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="205" ht="11" customHeight="true">
+      <c r="A205" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="B205" s="6" t="e"/>
+      <c r="C205" s="7" t="e"/>
+      <c r="D205" s="8" t="e"/>
+      <c r="E205" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F205" s="9" t="e"/>
+      <c r="G205" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H205" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I205" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="206" ht="11" customHeight="true">
+      <c r="A206" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="B206" s="6" t="e"/>
+      <c r="C206" s="7" t="e"/>
+      <c r="D206" s="8" t="e"/>
+      <c r="E206" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F206" s="9" t="e"/>
+      <c r="G206" s="10" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H206" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="I206" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="207" ht="11" customHeight="true">
+      <c r="A207" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="B207" s="6" t="e"/>
+      <c r="C207" s="7" t="e"/>
+      <c r="D207" s="8" t="e"/>
+      <c r="E207" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F207" s="9" t="e"/>
+      <c r="G207" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I207" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="208" ht="11" customHeight="true">
+      <c r="A208" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="B208" s="6" t="e"/>
+      <c r="C208" s="7" t="e"/>
+      <c r="D208" s="8" t="e"/>
+      <c r="E208" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F208" s="9" t="e"/>
+      <c r="G208" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H208" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="I208" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="209" ht="11" customHeight="true">
+      <c r="A209" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="B209" s="6" t="e"/>
+      <c r="C209" s="7" t="e"/>
+      <c r="D209" s="8" t="e"/>
+      <c r="E209" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F209" s="9" t="e"/>
+      <c r="G209" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H209" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I209" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="210" ht="11" customHeight="true">
+      <c r="A210" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="B210" s="6" t="e"/>
+      <c r="C210" s="7" t="e"/>
+      <c r="D210" s="8" t="e"/>
+      <c r="E210" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F210" s="9" t="e"/>
+      <c r="G210" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H210" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I210" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="211" ht="11" customHeight="true">
+      <c r="A211" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="B211" s="6" t="e"/>
+      <c r="C211" s="7" t="e"/>
+      <c r="D211" s="8" t="e"/>
+      <c r="E211" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F211" s="9" t="e"/>
+      <c r="G211" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H211" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I211" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="212" ht="11" customHeight="true">
+      <c r="A212" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="B212" s="6" t="e"/>
+      <c r="C212" s="7" t="e"/>
+      <c r="D212" s="8" t="e"/>
+      <c r="E212" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F212" s="9" t="e"/>
+      <c r="G212" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H212" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I212" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="213" ht="23" customHeight="true">
+      <c r="A213" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="B213" s="6" t="e"/>
+      <c r="C213" s="7" t="e"/>
+      <c r="D213" s="8" t="e"/>
+      <c r="E213" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F213" s="9" t="e"/>
+      <c r="G213" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H213" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I213" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="214" ht="11" customHeight="true">
+      <c r="A214" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="B214" s="6" t="e"/>
+      <c r="C214" s="7" t="e"/>
+      <c r="D214" s="8" t="e"/>
+      <c r="E214" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F214" s="9" t="e"/>
+      <c r="G214" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H214" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I214" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="215" ht="11" customHeight="true">
+      <c r="A215" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="B215" s="6" t="e"/>
+      <c r="C215" s="7" t="e"/>
+      <c r="D215" s="8" t="e"/>
+      <c r="E215" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F215" s="9" t="e"/>
+      <c r="G215" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H215" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I215" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="216" ht="11" customHeight="true">
+      <c r="A216" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="B216" s="6" t="e"/>
+      <c r="C216" s="7" t="e"/>
+      <c r="D216" s="8" t="e"/>
+      <c r="E216" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="F216" s="9" t="e"/>
+      <c r="G216" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H216" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I216" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="217" ht="11" customHeight="true">
+      <c r="A217" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="B217" s="6" t="e"/>
+      <c r="C217" s="7" t="e"/>
+      <c r="D217" s="8" t="e"/>
+      <c r="E217" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F217" s="9" t="e"/>
+      <c r="G217" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H217" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I217" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="218" ht="11" customHeight="true">
+      <c r="A218" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="B218" s="6" t="e"/>
+      <c r="C218" s="7" t="e"/>
+      <c r="D218" s="8" t="e"/>
+      <c r="E218" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F218" s="9" t="e"/>
+      <c r="G218" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H218" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I218" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="219" ht="11" customHeight="true">
+      <c r="A219" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="B219" s="6" t="e"/>
+      <c r="C219" s="7" t="e"/>
+      <c r="D219" s="8" t="e"/>
+      <c r="E219" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F219" s="9" t="e"/>
+      <c r="G219" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="H219" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I219" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="220" ht="11" customHeight="true">
+      <c r="A220" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="B220" s="6" t="e"/>
+      <c r="C220" s="7" t="e"/>
+      <c r="D220" s="8" t="e"/>
+      <c r="E220" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F220" s="9" t="e"/>
+      <c r="G220" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H220" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I220" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="221" ht="11" customHeight="true">
+      <c r="A221" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="B221" s="6" t="e"/>
+      <c r="C221" s="7" t="e"/>
+      <c r="D221" s="8" t="e"/>
+      <c r="E221" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F221" s="9" t="e"/>
+      <c r="G221" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H221" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I221" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="222" ht="11" customHeight="true">
+      <c r="A222" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="B222" s="6" t="e"/>
+      <c r="C222" s="7" t="e"/>
+      <c r="D222" s="8" t="e"/>
+      <c r="E222" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F222" s="9" t="e"/>
+      <c r="G222" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H222" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I222" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="223" ht="11" customHeight="true">
+      <c r="A223" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="B223" s="6" t="e"/>
+      <c r="C223" s="7" t="e"/>
+      <c r="D223" s="8" t="e"/>
+      <c r="E223" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="F223" s="9" t="e"/>
+      <c r="G223" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="H223" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I223" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="224" ht="11" customHeight="true">
+      <c r="A224" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="B224" s="6" t="e"/>
+      <c r="C224" s="7" t="e"/>
+      <c r="D224" s="8" t="e"/>
+      <c r="E224" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F224" s="9" t="e"/>
+      <c r="G224" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H224" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I224" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="225" ht="11" customHeight="true">
+      <c r="A225" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="B225" s="6" t="e"/>
+      <c r="C225" s="7" t="e"/>
+      <c r="D225" s="8" t="e"/>
+      <c r="E225" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F225" s="9" t="e"/>
+      <c r="G225" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H225" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I225" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="226" ht="11" customHeight="true">
+      <c r="A226" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="B226" s="6" t="e"/>
+      <c r="C226" s="7" t="e"/>
+      <c r="D226" s="8" t="e"/>
+      <c r="E226" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F226" s="9" t="e"/>
+      <c r="G226" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H226" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I226" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="227" ht="11" customHeight="true">
+      <c r="A227" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="B227" s="6" t="e"/>
+      <c r="C227" s="7" t="e"/>
+      <c r="D227" s="8" t="e"/>
+      <c r="E227" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F227" s="9" t="e"/>
+      <c r="G227" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H227" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I227" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="228" ht="11" customHeight="true">
+      <c r="A228" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="B228" s="6" t="e"/>
+      <c r="C228" s="7" t="e"/>
+      <c r="D228" s="8" t="e"/>
+      <c r="E228" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F228" s="9" t="e"/>
+      <c r="G228" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="H228" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I228" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="229" ht="11" customHeight="true">
+      <c r="A229" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="B229" s="6" t="e"/>
+      <c r="C229" s="7" t="e"/>
+      <c r="D229" s="8" t="e"/>
+      <c r="E229" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="F229" s="9" t="e"/>
+      <c r="G229" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H229" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I229" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="230" ht="11" customHeight="true">
+      <c r="A230" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="B230" s="6" t="e"/>
+      <c r="C230" s="7" t="e"/>
+      <c r="D230" s="8" t="e"/>
+      <c r="E230" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F230" s="9" t="e"/>
+      <c r="G230" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H230" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I230" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="231" ht="11" customHeight="true">
+      <c r="A231" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="B231" s="6" t="e"/>
+      <c r="C231" s="7" t="e"/>
+      <c r="D231" s="8" t="e"/>
+      <c r="E231" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F231" s="9" t="e"/>
+      <c r="G231" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H231" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I231" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="232" ht="11" customHeight="true">
+      <c r="A232" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="B232" s="6" t="e"/>
+      <c r="C232" s="7" t="e"/>
+      <c r="D232" s="8" t="e"/>
+      <c r="E232" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F232" s="9" t="e"/>
+      <c r="G232" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H232" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I232" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="233" ht="11" customHeight="true">
+      <c r="A233" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="B233" s="6" t="e"/>
+      <c r="C233" s="7" t="e"/>
+      <c r="D233" s="8" t="e"/>
+      <c r="E233" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F233" s="9" t="e"/>
+      <c r="G233" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H233" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I233" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true">
+      <c r="A234" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="B234" s="6" t="e"/>
+      <c r="C234" s="7" t="e"/>
+      <c r="D234" s="8" t="e"/>
+      <c r="E234" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="F234" s="9" t="e"/>
+      <c r="G234" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H234" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I234" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" ht="11" customHeight="true">
+      <c r="A235" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="B235" s="6" t="e"/>
+      <c r="C235" s="7" t="e"/>
+      <c r="D235" s="8" t="e"/>
+      <c r="E235" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F235" s="9" t="e"/>
+      <c r="G235" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H235" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I235" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="236" ht="11" customHeight="true">
+      <c r="A236" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="B236" s="6" t="e"/>
+      <c r="C236" s="7" t="e"/>
+      <c r="D236" s="8" t="e"/>
+      <c r="E236" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="F236" s="9" t="e"/>
+      <c r="G236" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H236" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I236" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" ht="11" customHeight="true">
+      <c r="A237" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="B237" s="6" t="e"/>
+      <c r="C237" s="7" t="e"/>
+      <c r="D237" s="8" t="e"/>
+      <c r="E237" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="F237" s="9" t="e"/>
+      <c r="G237" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H237" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I237" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" ht="11" customHeight="true">
+      <c r="A238" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="B238" s="6" t="e"/>
+      <c r="C238" s="7" t="e"/>
+      <c r="D238" s="8" t="e"/>
+      <c r="E238" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F238" s="9" t="e"/>
+      <c r="G238" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H238" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I238" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" ht="11" customHeight="true">
+      <c r="A239" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="B239" s="6" t="e"/>
+      <c r="C239" s="7" t="e"/>
+      <c r="D239" s="8" t="e"/>
+      <c r="E239" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F239" s="9" t="e"/>
+      <c r="G239" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H239" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I239" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="240" ht="11" customHeight="true">
+      <c r="A240" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="B240" s="6" t="e"/>
+      <c r="C240" s="7" t="e"/>
+      <c r="D240" s="8" t="e"/>
+      <c r="E240" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F240" s="9" t="e"/>
+      <c r="G240" s="10" t="n">
+        <v>30.636</v>
+      </c>
+      <c r="H240" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I240" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="241" ht="11" customHeight="true">
+      <c r="A241" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="B241" s="6" t="e"/>
+      <c r="C241" s="7" t="e"/>
+      <c r="D241" s="8" t="e"/>
+      <c r="E241" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F241" s="9" t="e"/>
+      <c r="G241" s="10" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="H241" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I241" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" ht="11" customHeight="true">
+      <c r="A242" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="B242" s="6" t="e"/>
+      <c r="C242" s="7" t="e"/>
+      <c r="D242" s="8" t="e"/>
+      <c r="E242" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F242" s="9" t="e"/>
+      <c r="G242" s="10" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H242" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I242" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="243" ht="11" customHeight="true">
+      <c r="A243" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="B243" s="6" t="e"/>
+      <c r="C243" s="7" t="e"/>
+      <c r="D243" s="8" t="e"/>
+      <c r="E243" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F243" s="9" t="e"/>
+      <c r="G243" s="10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H243" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I243" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="244" ht="11" customHeight="true">
+      <c r="A244" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="B244" s="6" t="e"/>
+      <c r="C244" s="7" t="e"/>
+      <c r="D244" s="8" t="e"/>
+      <c r="E244" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F244" s="9" t="e"/>
+      <c r="G244" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H244" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I244" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="245" ht="11" customHeight="true">
+      <c r="A245" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="B245" s="6" t="e"/>
+      <c r="C245" s="7" t="e"/>
+      <c r="D245" s="8" t="e"/>
+      <c r="E245" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="F245" s="9" t="e"/>
+      <c r="G245" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H245" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I245" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="246" ht="11" customHeight="true">
+      <c r="A246" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="B246" s="6" t="e"/>
+      <c r="C246" s="7" t="e"/>
+      <c r="D246" s="8" t="e"/>
+      <c r="E246" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F246" s="9" t="e"/>
+      <c r="G246" s="10" t="n">
+        <v>3.532</v>
+      </c>
+      <c r="H246" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I246" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="247" ht="11" customHeight="true">
+      <c r="A247" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="B247" s="6" t="e"/>
+      <c r="C247" s="7" t="e"/>
+      <c r="D247" s="8" t="e"/>
+      <c r="E247" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F247" s="9" t="e"/>
+      <c r="G247" s="10" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="H247" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I247" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="248" ht="11" customHeight="true">
+      <c r="A248" s="5" t="n">
+        <v>239</v>
+      </c>
+      <c r="B248" s="6" t="e"/>
+      <c r="C248" s="7" t="e"/>
+      <c r="D248" s="8" t="e"/>
+      <c r="E248" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F248" s="9" t="e"/>
+      <c r="G248" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H248" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I248" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="249" ht="11" customHeight="true">
+      <c r="A249" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="B249" s="6" t="e"/>
+      <c r="C249" s="7" t="e"/>
+      <c r="D249" s="8" t="e"/>
+      <c r="E249" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F249" s="9" t="e"/>
+      <c r="G249" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H249" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I249" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="250" ht="11" customHeight="true">
+      <c r="A250" s="5" t="n">
+        <v>241</v>
+      </c>
+      <c r="B250" s="6" t="e"/>
+      <c r="C250" s="7" t="e"/>
+      <c r="D250" s="8" t="e"/>
+      <c r="E250" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F250" s="9" t="e"/>
+      <c r="G250" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H250" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I250" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="251" ht="11" customHeight="true">
+      <c r="A251" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="B251" s="6" t="e"/>
+      <c r="C251" s="7" t="e"/>
+      <c r="D251" s="8" t="e"/>
+      <c r="E251" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F251" s="9" t="e"/>
+      <c r="G251" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H251" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I251" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="252" ht="11" customHeight="true">
+      <c r="A252" s="5" t="n">
+        <v>243</v>
+      </c>
+      <c r="B252" s="6" t="e"/>
+      <c r="C252" s="7" t="e"/>
+      <c r="D252" s="8" t="e"/>
+      <c r="E252" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F252" s="9" t="e"/>
+      <c r="G252" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H252" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I252" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="253" ht="11" customHeight="true">
+      <c r="A253" s="5" t="n">
+        <v>244</v>
+      </c>
+      <c r="B253" s="6" t="e"/>
+      <c r="C253" s="7" t="e"/>
+      <c r="D253" s="8" t="e"/>
+      <c r="E253" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F253" s="9" t="e"/>
+      <c r="G253" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H253" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I253" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="254" ht="11" customHeight="true">
+      <c r="A254" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="B254" s="6" t="e"/>
+      <c r="C254" s="7" t="e"/>
+      <c r="D254" s="8" t="e"/>
+      <c r="E254" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F254" s="9" t="e"/>
+      <c r="G254" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H254" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I254" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="255" ht="11" customHeight="true">
+      <c r="A255" s="5" t="n">
+        <v>246</v>
+      </c>
+      <c r="B255" s="6" t="e"/>
+      <c r="C255" s="7" t="e"/>
+      <c r="D255" s="8" t="e"/>
+      <c r="E255" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F255" s="9" t="e"/>
+      <c r="G255" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H255" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I255" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="256" ht="11" customHeight="true">
+      <c r="A256" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="B256" s="6" t="e"/>
+      <c r="C256" s="7" t="e"/>
+      <c r="D256" s="8" t="e"/>
+      <c r="E256" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F256" s="9" t="e"/>
+      <c r="G256" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H256" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I256" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="257" ht="11" customHeight="true">
+      <c r="A257" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="B257" s="6" t="e"/>
+      <c r="C257" s="7" t="e"/>
+      <c r="D257" s="8" t="e"/>
+      <c r="E257" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F257" s="9" t="e"/>
+      <c r="G257" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H257" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I257" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="258" ht="11" customHeight="true">
+      <c r="A258" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="B258" s="6" t="e"/>
+      <c r="C258" s="7" t="e"/>
+      <c r="D258" s="8" t="e"/>
+      <c r="E258" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F258" s="9" t="e"/>
+      <c r="G258" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H258" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I258" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="259" ht="11" customHeight="true">
+      <c r="A259" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="B259" s="6" t="e"/>
+      <c r="C259" s="7" t="e"/>
+      <c r="D259" s="8" t="e"/>
+      <c r="E259" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F259" s="9" t="e"/>
+      <c r="G259" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H259" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I259" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="260" ht="11" customHeight="true">
+      <c r="A260" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="B260" s="6" t="e"/>
+      <c r="C260" s="7" t="e"/>
+      <c r="D260" s="8" t="e"/>
+      <c r="E260" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F260" s="9" t="e"/>
+      <c r="G260" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H260" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I260" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="261" ht="11" customHeight="true">
+      <c r="A261" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="B261" s="6" t="e"/>
+      <c r="C261" s="7" t="e"/>
+      <c r="D261" s="8" t="e"/>
+      <c r="E261" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F261" s="9" t="e"/>
+      <c r="G261" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H261" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I261" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="262" ht="11" customHeight="true">
+      <c r="A262" s="5" t="n">
+        <v>253</v>
+      </c>
+      <c r="B262" s="6" t="e"/>
+      <c r="C262" s="7" t="e"/>
+      <c r="D262" s="8" t="e"/>
+      <c r="E262" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F262" s="9" t="e"/>
+      <c r="G262" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H262" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I262" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="263" ht="11" customHeight="true">
+      <c r="A263" s="5" t="n">
+        <v>254</v>
+      </c>
+      <c r="B263" s="6" t="e"/>
+      <c r="C263" s="7" t="e"/>
+      <c r="D263" s="8" t="e"/>
+      <c r="E263" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F263" s="9" t="e"/>
+      <c r="G263" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H263" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I263" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="264" ht="11" customHeight="true">
+      <c r="A264" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="B264" s="6" t="e"/>
+      <c r="C264" s="7" t="e"/>
+      <c r="D264" s="8" t="e"/>
+      <c r="E264" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F264" s="9" t="e"/>
+      <c r="G264" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H264" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I264" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="265" ht="11" customHeight="true">
+      <c r="A265" s="5" t="n">
+        <v>256</v>
+      </c>
+      <c r="B265" s="6" t="e"/>
+      <c r="C265" s="7" t="e"/>
+      <c r="D265" s="8" t="e"/>
+      <c r="E265" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F265" s="9" t="e"/>
+      <c r="G265" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H265" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I265" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="266" ht="11" customHeight="true">
+      <c r="A266" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="B266" s="6" t="e"/>
+      <c r="C266" s="7" t="e"/>
+      <c r="D266" s="8" t="e"/>
+      <c r="E266" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="F266" s="9" t="e"/>
+      <c r="G266" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H266" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I266" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="267" ht="11" customHeight="true">
+      <c r="A267" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="B267" s="6" t="e"/>
+      <c r="C267" s="7" t="e"/>
+      <c r="D267" s="8" t="e"/>
+      <c r="E267" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F267" s="9" t="e"/>
+      <c r="G267" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H267" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I267" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="268" ht="11" customHeight="true">
+      <c r="A268" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="B268" s="6" t="e"/>
+      <c r="C268" s="7" t="e"/>
+      <c r="D268" s="8" t="e"/>
+      <c r="E268" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="F268" s="9" t="e"/>
+      <c r="G268" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H268" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I268" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="269" ht="11" customHeight="true">
+      <c r="A269" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="B269" s="6" t="e"/>
+      <c r="C269" s="7" t="e"/>
+      <c r="D269" s="8" t="e"/>
+      <c r="E269" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F269" s="9" t="e"/>
+      <c r="G269" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H269" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I269" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="270" ht="11" customHeight="true">
+      <c r="A270" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="B270" s="6" t="e"/>
+      <c r="C270" s="7" t="e"/>
+      <c r="D270" s="8" t="e"/>
+      <c r="E270" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F270" s="9" t="e"/>
+      <c r="G270" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H270" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I270" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true">
+      <c r="A271" s="5" t="n">
+        <v>262</v>
+      </c>
+      <c r="B271" s="6" t="e"/>
+      <c r="C271" s="7" t="e"/>
+      <c r="D271" s="8" t="e"/>
+      <c r="E271" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F271" s="9" t="e"/>
+      <c r="G271" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H271" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I271" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="272" ht="11" customHeight="true">
+      <c r="A272" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="B272" s="6" t="e"/>
+      <c r="C272" s="7" t="e"/>
+      <c r="D272" s="8" t="e"/>
+      <c r="E272" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F272" s="9" t="e"/>
+      <c r="G272" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H272" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I272" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="273" ht="11" customHeight="true">
+      <c r="A273" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="B273" s="6" t="e"/>
+      <c r="C273" s="7" t="e"/>
+      <c r="D273" s="8" t="e"/>
+      <c r="E273" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F273" s="9" t="e"/>
+      <c r="G273" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I273" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="274" ht="11" customHeight="true">
+      <c r="A274" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="B274" s="6" t="e"/>
+      <c r="C274" s="7" t="e"/>
+      <c r="D274" s="8" t="e"/>
+      <c r="E274" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="F274" s="9" t="e"/>
+      <c r="G274" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H274" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I274" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="275" ht="11" customHeight="true">
+      <c r="A275" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="B275" s="6" t="e"/>
+      <c r="C275" s="7" t="e"/>
+      <c r="D275" s="8" t="e"/>
+      <c r="E275" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F275" s="9" t="e"/>
+      <c r="G275" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H275" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I275" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="276" ht="11" customHeight="true">
+      <c r="A276" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="B276" s="6" t="e"/>
+      <c r="C276" s="7" t="e"/>
+      <c r="D276" s="8" t="e"/>
+      <c r="E276" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="F276" s="9" t="e"/>
+      <c r="G276" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H276" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I276" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="277" ht="11" customHeight="true">
+      <c r="A277" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="B277" s="6" t="e"/>
+      <c r="C277" s="7" t="e"/>
+      <c r="D277" s="8" t="e"/>
+      <c r="E277" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F277" s="9" t="e"/>
+      <c r="G277" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I277" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="278" ht="11" customHeight="true">
+      <c r="A278" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="B278" s="6" t="e"/>
+      <c r="C278" s="7" t="e"/>
+      <c r="D278" s="8" t="e"/>
+      <c r="E278" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F278" s="9" t="e"/>
+      <c r="G278" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I278" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="279" ht="11" customHeight="true">
+      <c r="A279" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="B279" s="6" t="e"/>
+      <c r="C279" s="7" t="e"/>
+      <c r="D279" s="8" t="e"/>
+      <c r="E279" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="F279" s="9" t="e"/>
+      <c r="G279" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H279" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I279" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="280" ht="11" customHeight="true">
+      <c r="A280" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="B280" s="6" t="e"/>
+      <c r="C280" s="7" t="e"/>
+      <c r="D280" s="8" t="e"/>
+      <c r="E280" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F280" s="9" t="e"/>
+      <c r="G280" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="I280" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="281" ht="11" customHeight="true">
+      <c r="A281" s="5" t="n">
+        <v>272</v>
+      </c>
+      <c r="B281" s="6" t="e"/>
+      <c r="C281" s="7" t="e"/>
+      <c r="D281" s="8" t="e"/>
+      <c r="E281" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F281" s="9" t="e"/>
+      <c r="G281" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I281" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" ht="11" customHeight="true">
+      <c r="A282" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="B282" s="6" t="e"/>
+      <c r="C282" s="7" t="e"/>
+      <c r="D282" s="8" t="e"/>
+      <c r="E282" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="F282" s="9" t="e"/>
+      <c r="G282" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="I282" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" ht="11" customHeight="true">
+      <c r="A283" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="B283" s="6" t="e"/>
+      <c r="C283" s="7" t="e"/>
+      <c r="D283" s="8" t="e"/>
+      <c r="E283" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F283" s="9" t="e"/>
+      <c r="G283" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H283" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I283" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" ht="23" customHeight="true">
+      <c r="A284" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="B284" s="6" t="e"/>
+      <c r="C284" s="7" t="e"/>
+      <c r="D284" s="8" t="e"/>
+      <c r="E284" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F284" s="9" t="e"/>
+      <c r="G284" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H284" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I284" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="285" ht="11" customHeight="true">
+      <c r="A285" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="B285" s="6" t="e"/>
+      <c r="C285" s="7" t="e"/>
+      <c r="D285" s="8" t="e"/>
+      <c r="E285" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F285" s="9" t="e"/>
+      <c r="G285" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H285" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I285" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="286" ht="11" customHeight="true">
+      <c r="A286" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="B286" s="6" t="e"/>
+      <c r="C286" s="7" t="e"/>
+      <c r="D286" s="8" t="e"/>
+      <c r="E286" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F286" s="9" t="e"/>
+      <c r="G286" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H286" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I286" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="287" ht="11" customHeight="true">
+      <c r="A287" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="B287" s="6" t="e"/>
+      <c r="C287" s="7" t="e"/>
+      <c r="D287" s="8" t="e"/>
+      <c r="E287" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F287" s="9" t="e"/>
+      <c r="G287" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H287" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I287" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="288" ht="23" customHeight="true">
+      <c r="A288" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="B288" s="6" t="e"/>
+      <c r="C288" s="7" t="e"/>
+      <c r="D288" s="8" t="e"/>
+      <c r="E288" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F288" s="9" t="e"/>
+      <c r="G288" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H288" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I288" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="289" ht="11" customHeight="true">
+      <c r="A289" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="B289" s="6" t="e"/>
+      <c r="C289" s="7" t="e"/>
+      <c r="D289" s="8" t="e"/>
+      <c r="E289" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F289" s="9" t="e"/>
+      <c r="G289" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H289" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I289" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="290" ht="11" customHeight="true">
+      <c r="A290" s="5" t="n">
+        <v>281</v>
+      </c>
+      <c r="B290" s="6" t="e"/>
+      <c r="C290" s="7" t="e"/>
+      <c r="D290" s="8" t="e"/>
+      <c r="E290" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F290" s="9" t="e"/>
+      <c r="G290" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H290" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="I290" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="291" ht="11" customHeight="true">
+      <c r="A291" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="B291" s="6" t="e"/>
+      <c r="C291" s="7" t="e"/>
+      <c r="D291" s="8" t="e"/>
+      <c r="E291" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F291" s="9" t="e"/>
+      <c r="G291" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H291" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I291" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="292" ht="11" customHeight="true">
+      <c r="A292" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="B292" s="6" t="e"/>
+      <c r="C292" s="7" t="e"/>
+      <c r="D292" s="8" t="e"/>
+      <c r="E292" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F292" s="9" t="e"/>
+      <c r="G292" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H292" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I292" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="293" ht="23" customHeight="true">
+      <c r="A293" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="B293" s="6" t="e"/>
+      <c r="C293" s="7" t="e"/>
+      <c r="D293" s="8" t="e"/>
+      <c r="E293" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F293" s="9" t="e"/>
+      <c r="G293" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H293" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I293" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="294" ht="11" customHeight="true">
+      <c r="A294" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="B294" s="6" t="e"/>
+      <c r="C294" s="7" t="e"/>
+      <c r="D294" s="8" t="e"/>
+      <c r="E294" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F294" s="9" t="e"/>
+      <c r="G294" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H294" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="I294" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="295" ht="11" customHeight="true">
+      <c r="A295" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="B295" s="6" t="e"/>
+      <c r="C295" s="7" t="e"/>
+      <c r="D295" s="8" t="e"/>
+      <c r="E295" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F295" s="9" t="e"/>
+      <c r="G295" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H295" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I295" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="296" ht="11" customHeight="true">
+      <c r="A296" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="B296" s="6" t="e"/>
+      <c r="C296" s="7" t="e"/>
+      <c r="D296" s="8" t="e"/>
+      <c r="E296" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F296" s="9" t="e"/>
+      <c r="G296" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H296" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I296" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="297" ht="23" customHeight="true">
+      <c r="A297" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="B297" s="6" t="e"/>
+      <c r="C297" s="7" t="e"/>
+      <c r="D297" s="8" t="e"/>
+      <c r="E297" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F297" s="9" t="e"/>
+      <c r="G297" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H297" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I297" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="298" ht="11" customHeight="true">
+      <c r="A298" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="B298" s="6" t="e"/>
+      <c r="C298" s="7" t="e"/>
+      <c r="D298" s="8" t="e"/>
+      <c r="E298" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F298" s="9" t="e"/>
+      <c r="G298" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H298" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I298" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="299" ht="23" customHeight="true">
+      <c r="A299" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="B299" s="6" t="e"/>
+      <c r="C299" s="7" t="e"/>
+      <c r="D299" s="8" t="e"/>
+      <c r="E299" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F299" s="9" t="e"/>
+      <c r="G299" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H299" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I299" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="300" ht="11" customHeight="true">
+      <c r="A300" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="B300" s="6" t="e"/>
+      <c r="C300" s="7" t="e"/>
+      <c r="D300" s="8" t="e"/>
+      <c r="E300" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F300" s="9" t="e"/>
+      <c r="G300" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H300" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I300" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="301" ht="11" customHeight="true">
+      <c r="A301" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="B301" s="6" t="e"/>
+      <c r="C301" s="7" t="e"/>
+      <c r="D301" s="8" t="e"/>
+      <c r="E301" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F301" s="9" t="e"/>
+      <c r="G301" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H301" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="I301" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="302" ht="11" customHeight="true">
+      <c r="A302" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="B302" s="6" t="e"/>
+      <c r="C302" s="7" t="e"/>
+      <c r="D302" s="8" t="e"/>
+      <c r="E302" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F302" s="9" t="e"/>
+      <c r="G302" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H302" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I302" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="303" ht="23" customHeight="true">
+      <c r="A303" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="B303" s="6" t="e"/>
+      <c r="C303" s="7" t="e"/>
+      <c r="D303" s="8" t="e"/>
+      <c r="E303" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="F303" s="9" t="e"/>
+      <c r="G303" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H303" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I303" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" ht="11" customHeight="true">
+      <c r="A304" s="5" t="n">
+        <v>295</v>
+      </c>
+      <c r="B304" s="6" t="e"/>
+      <c r="C304" s="7" t="e"/>
+      <c r="D304" s="8" t="e"/>
+      <c r="E304" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F304" s="9" t="e"/>
+      <c r="G304" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H304" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I304" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="305" ht="11" customHeight="true">
+      <c r="A305" s="5" t="n">
+        <v>296</v>
+      </c>
+      <c r="B305" s="6" t="e"/>
+      <c r="C305" s="7" t="e"/>
+      <c r="D305" s="8" t="e"/>
+      <c r="E305" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F305" s="9" t="e"/>
+      <c r="G305" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H305" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I305" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" ht="23" customHeight="true">
+      <c r="A306" s="5" t="n">
+        <v>297</v>
+      </c>
+      <c r="B306" s="6" t="e"/>
+      <c r="C306" s="7" t="e"/>
+      <c r="D306" s="8" t="e"/>
+      <c r="E306" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F306" s="9" t="e"/>
+      <c r="G306" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H306" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I306" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" ht="11" customHeight="true">
+      <c r="A307" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="B307" s="6" t="e"/>
+      <c r="C307" s="7" t="e"/>
+      <c r="D307" s="8" t="e"/>
+      <c r="E307" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F307" s="9" t="e"/>
+      <c r="G307" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="I307" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="308" ht="11" customHeight="true">
+      <c r="A308" s="5" t="n">
+        <v>299</v>
+      </c>
+      <c r="B308" s="6" t="e"/>
+      <c r="C308" s="7" t="e"/>
+      <c r="D308" s="8" t="e"/>
+      <c r="E308" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F308" s="9" t="e"/>
+      <c r="G308" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H308" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I308" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="309" ht="11" customHeight="true">
+      <c r="A309" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="B309" s="6" t="e"/>
+      <c r="C309" s="7" t="e"/>
+      <c r="D309" s="8" t="e"/>
+      <c r="E309" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F309" s="9" t="e"/>
+      <c r="G309" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H309" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I309" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" ht="11" customHeight="true">
+      <c r="A310" s="5" t="n">
+        <v>301</v>
+      </c>
+      <c r="B310" s="6" t="e"/>
+      <c r="C310" s="7" t="e"/>
+      <c r="D310" s="8" t="e"/>
+      <c r="E310" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F310" s="9" t="e"/>
+      <c r="G310" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H310" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I310" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="311" ht="11" customHeight="true">
+      <c r="A311" s="5" t="n">
+        <v>302</v>
+      </c>
+      <c r="B311" s="6" t="e"/>
+      <c r="C311" s="7" t="e"/>
+      <c r="D311" s="8" t="e"/>
+      <c r="E311" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F311" s="9" t="e"/>
+      <c r="G311" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H311" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I311" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" ht="11" customHeight="true">
+      <c r="A312" s="5" t="n">
+        <v>303</v>
+      </c>
+      <c r="B312" s="6" t="e"/>
+      <c r="C312" s="7" t="e"/>
+      <c r="D312" s="8" t="e"/>
+      <c r="E312" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="F312" s="9" t="e"/>
+      <c r="G312" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I312" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="313" ht="11" customHeight="true">
+      <c r="A313" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="B313" s="6" t="e"/>
+      <c r="C313" s="7" t="e"/>
+      <c r="D313" s="8" t="e"/>
+      <c r="E313" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F313" s="9" t="e"/>
+      <c r="G313" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I313" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="314" ht="11" customHeight="true">
+      <c r="A314" s="5" t="n">
+        <v>305</v>
+      </c>
+      <c r="B314" s="6" t="e"/>
+      <c r="C314" s="7" t="e"/>
+      <c r="D314" s="8" t="e"/>
+      <c r="E314" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="F314" s="9" t="e"/>
+      <c r="G314" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H314" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I314" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="315" ht="11" customHeight="true">
+      <c r="A315" s="5" t="n">
+        <v>306</v>
+      </c>
+      <c r="B315" s="6" t="e"/>
+      <c r="C315" s="7" t="e"/>
+      <c r="D315" s="8" t="e"/>
+      <c r="E315" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F315" s="9" t="e"/>
+      <c r="G315" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H315" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I315" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" ht="11" customHeight="true">
+      <c r="A316" s="5" t="n">
+        <v>307</v>
+      </c>
+      <c r="B316" s="6" t="e"/>
+      <c r="C316" s="7" t="e"/>
+      <c r="D316" s="8" t="e"/>
+      <c r="E316" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="F316" s="9" t="e"/>
+      <c r="G316" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H316" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I316" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="317" ht="23" customHeight="true">
+      <c r="A317" s="5" t="n">
+        <v>308</v>
+      </c>
+      <c r="B317" s="6" t="e"/>
+      <c r="C317" s="7" t="e"/>
+      <c r="D317" s="8" t="e"/>
+      <c r="E317" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="F317" s="9" t="e"/>
+      <c r="G317" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H317" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I317" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="318" ht="11" customHeight="true">
+      <c r="A318" s="5" t="n">
+        <v>309</v>
+      </c>
+      <c r="B318" s="6" t="e"/>
+      <c r="C318" s="7" t="e"/>
+      <c r="D318" s="8" t="e"/>
+      <c r="E318" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F318" s="9" t="e"/>
+      <c r="G318" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H318" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I318" s="9" t="s">
+        <v>314</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="312">
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E9:F9"/>
@@ -1428,6 +7794,274 @@
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="E120:F120"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="E122:F122"/>
+    <mergeCell ref="E123:F123"/>
+    <mergeCell ref="E124:F124"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="E142:F142"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="E146:F146"/>
+    <mergeCell ref="E147:F147"/>
+    <mergeCell ref="E148:F148"/>
+    <mergeCell ref="E149:F149"/>
+    <mergeCell ref="E150:F150"/>
+    <mergeCell ref="E151:F151"/>
+    <mergeCell ref="E152:F152"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="E156:F156"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="E158:F158"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="E164:F164"/>
+    <mergeCell ref="E165:F165"/>
+    <mergeCell ref="E166:F166"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="E168:F168"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="E173:F173"/>
+    <mergeCell ref="E174:F174"/>
+    <mergeCell ref="E175:F175"/>
+    <mergeCell ref="E176:F176"/>
+    <mergeCell ref="E177:F177"/>
+    <mergeCell ref="E178:F178"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="E180:F180"/>
+    <mergeCell ref="E181:F181"/>
+    <mergeCell ref="E182:F182"/>
+    <mergeCell ref="E183:F183"/>
+    <mergeCell ref="E184:F184"/>
+    <mergeCell ref="E185:F185"/>
+    <mergeCell ref="E186:F186"/>
+    <mergeCell ref="E187:F187"/>
+    <mergeCell ref="E188:F188"/>
+    <mergeCell ref="E189:F189"/>
+    <mergeCell ref="E190:F190"/>
+    <mergeCell ref="E191:F191"/>
+    <mergeCell ref="E192:F192"/>
+    <mergeCell ref="E193:F193"/>
+    <mergeCell ref="E194:F194"/>
+    <mergeCell ref="E195:F195"/>
+    <mergeCell ref="E196:F196"/>
+    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="E198:F198"/>
+    <mergeCell ref="E199:F199"/>
+    <mergeCell ref="E200:F200"/>
+    <mergeCell ref="E201:F201"/>
+    <mergeCell ref="E202:F202"/>
+    <mergeCell ref="E203:F203"/>
+    <mergeCell ref="E204:F204"/>
+    <mergeCell ref="E205:F205"/>
+    <mergeCell ref="E206:F206"/>
+    <mergeCell ref="E207:F207"/>
+    <mergeCell ref="E208:F208"/>
+    <mergeCell ref="E209:F209"/>
+    <mergeCell ref="E210:F210"/>
+    <mergeCell ref="E211:F211"/>
+    <mergeCell ref="E212:F212"/>
+    <mergeCell ref="E213:F213"/>
+    <mergeCell ref="E214:F214"/>
+    <mergeCell ref="E215:F215"/>
+    <mergeCell ref="E216:F216"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="E218:F218"/>
+    <mergeCell ref="E219:F219"/>
+    <mergeCell ref="E220:F220"/>
+    <mergeCell ref="E221:F221"/>
+    <mergeCell ref="E222:F222"/>
+    <mergeCell ref="E223:F223"/>
+    <mergeCell ref="E224:F224"/>
+    <mergeCell ref="E225:F225"/>
+    <mergeCell ref="E226:F226"/>
+    <mergeCell ref="E227:F227"/>
+    <mergeCell ref="E228:F228"/>
+    <mergeCell ref="E229:F229"/>
+    <mergeCell ref="E230:F230"/>
+    <mergeCell ref="E231:F231"/>
+    <mergeCell ref="E232:F232"/>
+    <mergeCell ref="E233:F233"/>
+    <mergeCell ref="E234:F234"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="E236:F236"/>
+    <mergeCell ref="E237:F237"/>
+    <mergeCell ref="E238:F238"/>
+    <mergeCell ref="E239:F239"/>
+    <mergeCell ref="E240:F240"/>
+    <mergeCell ref="E241:F241"/>
+    <mergeCell ref="E242:F242"/>
+    <mergeCell ref="E243:F243"/>
+    <mergeCell ref="E244:F244"/>
+    <mergeCell ref="E245:F245"/>
+    <mergeCell ref="E246:F246"/>
+    <mergeCell ref="E247:F247"/>
+    <mergeCell ref="E248:F248"/>
+    <mergeCell ref="E249:F249"/>
+    <mergeCell ref="E250:F250"/>
+    <mergeCell ref="E251:F251"/>
+    <mergeCell ref="E252:F252"/>
+    <mergeCell ref="E253:F253"/>
+    <mergeCell ref="E254:F254"/>
+    <mergeCell ref="E255:F255"/>
+    <mergeCell ref="E256:F256"/>
+    <mergeCell ref="E257:F257"/>
+    <mergeCell ref="E258:F258"/>
+    <mergeCell ref="E259:F259"/>
+    <mergeCell ref="E260:F260"/>
+    <mergeCell ref="E261:F261"/>
+    <mergeCell ref="E262:F262"/>
+    <mergeCell ref="E263:F263"/>
+    <mergeCell ref="E264:F264"/>
+    <mergeCell ref="E265:F265"/>
+    <mergeCell ref="E266:F266"/>
+    <mergeCell ref="E267:F267"/>
+    <mergeCell ref="E268:F268"/>
+    <mergeCell ref="E269:F269"/>
+    <mergeCell ref="E270:F270"/>
+    <mergeCell ref="E271:F271"/>
+    <mergeCell ref="E272:F272"/>
+    <mergeCell ref="E273:F273"/>
+    <mergeCell ref="E274:F274"/>
+    <mergeCell ref="E275:F275"/>
+    <mergeCell ref="E276:F276"/>
+    <mergeCell ref="E277:F277"/>
+    <mergeCell ref="E278:F278"/>
+    <mergeCell ref="E279:F279"/>
+    <mergeCell ref="E280:F280"/>
+    <mergeCell ref="E281:F281"/>
+    <mergeCell ref="E282:F282"/>
+    <mergeCell ref="E283:F283"/>
+    <mergeCell ref="E284:F284"/>
+    <mergeCell ref="E285:F285"/>
+    <mergeCell ref="E286:F286"/>
+    <mergeCell ref="E287:F287"/>
+    <mergeCell ref="E288:F288"/>
+    <mergeCell ref="E289:F289"/>
+    <mergeCell ref="E290:F290"/>
+    <mergeCell ref="E291:F291"/>
+    <mergeCell ref="E292:F292"/>
+    <mergeCell ref="E293:F293"/>
+    <mergeCell ref="E294:F294"/>
+    <mergeCell ref="E295:F295"/>
+    <mergeCell ref="E296:F296"/>
+    <mergeCell ref="E297:F297"/>
+    <mergeCell ref="E298:F298"/>
+    <mergeCell ref="E299:F299"/>
+    <mergeCell ref="E300:F300"/>
+    <mergeCell ref="E301:F301"/>
+    <mergeCell ref="E302:F302"/>
+    <mergeCell ref="E303:F303"/>
+    <mergeCell ref="E304:F304"/>
+    <mergeCell ref="E305:F305"/>
+    <mergeCell ref="E306:F306"/>
+    <mergeCell ref="E307:F307"/>
+    <mergeCell ref="E308:F308"/>
+    <mergeCell ref="E309:F309"/>
+    <mergeCell ref="E310:F310"/>
+    <mergeCell ref="E311:F311"/>
+    <mergeCell ref="E312:F312"/>
+    <mergeCell ref="E313:F313"/>
+    <mergeCell ref="E314:F314"/>
+    <mergeCell ref="E315:F315"/>
+    <mergeCell ref="E316:F316"/>
+    <mergeCell ref="E317:F317"/>
+    <mergeCell ref="E318:F318"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" fitToHeight="0" fitToWidth="1" pageOrder="overThenDown" orientation="portrait" paperSize="9"/>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Desktop\ruAstro\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466F28A1-FC91-4CA3-9E77-660776BDFD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3435767-70AE-44CB-BCDA-F626F79F0427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6045" yWindow="1650" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="193">
   <si>
     <t>№ п/п</t>
   </si>
@@ -315,18 +315,6 @@
     <t>ЛГУП-6540</t>
   </si>
   <si>
-    <t>УЗНО Труба D20х5 БрКМц 3-1 ГОСТ 1208-2014</t>
-  </si>
-  <si>
-    <t>ЛГУП-6542</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D75х10 БрКМц 3-1 ГОСТ 1628-78</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D85х15 БрКМц 3-1 ГОСТ 1628-78</t>
-  </si>
-  <si>
     <t>ТОР 50</t>
   </si>
   <si>
@@ -408,39 +396,6 @@
     <t>ЛГУП-6584</t>
   </si>
   <si>
-    <t>УЗНО Шпилька М16-6gx220 ГОСТ 22042-76</t>
-  </si>
-  <si>
-    <t>ЛГУП-6590</t>
-  </si>
-  <si>
-    <t>УЗНО Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
-  </si>
-  <si>
-    <t>УЗНО Шайба А 16.37 ГОСТ 6958-78</t>
-  </si>
-  <si>
-    <t>УЗНО Саморез для сэндвич панелей 5,5х100</t>
-  </si>
-  <si>
-    <t>УЗНО Заклепка 4,8х8 оцинкованная</t>
-  </si>
-  <si>
-    <t>УЗНО Заклепка 4,8х10</t>
-  </si>
-  <si>
-    <t>УЗНО Саморез 4,2х19 оцинк. со сверлом</t>
-  </si>
-  <si>
-    <t>УЗНО Саморез кровельный 5,5х19 RAL9016 (белый)</t>
-  </si>
-  <si>
-    <t>УЗНО Саморез для сэндвич панелей 5,5х130</t>
-  </si>
-  <si>
-    <t>Заклепка резьбовая Сварком М 5 НЕРЖ цб А2</t>
-  </si>
-  <si>
     <t>УЗНО дверь левая с доводчиком 1900х1000мм(полотно/коробка RAL7042)с рег вент-ми отверстием</t>
   </si>
   <si>
@@ -474,21 +429,6 @@
     <t>ЛГУП-6600</t>
   </si>
   <si>
-    <t>УЗНО Прибор-контрольный охранно пожарный ППКОП 0104065-4-1 "С2000-4"</t>
-  </si>
-  <si>
-    <t>ЛГУП-6602</t>
-  </si>
-  <si>
-    <t>МИП-24 исп.20 (МИП-24-2/П5-Р-RS), до двух АКБ 12 В 17 Ач</t>
-  </si>
-  <si>
-    <t>Блок коммутации 24В БК-24-RS485-01</t>
-  </si>
-  <si>
-    <t>Аккумулятор 12 В 17 Ач SF 1217</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Датчик температуры ТПС 108Exd-100/80-M20x1,5/8-C10-100M-B/-50/50-0,25-F-FECA1I-П</t>
   </si>
   <si>
@@ -661,6 +601,9 @@
   </si>
   <si>
     <t>Условие оплаты</t>
+  </si>
+  <si>
+    <t>ЛГУП-6622</t>
   </si>
 </sst>
 </file>
@@ -1160,13 +1103,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1229,7 +1172,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5" s="6">
         <v>300</v>
@@ -1247,7 +1190,7 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="6">
         <v>300</v>
@@ -1265,7 +1208,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="6">
         <v>300</v>
@@ -1283,7 +1226,7 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6">
         <v>300</v>
@@ -1319,10 +1262,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="10" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D10" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>7</v>
@@ -1337,10 +1280,10 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>7</v>
@@ -1355,10 +1298,10 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D12" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>7</v>
@@ -1373,10 +1316,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>7</v>
@@ -1391,10 +1334,10 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>7</v>
@@ -1409,13 +1352,13 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="10" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D15" s="6">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>22</v>
@@ -1427,10 +1370,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" s="6">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>7</v>
@@ -1445,10 +1388,10 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D17" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>7</v>
@@ -1463,7 +1406,7 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D18" s="6">
         <v>1</v>
@@ -1481,10 +1424,10 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="10" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D19" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>7</v>
@@ -1499,10 +1442,10 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D20" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>7</v>
@@ -1517,10 +1460,10 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="10" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D21" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>7</v>
@@ -1535,7 +1478,7 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="10" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D22" s="6">
         <v>4</v>
@@ -1553,10 +1496,10 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D23" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>7</v>
@@ -1571,10 +1514,10 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="10" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D24" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>7</v>
@@ -1589,10 +1532,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="10" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D25" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>7</v>
@@ -1607,10 +1550,10 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="10" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D26" s="6">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>39</v>
@@ -1625,10 +1568,10 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D27" s="6">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>39</v>
@@ -1643,13 +1586,13 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="10" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D28" s="6">
-        <v>2</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>22</v>
@@ -1661,13 +1604,13 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D29" s="6">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>22</v>
@@ -1679,10 +1622,10 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D30" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>7</v>
@@ -1697,10 +1640,10 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D31" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>7</v>
@@ -1715,7 +1658,7 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D32" s="6">
         <v>2</v>
@@ -1733,10 +1676,10 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="10" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D33" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>7</v>
@@ -1751,10 +1694,10 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="10" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D34" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>7</v>
@@ -1769,10 +1712,10 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="10" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D35" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>7</v>
@@ -1787,10 +1730,10 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="10" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D36" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>7</v>
@@ -1805,13 +1748,13 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="10" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D37" s="6">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>22</v>
@@ -1823,10 +1766,10 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="10" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D38" s="6">
-        <v>0.44400000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>39</v>
@@ -1841,13 +1784,13 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="10" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D39" s="6">
-        <v>0.08</v>
+        <v>4</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>22</v>
@@ -1859,13 +1802,13 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="10" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D40" s="6">
-        <v>0.22</v>
+        <v>4</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>22</v>
@@ -1877,10 +1820,10 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="10" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D41" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>7</v>
@@ -1913,7 +1856,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D43" s="6">
         <v>1</v>
@@ -1931,7 +1874,7 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D44" s="6">
         <v>1</v>
@@ -1967,10 +1910,10 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="10" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D46" s="6">
-        <v>0.68</v>
+        <v>617.29999999999995</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>39</v>
@@ -1985,10 +1928,10 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="10" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D47" s="6">
-        <v>0.56999999999999995</v>
+        <v>7.24</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>39</v>
@@ -2003,10 +1946,10 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="10" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D48" s="6">
-        <v>2.85</v>
+        <v>36.6</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>39</v>
@@ -2021,10 +1964,10 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="10" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D49" s="6">
-        <v>1.25</v>
+        <v>39.42</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>39</v>
@@ -2039,10 +1982,10 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="10" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D50" s="6">
-        <v>18.48</v>
+        <v>7.45</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>39</v>
@@ -2057,10 +2000,10 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="10" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D51" s="6">
-        <v>33.4</v>
+        <v>1.36</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>39</v>
@@ -2075,10 +2018,10 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D52" s="6">
-        <v>2.9</v>
+        <v>33.4</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>39</v>
@@ -2093,10 +2036,10 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D53" s="6">
-        <v>14.12</v>
+        <v>18.48</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>39</v>
@@ -2111,10 +2054,10 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="10" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D54" s="6">
-        <v>3.32</v>
+        <v>1.25</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>39</v>
@@ -2129,10 +2072,10 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="10" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D55" s="8">
-        <v>1144.9100000000001</v>
+        <v>2.85</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>39</v>
@@ -2147,10 +2090,10 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D56" s="6">
-        <v>32.19</v>
+        <v>18.91</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>39</v>
@@ -2165,10 +2108,10 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="10" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D57" s="6">
-        <v>617.29999999999995</v>
+        <v>13.2</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>39</v>
@@ -2183,10 +2126,10 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="10" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D58" s="6">
-        <v>6.45</v>
+        <v>3.7</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>39</v>
@@ -2201,10 +2144,10 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D59" s="6">
-        <v>14.38</v>
+        <v>66.959999999999994</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>39</v>
@@ -2219,10 +2162,10 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D60" s="6">
-        <v>167.75</v>
+        <v>3.9</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>39</v>
@@ -2255,10 +2198,10 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D62" s="6">
-        <v>3.9</v>
+        <v>167.75</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>39</v>
@@ -2273,10 +2216,10 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D63" s="6">
-        <v>18.91</v>
+        <v>14.38</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>39</v>
@@ -2291,10 +2234,10 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D64" s="6">
-        <v>66.959999999999994</v>
+        <v>6.45</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>39</v>
@@ -2309,10 +2252,10 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="10" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D65" s="6">
-        <v>36.6</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>39</v>
@@ -2327,10 +2270,10 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="10" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D66" s="6">
-        <v>13.2</v>
+        <v>12.88</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>39</v>
@@ -2345,10 +2288,10 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="10" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D67" s="6">
-        <v>3.7</v>
+        <v>0.68</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>39</v>
@@ -2363,10 +2306,10 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="10" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D68" s="6">
-        <v>39.42</v>
+        <v>32.19</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>39</v>
@@ -2381,10 +2324,10 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="10" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D69" s="6">
-        <v>7.24</v>
+        <v>1144.9100000000001</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>39</v>
@@ -2399,10 +2342,10 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D70" s="6">
-        <v>7.45</v>
+        <v>3.32</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>39</v>
@@ -2417,10 +2360,10 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="10" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D71" s="6">
-        <v>1.36</v>
+        <v>14.12</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>39</v>
@@ -2435,10 +2378,10 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="10" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D72" s="6">
-        <v>12.88</v>
+        <v>2.9</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>39</v>
@@ -2471,7 +2414,7 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D74" s="6">
         <v>1</v>
@@ -2489,10 +2432,10 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D75" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>7</v>
@@ -2519,16 +2462,16 @@
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>76</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D77" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>7</v>
@@ -2543,10 +2486,10 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D78" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>7</v>
@@ -2582,10 +2525,10 @@
         <v>96</v>
       </c>
       <c r="D80" s="6">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>97</v>
@@ -2597,16 +2540,16 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D81" s="6">
-        <v>0.82</v>
+        <v>3</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2615,16 +2558,16 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D82" s="6">
+        <v>3</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="D82" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2636,13 +2579,13 @@
         <v>100</v>
       </c>
       <c r="D83" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2651,7 +2594,7 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D84" s="6">
         <v>3</v>
@@ -2660,25 +2603,25 @@
         <v>7</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>84</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D85" s="6">
         <v>3</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2687,16 +2630,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" s="6">
+        <v>16</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="D86" s="6">
-        <v>3</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2705,16 +2648,16 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D87" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2723,16 +2666,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="10" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D88" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2741,7 +2684,7 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="10" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D89" s="6">
         <v>8</v>
@@ -2750,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2759,16 +2702,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D90" s="6">
         <v>8</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2777,16 +2720,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D91" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2795,34 +2738,34 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="10" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D92" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>92</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D93" s="6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2831,16 +2774,16 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D94" s="6">
         <v>3</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2858,7 +2801,7 @@
         <v>7</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2867,7 +2810,7 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D96" s="6">
         <v>3</v>
@@ -2876,43 +2819,43 @@
         <v>7</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="10" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D97" s="6">
         <v>3</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="10" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D98" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2921,34 +2864,34 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D99" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D100" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2957,16 +2900,16 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="10" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D101" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2975,16 +2918,16 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D102" s="6">
         <v>1</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2993,16 +2936,16 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="10" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D103" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3011,16 +2954,16 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="10" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D104" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3029,16 +2972,16 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="10" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D105" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3047,7 +2990,7 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D106" s="6">
         <v>2</v>
@@ -3056,7 +2999,7 @@
         <v>7</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3065,16 +3008,16 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D107" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3083,7 +3026,7 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D108" s="6">
         <v>1</v>
@@ -3092,7 +3035,7 @@
         <v>7</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3101,16 +3044,16 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D109" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3119,7 +3062,7 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="10" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D110" s="6">
         <v>2</v>
@@ -3128,7 +3071,7 @@
         <v>7</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3137,19 +3080,19 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D111" s="6">
+        <v>1.71</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F111" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D111" s="6">
-        <v>2</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -3158,13 +3101,13 @@
         <v>121</v>
       </c>
       <c r="D112" s="6">
-        <v>1</v>
+        <v>11.6</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3173,16 +3116,16 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D113" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3191,16 +3134,16 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D114" s="6">
-        <v>1.71</v>
+        <v>8</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3209,16 +3152,16 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D115" s="6">
-        <v>11.6</v>
+        <v>16</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3227,16 +3170,16 @@
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D116" s="6">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3245,16 +3188,16 @@
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D117" s="6">
+        <v>11.52</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F117" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="D117" s="6">
-        <v>32</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3263,16 +3206,16 @@
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D118" s="6">
-        <v>32</v>
+        <v>235.28</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3281,16 +3224,16 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="10" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D119" s="6">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3299,16 +3242,16 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="10" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D120" s="6">
-        <v>240</v>
+        <v>5</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3317,16 +3260,16 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="10" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D121" s="6">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3335,16 +3278,16 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D122" s="6">
-        <v>960</v>
+        <v>2</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3353,16 +3296,16 @@
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="10" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="D123" s="6">
-        <v>62.4</v>
+        <v>1</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3371,16 +3314,16 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D124" s="8">
+        <v>2</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F124" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="D124" s="8">
-        <v>2000</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3389,16 +3332,16 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D125" s="6">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3407,34 +3350,34 @@
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="10" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D126" s="6">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D127" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3443,16 +3386,16 @@
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="10" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D128" s="6">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3461,16 +3404,16 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D129" s="6">
-        <v>11.52</v>
+        <v>22</v>
       </c>
       <c r="E129" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F129" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3479,16 +3422,16 @@
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="10" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D130" s="6">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3497,16 +3440,16 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="10" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="D131" s="6">
-        <v>8</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3515,13 +3458,13 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="10" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D132" s="6">
-        <v>235.28</v>
+        <v>1</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>148</v>
@@ -3533,16 +3476,16 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="10" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D133" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3551,7 +3494,7 @@
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D134" s="6">
         <v>1</v>
@@ -3560,7 +3503,7 @@
         <v>7</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3569,16 +3512,16 @@
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D135" s="6">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3587,70 +3530,70 @@
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D136" s="6">
-        <v>2</v>
+        <v>0.13</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>136</v>
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D137" s="6">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>137</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D138" s="6">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>138</v>
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D139" s="6">
-        <v>5</v>
+        <v>2E-3</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3659,16 +3602,16 @@
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="10" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D140" s="6">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3677,16 +3620,16 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D141" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3695,34 +3638,34 @@
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D142" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>142</v>
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="10" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D143" s="6">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3731,16 +3674,16 @@
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D144" s="6">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3749,16 +3692,16 @@
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D145" s="6">
-        <v>22</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3767,16 +3710,16 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="10" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="D146" s="6">
-        <v>17</v>
+        <v>1.44</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3785,7 +3728,7 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="10" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D147" s="6">
         <v>3</v>
@@ -3794,7 +3737,7 @@
         <v>7</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3803,16 +3746,16 @@
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="10" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D148" s="6">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3821,16 +3764,16 @@
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D149" s="6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>170</v>
+        <v>7</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3839,16 +3782,16 @@
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="10" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="D150" s="6">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>143</v>
+        <v>7</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3857,16 +3800,16 @@
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D151" s="6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>172</v>
+        <v>7</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3875,16 +3818,16 @@
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="10" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D152" s="6">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3893,16 +3836,16 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="10" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D153" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3911,16 +3854,16 @@
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="10" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="D154" s="6">
-        <v>0.13</v>
+        <v>1</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3929,16 +3872,16 @@
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="10" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D155" s="6">
-        <v>2.1999999999999999E-2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>177</v>
+        <v>7</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3947,16 +3890,16 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="10" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="D156" s="6">
-        <v>2E-3</v>
+        <v>2</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3965,16 +3908,16 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D157" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3983,7 +3926,7 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D158" s="6">
         <v>1</v>
@@ -3992,16 +3935,16 @@
         <v>7</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>158</v>
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D159" s="6">
         <v>1</v>
@@ -4010,7 +3953,7 @@
         <v>7</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4019,16 +3962,16 @@
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D160" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4037,16 +3980,16 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D161" s="6">
+        <v>2</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F161" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="D161" s="6">
-        <v>1</v>
-      </c>
-      <c r="E161" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4055,16 +3998,16 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D162" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>7</v>
+        <v>182</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4073,16 +4016,16 @@
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="10" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="D163" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4091,16 +4034,16 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D164" s="6">
-        <v>1</v>
+        <v>1248.52</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4109,16 +4052,16 @@
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="10" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="D165" s="6">
-        <v>1</v>
+        <v>1248.52</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4127,16 +4070,16 @@
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D166" s="6">
-        <v>4</v>
+        <v>312.13</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4148,13 +4091,13 @@
         <v>187</v>
       </c>
       <c r="D167" s="6">
-        <v>10</v>
+        <v>312.13</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4163,16 +4106,16 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D168" s="6">
+        <v>312.13</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F168" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="D168" s="6">
-        <v>1</v>
-      </c>
-      <c r="E168" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4181,16 +4124,16 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="10" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D169" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>7</v>
+        <v>182</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4199,305 +4142,145 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D170" s="6">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="3">
-        <v>170</v>
-      </c>
+      <c r="A171" s="3"/>
       <c r="B171" s="4"/>
-      <c r="C171" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="D171" s="6">
-        <v>1</v>
-      </c>
-      <c r="E171" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>168</v>
-      </c>
+      <c r="C171" s="10"/>
+      <c r="D171" s="6"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="5"/>
     </row>
     <row r="172" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="3">
-        <v>171</v>
-      </c>
+      <c r="A172" s="3"/>
       <c r="B172" s="4"/>
-      <c r="C172" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="D172" s="6">
-        <v>3</v>
-      </c>
-      <c r="E172" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>168</v>
-      </c>
+      <c r="C172" s="10"/>
+      <c r="D172" s="6"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="5"/>
     </row>
     <row r="173" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="3">
-        <v>172</v>
-      </c>
+      <c r="A173" s="3"/>
       <c r="B173" s="4"/>
-      <c r="C173" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="D173" s="6">
-        <v>22</v>
-      </c>
-      <c r="E173" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>168</v>
-      </c>
+      <c r="C173" s="10"/>
+      <c r="D173" s="6"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="5"/>
     </row>
     <row r="174" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="3">
-        <v>173</v>
-      </c>
+      <c r="A174" s="3"/>
       <c r="B174" s="4"/>
-      <c r="C174" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D174" s="6">
-        <v>63</v>
-      </c>
-      <c r="E174" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>168</v>
-      </c>
+      <c r="C174" s="10"/>
+      <c r="D174" s="6"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="5"/>
     </row>
     <row r="175" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="3">
-        <v>174</v>
-      </c>
+      <c r="A175" s="3"/>
       <c r="B175" s="4"/>
-      <c r="C175" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D175" s="6">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="E175" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>168</v>
-      </c>
+      <c r="C175" s="10"/>
+      <c r="D175" s="6"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="5"/>
     </row>
     <row r="176" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="3">
-        <v>175</v>
-      </c>
+      <c r="A176" s="3"/>
       <c r="B176" s="4"/>
-      <c r="C176" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="D176" s="6">
-        <v>1</v>
-      </c>
-      <c r="E176" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>197</v>
-      </c>
+      <c r="C176" s="10"/>
+      <c r="D176" s="6"/>
+      <c r="E176" s="7"/>
+      <c r="F176" s="5"/>
     </row>
     <row r="177" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="3">
-        <v>176</v>
-      </c>
+      <c r="A177" s="3"/>
       <c r="B177" s="4"/>
-      <c r="C177" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="D177" s="6">
-        <v>1</v>
-      </c>
-      <c r="E177" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>199</v>
-      </c>
+      <c r="C177" s="10"/>
+      <c r="D177" s="6"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="5"/>
     </row>
     <row r="178" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="3">
-        <v>177</v>
-      </c>
+      <c r="A178" s="3"/>
       <c r="B178" s="4"/>
-      <c r="C178" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D178" s="6">
-        <v>1</v>
-      </c>
-      <c r="E178" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>199</v>
-      </c>
+      <c r="C178" s="10"/>
+      <c r="D178" s="6"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="5"/>
     </row>
     <row r="179" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="3">
-        <v>178</v>
-      </c>
+      <c r="A179" s="3"/>
       <c r="B179" s="4"/>
-      <c r="C179" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="D179" s="6">
-        <v>2</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>203</v>
-      </c>
+      <c r="C179" s="10"/>
+      <c r="D179" s="6"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="5"/>
     </row>
     <row r="180" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="3">
-        <v>179</v>
-      </c>
+      <c r="A180" s="3"/>
       <c r="B180" s="4"/>
-      <c r="C180" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D180" s="6">
-        <v>2</v>
-      </c>
-      <c r="E180" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>203</v>
-      </c>
+      <c r="C180" s="10"/>
+      <c r="D180" s="6"/>
+      <c r="E180" s="7"/>
+      <c r="F180" s="5"/>
     </row>
     <row r="181" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="3">
-        <v>180</v>
-      </c>
+      <c r="A181" s="3"/>
       <c r="B181" s="4"/>
-      <c r="C181" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D181" s="6">
-        <v>12</v>
-      </c>
-      <c r="E181" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>206</v>
-      </c>
+      <c r="C181" s="10"/>
+      <c r="D181" s="6"/>
+      <c r="E181" s="7"/>
+      <c r="F181" s="5"/>
     </row>
     <row r="182" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="3">
-        <v>181</v>
-      </c>
+      <c r="A182" s="3"/>
       <c r="B182" s="4"/>
-      <c r="C182" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D182" s="8">
-        <v>1248.52</v>
-      </c>
-      <c r="E182" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>208</v>
-      </c>
+      <c r="C182" s="10"/>
+      <c r="D182" s="8"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="5"/>
     </row>
     <row r="183" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="3">
-        <v>182</v>
-      </c>
+      <c r="A183" s="3"/>
       <c r="B183" s="4"/>
-      <c r="C183" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D183" s="8">
-        <v>1248.52</v>
-      </c>
-      <c r="E183" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>208</v>
-      </c>
+      <c r="C183" s="10"/>
+      <c r="D183" s="8"/>
+      <c r="E183" s="7"/>
+      <c r="F183" s="5"/>
     </row>
     <row r="184" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="3">
-        <v>183</v>
-      </c>
+      <c r="A184" s="3"/>
       <c r="B184" s="4"/>
-      <c r="C184" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D184" s="6">
-        <v>312.13</v>
-      </c>
-      <c r="E184" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>208</v>
-      </c>
+      <c r="C184" s="10"/>
+      <c r="D184" s="6"/>
+      <c r="E184" s="7"/>
+      <c r="F184" s="5"/>
     </row>
     <row r="185" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="3">
-        <v>184</v>
-      </c>
+      <c r="A185" s="3"/>
       <c r="B185" s="4"/>
-      <c r="C185" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D185" s="6">
-        <v>312.13</v>
-      </c>
-      <c r="E185" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>208</v>
-      </c>
+      <c r="C185" s="10"/>
+      <c r="D185" s="6"/>
+      <c r="E185" s="7"/>
+      <c r="F185" s="5"/>
     </row>
     <row r="186" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="3">
-        <v>185</v>
-      </c>
+      <c r="A186" s="3"/>
       <c r="B186" s="4"/>
-      <c r="C186" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D186" s="6">
-        <v>312.13</v>
-      </c>
-      <c r="E186" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>208</v>
-      </c>
+      <c r="C186" s="10"/>
+      <c r="D186" s="6"/>
+      <c r="E186" s="7"/>
+      <c r="F186" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Desktop\ruAstro\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3435767-70AE-44CB-BCDA-F626F79F0427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBAEC6B-4348-4F05-8076-6D1296D931C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="140">
   <si>
     <t>№ п/п</t>
   </si>
@@ -45,24 +45,12 @@
     <t>Примечание</t>
   </si>
   <si>
-    <t>УЗНО Термостат MTK-CT0</t>
-  </si>
-  <si>
     <t>шт</t>
   </si>
   <si>
     <t>ЛГУП-6441</t>
   </si>
   <si>
-    <t>Масло индустриальное YMOIL HC-68 (200л)</t>
-  </si>
-  <si>
-    <t>ЛГУП-6488</t>
-  </si>
-  <si>
-    <t>УЗНО Счетчик Тор-50 Ха 2.833.034 1ExdIICT4 X, IP65</t>
-  </si>
-  <si>
     <t>ЛГУП-6489</t>
   </si>
   <si>
@@ -90,105 +78,12 @@
     <t>НТ00-000048</t>
   </si>
   <si>
-    <t>УЗНО Кольцо А18х1,2 ГОСТ 13942-86</t>
-  </si>
-  <si>
     <t>ЛГУП-6531</t>
   </si>
   <si>
-    <t>УЗНО Кольцо А20х1,2 ГОСТ 13940-86</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо А75 ГОСТ 13943-86 (с пазами)</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо А75х1,7 ГОСТ 13943-86_УЗНО</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо уплотнительное НТ.300.000.010.0</t>
-  </si>
-  <si>
-    <t>УЗНО Магнит D4х5 неодимовый</t>
-  </si>
-  <si>
-    <t>УЗНО Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
-  </si>
-  <si>
-    <t>УЗНО Пружина №442 НТ.110.000.007.0</t>
-  </si>
-  <si>
-    <t>УЗНО Пружина №467 НТ.200.000.029.0</t>
-  </si>
-  <si>
-    <t>УЗНО Пружина крышки НТ.200.004.003.0</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 018-021-19-2-3 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 014-018-25 ГОСТ 9833-73 (фторкаучук)</t>
-  </si>
-  <si>
-    <t>УЗНО 2-х вентильный клапанный блок КБ-2х40.01(M20x1,5Н,M20x1,5B; M14x1,5B)</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 200-210-46-1-1 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 100-106-36-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 096-102-36-2-3 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Полиамид D70 П-12Б-20 ТУ 6-05-898-73</t>
-  </si>
-  <si>
     <t>кг</t>
   </si>
   <si>
-    <t>УЗНО Полиамид D80 П-12Б-20 ТУ 6-05-988-87</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 080-086-36-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 080-085-30-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 070-076-36-2-4 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 062-068-36-2-3 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 060-065-30-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 055-060-30-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 028-032-25-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Кольцо 020-025-30-2-4 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>УЗНО Паронит ПМБ 2 ГОСТ 481-80</t>
-  </si>
-  <si>
-    <t>УЗНО Паронит ПОН 2,0 ГОСТ 481-80 (кг)</t>
-  </si>
-  <si>
-    <t>УЗНО Полиамид D30 П-15Б-20  ТУ 6-05-988-87</t>
-  </si>
-  <si>
-    <t>УЗНО Полиамид D40 П-15Б-20 ТУ 6-05-988-87</t>
-  </si>
-  <si>
     <t>Кольцо уплотнительное НТ.202.003.004.0</t>
   </si>
   <si>
@@ -198,120 +93,15 @@
     <t>ЛГУП-6533</t>
   </si>
   <si>
-    <t>УЗНО Рычаг НТ.510.000.003.0 (лазер)</t>
-  </si>
-  <si>
     <t>Шибер НТ.530.000.005.0 (лазер)</t>
   </si>
   <si>
-    <t>УЗНО Труба D22х4 09Г2С</t>
-  </si>
-  <si>
-    <t>ЛГУП-6534</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D20х6 09Г2С</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D85х10 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D152х5 09Г2С ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D14х2 09Г2С ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D133х32 Ст.20 ГОСТ 8372-78</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D133х28 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D133х25 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D108х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D108х19 ГОСТ 8732-78/ Ст.09Г2С ГОСТ 19281-14</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D1020х16 ст.09Г2С ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>УЗНО Труба 108х8 ст.09Г2С ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D720х14 Ст.09Г2С-К50 ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D89х8 Ст.35 ГОСТ 1050-80</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D83х12 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D57х6 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D159х14 ГОСТ 8732-78/ Ст.09Г2С-3 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D480х16 10Г2 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D159х25 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D219х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D32х4 Ст.09Г2С ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D273х16 Ст.09Г2С-3 ГОСТ 8731-87</t>
-  </si>
-  <si>
     <t>Клапан предохранительный СППК4р 17с25нж Ду80 Ру40</t>
   </si>
   <si>
     <t>ЛГУП-6535</t>
   </si>
   <si>
-    <t>УЗНО Задвижка ЗКЛ 50-40 ХЛ1 30лс15нж класс герм. А, исп.F ХЛ1 L=216 без КОФ</t>
-  </si>
-  <si>
-    <t>УЗНО Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
-  </si>
-  <si>
-    <t>УЗНО Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>УЗНО Задвижка клиновая стальная ЗКС Ду25 Ру160 УХЛ1, класс герметичности "А"</t>
-  </si>
-  <si>
     <t>ЛГУП-6540</t>
   </si>
   <si>
@@ -384,216 +174,45 @@
     <t>Шланг пескоструйный Диаметр 25х39, 40 метров, байонетное сцепление</t>
   </si>
   <si>
-    <t>УЗНО Лист S=3 Ст.20 ГОСТ 16523-97</t>
-  </si>
-  <si>
-    <t>ЛГУП-6583</t>
-  </si>
-  <si>
-    <t>УЗНО Круг D98 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>ЛГУП-6584</t>
-  </si>
-  <si>
-    <t>УЗНО дверь левая с доводчиком 1900х1000мм(полотно/коробка RAL7042)с рег вент-ми отверстием</t>
-  </si>
-  <si>
-    <t>ЛГУП-6591</t>
-  </si>
-  <si>
-    <t>УЗНО Магнит ПСМНТ.001.021.001</t>
-  </si>
-  <si>
     <t>ЛГУП-6598</t>
   </si>
   <si>
-    <t>УЗНО Мин. вата типа "URSA" П-125</t>
-  </si>
-  <si>
     <t>м3</t>
   </si>
   <si>
     <t>ЛГУП-6599</t>
   </si>
   <si>
-    <t>УЗНО Петля накладная ПН1-70 ГОСТ 5088-2005</t>
-  </si>
-  <si>
-    <t>УЗНО Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
-  </si>
-  <si>
-    <t>УЗНО Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
-  </si>
-  <si>
-    <t>ЛГУП-6600</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Датчик температуры ТПС 108Exd-100/80-M20x1,5/8-C10-100M-B/-50/50-0,25-F-FECA1I-П</t>
-  </si>
-  <si>
     <t>ЛГУП-6610</t>
   </si>
   <si>
     <t>Преобразователь избыточного давления ТП-ДИП 0 ... 6МПа IP67; Exd 4-20мА+HART М20х1,5</t>
   </si>
   <si>
-    <t>УЗНО Манометр МП4 P=0..6МПа, ХЛ1 ст.защиты корпуса IP54, кл.точн. 1,0. Присоед-е: М20х1,5 - наружн</t>
-  </si>
-  <si>
-    <t>Влагомер сырой нефти ВСН-2 Ду 80, Ру 40 (угловой)</t>
-  </si>
-  <si>
-    <t>УЗНО Датчик изгибающего момента тип 108 длина крыла 64мм</t>
-  </si>
-  <si>
     <t>Термометр показывающий БТ-52.220-100-1,5-( 0...+100С) М20х1,5</t>
   </si>
   <si>
     <t>Расходомер ЭМИС-МАСС 260-Ех-80-Д-Ж-4,0 вых.сигнал частотно-импульсный, RS-485 Modbus RTU</t>
   </si>
   <si>
-    <t>УЗНО Прокладка А-150-40-А ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>ЛГУП-6611</t>
-  </si>
-  <si>
-    <t>УЗНО Прокладка Б-80-40-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>УЗНО Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>УЗНО Прокладка Б-450-40-ПМБ-1-2 ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>УЗНО Смола ЭД-20 ГОСТ 10587-84</t>
-  </si>
-  <si>
     <t>ЛГУП-6612</t>
   </si>
   <si>
-    <t>УЗНО Скотч защитный термоусадочный Magnapak цвет белый, 5 см</t>
-  </si>
-  <si>
     <t>м</t>
   </si>
   <si>
-    <t>УЗНО Лента ПСУЛ 20х8/40</t>
-  </si>
-  <si>
     <t>пог. м</t>
   </si>
   <si>
-    <t>УЗНО Изолон НПЭ В 4мм несортовой ТУ 2244-020-00203474-2004</t>
-  </si>
-  <si>
-    <t>УЗНО Пленка полиэтиленовая рукав 0,3х3000 ГОСТ 10354-82</t>
-  </si>
-  <si>
-    <t>УЗНО Литол 24 /кг/</t>
-  </si>
-  <si>
-    <t>УЗНО Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
-  </si>
-  <si>
-    <t>м2</t>
-  </si>
-  <si>
-    <t>УЗНО Отвердитель ПЭПА</t>
-  </si>
-  <si>
-    <t>УЗНО Герметик "Макрофлекс"  силик. универс. белый 290мл</t>
-  </si>
-  <si>
-    <t>УЗНО Герметик силиконовый универс. белый 310мл</t>
-  </si>
-  <si>
-    <t>УЗНО Емкость пластиковая 0,5л (дно плоское, форма емкости - квадрат или прямоугольник)</t>
-  </si>
-  <si>
-    <t>УЗНО Замок навесной 50мм, влагозащищенный, с заглушкой</t>
-  </si>
-  <si>
-    <t>УЗНО Лезвие для ножа профессионального для резки пленки Магнапак</t>
-  </si>
-  <si>
-    <t>УЗНО Пена монтажная "MAKROFLEX " V=1000 мл</t>
-  </si>
-  <si>
-    <t>УЗНО Пленка воздушно-пузырчатая 1500мм*100пог.м 2 сл (рул)</t>
-  </si>
-  <si>
-    <t>УЗНО Скотч 50мм*120м PROFITTO /6/54 прозрачн</t>
-  </si>
-  <si>
-    <t>УЗНО Скотч-малярный</t>
-  </si>
-  <si>
-    <t>УЗНО Стул ЗФ.6.156.005М</t>
-  </si>
-  <si>
-    <t>УЗНО Стяжка нейлон 200мм (упак)</t>
-  </si>
-  <si>
-    <t>УЗНО Хомут 4х300 пластиковый</t>
-  </si>
-  <si>
-    <t>УЗНО Ящик для техновека/нягань (габариты 1500*600*600мм)</t>
-  </si>
-  <si>
-    <t>УЗНО Ящик УОК НКТ НТ.007.094.000</t>
-  </si>
-  <si>
-    <t>УЗНО Пленка термоусадочная Magnapak белая (ширина 9,8 м, толщина 190 мкм)</t>
-  </si>
-  <si>
-    <t>УЗНО Стропа Magnapack</t>
-  </si>
-  <si>
-    <t>УЗНО Маты МБП-20-10000х1000х50</t>
-  </si>
-  <si>
-    <t>УЗНО Упаковка картонная на УРПД-3.1 405(Д)х225(Ш)х80(В) самосборная</t>
-  </si>
-  <si>
-    <t>АХУП-000302</t>
-  </si>
-  <si>
-    <t>УЗНО Заглушка 108х8-09Г2С ГОСТ 17379-2001</t>
-  </si>
-  <si>
-    <t>ЛГУП-6613</t>
-  </si>
-  <si>
-    <t>УЗНО Заглушка 89х8 ст.09Г2С ГОСТ 17379-2001</t>
-  </si>
-  <si>
     <t>Сапоги летние</t>
   </si>
   <si>
     <t>пар</t>
   </si>
   <si>
-    <t>НТ00-000049</t>
-  </si>
-  <si>
     <t>Костюм рабочий</t>
   </si>
   <si>
-    <t>УЗНО Лист профилированный С21-1000-0,7 L=1510мм RAL2008 (оранж)</t>
-  </si>
-  <si>
-    <t>ЛГУП-6618</t>
-  </si>
-  <si>
-    <t>УЗНО Труба D720х12 Ст.09Г2С ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>ЛГУП-6620</t>
-  </si>
-  <si>
     <t>Цена</t>
   </si>
   <si>
@@ -604,6 +223,228 @@
   </si>
   <si>
     <t>ЛГУП-6622</t>
+  </si>
+  <si>
+    <t>Ботинки летние 42 р</t>
+  </si>
+  <si>
+    <t>НТУП-017701</t>
+  </si>
+  <si>
+    <t>Костюм летний от загрязнений и противоэнцефалитный</t>
+  </si>
+  <si>
+    <t>Сцепление крабовое для рукава 25-39мм</t>
+  </si>
+  <si>
+    <t>Термостат MTK-CT0</t>
+  </si>
+  <si>
+    <t>Счетчик Тор-50 Ха 2.833.034 1ExdIICT4 X, IP65</t>
+  </si>
+  <si>
+    <t>Кольцо 020-025-30-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-085-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 096-102-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 100-106-36-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
+  </si>
+  <si>
+    <t>Кольцо А20х1,2 ГОСТ 13940-86</t>
+  </si>
+  <si>
+    <t>Кольцо А75 ГОСТ 13943-86 (с пазами)</t>
+  </si>
+  <si>
+    <t>2-х вентильный клапанный блок КБ-2х40.01(M20x1,5Н,M20x1,5B; M14x1,5B)</t>
+  </si>
+  <si>
+    <t>Пружина крышки НТ.200.004.003.0</t>
+  </si>
+  <si>
+    <t>Кольцо 028-032-25-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 018-021-19-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 014-018-25 ГОСТ 9833-73 (фторкаучук)</t>
+  </si>
+  <si>
+    <t>Кольцо 080-086-36-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 055-060-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 060-065-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 062-068-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 070-076-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное НТ.300.000.010.0</t>
+  </si>
+  <si>
+    <t>Магнит D4х5 неодимовый</t>
+  </si>
+  <si>
+    <t>Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
+  </si>
+  <si>
+    <t>Пружина №442 НТ.110.000.007.0</t>
+  </si>
+  <si>
+    <t>Пружина №467 НТ.200.000.029.0</t>
+  </si>
+  <si>
+    <t>Кольцо 200-210-46-1-1 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Паронит ПМБ 2 ГОСТ 481-80</t>
+  </si>
+  <si>
+    <t>Паронит ПОН 2,0 ГОСТ 481-80 (кг)</t>
+  </si>
+  <si>
+    <t>Полиамид D80 П-12Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Полиамид D70 П-12Б-20 ТУ 6-05-898-73</t>
+  </si>
+  <si>
+    <t>Полиамид D40 П-15Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Полиамид D30 П-15Б-20  ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Рычаг НТ.510.000.003.0 (лазер)</t>
+  </si>
+  <si>
+    <t>Задвижка ЗКЛ 50-40 ХЛ1 30лс15нж класс герм. А, исп.F ХЛ1 L=216 без КОФ</t>
+  </si>
+  <si>
+    <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая стальная ЗКС Ду25 Ру160 УХЛ1, класс герметичности "А"</t>
+  </si>
+  <si>
+    <t>Магнит ПСМНТ.001.021.001</t>
+  </si>
+  <si>
+    <t>Петля накладная ПН1-70 ГОСТ 5088-2005</t>
+  </si>
+  <si>
+    <t>Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
+  </si>
+  <si>
+    <t>Мин. вата типа "URSA" П-125</t>
+  </si>
+  <si>
+    <t>Датчик изгибающего момента тип 108 длина крыла 64мм</t>
+  </si>
+  <si>
+    <t>Манометр МП4 P=0..6МПа, ХЛ1 ст.защиты корпуса IP54, кл.точн. 1,0. Присоед-е: М20х1,5 - наружн</t>
+  </si>
+  <si>
+    <t>Влагомер сырой нефти ВСН-2 Ду 80, Ру 40 (угловой) взрывозащ.1Ex ib IIA T6, IP67</t>
+  </si>
+  <si>
+    <t>Датчик температуры ТПС 108Exd-100/80-M20x1,5/8-C10-100M-B/-50/50-0,25-F-FECA1I-П</t>
+  </si>
+  <si>
+    <t>Изолон НПЭ В 4мм несортовой ТУ 2244-020-00203474-2004</t>
+  </si>
+  <si>
+    <t>Литол 24 /кг/</t>
+  </si>
+  <si>
+    <t>Пленка полиэтиленовая рукав 0,3х3000 ГОСТ 10354-82</t>
+  </si>
+  <si>
+    <t>Отвердитель ПЭПА</t>
+  </si>
+  <si>
+    <t>Лента ПСУЛ 20х8/40</t>
+  </si>
+  <si>
+    <t>Скотч защитный термоусадочный Magnapak цвет белый, 5 см</t>
+  </si>
+  <si>
+    <t>Смола ЭД-20 ГОСТ 10587-84</t>
+  </si>
+  <si>
+    <t>Замок навесной 50мм, влагозащищенный, с заглушкой</t>
+  </si>
+  <si>
+    <t>Лезвие для ножа профессионального для резки пленки Магнапак</t>
+  </si>
+  <si>
+    <t>Стропа Magnapack</t>
+  </si>
+  <si>
+    <t>Ящик УОК НКТ НТ.007.094.000</t>
+  </si>
+  <si>
+    <t>Ящик для техновека/нягань (габариты 1500*600*600мм)</t>
+  </si>
+  <si>
+    <t>Хомут 4х300 пластиковый</t>
+  </si>
+  <si>
+    <t>Стяжка нейлон 200мм (упак)</t>
+  </si>
+  <si>
+    <t>Стул ЗФ.6.156.005М</t>
+  </si>
+  <si>
+    <t>Скотч-малярный</t>
+  </si>
+  <si>
+    <t>Скотч 50мм*120м PROFITTO /6/54 прозрачн</t>
+  </si>
+  <si>
+    <t>Пленка воздушно-пузырчатая 1500мм*100пог.м 2 сл (рул)</t>
+  </si>
+  <si>
+    <t>Пленка термоусадочная Magnapak белая (ширина 9,8 м, толщина 190 мкм)</t>
+  </si>
+  <si>
+    <t>Маты МБП-20-10000х1000х50</t>
+  </si>
+  <si>
+    <t>Пена монтажная "MAKROFLEX " V=1000 мл</t>
+  </si>
+  <si>
+    <t>Емкость пластиковая 0,5л (дно плоское, форма емкости - квадрат или прямоугольник)</t>
+  </si>
+  <si>
+    <t>Герметик силиконовый универс. белый 310мл</t>
+  </si>
+  <si>
+    <t>Герметик "Макрофлекс"  силик. универс. белый 290мл</t>
+  </si>
+  <si>
+    <t>Кольцо А75х1,7 ГОСТ 13943-86</t>
   </si>
 </sst>
 </file>
@@ -1103,13 +944,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>189</v>
+        <v>62</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>191</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1118,16 +959,16 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="10" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D2" s="6">
         <v>5</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1136,16 +977,16 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="10" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="D3" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1154,16 +995,16 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="6">
-        <v>8</v>
+        <v>300</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1172,16 +1013,16 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="10" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D5" s="6">
         <v>300</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1190,16 +1031,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6">
         <v>300</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1208,16 +1049,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="6">
         <v>300</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1226,16 +1067,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="6">
+        <v>50</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="6">
-        <v>300</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>7</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1244,16 +1085,16 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="10" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D9" s="6">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1262,16 +1103,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="10" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1280,16 +1121,16 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="10" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="D11" s="6">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1298,16 +1139,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="10" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="D12" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1316,16 +1157,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="10" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D13" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1334,16 +1175,16 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="10" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D14" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1352,16 +1193,16 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="10" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="D15" s="6">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1370,16 +1211,16 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="10" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="D16" s="6">
         <v>1</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1388,16 +1229,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="10" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D17" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1406,16 +1247,16 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="10" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="D18" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1424,16 +1265,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="10" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="D19" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1442,16 +1283,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="10" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="D20" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1460,16 +1301,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="10" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="D21" s="6">
         <v>2</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1478,16 +1319,16 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="10" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D22" s="6">
         <v>4</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1496,16 +1337,16 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="10" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="D23" s="6">
         <v>2</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1514,16 +1355,16 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="10" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D24" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1532,16 +1373,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="10" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="D25" s="6">
         <v>3</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1550,16 +1391,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="10" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="D26" s="6">
-        <v>0.22</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1568,16 +1409,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="10" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="D27" s="6">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1586,16 +1427,16 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="10" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D28" s="6">
-        <v>0.44400000000000001</v>
+        <v>4</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1604,16 +1445,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="10" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="D29" s="6">
-        <v>0.17</v>
+        <v>40</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1622,16 +1463,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="10" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D30" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1640,16 +1481,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="10" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D31" s="6">
         <v>1</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1658,16 +1499,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="10" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="D32" s="6">
         <v>2</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1676,16 +1517,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="10" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="D33" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1694,16 +1535,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="10" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="D34" s="6">
-        <v>6</v>
+        <v>0.17</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1712,16 +1553,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="10" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D35" s="6">
-        <v>2</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1730,16 +1571,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D36" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1748,16 +1589,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="10" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="D37" s="6">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1766,16 +1607,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="10" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="D38" s="6">
         <v>0.44</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1784,16 +1625,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="10" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D39" s="6">
-        <v>4</v>
+        <v>0.22</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1802,16 +1643,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="10" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D40" s="6">
-        <v>4</v>
+        <v>0.08</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1820,16 +1661,16 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="10" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D41" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1838,16 +1679,16 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="10" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="D42" s="6">
         <v>1</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1856,16 +1697,16 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="10" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D43" s="6">
         <v>1</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1874,16 +1715,16 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="10" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D44" s="6">
         <v>1</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1892,16 +1733,16 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="10" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="D45" s="6">
-        <v>1.59</v>
+        <v>4</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1910,16 +1751,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="10" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D46" s="6">
-        <v>617.29999999999995</v>
+        <v>2</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1928,16 +1769,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="10" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D47" s="6">
-        <v>7.24</v>
+        <v>7</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1946,16 +1787,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="10" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="D48" s="6">
-        <v>36.6</v>
+        <v>1</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1964,16 +1805,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="10" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D49" s="6">
-        <v>39.42</v>
+        <v>3</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1982,16 +1823,16 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="10" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D50" s="6">
-        <v>7.45</v>
+        <v>1</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2000,16 +1841,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="10" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="D51" s="6">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2018,16 +1859,16 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="10" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D52" s="6">
-        <v>33.4</v>
+        <v>3</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2036,16 +1877,16 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="10" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D53" s="6">
-        <v>18.48</v>
+        <v>3</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2054,16 +1895,16 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="10" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D54" s="6">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2072,16 +1913,16 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="10" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D55" s="8">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2090,16 +1931,16 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="10" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="D56" s="6">
-        <v>18.91</v>
+        <v>8</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2108,16 +1949,16 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="10" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="D57" s="6">
-        <v>13.2</v>
+        <v>8</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2126,16 +1967,16 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="10" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="D58" s="6">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2144,16 +1985,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="10" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="D59" s="6">
-        <v>66.959999999999994</v>
+        <v>16</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2162,16 +2003,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="10" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="D60" s="6">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2180,16 +2021,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="10" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="D61" s="6">
-        <v>0.69</v>
+        <v>3</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2198,16 +2039,16 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="10" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="D62" s="6">
-        <v>167.75</v>
+        <v>3</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2216,16 +2057,16 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="10" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="D63" s="6">
-        <v>14.38</v>
+        <v>3</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2234,16 +2075,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="10" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="D64" s="6">
-        <v>6.45</v>
+        <v>3</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2252,16 +2093,16 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="10" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D65" s="6">
-        <v>0.56999999999999995</v>
+        <v>3</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2270,16 +2111,16 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="10" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="D66" s="6">
-        <v>12.88</v>
+        <v>3</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2288,16 +2129,16 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="10" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D67" s="6">
-        <v>0.68</v>
+        <v>3</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2306,16 +2147,16 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="10" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="D68" s="6">
-        <v>32.19</v>
+        <v>1</v>
       </c>
       <c r="E68" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2324,16 +2165,16 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="10" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D69" s="6">
-        <v>1144.9100000000001</v>
+        <v>2</v>
       </c>
       <c r="E69" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F69" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2342,16 +2183,16 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="10" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D70" s="6">
-        <v>3.32</v>
+        <v>1</v>
       </c>
       <c r="E70" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2360,16 +2201,16 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="10" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D71" s="6">
-        <v>14.12</v>
+        <v>1</v>
       </c>
       <c r="E71" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F71" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2378,16 +2219,16 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="10" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D72" s="6">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="E72" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2396,16 +2237,16 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="10" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D73" s="6">
-        <v>44.31</v>
+        <v>2</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2414,16 +2255,16 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="10" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="D74" s="6">
         <v>1</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2432,16 +2273,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="10" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D75" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2450,16 +2291,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="10" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D76" s="6">
         <v>2</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2468,16 +2309,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="10" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="D77" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2486,16 +2327,16 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="10" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D78" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2504,16 +2345,16 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="10" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D79" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2522,16 +2363,16 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="10" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D80" s="6">
         <v>1</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2540,16 +2381,16 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="10" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="D81" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2558,16 +2399,16 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="10" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D82" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2576,16 +2417,16 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="10" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D83" s="6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2594,16 +2435,16 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="10" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D84" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2612,16 +2453,16 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="10" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D85" s="6">
-        <v>3</v>
+        <v>11.52</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2630,16 +2471,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="10" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="D86" s="6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2648,16 +2489,16 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="10" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D87" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2666,16 +2507,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="10" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D88" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2684,16 +2525,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="10" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D89" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2702,16 +2543,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="10" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="D90" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2720,16 +2561,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="10" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="D91" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2738,16 +2579,16 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="10" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D92" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2756,16 +2597,16 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="10" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D93" s="6">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2774,16 +2615,16 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="10" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D94" s="6">
-        <v>3</v>
+        <v>0.13</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2792,16 +2633,16 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="10" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D95" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2810,16 +2651,16 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="10" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D96" s="6">
-        <v>3</v>
+        <v>2E-3</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2828,16 +2669,16 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="10" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D97" s="6">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2846,16 +2687,16 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="10" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D98" s="6">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2864,16 +2705,16 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="10" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D99" s="6">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2882,16 +2723,16 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="D100" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2900,16 +2741,16 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="10" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D101" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2918,16 +2759,16 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="10" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="D102" s="6">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2936,34 +2777,34 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="10" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D103" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="10" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D104" s="6">
         <v>1</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2972,16 +2813,16 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="10" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D105" s="6">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2990,16 +2831,16 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="10" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D106" s="6">
         <v>2</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3008,16 +2849,16 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="10" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D107" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3026,16 +2867,16 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="10" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="D108" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3044,16 +2885,16 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="10" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D109" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3062,16 +2903,16 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D110" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3080,16 +2921,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="10" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D111" s="6">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -3098,16 +2939,16 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="10" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D112" s="6">
-        <v>11.6</v>
+        <v>2</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3116,16 +2957,16 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="10" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D113" s="6">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3134,16 +2975,16 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D114" s="6">
-        <v>8</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3152,16 +2993,16 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="10" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D115" s="6">
-        <v>16</v>
+        <v>1.44</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3170,16 +3011,16 @@
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D116" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3188,16 +3029,16 @@
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="10" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D117" s="6">
-        <v>11.52</v>
+        <v>1</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3206,16 +3047,16 @@
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="10" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D118" s="6">
-        <v>235.28</v>
+        <v>1</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3227,13 +3068,13 @@
         <v>138</v>
       </c>
       <c r="D119" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>135</v>
+        <v>56</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3242,16 +3083,16 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="10" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="D120" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3260,16 +3101,16 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="10" t="s">
-        <v>141</v>
+        <v>59</v>
       </c>
       <c r="D121" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3278,16 +3119,16 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="D122" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3296,16 +3137,16 @@
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="10" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="D123" s="6">
         <v>1</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3314,16 +3155,16 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="10" t="s">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="D124" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3332,827 +3173,377 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="10" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="D125" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="3">
-        <v>125</v>
-      </c>
+      <c r="A126" s="3"/>
       <c r="B126" s="4"/>
-      <c r="C126" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D126" s="6">
-        <v>3</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>143</v>
-      </c>
+      <c r="C126" s="10"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="5"/>
     </row>
     <row r="127" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="3">
-        <v>126</v>
-      </c>
+      <c r="A127" s="3"/>
       <c r="B127" s="4"/>
-      <c r="C127" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="D127" s="6">
-        <v>1</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>143</v>
-      </c>
+      <c r="C127" s="10"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="5"/>
     </row>
     <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="3">
-        <v>127</v>
-      </c>
+      <c r="A128" s="3"/>
       <c r="B128" s="4"/>
-      <c r="C128" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D128" s="6">
-        <v>17</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>143</v>
-      </c>
+      <c r="C128" s="10"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="5"/>
     </row>
     <row r="129" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="3">
-        <v>128</v>
-      </c>
+      <c r="A129" s="3"/>
       <c r="B129" s="4"/>
-      <c r="C129" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D129" s="6">
-        <v>22</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>143</v>
-      </c>
+      <c r="C129" s="10"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="5"/>
     </row>
     <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="3">
-        <v>129</v>
-      </c>
+      <c r="A130" s="3"/>
       <c r="B130" s="4"/>
-      <c r="C130" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D130" s="6">
-        <v>1</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C130" s="10"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="5"/>
     </row>
     <row r="131" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="3">
-        <v>130</v>
-      </c>
+      <c r="A131" s="3"/>
       <c r="B131" s="4"/>
-      <c r="C131" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D131" s="6">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="E131" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C131" s="10"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="5"/>
     </row>
     <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="3">
-        <v>131</v>
-      </c>
+      <c r="A132" s="3"/>
       <c r="B132" s="4"/>
-      <c r="C132" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D132" s="6">
-        <v>1</v>
-      </c>
-      <c r="E132" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C132" s="10"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="5"/>
     </row>
     <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="3">
-        <v>132</v>
-      </c>
+      <c r="A133" s="3"/>
       <c r="B133" s="4"/>
-      <c r="C133" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D133" s="6">
-        <v>6</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C133" s="10"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="5"/>
     </row>
     <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="3">
-        <v>133</v>
-      </c>
+      <c r="A134" s="3"/>
       <c r="B134" s="4"/>
-      <c r="C134" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="D134" s="6">
-        <v>1</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C134" s="10"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="5"/>
     </row>
     <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="3">
-        <v>134</v>
-      </c>
+      <c r="A135" s="3"/>
       <c r="B135" s="4"/>
-      <c r="C135" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D135" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C135" s="10"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="5"/>
     </row>
     <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="3">
-        <v>135</v>
-      </c>
+      <c r="A136" s="3"/>
       <c r="B136" s="4"/>
-      <c r="C136" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="D136" s="6">
-        <v>0.13</v>
-      </c>
-      <c r="E136" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C136" s="10"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="5"/>
     </row>
     <row r="137" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="3">
-        <v>136</v>
-      </c>
+      <c r="A137" s="3"/>
       <c r="B137" s="4"/>
-      <c r="C137" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="D137" s="6">
-        <v>36</v>
-      </c>
-      <c r="E137" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C137" s="10"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="5"/>
     </row>
     <row r="138" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="3">
-        <v>137</v>
-      </c>
+      <c r="A138" s="3"/>
       <c r="B138" s="4"/>
-      <c r="C138" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D138" s="6">
-        <v>38</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C138" s="10"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="5"/>
     </row>
     <row r="139" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="3">
-        <v>138</v>
-      </c>
+      <c r="A139" s="3"/>
       <c r="B139" s="4"/>
-      <c r="C139" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D139" s="6">
-        <v>2E-3</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C139" s="10"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="5"/>
     </row>
     <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="3">
-        <v>139</v>
-      </c>
+      <c r="A140" s="3"/>
       <c r="B140" s="4"/>
-      <c r="C140" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D140" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C140" s="10"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="5"/>
     </row>
     <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="3">
-        <v>140</v>
-      </c>
+      <c r="A141" s="3"/>
       <c r="B141" s="4"/>
-      <c r="C141" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D141" s="6">
-        <v>3</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C141" s="10"/>
+      <c r="D141" s="6"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="5"/>
     </row>
     <row r="142" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="3">
-        <v>141</v>
-      </c>
+      <c r="A142" s="3"/>
       <c r="B142" s="4"/>
-      <c r="C142" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D142" s="6">
-        <v>1</v>
-      </c>
-      <c r="E142" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C142" s="10"/>
+      <c r="D142" s="6"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="5"/>
     </row>
     <row r="143" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="3">
-        <v>142</v>
-      </c>
+      <c r="A143" s="3"/>
       <c r="B143" s="4"/>
-      <c r="C143" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D143" s="6">
-        <v>63</v>
-      </c>
-      <c r="E143" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C143" s="10"/>
+      <c r="D143" s="6"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="5"/>
     </row>
     <row r="144" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="3">
-        <v>143</v>
-      </c>
+      <c r="A144" s="3"/>
       <c r="B144" s="4"/>
-      <c r="C144" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D144" s="6">
-        <v>22</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C144" s="10"/>
+      <c r="D144" s="6"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="5"/>
     </row>
     <row r="145" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="3">
-        <v>144</v>
-      </c>
+      <c r="A145" s="3"/>
       <c r="B145" s="4"/>
-      <c r="C145" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D145" s="6">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="E145" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C145" s="10"/>
+      <c r="D145" s="6"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="5"/>
     </row>
     <row r="146" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="3">
-        <v>145</v>
-      </c>
+      <c r="A146" s="3"/>
       <c r="B146" s="4"/>
-      <c r="C146" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D146" s="6">
-        <v>1.44</v>
-      </c>
-      <c r="E146" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C146" s="10"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="5"/>
     </row>
     <row r="147" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="3">
-        <v>146</v>
-      </c>
+      <c r="A147" s="3"/>
       <c r="B147" s="4"/>
-      <c r="C147" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D147" s="6">
-        <v>3</v>
-      </c>
-      <c r="E147" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C147" s="10"/>
+      <c r="D147" s="6"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="5"/>
     </row>
     <row r="148" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="3">
-        <v>147</v>
-      </c>
+      <c r="A148" s="3"/>
       <c r="B148" s="4"/>
-      <c r="C148" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="D148" s="6">
-        <v>1</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C148" s="10"/>
+      <c r="D148" s="6"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="5"/>
     </row>
     <row r="149" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="3">
-        <v>148</v>
-      </c>
+      <c r="A149" s="3"/>
       <c r="B149" s="4"/>
-      <c r="C149" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D149" s="6">
-        <v>32</v>
-      </c>
-      <c r="E149" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C149" s="10"/>
+      <c r="D149" s="6"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="5"/>
     </row>
     <row r="150" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="3">
-        <v>149</v>
-      </c>
+      <c r="A150" s="3"/>
       <c r="B150" s="4"/>
-      <c r="C150" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="D150" s="6">
-        <v>2</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C150" s="10"/>
+      <c r="D150" s="6"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="5"/>
     </row>
     <row r="151" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="3">
-        <v>150</v>
-      </c>
+      <c r="A151" s="3"/>
       <c r="B151" s="4"/>
-      <c r="C151" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="D151" s="6">
-        <v>1</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C151" s="10"/>
+      <c r="D151" s="6"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="5"/>
     </row>
     <row r="152" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="3">
-        <v>151</v>
-      </c>
+      <c r="A152" s="3"/>
       <c r="B152" s="4"/>
-      <c r="C152" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="D152" s="6">
-        <v>10</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C152" s="10"/>
+      <c r="D152" s="6"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="5"/>
     </row>
     <row r="153" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="3">
-        <v>152</v>
-      </c>
+      <c r="A153" s="3"/>
       <c r="B153" s="4"/>
-      <c r="C153" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D153" s="6">
-        <v>4</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C153" s="10"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="5"/>
     </row>
     <row r="154" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="3">
-        <v>153</v>
-      </c>
+      <c r="A154" s="3"/>
       <c r="B154" s="4"/>
-      <c r="C154" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D154" s="6">
-        <v>1</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C154" s="10"/>
+      <c r="D154" s="6"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="5"/>
     </row>
     <row r="155" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="3">
-        <v>154</v>
-      </c>
+      <c r="A155" s="3"/>
       <c r="B155" s="4"/>
-      <c r="C155" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="D155" s="6">
-        <v>1</v>
-      </c>
-      <c r="E155" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C155" s="10"/>
+      <c r="D155" s="6"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="5"/>
     </row>
     <row r="156" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="3">
-        <v>155</v>
-      </c>
+      <c r="A156" s="3"/>
       <c r="B156" s="4"/>
-      <c r="C156" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D156" s="6">
-        <v>2</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C156" s="10"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="5"/>
     </row>
     <row r="157" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="3">
-        <v>156</v>
-      </c>
+      <c r="A157" s="3"/>
       <c r="B157" s="4"/>
-      <c r="C157" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D157" s="6">
-        <v>5</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="C157" s="10"/>
+      <c r="D157" s="6"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="5"/>
     </row>
     <row r="158" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="3">
-        <v>157</v>
-      </c>
+      <c r="A158" s="3"/>
       <c r="B158" s="4"/>
-      <c r="C158" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="D158" s="6">
-        <v>1</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>177</v>
-      </c>
+      <c r="C158" s="10"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="5"/>
     </row>
     <row r="159" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="3">
-        <v>158</v>
-      </c>
+      <c r="A159" s="3"/>
       <c r="B159" s="4"/>
-      <c r="C159" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="D159" s="6">
-        <v>1</v>
-      </c>
-      <c r="E159" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>179</v>
-      </c>
+      <c r="C159" s="10"/>
+      <c r="D159" s="6"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="5"/>
     </row>
     <row r="160" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="3">
-        <v>159</v>
-      </c>
+      <c r="A160" s="3"/>
       <c r="B160" s="4"/>
-      <c r="C160" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D160" s="6">
-        <v>1</v>
-      </c>
-      <c r="E160" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>179</v>
-      </c>
+      <c r="C160" s="10"/>
+      <c r="D160" s="6"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="5"/>
     </row>
     <row r="161" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="3">
-        <v>160</v>
-      </c>
+      <c r="A161" s="3"/>
       <c r="B161" s="4"/>
-      <c r="C161" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D161" s="6">
-        <v>2</v>
-      </c>
-      <c r="E161" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>183</v>
-      </c>
+      <c r="C161" s="10"/>
+      <c r="D161" s="6"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="5"/>
     </row>
     <row r="162" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="3">
-        <v>161</v>
-      </c>
+      <c r="A162" s="3"/>
       <c r="B162" s="4"/>
-      <c r="C162" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="D162" s="6">
-        <v>2</v>
-      </c>
-      <c r="E162" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>183</v>
-      </c>
+      <c r="C162" s="10"/>
+      <c r="D162" s="6"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="5"/>
     </row>
     <row r="163" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="3">
-        <v>162</v>
-      </c>
+      <c r="A163" s="3"/>
       <c r="B163" s="4"/>
-      <c r="C163" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="D163" s="6">
-        <v>12</v>
-      </c>
-      <c r="E163" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>186</v>
-      </c>
+      <c r="C163" s="10"/>
+      <c r="D163" s="6"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="5"/>
     </row>
     <row r="164" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="3">
-        <v>163</v>
-      </c>
+      <c r="A164" s="3"/>
       <c r="B164" s="4"/>
-      <c r="C164" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D164" s="6">
-        <v>1248.52</v>
-      </c>
-      <c r="E164" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>188</v>
-      </c>
+      <c r="C164" s="10"/>
+      <c r="D164" s="6"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="5"/>
     </row>
     <row r="165" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="3">
-        <v>164</v>
-      </c>
+      <c r="A165" s="3"/>
       <c r="B165" s="4"/>
-      <c r="C165" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D165" s="6">
-        <v>1248.52</v>
-      </c>
-      <c r="E165" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>188</v>
-      </c>
+      <c r="C165" s="10"/>
+      <c r="D165" s="6"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="5"/>
     </row>
     <row r="166" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="3">
-        <v>165</v>
-      </c>
+      <c r="A166" s="3"/>
       <c r="B166" s="4"/>
-      <c r="C166" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D166" s="6">
-        <v>312.13</v>
-      </c>
-      <c r="E166" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>188</v>
-      </c>
+      <c r="C166" s="10"/>
+      <c r="D166" s="6"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="5"/>
     </row>
     <row r="167" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="3">
-        <v>166</v>
-      </c>
+      <c r="A167" s="3"/>
       <c r="B167" s="4"/>
-      <c r="C167" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D167" s="6">
-        <v>312.13</v>
-      </c>
-      <c r="E167" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>188</v>
-      </c>
+      <c r="C167" s="10"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="5"/>
     </row>
     <row r="168" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="3">
-        <v>167</v>
-      </c>
+      <c r="A168" s="3"/>
       <c r="B168" s="4"/>
-      <c r="C168" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D168" s="6">
-        <v>312.13</v>
-      </c>
-      <c r="E168" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>188</v>
-      </c>
+      <c r="C168" s="10"/>
+      <c r="D168" s="6"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="5"/>
     </row>
     <row r="169" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="3">
-        <v>168</v>
-      </c>
+      <c r="A169" s="3"/>
       <c r="B169" s="4"/>
-      <c r="C169" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="D169" s="6">
-        <v>5</v>
-      </c>
-      <c r="E169" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>192</v>
-      </c>
+      <c r="C169" s="10"/>
+      <c r="D169" s="6"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="5"/>
     </row>
     <row r="170" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="3">
-        <v>169</v>
-      </c>
+      <c r="A170" s="3"/>
       <c r="B170" s="4"/>
-      <c r="C170" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D170" s="6">
-        <v>5</v>
-      </c>
-      <c r="E170" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>192</v>
-      </c>
+      <c r="C170" s="10"/>
+      <c r="D170" s="6"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="5"/>
     </row>
     <row r="171" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="3"/>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Desktop\ruAstro\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBAEC6B-4348-4F05-8076-6D1296D931C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0662C05D-CC3B-4861-AF00-BFF5A050D674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="96">
   <si>
     <t>№ п/п</t>
   </si>
@@ -69,15 +69,9 @@
     <t>Хомуты НТ.010.000.000 СБ (Корпус) (литье из стали 20Л)</t>
   </si>
   <si>
-    <t>Удостоверение</t>
-  </si>
-  <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>НТ00-000048</t>
-  </si>
-  <si>
     <t>ЛГУП-6531</t>
   </si>
   <si>
@@ -111,42 +105,6 @@
     <t>НТУП-017684</t>
   </si>
   <si>
-    <t>Панель оператора Weintek cMT2158X, 15″</t>
-  </si>
-  <si>
-    <t>ЛГУП-6575</t>
-  </si>
-  <si>
-    <t>Модуль дискретного ввода-вывода (16 каналов) АВПЮ.426441.360-04-01 исполнение 4.1-1</t>
-  </si>
-  <si>
-    <t>Модуль аналогового ввода (Ai) (16 каналов) версия 1 АВПЮ.426439.001-04-01</t>
-  </si>
-  <si>
-    <t>Онлайн ИБП ST1101 SL (1000 ВА / 900 Вт) Штиль</t>
-  </si>
-  <si>
-    <t>Контролер Ария ver.4.5 (4 AI, 4 DI/DO, 4 порта RS485) АВПЮ.426441.358-10-02</t>
-  </si>
-  <si>
-    <t>компл</t>
-  </si>
-  <si>
-    <t>ЛГУП-6576</t>
-  </si>
-  <si>
-    <t>ЛГУП-6577</t>
-  </si>
-  <si>
-    <t>Блок питания AC-DC, 120Вт, вход 90-264V AC, 47-63Гц,127-370В DC, выход 24В,5A, рег. вых 24-28В, в ко</t>
-  </si>
-  <si>
-    <t>Блок питания AC-DC 100Вт вх.85-264V AC 47-63Гц 120-370В вых.24В кожух DIN-рейки MDR-100-24 Mean Well</t>
-  </si>
-  <si>
-    <t>ЛГУП-6578</t>
-  </si>
-  <si>
     <t>Инвентарь:щётка жёсткая</t>
   </si>
   <si>
@@ -195,15 +153,6 @@
     <t>Расходомер ЭМИС-МАСС 260-Ех-80-Д-Ж-4,0 вых.сигнал частотно-импульсный, RS-485 Modbus RTU</t>
   </si>
   <si>
-    <t>ЛГУП-6612</t>
-  </si>
-  <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>пог. м</t>
-  </si>
-  <si>
     <t>Сапоги летние</t>
   </si>
   <si>
@@ -225,223 +174,142 @@
     <t>ЛГУП-6622</t>
   </si>
   <si>
-    <t>Ботинки летние 42 р</t>
-  </si>
-  <si>
-    <t>НТУП-017701</t>
-  </si>
-  <si>
-    <t>Костюм летний от загрязнений и противоэнцефалитный</t>
-  </si>
-  <si>
     <t>Сцепление крабовое для рукава 25-39мм</t>
   </si>
   <si>
+    <t xml:space="preserve"> Датчик температуры ТПС 108Exd-100/80-M20x1,5/8-C10-100M-B/-50/50-0,25-F-FECA1I-П</t>
+  </si>
+  <si>
+    <t>Манометр МП4 P=0..6МПа, ХЛ1 ст.защиты корпуса IP54, кл.точн. 1,0. Присоед-е: М20х1,5 - наружн</t>
+  </si>
+  <si>
+    <t>Датчик изгибающего момента тип 108 длина крыла 64мм</t>
+  </si>
+  <si>
+    <t>Влагомер сырой нефти ВСН-2 Ду 80, Ру 40 (угловой) взрывозащ.1Ex ib IIA T6, IP67</t>
+  </si>
+  <si>
+    <t>Мин. вата типа "URSA" П-125</t>
+  </si>
+  <si>
+    <t>Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
+  </si>
+  <si>
+    <t>Петля накладная ПН1-70 ГОСТ 5088-2005</t>
+  </si>
+  <si>
+    <t>Магнит ПСМНТ.001.021.001</t>
+  </si>
+  <si>
+    <t>Счетчик Тор-50 Ха 2.833.034 1ExdIICT4 X, IP65</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая стальная ЗКС Ду25 Ру160 УХЛ1, класс герметичности "А"</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+  </si>
+  <si>
+    <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
+  </si>
+  <si>
+    <t>Задвижка ЗКЛ 50-40 ХЛ1 30лс15нж класс герм. А, исп.F ХЛ1 L=216 без КОФ</t>
+  </si>
+  <si>
+    <t>Паронит ПОН 2,0 ГОСТ 481-80 (кг)</t>
+  </si>
+  <si>
+    <t>Полиамид D30 П-15Б-20  ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Полиамид D40 П-15Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Полиамид D70 П-12Б-20 ТУ 6-05-898-73</t>
+  </si>
+  <si>
+    <t>Полиамид D80 П-12Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Кольцо А20х1,2 ГОСТ 13940-86</t>
+  </si>
+  <si>
+    <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
+  </si>
+  <si>
+    <t>Кольцо 018-021-19-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 014-018-25 ГОСТ 9833-73 (фторкаучук)</t>
+  </si>
+  <si>
+    <t>2-х вентильный клапанный блок КБ-2х40.01(M20x1,5Н,M20x1,5B; M14x1,5B)</t>
+  </si>
+  <si>
+    <t>Кольцо 100-106-36-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 096-102-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-086-36-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-085-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 070-076-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 062-068-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 060-065-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 055-060-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
     <t>Термостат MTK-CT0</t>
   </si>
   <si>
-    <t>Счетчик Тор-50 Ха 2.833.034 1ExdIICT4 X, IP65</t>
+    <t>Кольцо А75 ГОСТ 13943-86 (с пазами)</t>
+  </si>
+  <si>
+    <t>Паронит ПМБ 2 ГОСТ 481-80</t>
+  </si>
+  <si>
+    <t>Кольцо 200-210-46-1-1 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное НТ.300.000.010.0</t>
+  </si>
+  <si>
+    <t>Магнит D4х5 неодимовый</t>
+  </si>
+  <si>
+    <t>Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
+  </si>
+  <si>
+    <t>Пружина №442 НТ.110.000.007.0</t>
+  </si>
+  <si>
+    <t>Пружина №467 НТ.200.000.029.0</t>
+  </si>
+  <si>
+    <t>Пружина крышки НТ.200.004.003.0</t>
   </si>
   <si>
     <t>Кольцо 020-025-30-2-4 ГОСТ 9833-73</t>
   </si>
   <si>
-    <t>Кольцо 080-085-30-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 096-102-36-2-3 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 100-106-36-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
-  </si>
-  <si>
-    <t>Кольцо А20х1,2 ГОСТ 13940-86</t>
-  </si>
-  <si>
-    <t>Кольцо А75 ГОСТ 13943-86 (с пазами)</t>
-  </si>
-  <si>
-    <t>2-х вентильный клапанный блок КБ-2х40.01(M20x1,5Н,M20x1,5B; M14x1,5B)</t>
-  </si>
-  <si>
-    <t>Пружина крышки НТ.200.004.003.0</t>
-  </si>
-  <si>
     <t>Кольцо 028-032-25-1-6 ГОСТ 9833-73</t>
   </si>
   <si>
-    <t>Кольцо 018-021-19-2-3 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 014-018-25 ГОСТ 9833-73 (фторкаучук)</t>
-  </si>
-  <si>
-    <t>Кольцо 080-086-36-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
     <t>Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
   </si>
   <si>
-    <t>Кольцо 055-060-30-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 060-065-30-1-6 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 062-068-36-2-3 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 070-076-36-2-4 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо уплотнительное НТ.300.000.010.0</t>
-  </si>
-  <si>
-    <t>Магнит D4х5 неодимовый</t>
-  </si>
-  <si>
-    <t>Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
-  </si>
-  <si>
-    <t>Пружина №442 НТ.110.000.007.0</t>
-  </si>
-  <si>
-    <t>Пружина №467 НТ.200.000.029.0</t>
-  </si>
-  <si>
-    <t>Кольцо 200-210-46-1-1 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Паронит ПМБ 2 ГОСТ 481-80</t>
-  </si>
-  <si>
-    <t>Паронит ПОН 2,0 ГОСТ 481-80 (кг)</t>
-  </si>
-  <si>
-    <t>Полиамид D80 П-12Б-20 ТУ 6-05-988-87</t>
-  </si>
-  <si>
-    <t>Полиамид D70 П-12Б-20 ТУ 6-05-898-73</t>
-  </si>
-  <si>
-    <t>Полиамид D40 П-15Б-20 ТУ 6-05-988-87</t>
-  </si>
-  <si>
-    <t>Полиамид D30 П-15Б-20  ТУ 6-05-988-87</t>
-  </si>
-  <si>
     <t>Рычаг НТ.510.000.003.0 (лазер)</t>
-  </si>
-  <si>
-    <t>Задвижка ЗКЛ 50-40 ХЛ1 30лс15нж класс герм. А, исп.F ХЛ1 L=216 без КОФ</t>
-  </si>
-  <si>
-    <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая стальная ЗКС Ду25 Ру160 УХЛ1, класс герметичности "А"</t>
-  </si>
-  <si>
-    <t>Магнит ПСМНТ.001.021.001</t>
-  </si>
-  <si>
-    <t>Петля накладная ПН1-70 ГОСТ 5088-2005</t>
-  </si>
-  <si>
-    <t>Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
-  </si>
-  <si>
-    <t>Мин. вата типа "URSA" П-125</t>
-  </si>
-  <si>
-    <t>Датчик изгибающего момента тип 108 длина крыла 64мм</t>
-  </si>
-  <si>
-    <t>Манометр МП4 P=0..6МПа, ХЛ1 ст.защиты корпуса IP54, кл.точн. 1,0. Присоед-е: М20х1,5 - наружн</t>
-  </si>
-  <si>
-    <t>Влагомер сырой нефти ВСН-2 Ду 80, Ру 40 (угловой) взрывозащ.1Ex ib IIA T6, IP67</t>
-  </si>
-  <si>
-    <t>Датчик температуры ТПС 108Exd-100/80-M20x1,5/8-C10-100M-B/-50/50-0,25-F-FECA1I-П</t>
-  </si>
-  <si>
-    <t>Изолон НПЭ В 4мм несортовой ТУ 2244-020-00203474-2004</t>
-  </si>
-  <si>
-    <t>Литол 24 /кг/</t>
-  </si>
-  <si>
-    <t>Пленка полиэтиленовая рукав 0,3х3000 ГОСТ 10354-82</t>
-  </si>
-  <si>
-    <t>Отвердитель ПЭПА</t>
-  </si>
-  <si>
-    <t>Лента ПСУЛ 20х8/40</t>
-  </si>
-  <si>
-    <t>Скотч защитный термоусадочный Magnapak цвет белый, 5 см</t>
-  </si>
-  <si>
-    <t>Смола ЭД-20 ГОСТ 10587-84</t>
-  </si>
-  <si>
-    <t>Замок навесной 50мм, влагозащищенный, с заглушкой</t>
-  </si>
-  <si>
-    <t>Лезвие для ножа профессионального для резки пленки Магнапак</t>
-  </si>
-  <si>
-    <t>Стропа Magnapack</t>
-  </si>
-  <si>
-    <t>Ящик УОК НКТ НТ.007.094.000</t>
-  </si>
-  <si>
-    <t>Ящик для техновека/нягань (габариты 1500*600*600мм)</t>
-  </si>
-  <si>
-    <t>Хомут 4х300 пластиковый</t>
-  </si>
-  <si>
-    <t>Стяжка нейлон 200мм (упак)</t>
-  </si>
-  <si>
-    <t>Стул ЗФ.6.156.005М</t>
-  </si>
-  <si>
-    <t>Скотч-малярный</t>
-  </si>
-  <si>
-    <t>Скотч 50мм*120м PROFITTO /6/54 прозрачн</t>
-  </si>
-  <si>
-    <t>Пленка воздушно-пузырчатая 1500мм*100пог.м 2 сл (рул)</t>
-  </si>
-  <si>
-    <t>Пленка термоусадочная Magnapak белая (ширина 9,8 м, толщина 190 мкм)</t>
-  </si>
-  <si>
-    <t>Маты МБП-20-10000х1000х50</t>
-  </si>
-  <si>
-    <t>Пена монтажная "MAKROFLEX " V=1000 мл</t>
-  </si>
-  <si>
-    <t>Емкость пластиковая 0,5л (дно плоское, форма емкости - квадрат или прямоугольник)</t>
-  </si>
-  <si>
-    <t>Герметик силиконовый универс. белый 310мл</t>
-  </si>
-  <si>
-    <t>Герметик "Макрофлекс"  силик. универс. белый 290мл</t>
   </si>
   <si>
     <t>Кольцо А75х1,7 ГОСТ 13943-86</t>
@@ -944,13 +812,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -959,7 +827,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="10" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6">
         <v>5</v>
@@ -977,7 +845,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="10" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D3" s="6">
         <v>8</v>
@@ -995,7 +863,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="6">
         <v>300</v>
@@ -1013,7 +881,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" s="6">
         <v>300</v>
@@ -1031,7 +899,7 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6">
         <v>300</v>
@@ -1049,7 +917,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6">
         <v>300</v>
@@ -1067,16 +935,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D8" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1085,16 +953,16 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="10" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D9" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1103,16 +971,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="10" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D10" s="6">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1124,13 +992,13 @@
         <v>84</v>
       </c>
       <c r="D11" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1139,16 +1007,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="10" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D12" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1157,16 +1025,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="10" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D13" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1175,16 +1043,16 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="10" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D14" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1193,16 +1061,16 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D15" s="6">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1211,7 +1079,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="10" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D16" s="6">
         <v>1</v>
@@ -1220,7 +1088,7 @@
         <v>6</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1229,16 +1097,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="10" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D17" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1247,16 +1115,16 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="10" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D18" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1265,16 +1133,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="10" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D19" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1283,7 +1151,7 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="10" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D20" s="6">
         <v>3</v>
@@ -1292,7 +1160,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1301,7 +1169,7 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D21" s="6">
         <v>2</v>
@@ -1310,7 +1178,7 @@
         <v>6</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1319,7 +1187,7 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="10" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D22" s="6">
         <v>4</v>
@@ -1328,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1337,7 +1205,7 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="10" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D23" s="6">
         <v>2</v>
@@ -1346,7 +1214,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1355,7 +1223,7 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="10" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D24" s="6">
         <v>4</v>
@@ -1364,7 +1232,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1373,7 +1241,7 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="10" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D25" s="6">
         <v>3</v>
@@ -1382,7 +1250,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1391,7 +1259,7 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="10" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
@@ -1400,7 +1268,7 @@
         <v>6</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1409,7 +1277,7 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="10" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D27" s="6">
         <v>2</v>
@@ -1418,7 +1286,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1427,16 +1295,16 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="10" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D28" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1445,16 +1313,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="10" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D29" s="6">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1463,16 +1331,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="10" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D30" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1481,16 +1349,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="10" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="D31" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1499,7 +1367,7 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="10" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D32" s="6">
         <v>2</v>
@@ -1508,7 +1376,7 @@
         <v>6</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1517,16 +1385,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="10" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D33" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1535,16 +1403,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="10" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="D34" s="6">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1553,16 +1421,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="10" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="D35" s="6">
-        <v>0.44400000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1571,16 +1439,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="10" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="D36" s="6">
-        <v>1</v>
+        <v>0.44</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1589,16 +1457,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="10" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="D37" s="6">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1607,16 +1475,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="10" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="D38" s="6">
-        <v>0.44</v>
+        <v>0.08</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1625,16 +1493,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="10" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D39" s="6">
-        <v>0.22</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1643,16 +1511,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="10" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="D40" s="6">
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1670,7 +1538,7 @@
         <v>6</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1679,7 +1547,7 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="10" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D42" s="6">
         <v>1</v>
@@ -1688,7 +1556,7 @@
         <v>6</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1697,7 +1565,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D43" s="6">
         <v>1</v>
@@ -1706,7 +1574,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1715,16 +1583,16 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="10" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D44" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1733,16 +1601,16 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="10" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="D45" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1751,16 +1619,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="10" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="D46" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1769,16 +1637,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="10" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="D47" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1787,16 +1655,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="10" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="D48" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1805,10 +1673,10 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="10" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="D49" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>6</v>
@@ -1823,10 +1691,10 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D50" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>6</v>
@@ -1841,16 +1709,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D51" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1859,16 +1727,16 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D52" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1877,16 +1745,16 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D53" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1895,16 +1763,16 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="10" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D54" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1913,16 +1781,16 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D55" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1934,13 +1802,13 @@
         <v>28</v>
       </c>
       <c r="D56" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1949,16 +1817,16 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D57" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1967,16 +1835,16 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D58" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1985,10 +1853,10 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="10" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D59" s="6">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>6</v>
@@ -2003,16 +1871,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="10" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D60" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2021,16 +1889,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="10" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D61" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2039,16 +1907,16 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="10" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D62" s="6">
-        <v>3</v>
+        <v>11.52</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2057,16 +1925,16 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="10" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D63" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2075,16 +1943,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="10" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D64" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2093,16 +1961,16 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" s="6">
+        <v>2</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="D65" s="6">
-        <v>3</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2111,16 +1979,16 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="10" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D66" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2129,16 +1997,16 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="10" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D67" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2147,16 +2015,16 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="10" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D68" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2165,16 +2033,16 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="10" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D69" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2183,16 +2051,16 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="10" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D70" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2201,989 +2069,449 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="10" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D71" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
-        <v>71</v>
-      </c>
+      <c r="A72" s="3"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" s="6">
-        <v>1</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="5"/>
     </row>
     <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
-        <v>72</v>
-      </c>
+      <c r="A73" s="3"/>
       <c r="B73" s="4"/>
-      <c r="C73" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D73" s="6">
-        <v>2</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C73" s="10"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="5"/>
     </row>
     <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
-        <v>73</v>
-      </c>
+      <c r="A74" s="3"/>
       <c r="B74" s="4"/>
-      <c r="C74" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D74" s="6">
-        <v>1</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C74" s="10"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="5"/>
     </row>
     <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
-        <v>74</v>
-      </c>
+      <c r="A75" s="3"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D75" s="6">
-        <v>1</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C75" s="10"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="5"/>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
-        <v>75</v>
-      </c>
+      <c r="A76" s="3"/>
       <c r="B76" s="4"/>
-      <c r="C76" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D76" s="6">
-        <v>2</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C76" s="10"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="5"/>
     </row>
     <row r="77" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
-        <v>76</v>
-      </c>
+      <c r="A77" s="3"/>
       <c r="B77" s="4"/>
-      <c r="C77" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D77" s="6">
-        <v>2</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C77" s="10"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="5"/>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
-        <v>77</v>
-      </c>
+      <c r="A78" s="3"/>
       <c r="B78" s="4"/>
-      <c r="C78" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D78" s="6">
-        <v>2</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C78" s="10"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="5"/>
     </row>
     <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
-        <v>78</v>
-      </c>
+      <c r="A79" s="3"/>
       <c r="B79" s="4"/>
-      <c r="C79" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D79" s="6">
-        <v>2</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C79" s="10"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
-        <v>79</v>
-      </c>
+      <c r="A80" s="3"/>
       <c r="B80" s="4"/>
-      <c r="C80" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D80" s="6">
-        <v>1</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C80" s="10"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
-        <v>80</v>
-      </c>
+      <c r="A81" s="3"/>
       <c r="B81" s="4"/>
-      <c r="C81" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D81" s="6">
-        <v>2</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="C81" s="10"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="5"/>
     </row>
     <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
-        <v>81</v>
-      </c>
+      <c r="A82" s="3"/>
       <c r="B82" s="4"/>
-      <c r="C82" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D82" s="6">
-        <v>8</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="C82" s="10"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
-        <v>82</v>
-      </c>
+      <c r="A83" s="3"/>
       <c r="B83" s="4"/>
-      <c r="C83" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D83" s="6">
-        <v>16</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="C83" s="10"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
-        <v>83</v>
-      </c>
+      <c r="A84" s="3"/>
       <c r="B84" s="4"/>
-      <c r="C84" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D84" s="6">
-        <v>8</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="C84" s="10"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="5"/>
     </row>
     <row r="85" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
-        <v>84</v>
-      </c>
+      <c r="A85" s="3"/>
       <c r="B85" s="4"/>
-      <c r="C85" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D85" s="6">
-        <v>11.52</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="C85" s="10"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="5"/>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
-        <v>85</v>
-      </c>
+      <c r="A86" s="3"/>
       <c r="B86" s="4"/>
-      <c r="C86" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D86" s="6">
-        <v>2</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C86" s="10"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="5"/>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
-        <v>86</v>
-      </c>
+      <c r="A87" s="3"/>
       <c r="B87" s="4"/>
-      <c r="C87" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D87" s="6">
-        <v>2</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C87" s="10"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="5"/>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
-        <v>87</v>
-      </c>
+      <c r="A88" s="3"/>
       <c r="B88" s="4"/>
-      <c r="C88" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D88" s="6">
-        <v>5</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C88" s="10"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="5"/>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
-        <v>88</v>
-      </c>
+      <c r="A89" s="3"/>
       <c r="B89" s="4"/>
-      <c r="C89" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D89" s="6">
-        <v>1</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C89" s="10"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="5"/>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
-        <v>89</v>
-      </c>
+      <c r="A90" s="3"/>
       <c r="B90" s="4"/>
-      <c r="C90" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D90" s="6">
-        <v>1</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C90" s="10"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="5"/>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
-        <v>90</v>
-      </c>
+      <c r="A91" s="3"/>
       <c r="B91" s="4"/>
-      <c r="C91" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D91" s="6">
-        <v>2</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C91" s="10"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="5"/>
     </row>
     <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
-        <v>91</v>
-      </c>
+      <c r="A92" s="3"/>
       <c r="B92" s="4"/>
-      <c r="C92" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D92" s="6">
-        <v>1</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="C92" s="10"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="5"/>
     </row>
     <row r="93" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
-        <v>92</v>
-      </c>
+      <c r="A93" s="3"/>
       <c r="B93" s="4"/>
-      <c r="C93" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D93" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C93" s="10"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="5"/>
     </row>
     <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
-        <v>93</v>
-      </c>
+      <c r="A94" s="3"/>
       <c r="B94" s="4"/>
-      <c r="C94" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D94" s="6">
-        <v>0.13</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C94" s="10"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="5"/>
     </row>
     <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
-        <v>94</v>
-      </c>
+      <c r="A95" s="3"/>
       <c r="B95" s="4"/>
-      <c r="C95" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D95" s="6">
-        <v>1</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C95" s="10"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="5"/>
     </row>
     <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
-        <v>95</v>
-      </c>
+      <c r="A96" s="3"/>
       <c r="B96" s="4"/>
-      <c r="C96" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D96" s="6">
-        <v>2E-3</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="5"/>
     </row>
     <row r="97" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
-        <v>96</v>
-      </c>
+      <c r="A97" s="3"/>
       <c r="B97" s="4"/>
-      <c r="C97" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D97" s="6">
-        <v>36</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C97" s="10"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="5"/>
     </row>
     <row r="98" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
-        <v>97</v>
-      </c>
+      <c r="A98" s="3"/>
       <c r="B98" s="4"/>
-      <c r="C98" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D98" s="6">
-        <v>38</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C98" s="10"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="5"/>
     </row>
     <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="3">
-        <v>98</v>
-      </c>
+      <c r="A99" s="3"/>
       <c r="B99" s="4"/>
-      <c r="C99" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D99" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C99" s="10"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="5"/>
     </row>
     <row r="100" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="3">
-        <v>99</v>
-      </c>
+      <c r="A100" s="3"/>
       <c r="B100" s="4"/>
-      <c r="C100" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="D100" s="6">
-        <v>3</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="5"/>
     </row>
     <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="3">
-        <v>100</v>
-      </c>
+      <c r="A101" s="3"/>
       <c r="B101" s="4"/>
-      <c r="C101" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D101" s="6">
-        <v>1</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C101" s="10"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="5"/>
     </row>
     <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="3">
-        <v>101</v>
-      </c>
+      <c r="A102" s="3"/>
       <c r="B102" s="4"/>
-      <c r="C102" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D102" s="6">
-        <v>63</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C102" s="10"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="5"/>
     </row>
     <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="3">
-        <v>102</v>
-      </c>
+      <c r="A103" s="3"/>
       <c r="B103" s="4"/>
-      <c r="C103" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D103" s="6">
-        <v>3</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C103" s="10"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="5"/>
     </row>
     <row r="104" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="3">
-        <v>103</v>
-      </c>
+      <c r="A104" s="3"/>
       <c r="B104" s="4"/>
-      <c r="C104" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D104" s="6">
-        <v>1</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C104" s="10"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="5"/>
     </row>
     <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="3">
-        <v>104</v>
-      </c>
+      <c r="A105" s="3"/>
       <c r="B105" s="4"/>
-      <c r="C105" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D105" s="6">
-        <v>32</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C105" s="10"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="5"/>
     </row>
     <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="3">
-        <v>105</v>
-      </c>
+      <c r="A106" s="3"/>
       <c r="B106" s="4"/>
-      <c r="C106" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D106" s="6">
-        <v>2</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C106" s="10"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="5"/>
     </row>
     <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="3">
-        <v>106</v>
-      </c>
+      <c r="A107" s="3"/>
       <c r="B107" s="4"/>
-      <c r="C107" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D107" s="6">
-        <v>1</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C107" s="10"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="5"/>
     </row>
     <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="3">
-        <v>107</v>
-      </c>
+      <c r="A108" s="3"/>
       <c r="B108" s="4"/>
-      <c r="C108" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D108" s="6">
-        <v>10</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C108" s="10"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="5"/>
     </row>
     <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="3">
-        <v>108</v>
-      </c>
+      <c r="A109" s="3"/>
       <c r="B109" s="4"/>
-      <c r="C109" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D109" s="6">
-        <v>4</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C109" s="10"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="5"/>
     </row>
     <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="3">
-        <v>109</v>
-      </c>
+      <c r="A110" s="3"/>
       <c r="B110" s="4"/>
-      <c r="C110" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D110" s="6">
-        <v>1</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C110" s="10"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="5"/>
     </row>
     <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="3">
-        <v>110</v>
-      </c>
+      <c r="A111" s="3"/>
       <c r="B111" s="4"/>
-      <c r="C111" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D111" s="6">
-        <v>1</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C111" s="10"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="5"/>
     </row>
     <row r="112" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="3">
-        <v>111</v>
-      </c>
+      <c r="A112" s="3"/>
       <c r="B112" s="4"/>
-      <c r="C112" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D112" s="6">
-        <v>2</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C112" s="10"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="5"/>
     </row>
     <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
-        <v>112</v>
-      </c>
+      <c r="A113" s="3"/>
       <c r="B113" s="4"/>
-      <c r="C113" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D113" s="6">
-        <v>22</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C113" s="10"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="5"/>
     </row>
     <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="3">
-        <v>113</v>
-      </c>
+      <c r="A114" s="3"/>
       <c r="B114" s="4"/>
-      <c r="C114" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D114" s="6">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C114" s="10"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="5"/>
     </row>
     <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="3">
-        <v>114</v>
-      </c>
+      <c r="A115" s="3"/>
       <c r="B115" s="4"/>
-      <c r="C115" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D115" s="6">
-        <v>1.44</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C115" s="10"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="5"/>
     </row>
     <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="3">
-        <v>115</v>
-      </c>
+      <c r="A116" s="3"/>
       <c r="B116" s="4"/>
-      <c r="C116" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D116" s="6">
-        <v>5</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C116" s="10"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="5"/>
     </row>
     <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="3">
-        <v>116</v>
-      </c>
+      <c r="A117" s="3"/>
       <c r="B117" s="4"/>
-      <c r="C117" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="D117" s="6">
-        <v>1</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C117" s="10"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="5"/>
     </row>
     <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="3">
-        <v>117</v>
-      </c>
+      <c r="A118" s="3"/>
       <c r="B118" s="4"/>
-      <c r="C118" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D118" s="6">
-        <v>1</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C118" s="10"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="5"/>
     </row>
     <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="3">
-        <v>118</v>
-      </c>
+      <c r="A119" s="3"/>
       <c r="B119" s="4"/>
-      <c r="C119" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D119" s="6">
-        <v>6</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C119" s="10"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="5"/>
     </row>
     <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="3">
-        <v>119</v>
-      </c>
+      <c r="A120" s="3"/>
       <c r="B120" s="4"/>
-      <c r="C120" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D120" s="6">
-        <v>4</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="C120" s="10"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="5"/>
     </row>
     <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="3">
-        <v>120</v>
-      </c>
+      <c r="A121" s="3"/>
       <c r="B121" s="4"/>
-      <c r="C121" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D121" s="6">
-        <v>4</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="C121" s="10"/>
+      <c r="D121" s="6"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="5"/>
     </row>
     <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="3">
-        <v>121</v>
-      </c>
+      <c r="A122" s="3"/>
       <c r="B122" s="4"/>
-      <c r="C122" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D122" s="6">
-        <v>1</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="C122" s="10"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="5"/>
     </row>
     <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="3">
-        <v>122</v>
-      </c>
+      <c r="A123" s="3"/>
       <c r="B123" s="4"/>
-      <c r="C123" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D123" s="6">
-        <v>1</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="C123" s="10"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="5"/>
     </row>
     <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="3">
-        <v>123</v>
-      </c>
+      <c r="A124" s="3"/>
       <c r="B124" s="4"/>
-      <c r="C124" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D124" s="8">
-        <v>1</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="C124" s="10"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="5"/>
     </row>
     <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="3">
-        <v>124</v>
-      </c>
+      <c r="A125" s="3"/>
       <c r="B125" s="4"/>
-      <c r="C125" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D125" s="6">
-        <v>1</v>
-      </c>
-      <c r="E125" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="C125" s="10"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="5"/>
     </row>
     <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3"/>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210AFC85-5DEA-4870-B619-B14694FFC144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E24138F-C94B-492C-B10E-8997FD338C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26040" yWindow="2385" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25695" yWindow="2730" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
   <si>
     <t>№ п/п</t>
   </si>
@@ -87,55 +87,28 @@
     <t>м3</t>
   </si>
   <si>
-    <t>Сапоги летние</t>
-  </si>
-  <si>
-    <t>пар</t>
-  </si>
-  <si>
-    <t>ЛГУП-6622</t>
-  </si>
-  <si>
-    <t>Костюм рабочий</t>
+    <t>АХ00-000022</t>
+  </si>
+  <si>
+    <t>АХУП-000348</t>
+  </si>
+  <si>
+    <t>АХУП-000349</t>
+  </si>
+  <si>
+    <t>АХУП-000350</t>
+  </si>
+  <si>
+    <t>Шкаф ПС и ОС АГЗУ 14-400 Удмуртнефть</t>
   </si>
   <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>АХ00-000022</t>
-  </si>
-  <si>
-    <t>АХУП-000348</t>
-  </si>
-  <si>
-    <t>АХУП-000349</t>
-  </si>
-  <si>
-    <t>АХУП-000350</t>
-  </si>
-  <si>
     <t>ЛГУП-6654</t>
   </si>
   <si>
-    <t>Рукав пожарный напорный РПК(В)-50-1,0-УХЛ1 L=20±2м., с ГР-50 АП</t>
-  </si>
-  <si>
-    <t>ЛГУП-6655</t>
-  </si>
-  <si>
-    <t>Проявитель SHERWIN D-100, аэрозоль 500мл</t>
-  </si>
-  <si>
-    <t>НТУП-017715</t>
-  </si>
-  <si>
-    <t>Пенетрант SHERWIN DR-55, аэрозоль 500мл</t>
-  </si>
-  <si>
-    <t>Очиститель SHERWIN DR-60, аэрозоль 500мл</t>
-  </si>
-  <si>
-    <t>ЛГУП-6657</t>
+    <t>ЛГУП-6658</t>
   </si>
   <si>
     <t>Термостат MTK-CT0</t>
@@ -177,13 +150,19 @@
     <t>Шкаф силовой</t>
   </si>
   <si>
-    <t>ПС и ОС АГЗУ 14-400 Удмуртнефть</t>
-  </si>
-  <si>
     <t>Влагомер сырой нефти ВСН-2 Ду 80, Ру 40 (угловой) взрывозащ.1Ex ib IIA T6, IP67</t>
   </si>
   <si>
-    <t>Герметик "Макрофлекс" силик. универс. белый 290мл</t>
+    <t>Пресс-форма крышка ПСМНТ 001.000.007 СБ</t>
+  </si>
+  <si>
+    <t>Пресс-форма хомуты НТ 010.000.000 СБ</t>
+  </si>
+  <si>
+    <t>Пресс-форма клапан пред-ний НТ 3.02.00.00.000 СБ</t>
+  </si>
+  <si>
+    <t>пресс-форма Угольник ПСМНТ 001.029.000 СБ</t>
   </si>
 </sst>
 </file>
@@ -632,11 +611,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="47" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="74.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
@@ -669,7 +648,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="9" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D2" s="6">
         <v>5</v>
@@ -687,7 +666,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="9" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D3" s="6">
         <v>8</v>
@@ -705,7 +684,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
@@ -759,7 +738,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -771,13 +750,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="9" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D8" s="6">
         <v>7</v>
@@ -795,7 +774,7 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D9" s="6">
         <v>2</v>
@@ -813,7 +792,7 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6">
         <v>4</v>
@@ -849,7 +828,7 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="9" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D12" s="6">
         <v>3</v>
@@ -885,7 +864,7 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="9" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D14" s="6">
         <v>8</v>
@@ -903,7 +882,7 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="9" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D15" s="6">
         <v>8</v>
@@ -921,7 +900,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D16" s="6">
         <v>16</v>
@@ -939,7 +918,7 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="9" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D17" s="6">
         <v>11.52</v>
@@ -957,16 +936,16 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6">
+        <v>8</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="D18" s="6">
-        <v>4</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -975,16 +954,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D19" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -993,16 +972,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D20" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1011,16 +990,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="9" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D21" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1029,7 +1008,7 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -1038,7 +1017,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1047,7 +1026,7 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="9" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
@@ -1056,25 +1035,25 @@
         <v>6</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D24" s="6">
         <v>1</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1083,7 +1062,7 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
@@ -1092,25 +1071,25 @@
         <v>6</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="9" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1119,16 +1098,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D27" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1137,70 +1116,16 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="9" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D28" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="6">
-        <v>3</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="6">
-        <v>3</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="6">
-        <v>15</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E24138F-C94B-492C-B10E-8997FD338C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81BE5AC-4C64-47B2-BC64-A246BED3CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25695" yWindow="2730" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
   <si>
     <t>№ п/п</t>
   </si>
@@ -51,9 +51,6 @@
     <t>ЛГУП-6441</t>
   </si>
   <si>
-    <t>ЛГУП-6489</t>
-  </si>
-  <si>
     <t>ЛГУП-6533</t>
   </si>
   <si>
@@ -69,9 +66,6 @@
     <t>Клапан предохранительный СППК4р 17с25нж Ду80 Ру40</t>
   </si>
   <si>
-    <t>ЛГУП-6540</t>
-  </si>
-  <si>
     <t>ТОР 50</t>
   </si>
   <si>
@@ -114,12 +108,12 @@
     <t>Термостат MTK-CT0</t>
   </si>
   <si>
-    <t>Счетчик Тор-50 Ха 2.833.034 1ExdIICT4 X, IP65</t>
-  </si>
-  <si>
     <t>Рычаг НТ.510.000.003.0 (лазер)</t>
   </si>
   <si>
+    <t>Задвижка ЗКЛ 50-40 ХЛ1 30лс15нж класс герм. А, исп.F ХЛ1 L=216 без КОФ</t>
+  </si>
+  <si>
     <t>Задвижка клиновая стальная ЗКС Ду25 Ру160 УХЛ1, класс герметичности "А"</t>
   </si>
   <si>
@@ -127,9 +121,6 @@
   </si>
   <si>
     <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
-  </si>
-  <si>
-    <t>Задвижка ЗКЛ 50-40 ХЛ1 30лс15нж класс герм. А, исп.F ХЛ1 L=216 без КОФ</t>
   </si>
   <si>
     <t>Магнит ПСМНТ.001.021.001</t>
@@ -611,12 +602,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="72.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
@@ -648,7 +639,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="6">
         <v>5</v>
@@ -666,10 +657,10 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>6</v>
@@ -684,7 +675,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="9" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
@@ -693,7 +684,7 @@
         <v>6</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -711,7 +702,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -720,16 +711,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6">
+        <v>4</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -738,7 +729,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -747,43 +738,43 @@
         <v>6</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D9" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -792,16 +783,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D10" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -819,7 +810,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -828,16 +819,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D12" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -846,10 +837,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="9" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D13" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>6</v>
@@ -864,16 +855,16 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -882,16 +873,16 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" s="6">
-        <v>8</v>
+        <v>11.52</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -900,10 +891,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" s="6">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>6</v>
@@ -918,16 +909,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="6">
-        <v>11.52</v>
+        <v>3</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -936,10 +927,10 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D18" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>6</v>
@@ -954,10 +945,10 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D19" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>6</v>
@@ -972,7 +963,7 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D20" s="6">
         <v>1</v>
@@ -981,7 +972,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -990,7 +981,7 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="9" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -999,25 +990,25 @@
         <v>6</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1026,7 +1017,7 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="9" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
@@ -1035,25 +1026,25 @@
         <v>6</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" s="6">
         <v>1</v>
       </c>
       <c r="E24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1062,7 +1053,7 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
@@ -1071,7 +1062,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1080,7 +1071,7 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
@@ -1089,43 +1080,7 @@
         <v>6</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="6">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Desktop\ruAstro\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81BE5AC-4C64-47B2-BC64-A246BED3CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153CDC92-D266-4EAD-925F-13999E5526D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25695" yWindow="2730" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="1890" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="105">
   <si>
     <t>№ п/п</t>
   </si>
@@ -48,112 +48,298 @@
     <t>шт</t>
   </si>
   <si>
-    <t>ЛГУП-6441</t>
-  </si>
-  <si>
-    <t>ЛГУП-6533</t>
-  </si>
-  <si>
-    <t>Шибер НТ.530.000.005.0 (лазер)</t>
-  </si>
-  <si>
-    <t>Шибер НТ.530.000.005.0 (шлифовка)</t>
-  </si>
-  <si>
-    <t>ЛГУП-6535</t>
-  </si>
-  <si>
-    <t>Клапан предохранительный СППК4р 17с25нж Ду80 Ру40</t>
-  </si>
-  <si>
-    <t>ТОР 50</t>
-  </si>
-  <si>
-    <t>НТУП-017684</t>
-  </si>
-  <si>
-    <t>ЛГУП-6598</t>
-  </si>
-  <si>
-    <t>ЛГУП-6599</t>
-  </si>
-  <si>
-    <t>м3</t>
-  </si>
-  <si>
-    <t>АХ00-000022</t>
-  </si>
-  <si>
-    <t>АХУП-000348</t>
-  </si>
-  <si>
-    <t>АХУП-000349</t>
-  </si>
-  <si>
-    <t>АХУП-000350</t>
-  </si>
-  <si>
-    <t>Шкаф ПС и ОС АГЗУ 14-400 Удмуртнефть</t>
+    <t>ЛГУП-6661</t>
+  </si>
+  <si>
+    <t>Уплотнение тип УТД.136.090В1</t>
+  </si>
+  <si>
+    <t>ЛГУП-6662</t>
+  </si>
+  <si>
+    <t>Брелок EM-Marine</t>
   </si>
   <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>ЛГУП-6654</t>
-  </si>
-  <si>
-    <t>ЛГУП-6658</t>
-  </si>
-  <si>
-    <t>Термостат MTK-CT0</t>
-  </si>
-  <si>
-    <t>Рычаг НТ.510.000.003.0 (лазер)</t>
-  </si>
-  <si>
-    <t>Задвижка ЗКЛ 50-40 ХЛ1 30лс15нж класс герм. А, исп.F ХЛ1 L=216 без КОФ</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая стальная ЗКС Ду25 Ру160 УХЛ1, класс герметичности "А"</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
-  </si>
-  <si>
-    <t>Магнит ПСМНТ.001.021.001</t>
-  </si>
-  <si>
-    <t>Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
-  </si>
-  <si>
-    <t>Петля накладная ПН1-70 ГОСТ 5088-2005</t>
-  </si>
-  <si>
-    <t>Мин. вата типа "URSA" П-125</t>
-  </si>
-  <si>
-    <t>Шкаф управления</t>
-  </si>
-  <si>
-    <t>Шкаф силовой</t>
-  </si>
-  <si>
-    <t>Влагомер сырой нефти ВСН-2 Ду 80, Ру 40 (угловой) взрывозащ.1Ex ib IIA T6, IP67</t>
-  </si>
-  <si>
-    <t>Пресс-форма крышка ПСМНТ 001.000.007 СБ</t>
-  </si>
-  <si>
-    <t>Пресс-форма хомуты НТ 010.000.000 СБ</t>
-  </si>
-  <si>
-    <t>Пресс-форма клапан пред-ний НТ 3.02.00.00.000 СБ</t>
-  </si>
-  <si>
-    <t>пресс-форма Угольник ПСМНТ 001.029.000 СБ</t>
+    <t>ЛГУП-6668</t>
+  </si>
+  <si>
+    <t>ЛГУП-6669</t>
+  </si>
+  <si>
+    <t>Хомут 200х3.6мм белый (1упак=100шт) 25214 "DKC"</t>
+  </si>
+  <si>
+    <t>упак.</t>
+  </si>
+  <si>
+    <t>ЛГУП-6673</t>
+  </si>
+  <si>
+    <t>Клемма проходная, зажим push-in, 2 точки подключения, 4 кв.мм, синяя</t>
+  </si>
+  <si>
+    <t>Онлайн ИБП ST1101 SL (1000 ВА / 900 Вт) Штиль</t>
+  </si>
+  <si>
+    <t>Саморез Tech-Krep ШСММ сверло 4,2х16 (16 шт.), пакет 102398 код 15618712</t>
+  </si>
+  <si>
+    <t>уп.</t>
+  </si>
+  <si>
+    <t>Провод ПУГВ 1х1,0 Ч ГОСТ 31947-2012</t>
+  </si>
+  <si>
+    <t>мм</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВнг(A)-LS 1х2,5 синий</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>Профиль монтажный П-образный PSL толщ. 1,5 L 3000</t>
+  </si>
+  <si>
+    <t>Трубка ПВХ кембрик для электропроводки,белая ТМ-40</t>
+  </si>
+  <si>
+    <t>Клемма проходная, зажим push-in, 2 точки подключения, 4 кв.мм, серая</t>
+  </si>
+  <si>
+    <t>Клемма с предохранителями (SUPU арт. TC4-FUSE-BK)</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВ нг(А)LS 1х2.5 белый</t>
+  </si>
+  <si>
+    <t>Наконечник-гильза 8 мм с изолир.фланцем 1,00 кв.мм красный (НШВИ)</t>
+  </si>
+  <si>
+    <t>модуль расширения интерфейса для ИБП</t>
+  </si>
+  <si>
+    <t>Панель оператора Weintek MT8106iP  10дюймов</t>
+  </si>
+  <si>
+    <t>УЗИП Приборэнерго RS485-1-M</t>
+  </si>
+  <si>
+    <t>Блок питания NDR-120-24 Mean Well</t>
+  </si>
+  <si>
+    <t>Блок питания MDR-100-24 Mean Well</t>
+  </si>
+  <si>
+    <t>Нулевая шина на DIN-рейку REXANT 11-2318</t>
+  </si>
+  <si>
+    <t>Шина "РЕ" на DIN-рейку REXANT 11-2309</t>
+  </si>
+  <si>
+    <t>Клемма заземления, зажим push-in, 2 точки подключения, 4 кв.мм VPR-4-PE-YG</t>
+  </si>
+  <si>
+    <t>Клемма проходная, зажим push-in, 2 точки подключения, 2.5 кв.мм, серая VPR-2.5-GY</t>
+  </si>
+  <si>
+    <t>Сальник PG - 29, 15-25 IP68 DKC 53100</t>
+  </si>
+  <si>
+    <t>Сальник КЭАЗ PG21 (D проводника 15-18мм) IP54 143109</t>
+  </si>
+  <si>
+    <t>Розетка на дин рейкуРозетка РАр10-3-ОПс заземлением IEK</t>
+  </si>
+  <si>
+    <t>Контролер Ария ver.4.5 (4 AI, 4 DI/DO, 4 порта RS485) АВПЮ.426441.358-10-02</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВнг(А)-LS 1х0.5 белый</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВнг-LS 1х2,5ж/з</t>
+  </si>
+  <si>
+    <t>Держатель маркировки для ZBT008</t>
+  </si>
+  <si>
+    <t>упак</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический двухполюсный 10А С ВА47-29 4.5кА mcb4729-2-10C IEK</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический однополюсный 3А С ВА47-29 4.5кА MVA20-1-003-C IEK</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический однополюсный 6А C ВА47-29 4.5кА м IEK</t>
+  </si>
+  <si>
+    <t>Изолятор торцевой для клеммы VPR-4_х000D_</t>
+  </si>
+  <si>
+    <t>Изолятор торцевой для клеммы VPRTT-2.5_x000D_</t>
+  </si>
+  <si>
+    <t>Упор торцевой BTU, ZBT008_х000D DKC</t>
+  </si>
+  <si>
+    <t>Предохранитель стеклянный 5х20 0,63А 179020.0,63 Siba</t>
+  </si>
+  <si>
+    <t>Клемма двухуровневая, зажим push-in, 4 точки подключения, 2.5 кв.мм, серая PTP2.5-4-GY</t>
+  </si>
+  <si>
+    <t>Маркер самоклеящийся от 1 до 45 Rexant 07-6203</t>
+  </si>
+  <si>
+    <t>DIN-рейка 2000см перфорированная</t>
+  </si>
+  <si>
+    <t>Промежуточное реле в сборке HF41-24-DA hongfa</t>
+  </si>
+  <si>
+    <t>Кабель-канал перфорированный 25х60 ИМПАКТ IEK CKM50-025-060-1-K03</t>
+  </si>
+  <si>
+    <t>Наконечник штыревой втулочный изолированный НШВИ 0.5-8 79435</t>
+  </si>
+  <si>
+    <t>Наконечник НШВИ 2,5-08 синий (20шт/упак) (UGN10-4-D25-04-08)</t>
+  </si>
+  <si>
+    <t>Модуль аналогового ввода (Ai) (16 каналов) версия 1 АВПЮ.426439.001-04-01</t>
+  </si>
+  <si>
+    <t>Модуль дискретного ввода-вывода (16 каналов) АВПЮ.426441.360-04-01 исполнение 4.1-1</t>
+  </si>
+  <si>
+    <t>Стул офисный</t>
+  </si>
+  <si>
+    <t>ЛГУП-6674</t>
+  </si>
+  <si>
+    <t>Стол с выкатной тумбой 1400х600</t>
+  </si>
+  <si>
+    <t>Костюм летний от загрязнений и противоэнцефалитный</t>
+  </si>
+  <si>
+    <t>ЛГУП-6675</t>
+  </si>
+  <si>
+    <t>Ботинки летние 42 р</t>
+  </si>
+  <si>
+    <t>Тряпка для пола -1шт хлопок серый 80х100см</t>
+  </si>
+  <si>
+    <t>ЛГУП-6677</t>
+  </si>
+  <si>
+    <t>Перчатки нитриловые повышенной прочности, толщина 0,17мм светло-сиреневые размер L (100шт)</t>
+  </si>
+  <si>
+    <t>Средство для чистки универсальное Пемоксоль санитарный 500г.</t>
+  </si>
+  <si>
+    <t>Белизна-гель (0,9) 1л</t>
+  </si>
+  <si>
+    <t>Мешки для мусора 120л</t>
+  </si>
+  <si>
+    <t>Моющее средство Фери</t>
+  </si>
+  <si>
+    <t>Мыло хозяйственное отбеливающее (Китай)</t>
+  </si>
+  <si>
+    <t>Тряпка для пола из микрофибры Рыжий кот цвет:зеленый; размер: 80х100 см</t>
+  </si>
+  <si>
+    <t>Средство для чистки сантехники Антиржавчина Grass WC-gel 0,75 л</t>
+  </si>
+  <si>
+    <t>Туалетная бумага</t>
+  </si>
+  <si>
+    <t>Скрепки канцелярские</t>
+  </si>
+  <si>
+    <t>НТУП-017724</t>
+  </si>
+  <si>
+    <t>Ножницы LACO 215мм черные</t>
+  </si>
+  <si>
+    <t>Скобы для степлера 24/6</t>
+  </si>
+  <si>
+    <t>Шабер трехграный L=50 мм ARM</t>
+  </si>
+  <si>
+    <t>Степлер №24</t>
+  </si>
+  <si>
+    <t>Степлер №10 10л</t>
+  </si>
+  <si>
+    <t>Ручка гелевая черная</t>
+  </si>
+  <si>
+    <t>Маркер черный двухсторонний  перманентный черный</t>
+  </si>
+  <si>
+    <t>Маска респиратор НР3-0112 с клапаном FFP-2</t>
+  </si>
+  <si>
+    <t>Ластик BRAUBERG UNIVERSAL, 45х45х10мм, белый, треугольный, пластиковый держатель, 222473</t>
+  </si>
+  <si>
+    <t>Блок для записей BRAUBERG непроклееный, куб 9*9*9 см ,цветной</t>
+  </si>
+  <si>
+    <t>Перчатки (резиновые) для защиты от воды и растворов нетоксичных веществ</t>
+  </si>
+  <si>
+    <t>Файл-вкладыш А4 прозрачный гладкий 100 шт. в упаковке</t>
+  </si>
+  <si>
+    <t>Антистеплер для скоб № 10 и № 24/6, STAFF EVERYDAY, черный, 224628</t>
+  </si>
+  <si>
+    <t>Корзина для мусора</t>
+  </si>
+  <si>
+    <t>Нож канцелярский 18мм усиленный</t>
+  </si>
+  <si>
+    <t>Клей карандаш</t>
+  </si>
+  <si>
+    <t>Клапан КПСР 2.11-25-10-1.4001-СЧ-1.6-1-150-У привод TW-500 220В</t>
+  </si>
+  <si>
+    <t>ЛГУП-6678</t>
+  </si>
+  <si>
+    <t>Кольцо А75х1,7 ГОСТ 13943-86</t>
+  </si>
+  <si>
+    <t>Строп текстильный 5 т - 5 м</t>
+  </si>
+  <si>
+    <t>Корпус металлический ЩМП-4-0 (800х600х250мм) IP31 УХЛ3 (серый)</t>
   </si>
 </sst>
 </file>
@@ -191,7 +377,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -214,24 +400,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCC085"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCCC085"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCC085"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -242,9 +415,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -254,10 +424,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,12 +772,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="72.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="51.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
@@ -617,7 +787,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -638,16 +808,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="6">
-        <v>5</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="C2" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="5">
+        <v>30</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -656,53 +826,53 @@
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="5">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5">
+        <v>100</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="C5" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="5">
         <v>8</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -710,17 +880,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="6">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
+      <c r="C6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -728,17 +898,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -746,35 +916,35 @@
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="6">
-        <v>7</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>11</v>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -782,17 +952,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="6">
-        <v>2</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>11</v>
+      <c r="C10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5">
+        <v>25</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -800,17 +970,17 @@
         <v>10</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>14</v>
+      <c r="C11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -818,17 +988,17 @@
         <v>11</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="6">
-        <v>8</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>15</v>
+      <c r="C12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -836,16 +1006,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="6">
-        <v>8</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="C13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="5">
+        <v>5</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -854,16 +1024,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="6">
-        <v>16</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="C14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -872,16 +1042,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="6">
-        <v>11.52</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="C15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -890,17 +1060,17 @@
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="6">
-        <v>8</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>18</v>
+      <c r="C16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -908,17 +1078,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="6">
-        <v>3</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>19</v>
+      <c r="C17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -926,17 +1096,17 @@
         <v>17</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>20</v>
+      <c r="C18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -944,17 +1114,17 @@
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>21</v>
+      <c r="C19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -962,17 +1132,17 @@
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>21</v>
+      <c r="C20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -980,35 +1150,35 @@
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>24</v>
+      <c r="C22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1016,17 +1186,17 @@
         <v>22</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>25</v>
+      <c r="C23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1034,17 +1204,17 @@
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>25</v>
+      <c r="C24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1052,35 +1222,1043 @@
         <v>24</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="5">
+        <v>3</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="5">
+        <v>10</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="5">
+        <v>3</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="5">
+        <v>25</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>25</v>
+      <c r="D29" s="5">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="5">
+        <v>100</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="5">
+        <v>2</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="5">
+        <v>14</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="5">
+        <v>3</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="5">
+        <v>3</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="5">
+        <v>1</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="5">
+        <v>15</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="5">
+        <v>10</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="5">
+        <v>42</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="5">
+        <v>2</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="5">
+        <v>13</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" s="5">
+        <v>3</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="5">
+        <v>200</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" s="5">
+        <v>10</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" s="5">
+        <v>1</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" s="5">
+        <v>1</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="5">
+        <v>2</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" s="5">
+        <v>10</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="5">
+        <v>10</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="5">
+        <v>6</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="5">
+        <v>6</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D55" s="5">
+        <v>50</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" s="5">
+        <v>2</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" s="5">
+        <v>10</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" s="5">
+        <v>20</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="5">
+        <v>20</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D60" s="5">
+        <v>20</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" s="5">
+        <v>10</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="5">
+        <v>50</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63" s="5">
+        <v>2</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64" s="5">
+        <v>150</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="5">
+        <v>5</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" s="5">
+        <v>5</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67" s="5">
+        <v>5</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D68" s="5">
+        <v>2</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D69" s="5">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D70" s="5">
+        <v>1</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D71" s="5">
+        <v>10</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D72" s="5">
+        <v>10</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73" s="5">
+        <v>50</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74" s="5">
+        <v>5</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D75" s="5">
+        <v>5</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76" s="5">
+        <v>10</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D77" s="5">
+        <v>1</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D78" s="5">
+        <v>2</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D79" s="5">
+        <v>2</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D80" s="5">
+        <v>5</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D81" s="5">
+        <v>5</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" s="5">
+        <v>1</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Desktop\ruAstro\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153CDC92-D266-4EAD-925F-13999E5526D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218F3456-287F-4106-AF40-1936684D2B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3375" yWindow="1890" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="109">
   <si>
     <t>№ п/п</t>
   </si>
@@ -57,180 +57,171 @@
     <t>ЛГУП-6662</t>
   </si>
   <si>
-    <t>Брелок EM-Marine</t>
+    <t>Хомут 200х3.6мм белый (1упак=100шт) 25214 "DKC"</t>
+  </si>
+  <si>
+    <t>упак.</t>
+  </si>
+  <si>
+    <t>ЛГУП-6673</t>
+  </si>
+  <si>
+    <t>Держатель маркировки для ZBT008</t>
+  </si>
+  <si>
+    <t>упак</t>
+  </si>
+  <si>
+    <t>Саморез Tech-Krep ШСММ сверло 4,2х16 (16 шт.), пакет 102398 код 15618712</t>
+  </si>
+  <si>
+    <t>уп.</t>
+  </si>
+  <si>
+    <t>Провод ПУГВ 1х1,0 Ч ГОСТ 31947-2012</t>
+  </si>
+  <si>
+    <t>мм</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВнг(A)-LS 1х2,5 синий</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>Профиль монтажный П-образный PSL толщ. 1,5 L 3000</t>
+  </si>
+  <si>
+    <t>Трубка ПВХ кембрик для электропроводки,белая ТМ-40</t>
+  </si>
+  <si>
+    <t>Нулевая шина на DIN-рейку REXANT 11-2318</t>
+  </si>
+  <si>
+    <t>Шина "РЕ" на DIN-рейку REXANT 11-2309</t>
+  </si>
+  <si>
+    <t>Клемма проходная, зажим push-in, 2 точки подключения, 4 кв.мм, синяя</t>
+  </si>
+  <si>
+    <t>Клемма проходная, зажим push-in, 2 точки подключения, 4 кв.мм, серая</t>
+  </si>
+  <si>
+    <t>Клемма с предохранителями (SUPU арт. TC4-FUSE-BK)</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВ нг(А)LS 1х2.5 белый</t>
+  </si>
+  <si>
+    <t>Наконечник-гильза 8 мм с изолир.фланцем 1,00 кв.мм красный (НШВИ)</t>
+  </si>
+  <si>
+    <t>модуль расширения интерфейса для ИБП</t>
+  </si>
+  <si>
+    <t>Панель оператора Weintek MT8106iP  10дюймов</t>
+  </si>
+  <si>
+    <t>УЗИП Приборэнерго RS485-1-M</t>
+  </si>
+  <si>
+    <t>Блок питания NDR-120-24 Mean Well</t>
+  </si>
+  <si>
+    <t>Блок питания MDR-100-24 Mean Well</t>
+  </si>
+  <si>
+    <t>Розетка на дин рейкуРозетка РАр10-3-ОПс заземлением IEK</t>
+  </si>
+  <si>
+    <t>Онлайн ИБП ST1101 SL (1000 ВА / 900 Вт) Штиль</t>
+  </si>
+  <si>
+    <t>Клемма заземления, зажим push-in, 2 точки подключения, 4 кв.мм VPR-4-PE-YG</t>
+  </si>
+  <si>
+    <t>Клемма проходная, зажим push-in, 2 точки подключения, 2.5 кв.мм, серая VPR-2.5-GY</t>
+  </si>
+  <si>
+    <t>Сальник PG - 29, 15-25 IP68 DKC 53100</t>
+  </si>
+  <si>
+    <t>Сальник КЭАЗ PG21 (D проводника 15-18мм) IP54 143109</t>
+  </si>
+  <si>
+    <t>Контролер Ария ver.4.5 (4 AI, 4 DI/DO, 4 порта RS485) АВПЮ.426441.358-10-02</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВнг(А)-LS 1х0.5 белый</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВнг-LS 1х2,5ж/з</t>
+  </si>
+  <si>
+    <t>Маркер самоклеящийся от 1 до 45 Rexant 07-6203</t>
+  </si>
+  <si>
+    <t>DIN-рейка 2000см перфорированная</t>
+  </si>
+  <si>
+    <t>Промежуточное реле в сборке HF41-24-DA hongfa</t>
+  </si>
+  <si>
+    <t>Модуль дискретного ввода-вывода (16 каналов) АВПЮ.426441.360-04-01 исполнение 4.1-1</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический двухполюсный 10А С ВА47-29 4.5кА mcb4729-2-10C IEK</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический однополюсный 3А С ВА47-29 4.5кА MVA20-1-003-C IEK</t>
+  </si>
+  <si>
+    <t>Модуль аналогового ввода (Ai) (16 каналов) версия 1 АВПЮ.426439.001-04-01</t>
+  </si>
+  <si>
+    <t>Наконечник НШВИ 2,5-08 синий (20шт/упак) (UGN10-4-D25-04-08)</t>
+  </si>
+  <si>
+    <t>Наконечник штыревой втулочный изолированный НШВИ 0.5-8 79435</t>
+  </si>
+  <si>
+    <t>Кабель-канал перфорированный 25х60 ИМПАКТ IEK CKM50-025-060-1-K03</t>
+  </si>
+  <si>
+    <t>Клемма двухуровневая, зажим push-in, 4 точки подключения, 2.5 кв.мм, серая PTP2.5-4-GY</t>
+  </si>
+  <si>
+    <t>Предохранитель стеклянный 5х20 0,63А 179020.0,63 Siba</t>
+  </si>
+  <si>
+    <t>Упор торцевой BTU, ZBT008_х000D DKC</t>
+  </si>
+  <si>
+    <t>Изолятор торцевой для клеммы VPRTT-2.5_x000D_</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический однополюсный 6А C ВА47-29 4.5кА м IEK</t>
+  </si>
+  <si>
+    <t>Изолятор торцевой для клеммы VPR-4_х000D_</t>
+  </si>
+  <si>
+    <t>Стол с выкатной тумбой 1400х600</t>
   </si>
   <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>ЛГУП-6668</t>
-  </si>
-  <si>
-    <t>ЛГУП-6669</t>
-  </si>
-  <si>
-    <t>Хомут 200х3.6мм белый (1упак=100шт) 25214 "DKC"</t>
-  </si>
-  <si>
-    <t>упак.</t>
-  </si>
-  <si>
-    <t>ЛГУП-6673</t>
-  </si>
-  <si>
-    <t>Клемма проходная, зажим push-in, 2 точки подключения, 4 кв.мм, синяя</t>
-  </si>
-  <si>
-    <t>Онлайн ИБП ST1101 SL (1000 ВА / 900 Вт) Штиль</t>
-  </si>
-  <si>
-    <t>Саморез Tech-Krep ШСММ сверло 4,2х16 (16 шт.), пакет 102398 код 15618712</t>
-  </si>
-  <si>
-    <t>уп.</t>
-  </si>
-  <si>
-    <t>Провод ПУГВ 1х1,0 Ч ГОСТ 31947-2012</t>
-  </si>
-  <si>
-    <t>мм</t>
-  </si>
-  <si>
-    <t>Провод силовой ПуГВнг(A)-LS 1х2,5 синий</t>
-  </si>
-  <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>Профиль монтажный П-образный PSL толщ. 1,5 L 3000</t>
-  </si>
-  <si>
-    <t>Трубка ПВХ кембрик для электропроводки,белая ТМ-40</t>
-  </si>
-  <si>
-    <t>Клемма проходная, зажим push-in, 2 точки подключения, 4 кв.мм, серая</t>
-  </si>
-  <si>
-    <t>Клемма с предохранителями (SUPU арт. TC4-FUSE-BK)</t>
-  </si>
-  <si>
-    <t>Провод силовой ПуГВ нг(А)LS 1х2.5 белый</t>
-  </si>
-  <si>
-    <t>Наконечник-гильза 8 мм с изолир.фланцем 1,00 кв.мм красный (НШВИ)</t>
-  </si>
-  <si>
-    <t>модуль расширения интерфейса для ИБП</t>
-  </si>
-  <si>
-    <t>Панель оператора Weintek MT8106iP  10дюймов</t>
-  </si>
-  <si>
-    <t>УЗИП Приборэнерго RS485-1-M</t>
-  </si>
-  <si>
-    <t>Блок питания NDR-120-24 Mean Well</t>
-  </si>
-  <si>
-    <t>Блок питания MDR-100-24 Mean Well</t>
-  </si>
-  <si>
-    <t>Нулевая шина на DIN-рейку REXANT 11-2318</t>
-  </si>
-  <si>
-    <t>Шина "РЕ" на DIN-рейку REXANT 11-2309</t>
-  </si>
-  <si>
-    <t>Клемма заземления, зажим push-in, 2 точки подключения, 4 кв.мм VPR-4-PE-YG</t>
-  </si>
-  <si>
-    <t>Клемма проходная, зажим push-in, 2 точки подключения, 2.5 кв.мм, серая VPR-2.5-GY</t>
-  </si>
-  <si>
-    <t>Сальник PG - 29, 15-25 IP68 DKC 53100</t>
-  </si>
-  <si>
-    <t>Сальник КЭАЗ PG21 (D проводника 15-18мм) IP54 143109</t>
-  </si>
-  <si>
-    <t>Розетка на дин рейкуРозетка РАр10-3-ОПс заземлением IEK</t>
-  </si>
-  <si>
-    <t>Контролер Ария ver.4.5 (4 AI, 4 DI/DO, 4 порта RS485) АВПЮ.426441.358-10-02</t>
-  </si>
-  <si>
-    <t>компл</t>
-  </si>
-  <si>
-    <t>Провод силовой ПуГВнг(А)-LS 1х0.5 белый</t>
-  </si>
-  <si>
-    <t>Провод силовой ПуГВнг-LS 1х2,5ж/з</t>
-  </si>
-  <si>
-    <t>Держатель маркировки для ZBT008</t>
-  </si>
-  <si>
-    <t>упак</t>
-  </si>
-  <si>
-    <t>Выключатель автоматический двухполюсный 10А С ВА47-29 4.5кА mcb4729-2-10C IEK</t>
-  </si>
-  <si>
-    <t>Выключатель автоматический однополюсный 3А С ВА47-29 4.5кА MVA20-1-003-C IEK</t>
-  </si>
-  <si>
-    <t>Выключатель автоматический однополюсный 6А C ВА47-29 4.5кА м IEK</t>
-  </si>
-  <si>
-    <t>Изолятор торцевой для клеммы VPR-4_х000D_</t>
-  </si>
-  <si>
-    <t>Изолятор торцевой для клеммы VPRTT-2.5_x000D_</t>
-  </si>
-  <si>
-    <t>Упор торцевой BTU, ZBT008_х000D DKC</t>
-  </si>
-  <si>
-    <t>Предохранитель стеклянный 5х20 0,63А 179020.0,63 Siba</t>
-  </si>
-  <si>
-    <t>Клемма двухуровневая, зажим push-in, 4 точки подключения, 2.5 кв.мм, серая PTP2.5-4-GY</t>
-  </si>
-  <si>
-    <t>Маркер самоклеящийся от 1 до 45 Rexant 07-6203</t>
-  </si>
-  <si>
-    <t>DIN-рейка 2000см перфорированная</t>
-  </si>
-  <si>
-    <t>Промежуточное реле в сборке HF41-24-DA hongfa</t>
-  </si>
-  <si>
-    <t>Кабель-канал перфорированный 25х60 ИМПАКТ IEK CKM50-025-060-1-K03</t>
-  </si>
-  <si>
-    <t>Наконечник штыревой втулочный изолированный НШВИ 0.5-8 79435</t>
-  </si>
-  <si>
-    <t>Наконечник НШВИ 2,5-08 синий (20шт/упак) (UGN10-4-D25-04-08)</t>
-  </si>
-  <si>
-    <t>Модуль аналогового ввода (Ai) (16 каналов) версия 1 АВПЮ.426439.001-04-01</t>
-  </si>
-  <si>
-    <t>Модуль дискретного ввода-вывода (16 каналов) АВПЮ.426441.360-04-01 исполнение 4.1-1</t>
+    <t>ЛГУП-6674</t>
   </si>
   <si>
     <t>Стул офисный</t>
   </si>
   <si>
-    <t>ЛГУП-6674</t>
-  </si>
-  <si>
-    <t>Стол с выкатной тумбой 1400х600</t>
-  </si>
-  <si>
     <t>Костюм летний от загрязнений и противоэнцефалитный</t>
   </si>
   <si>
@@ -240,106 +231,127 @@
     <t>Ботинки летние 42 р</t>
   </si>
   <si>
-    <t>Тряпка для пола -1шт хлопок серый 80х100см</t>
-  </si>
-  <si>
-    <t>ЛГУП-6677</t>
-  </si>
-  <si>
-    <t>Перчатки нитриловые повышенной прочности, толщина 0,17мм светло-сиреневые размер L (100шт)</t>
-  </si>
-  <si>
-    <t>Средство для чистки универсальное Пемоксоль санитарный 500г.</t>
-  </si>
-  <si>
-    <t>Белизна-гель (0,9) 1л</t>
-  </si>
-  <si>
-    <t>Мешки для мусора 120л</t>
-  </si>
-  <si>
-    <t>Моющее средство Фери</t>
-  </si>
-  <si>
-    <t>Мыло хозяйственное отбеливающее (Китай)</t>
-  </si>
-  <si>
-    <t>Тряпка для пола из микрофибры Рыжий кот цвет:зеленый; размер: 80х100 см</t>
-  </si>
-  <si>
-    <t>Средство для чистки сантехники Антиржавчина Grass WC-gel 0,75 л</t>
-  </si>
-  <si>
-    <t>Туалетная бумага</t>
+    <t>Маска респиратор НР3-0112 с клапаном FFP-2</t>
+  </si>
+  <si>
+    <t>НТУП-017724</t>
+  </si>
+  <si>
+    <t>Маркер черный двухсторонний  перманентный черный</t>
+  </si>
+  <si>
+    <t>Шабер трехграный L=50 мм ARM</t>
+  </si>
+  <si>
+    <t>Скобы для степлера 24/6</t>
   </si>
   <si>
     <t>Скрепки канцелярские</t>
   </si>
   <si>
-    <t>НТУП-017724</t>
-  </si>
-  <si>
     <t>Ножницы LACO 215мм черные</t>
   </si>
   <si>
-    <t>Скобы для степлера 24/6</t>
-  </si>
-  <si>
-    <t>Шабер трехграный L=50 мм ARM</t>
+    <t>Ластик BRAUBERG UNIVERSAL, 45х45х10мм, белый, треугольный, пластиковый держатель, 222473</t>
+  </si>
+  <si>
+    <t>Ручка гелевая черная</t>
+  </si>
+  <si>
+    <t>Степлер №10 10л</t>
+  </si>
+  <si>
+    <t>Блок для записей BRAUBERG непроклееный, куб 9*9*9 см ,цветной</t>
+  </si>
+  <si>
+    <t>Файл-вкладыш А4 прозрачный гладкий 100 шт. в упаковке</t>
+  </si>
+  <si>
+    <t>Антистеплер для скоб № 10 и № 24/6, STAFF EVERYDAY, черный, 224628</t>
+  </si>
+  <si>
+    <t>Клей карандаш</t>
+  </si>
+  <si>
+    <t>Перчатки (резиновые) для защиты от воды и растворов нетоксичных веществ</t>
+  </si>
+  <si>
+    <t>Корзина для мусора</t>
+  </si>
+  <si>
+    <t>Нож канцелярский 18мм усиленный</t>
   </si>
   <si>
     <t>Степлер №24</t>
   </si>
   <si>
-    <t>Степлер №10 10л</t>
-  </si>
-  <si>
-    <t>Ручка гелевая черная</t>
-  </si>
-  <si>
-    <t>Маркер черный двухсторонний  перманентный черный</t>
-  </si>
-  <si>
-    <t>Маска респиратор НР3-0112 с клапаном FFP-2</t>
-  </si>
-  <si>
-    <t>Ластик BRAUBERG UNIVERSAL, 45х45х10мм, белый, треугольный, пластиковый держатель, 222473</t>
-  </si>
-  <si>
-    <t>Блок для записей BRAUBERG непроклееный, куб 9*9*9 см ,цветной</t>
-  </si>
-  <si>
-    <t>Перчатки (резиновые) для защиты от воды и растворов нетоксичных веществ</t>
-  </si>
-  <si>
-    <t>Файл-вкладыш А4 прозрачный гладкий 100 шт. в упаковке</t>
-  </si>
-  <si>
-    <t>Антистеплер для скоб № 10 и № 24/6, STAFF EVERYDAY, черный, 224628</t>
-  </si>
-  <si>
-    <t>Корзина для мусора</t>
-  </si>
-  <si>
-    <t>Нож канцелярский 18мм усиленный</t>
-  </si>
-  <si>
-    <t>Клей карандаш</t>
-  </si>
-  <si>
     <t>Клапан КПСР 2.11-25-10-1.4001-СЧ-1.6-1-150-У привод TW-500 220В</t>
   </si>
   <si>
     <t>ЛГУП-6678</t>
   </si>
   <si>
+    <t>ЛГУП-6681</t>
+  </si>
+  <si>
+    <t>ЛГУП-6682</t>
+  </si>
+  <si>
+    <t>Фланец типа ASME Класс 300 (Py 50) НФА.02.00.000-07 (Ду80, 3") ст.09Г2С</t>
+  </si>
+  <si>
     <t>Кольцо А75х1,7 ГОСТ 13943-86</t>
   </si>
   <si>
-    <t>Строп текстильный 5 т - 5 м</t>
-  </si>
-  <si>
     <t>Корпус металлический ЩМП-4-0 (800х600х250мм) IP31 УХЛ3 (серый)</t>
+  </si>
+  <si>
+    <t>Каркас двери (рама)</t>
+  </si>
+  <si>
+    <t>Фланец 80-16-11-1-E -09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-16-11-1-В Ст09Г2С-IV ГОСТ33259-15</t>
+  </si>
+  <si>
+    <t>Фланец 50-16-11-1-Е-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Фланец 50-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 50-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец х-50-40 ГОСТ12821 (заготовка-поковка ст.09Г2С гр.IV КП 195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Фланец ANSI CL300-3'' Ду80 - заготовка поковка ст.09Г2С</t>
+  </si>
+  <si>
+    <t>Крышка НТ.ЕС.040.001.003 А (Заглушка 2-450-4,0-092ГС АТК 24.200.02-90)</t>
+  </si>
+  <si>
+    <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 2-80-40 09Г2С ГОСТ 19281-80</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-Е-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 100-40-11-1-B-09Г2С-IV ГОСТ 33259-2015</t>
   </si>
 </sst>
 </file>
@@ -772,12 +784,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="51.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
@@ -809,7 +821,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="7" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D2" s="5">
         <v>30</v>
@@ -839,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -848,7 +860,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>11</v>
@@ -857,22 +869,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="7" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D5" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -881,16 +893,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -902,13 +914,13 @@
         <v>17</v>
       </c>
       <c r="D7" s="5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -917,16 +929,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -935,7 +947,7 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -944,7 +956,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -953,16 +965,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -974,13 +986,13 @@
         <v>23</v>
       </c>
       <c r="D11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -989,16 +1001,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1007,16 +1019,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1025,7 +1037,7 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="5">
         <v>3</v>
@@ -1034,7 +1046,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1043,7 +1055,7 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="5">
         <v>10</v>
@@ -1052,7 +1064,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1061,7 +1073,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="5">
         <v>2</v>
@@ -1070,7 +1082,7 @@
         <v>6</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1079,7 +1091,7 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="5">
         <v>1</v>
@@ -1088,7 +1100,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1097,7 +1109,7 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" s="5">
         <v>1</v>
@@ -1106,7 +1118,7 @@
         <v>6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1115,7 +1127,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="5">
         <v>1</v>
@@ -1124,7 +1136,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1133,7 +1145,7 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
@@ -1142,7 +1154,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1151,7 +1163,7 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -1160,7 +1172,7 @@
         <v>6</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1169,7 +1181,7 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D22" s="5">
         <v>1</v>
@@ -1178,7 +1190,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1187,7 +1199,7 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -1196,7 +1208,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1205,7 +1217,7 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" s="5">
         <v>1</v>
@@ -1214,7 +1226,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1223,7 +1235,7 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25" s="5">
         <v>3</v>
@@ -1232,7 +1244,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1241,7 +1253,7 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D26" s="5">
         <v>10</v>
@@ -1250,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1259,7 +1271,7 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="5">
         <v>3</v>
@@ -1268,7 +1280,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1277,7 +1289,7 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D28" s="5">
         <v>25</v>
@@ -1286,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1295,16 +1307,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="5">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="5">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>6</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1316,13 +1328,13 @@
         <v>43</v>
       </c>
       <c r="D30" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1331,16 +1343,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" s="5">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1349,16 +1361,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1367,70 +1379,70 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" s="5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D34" s="5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D35" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D36" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1439,16 +1451,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D37" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1457,7 +1469,7 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D38" s="5">
         <v>1</v>
@@ -1466,7 +1478,7 @@
         <v>6</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1475,16 +1487,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="7" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="D39" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1493,7 +1505,7 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D40" s="5">
         <v>10</v>
@@ -1502,25 +1514,25 @@
         <v>6</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D41" s="5">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1529,34 +1541,34 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D42" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D43" s="5">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1565,16 +1577,16 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D44" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1583,16 +1595,16 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D45" s="5">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1601,16 +1613,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D46" s="5">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1619,16 +1631,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D47" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1637,7 +1649,7 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="7" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="D48" s="5">
         <v>1</v>
@@ -1646,7 +1658,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1655,19 +1667,19 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="5">
+        <v>10</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="5">
-        <v>1</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1676,13 +1688,13 @@
         <v>64</v>
       </c>
       <c r="D50" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1694,10 +1706,10 @@
         <v>65</v>
       </c>
       <c r="D51" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>66</v>
@@ -1712,16 +1724,16 @@
         <v>67</v>
       </c>
       <c r="D52" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -1730,16 +1742,16 @@
         <v>68</v>
       </c>
       <c r="D53" s="5">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -1748,10 +1760,10 @@
         <v>70</v>
       </c>
       <c r="D54" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>69</v>
@@ -1766,13 +1778,13 @@
         <v>71</v>
       </c>
       <c r="D55" s="5">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1781,16 +1793,16 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D56" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1799,16 +1811,16 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D57" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1817,16 +1829,16 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D58" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1835,16 +1847,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D59" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1853,16 +1865,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D60" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1871,16 +1883,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D61" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1889,16 +1901,16 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D62" s="5">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1907,16 +1919,16 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D63" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1925,16 +1937,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D64" s="5">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1943,16 +1955,16 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D65" s="5">
         <v>5</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1961,16 +1973,16 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D66" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1979,16 +1991,16 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D67" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1997,16 +2009,16 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D68" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2015,16 +2027,16 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D69" s="5">
         <v>1</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2033,16 +2045,16 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D70" s="5">
         <v>1</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2051,133 +2063,133 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D71" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>71</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D72" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D73" s="5">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D74" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>74</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D75" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>75</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D76" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>76</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>77</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D78" s="5">
         <v>2</v>
@@ -2186,7 +2198,7 @@
         <v>6</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2195,61 +2207,61 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D79" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>79</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="7" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D80" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D81" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
@@ -2258,7 +2270,97 @@
         <v>6</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>101</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D83" s="5">
+        <v>1</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D84" s="5">
+        <v>4</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85" s="5">
+        <v>1</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D86" s="5">
+        <v>18</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D87" s="5">
+        <v>1</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200AFFA5-3C97-4AB5-B1FF-C167BCA2081E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32FD3BF-EE88-4077-9F6E-44731D0943F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3375" yWindow="1890" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="125">
   <si>
     <t>№ п/п</t>
   </si>
@@ -51,195 +51,126 @@
     <t>ЛГУП-7008</t>
   </si>
   <si>
-    <t>Сегмент ПСМНТ.001.014.000</t>
+    <t>кг</t>
+  </si>
+  <si>
+    <t>ЛГУП-7011</t>
+  </si>
+  <si>
+    <t>ЛГУП-7053</t>
+  </si>
+  <si>
+    <t>АМУП-000028</t>
+  </si>
+  <si>
+    <t>Эмаль Политон-УР (УФ) RAL 9003, комплект 25 кг (основа+отвердитель)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7088</t>
+  </si>
+  <si>
+    <t>не исп шарик 25.4-100 ГОСТ3722-81-от НТ</t>
+  </si>
+  <si>
+    <t>Стеллаж палетный для погрузчика L=6м H=5м</t>
+  </si>
+  <si>
+    <t>ЛГУП-6939</t>
+  </si>
+  <si>
+    <t>Стеллаж палетный для погрузчика L=6м H=4м</t>
+  </si>
+  <si>
+    <t>Стеллаж палетный для погрузчика L=6м H=3м</t>
+  </si>
+  <si>
+    <t>Стеллаж палетный для погрузчика L=9м H=3м</t>
+  </si>
+  <si>
+    <t>Вытяжной поворотный рукав для сварочных газов и дымов, диаметр 150 мм с авто-вентиляцией</t>
+  </si>
+  <si>
+    <t>ЛГУП-6943</t>
+  </si>
+  <si>
+    <t>ЛГУП-7097</t>
+  </si>
+  <si>
+    <t>ЛГУП-7099</t>
+  </si>
+  <si>
+    <t>ЛГУП-7101</t>
+  </si>
+  <si>
+    <t>ЛГУП-7103</t>
+  </si>
+  <si>
+    <t>Изготовление АГЗУ 14  скважин</t>
   </si>
   <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>ЛГУП-7009</t>
-  </si>
-  <si>
-    <t>кг</t>
-  </si>
-  <si>
-    <t>ЛГУП-7010</t>
-  </si>
-  <si>
-    <t>ЛГУП-7011</t>
-  </si>
-  <si>
-    <t>ЛГУП-7053</t>
-  </si>
-  <si>
-    <t>ЛГУП-7054</t>
-  </si>
-  <si>
-    <t>Эмаль Политон-УР (УФ) RAL 9003, комплект 25 кг (основа+отвердитель)</t>
-  </si>
-  <si>
-    <t>АМУП-000028</t>
-  </si>
-  <si>
-    <t>ЛГУП-7088</t>
-  </si>
-  <si>
-    <t>не исп шарик 25.4-100 ГОСТ3722-81-от НТ</t>
-  </si>
-  <si>
-    <t>Стеллаж палетный для погрузчика L=6м H=4м</t>
-  </si>
-  <si>
-    <t>ЛГУП-6939</t>
-  </si>
-  <si>
-    <t>Стеллаж палетный для погрузчика L=6м H=5м</t>
-  </si>
-  <si>
-    <t>Стеллаж палетный для погрузчика L=9м H=3м</t>
-  </si>
-  <si>
-    <t>Стеллаж палетный для погрузчика L=6м H=3м</t>
-  </si>
-  <si>
-    <t>Вытяжной поворотный рукав для сварочных газов и дымов, диаметр 150 мм с авто-вентиляцией</t>
-  </si>
-  <si>
-    <t>ЛГУП-6943</t>
-  </si>
-  <si>
-    <t>ЛГУП-7094</t>
-  </si>
-  <si>
-    <t>ЛГУП-7095</t>
-  </si>
-  <si>
-    <t>ЛГУП-7097</t>
-  </si>
-  <si>
-    <t>ЛГУП-7099</t>
-  </si>
-  <si>
-    <t>ЛГУП-7101</t>
-  </si>
-  <si>
-    <t>ЛГУП-7103</t>
-  </si>
-  <si>
-    <t>Изготовление АГЗУ 14  скважин</t>
-  </si>
-  <si>
     <t>АХУП-000484</t>
   </si>
   <si>
-    <t>ЛГУП-7108</t>
-  </si>
-  <si>
-    <t>НТУП-017869</t>
-  </si>
-  <si>
-    <t>Костюм летний от загрязнений и противоэнцефалитный</t>
+    <t>Модуль аналогового ввода (Ai) (16 каналов) версия 1 АВПЮ.426439.001-04-01</t>
+  </si>
+  <si>
+    <t>ЛГУП-7117</t>
+  </si>
+  <si>
+    <t>Модуль дискретного ввода-вывода (16 каналов) АВПЮ.426441.360-04-01 исполнение 4.1-1</t>
+  </si>
+  <si>
+    <t>Контролер Ария ver.4.5 (4 AI, 4 DI/DO, 4 порта RS485) АВПЮ.426441.358-10-02</t>
   </si>
   <si>
     <t>компл</t>
   </si>
   <si>
-    <t>НТУП-017870</t>
-  </si>
-  <si>
-    <t>Ботинки летние 42 р</t>
-  </si>
-  <si>
-    <t>ЛГУП-7115</t>
-  </si>
-  <si>
-    <t>Контролер Ария ver.4.5 (4 AI, 4 DI/DO, 4 порта RS485) АВПЮ.426441.358-10-02</t>
-  </si>
-  <si>
-    <t>ЛГУП-7117</t>
-  </si>
-  <si>
-    <t>Модуль аналогового ввода (Ai) (16 каналов) версия 1 АВПЮ.426439.001-04-01</t>
-  </si>
-  <si>
-    <t>Модуль дискретного ввода-вывода (16 каналов) АВПЮ.426441.360-04-01 исполнение 4.1-1</t>
-  </si>
-  <si>
-    <t>Волновой радарный уровнемер Левелтач-М</t>
-  </si>
-  <si>
-    <t>ЛГУП-7119</t>
-  </si>
-  <si>
-    <t>ЛГУП-7122</t>
-  </si>
-  <si>
-    <t>ЛГУП-7124</t>
+    <t>спец одежда летняя</t>
+  </si>
+  <si>
+    <t>ЛГУП-7125</t>
+  </si>
+  <si>
+    <t>ЛГУП-7132</t>
+  </si>
+  <si>
+    <t>Ценникодержатель Высота 80мм Длина 2500мм</t>
+  </si>
+  <si>
+    <t>ЛГУП-7138</t>
   </si>
   <si>
     <t>Фланец х-80-40 ГОСТ12821 (заготовка-поковка ст.20 гр.IV КП 195 ГОСТ 8479-70)</t>
   </si>
   <si>
-    <t>Рейка ПСМНТ.001.000.015</t>
-  </si>
-  <si>
-    <t>Корпус ПСМНТ.001.000.006 (заготовка литая СЧ18 ГОСТ 1412-85)</t>
-  </si>
-  <si>
-    <t>Корпус ПСМНТ.001.000.005 (заготовка литая СЧ18 ГОСТ1412-85)</t>
-  </si>
-  <si>
-    <t>Труба D89х6 ГОСТ 8732-78 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Труба 25х3,2 ГОСТ 3262-75 (D33,5)</t>
-  </si>
-  <si>
-    <t>Труба D108х16 ГОСТ 8732-78/ Ст.40Х  ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D159х10 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D83*10 Ст.20 ГОСТ 1050-88</t>
+    <t>Труба ГКРХХ 110х17,5 БрАЖН 10-4-4 ГОСТ 1208-90</t>
+  </si>
+  <si>
+    <t>Труба ГКРНх D60х13 БрАЖ9-4 ГОСТ 1628-78</t>
+  </si>
+  <si>
+    <t>Труба D60*13 ГКРХ БРКМц3-1 ГОСТ1628-78</t>
   </si>
   <si>
     <t>Труба 10х1,0 М3-ПТ ГОСТ 617-90</t>
   </si>
   <si>
-    <t>Труба ГКРНх D60х13 БрАЖ9-4 ГОСТ 1628-78</t>
-  </si>
-  <si>
-    <t>Труба ГКРХХ 110х17,5 БрАЖН 10-4-4 ГОСТ 1208-90</t>
-  </si>
-  <si>
     <t>Лист S=6 ГОСТ19903-74/20Х13 ГОСТ 19281-89</t>
   </si>
   <si>
-    <t>Труба D60*13 ГКРХ БРКМц3-1 ГОСТ1628-78</t>
-  </si>
-  <si>
     <t>разбавитель СОЛЬВ-УР</t>
   </si>
   <si>
+    <t>Кольцо МПК10В 75-10-02</t>
+  </si>
+  <si>
+    <t>Кольцо МПК10В 75-10-01</t>
+  </si>
+  <si>
     <t>Проставка МПК10В 77-40</t>
   </si>
   <si>
@@ -252,60 +183,39 @@
     <t>Кольцо уплотнительное МПК10В 75-60</t>
   </si>
   <si>
+    <t>Кольцо регулировочное МПК45.00.026 (0,5мм)</t>
+  </si>
+  <si>
+    <t>Не исп. Кольцо уплотнительное НТ.202.003.004.0</t>
+  </si>
+  <si>
+    <t>Кольцо регулировочное МПК45.00.026-03 (0,8мм)</t>
+  </si>
+  <si>
+    <t>Кольцо регулировочное МПК45.00.026-05 (1,0мм)</t>
+  </si>
+  <si>
+    <t>Ось-винт МПК45.11.007</t>
+  </si>
+  <si>
     <t>Болт МПК45.11.006</t>
   </si>
   <si>
-    <t>Ось-винт МПК45.11.007</t>
-  </si>
-  <si>
-    <t>Кольцо регулировочное МПК45.00.026-03 (0,8мм)</t>
-  </si>
-  <si>
-    <t>Кольцо регулировочное МПК45.00.026 (0,5мм)</t>
-  </si>
-  <si>
-    <t>Кольцо МПК10В 75-10-02</t>
-  </si>
-  <si>
-    <t>Кольцо МПК10В 75-10-01</t>
-  </si>
-  <si>
-    <t>Кольцо регулировочное МПК45.00.026-05 (1,0мм)</t>
-  </si>
-  <si>
-    <t>Не исп. Кольцо уплотнительное НТ.202.003.004.0</t>
-  </si>
-  <si>
-    <t>Шплинт 2х10.4 ГОСТ 397-79</t>
-  </si>
-  <si>
-    <t>Болт В.М10-6gх40.58 ГОСТ 3033-79</t>
-  </si>
-  <si>
-    <t>Гайка М10-6Н.8.20 ГОСТ 3032-76</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Шайба 10Л ГОСТ 6402-70</t>
-  </si>
-  <si>
-    <t>Болт М6-6gх32.58.019 ГОСТ 7798-70</t>
+    <t>Труба D73х5,5-К ГОСТ 633-80</t>
+  </si>
+  <si>
+    <t>Труба D40х1,5 Ст.20 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D30х3 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Труба D27х3 Ст20 ГОСТ 1050-2013</t>
   </si>
   <si>
     <t>Труба D95х16 Ст.35 ГОСТ 1050-2013</t>
   </si>
   <si>
-    <t>Труба D27х3 Ст20 ГОСТ 1050-2013</t>
-  </si>
-  <si>
-    <t>Труба D30х3 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D40х1,5 Ст.20 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D73х5,5-К ГОСТ 633-80</t>
-  </si>
-  <si>
     <t>Труба D20х5 БрКМц 3-1 ГОСТ 1208-2014</t>
   </si>
   <si>
@@ -318,64 +228,186 @@
     <t>Фланец 50-6-01-1-F-ВЧ40-IV-59 ГОСТ Р 54432-2011</t>
   </si>
   <si>
+    <t>Вентиль манометровый ВМ-01-000-22</t>
+  </si>
+  <si>
     <t>Краска порошковая красно-коричневая RAL 3009</t>
   </si>
   <si>
     <t>Эмаль алкидная 7040 (серая глянцевая) 3ton спрей 520мл</t>
   </si>
   <si>
-    <t>Вентиль манометровый ВМ-01-000-22</t>
-  </si>
-  <si>
-    <t>Фланец х-80-40 ГОСТ12821 (заготовка-поковка ст.09Г2С гр.IV КП 195 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Фланец х-50-40 ГОСТ12821 (заготовка-поковка ст.09Г2С гр.IV КП 195 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Фланец х-150-40 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Фланец 100-40-11-1-B-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 1-200-40 09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
-    <t>набор обмедненных инструментов</t>
-  </si>
-  <si>
-    <t>Тройник 57х5 09Г2С ГОСТ 17376-2001</t>
-  </si>
-  <si>
-    <t>Заглушка 108х8-09Г2С ГОСТ 17379-2001</t>
-  </si>
-  <si>
-    <t>Переход К-89х8-57х5 09Г2С ГОСТ 17378-2001</t>
-  </si>
-  <si>
-    <t>Отвод 90-57х6 09Г2С ГОСТ 17375-01</t>
-  </si>
-  <si>
-    <t>Заглушка 219х8 ГОСТ 09Г2С 17379-2001</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 3050х1000х150 мм RAL 9003 (белый)</t>
-  </si>
-  <si>
-    <t>Краска белая ПФ-115</t>
-  </si>
-  <si>
-    <t>Грунт ГФ-021 ГОСТ 25129-82 серый</t>
+    <t>Манометр МП4 P=0..6МПа, ХЛ1 ст.защиты корпуса IP54, кл.точн. 1,0. Присоед-е: М20х1,5 - наружн</t>
+  </si>
+  <si>
+    <t>Паронит ПМБ 2 ГОСТ 481-80</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.012</t>
+  </si>
+  <si>
+    <t>Уплотнение ПСМНТ.001.022.002</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.013 (покупная)</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.030</t>
+  </si>
+  <si>
+    <t>Кольцо 065-075-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 067-075-46-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 070-076-36 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 070-080-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 075-080-30-2-2 ГОСТ 9833-77</t>
+  </si>
+  <si>
+    <t>Кольцо 080-085-30-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 100-106-36-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 112-118-36 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 210-220-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 350-360-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
+  </si>
+  <si>
+    <t>Кольцо А75х1,7 ГОСТ 13943-86_УЗНО</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное ПСМНТ.001.000.025</t>
+  </si>
+  <si>
+    <t>Корпус 2 НТ.007.001.003</t>
+  </si>
+  <si>
+    <t>Кран шаровый штуцерно-ниппельный ЗАРД 025.040.30-03.P</t>
+  </si>
+  <si>
+    <t>Магнит ПСМНТ.001.021.001</t>
+  </si>
+  <si>
+    <t>Манометр МП-4У-6 МПа</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-80-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка БУИ7.840.013-01</t>
+  </si>
+  <si>
+    <t>Прокладка медная 8х11-II ГОСТ 19752-84</t>
+  </si>
+  <si>
+    <t>Прокладка ПСМНТ.001.000.018</t>
+  </si>
+  <si>
+    <t>Пружина №467 НТ.200.000.029.0</t>
+  </si>
+  <si>
+    <t>2-х вентильный клапанный блок КБ-2х40.01(M20x1,5Н,M20x1,5B; M14x1,5B)</t>
+  </si>
+  <si>
+    <t>Вентиль манометрический ВПЭМ 5х35 1/2-В М20х1,5-В</t>
+  </si>
+  <si>
+    <t>Кольцо 014-018-25 ГОСТ 9833-73 (фторкаучук)</t>
+  </si>
+  <si>
+    <t>Кольцо 016-020-25-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 018-021-19 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 020-025-30-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 040-048-46-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 048-054-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 055-060-30-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Пружина крышки НТ.200.004.003.0</t>
+  </si>
+  <si>
+    <t>Пружина НТ.3.02.00.00.002-01</t>
+  </si>
+  <si>
+    <t>Паронит ПОН 2,0 ГОСТ 481-80 (кг)</t>
+  </si>
+  <si>
+    <t>Паронит ПОН-Б 1мм /кг/</t>
+  </si>
+  <si>
+    <t>Полиамид D130 П-12Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Полиамид D20 П-12Б-20  ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Полиамид D40 ПА-6-210КС ОСТ6-11-498-79</t>
+  </si>
+  <si>
+    <t>Полиамид D50 П-12Б-20 ТУ 6-05-898-73</t>
+  </si>
+  <si>
+    <t>Полиамид D70 П-12Б-20 ТУ 6-05-898-73</t>
+  </si>
+  <si>
+    <t>Полиамид D80 П-12Б-20 ТУ  6-05-988-87</t>
+  </si>
+  <si>
+    <t>Полиамид D80 П-12Б-20 ТУ 6-05-988-87</t>
+  </si>
+  <si>
+    <t>Фторопласт Ф-4 пластина 2,0мм</t>
+  </si>
+  <si>
+    <t>Фторопласт Ф-4 ПН 1 ГОСТ 24222-80</t>
+  </si>
+  <si>
+    <t>Отвердитель ПЭПА</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -432,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -451,9 +483,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -803,13 +832,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -821,7 +850,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -839,8 +868,8 @@
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="8" t="s">
-        <v>50</v>
+      <c r="C2" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="D2" s="5">
         <v>11</v>
@@ -857,17 +886,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
+      <c r="C3" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="D3" s="5">
-        <v>11</v>
+        <v>23.43</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -875,17 +904,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="8" t="s">
-        <v>51</v>
+      <c r="C4" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="D4" s="5">
-        <v>11</v>
+        <v>7.48</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -893,17 +922,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="8" t="s">
-        <v>52</v>
+      <c r="C5" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D5" s="5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -911,17 +940,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="8" t="s">
-        <v>53</v>
+      <c r="C6" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="D6" s="5">
-        <v>11</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -929,17 +958,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="8" t="s">
-        <v>54</v>
+      <c r="C7" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="D7" s="5">
-        <v>44.77</v>
+        <v>13</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -947,17 +976,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="8" t="s">
-        <v>55</v>
+      <c r="C8" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D8" s="5">
-        <v>119.57</v>
+        <v>120</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -965,17 +994,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="8" t="s">
-        <v>56</v>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D9" s="5">
-        <v>43.67</v>
+        <v>250</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -983,17 +1012,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="8" t="s">
-        <v>57</v>
+      <c r="C10" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="D10" s="5">
-        <v>13.145</v>
+        <v>10</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1001,17 +1030,17 @@
         <v>10</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="8" t="s">
-        <v>58</v>
+      <c r="C11" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="D11" s="5">
-        <v>8.0299999999999994</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1019,17 +1048,17 @@
         <v>11</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="8" t="s">
-        <v>59</v>
+      <c r="C12" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D12" s="5">
-        <v>65.34</v>
+        <v>300</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1037,17 +1066,17 @@
         <v>12</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="5">
         <v>60</v>
       </c>
-      <c r="D13" s="5">
-        <v>72.27</v>
-      </c>
       <c r="E13" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1055,17 +1084,17 @@
         <v>13</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1886.06</v>
+      <c r="C14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="5">
+        <v>30</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1073,17 +1102,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="8" t="s">
-        <v>62</v>
+      <c r="C15" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D15" s="5">
-        <v>18.260000000000002</v>
+        <v>10</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1091,17 +1120,17 @@
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="8" t="s">
-        <v>63</v>
+      <c r="C16" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="D16" s="5">
-        <v>15.62</v>
+        <v>50</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1109,17 +1138,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="8" t="s">
-        <v>64</v>
+      <c r="C17" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D17" s="5">
-        <v>6.93</v>
+        <v>50</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1127,14 +1156,14 @@
         <v>17</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="8" t="s">
-        <v>65</v>
+      <c r="C18" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D18" s="5">
-        <v>8.7999999999999995E-2</v>
+        <v>50</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>13</v>
@@ -1145,14 +1174,14 @@
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="8" t="s">
-        <v>66</v>
+      <c r="C19" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D19" s="5">
-        <v>7.48</v>
+        <v>50</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>13</v>
@@ -1163,14 +1192,14 @@
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="8" t="s">
-        <v>67</v>
+      <c r="C20" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="D20" s="5">
-        <v>23.43</v>
+        <v>50</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>13</v>
@@ -1181,107 +1210,107 @@
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="8" t="s">
-        <v>68</v>
+      <c r="C21" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D21" s="5">
+        <v>50</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="8" t="s">
-        <v>69</v>
+      <c r="C22" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="D22" s="5">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="5">
+        <v>4</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="5">
-        <v>250</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="8" t="s">
-        <v>70</v>
+      <c r="C24" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="D24" s="5">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="8" t="s">
-        <v>71</v>
+      <c r="C25" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="D25" s="5">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="8" t="s">
-        <v>72</v>
+      <c r="C26" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="D26" s="5">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1289,179 +1318,179 @@
         <v>26</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="8" t="s">
-        <v>73</v>
+      <c r="C27" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="5">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="8" t="s">
-        <v>74</v>
+      <c r="C28" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="D28" s="5">
-        <v>10</v>
+        <v>17.62</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4"/>
-      <c r="C29" s="8" t="s">
-        <v>75</v>
+      <c r="C29" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="D29" s="5">
-        <v>10</v>
+        <v>1.62</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="C30" s="8" t="s">
-        <v>76</v>
+      <c r="C30" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="D30" s="5">
-        <v>50</v>
+        <v>2.09</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="8" t="s">
-        <v>77</v>
+      <c r="C31" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="D31" s="5">
-        <v>50</v>
+        <v>3.53</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="C32" s="8" t="s">
-        <v>78</v>
+      <c r="C32" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D32" s="5">
-        <v>50</v>
+        <v>4.41</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="C33" s="8" t="s">
-        <v>79</v>
+      <c r="C33" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="D33" s="5">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="C34" s="8" t="s">
-        <v>80</v>
+      <c r="C34" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="D34" s="5">
-        <v>10</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="4"/>
-      <c r="C35" s="8" t="s">
-        <v>81</v>
+      <c r="C35" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="D35" s="5">
-        <v>50</v>
+        <v>1.3</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="4"/>
-      <c r="C36" s="8" t="s">
-        <v>82</v>
+      <c r="C36" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="D36" s="5">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1469,89 +1498,89 @@
         <v>36</v>
       </c>
       <c r="B37" s="4"/>
-      <c r="C37" s="8" t="s">
-        <v>19</v>
+      <c r="C37" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="D37" s="5">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="8" t="s">
-        <v>20</v>
+      <c r="C38" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="D38" s="5">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" s="4"/>
-      <c r="C39" s="8" t="s">
-        <v>22</v>
+      <c r="C39" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="D39" s="5">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="8" t="s">
-        <v>23</v>
+      <c r="C40" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D40" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" s="4"/>
-      <c r="C41" s="8" t="s">
-        <v>24</v>
+      <c r="C41" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D41" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1559,35 +1588,35 @@
         <v>41</v>
       </c>
       <c r="B42" s="4"/>
-      <c r="C42" s="8" t="s">
-        <v>25</v>
+      <c r="C42" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D42" s="5">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="4"/>
-      <c r="C43" s="8" t="s">
-        <v>83</v>
+      <c r="C43" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D43" s="5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1595,233 +1624,233 @@
         <v>43</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="C44" s="8" t="s">
-        <v>84</v>
+      <c r="C44" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D44" s="5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4"/>
-      <c r="C45" s="8" t="s">
-        <v>85</v>
+      <c r="C45" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="D45" s="5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
       <c r="B46" s="4"/>
-      <c r="C46" s="8" t="s">
-        <v>86</v>
+      <c r="C46" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="D46" s="5">
-        <v>13</v>
+        <v>0.17</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46</v>
       </c>
       <c r="B47" s="4"/>
-      <c r="C47" s="8" t="s">
-        <v>87</v>
+      <c r="C47" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="D47" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="C48" s="8" t="s">
-        <v>88</v>
+      <c r="C48" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="D48" s="5">
-        <v>4.41</v>
+        <v>4</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>48</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="C49" s="8" t="s">
-        <v>89</v>
+      <c r="C49" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="D49" s="5">
-        <v>3.53</v>
+        <v>1</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="4"/>
-      <c r="C50" s="8" t="s">
-        <v>90</v>
+      <c r="C50" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="D50" s="5">
-        <v>2.09</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" s="4"/>
-      <c r="C51" s="8" t="s">
-        <v>91</v>
+      <c r="C51" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D51" s="5">
-        <v>1.62</v>
+        <v>14</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="4"/>
-      <c r="C52" s="8" t="s">
-        <v>92</v>
+      <c r="C52" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="D52" s="5">
-        <v>17.62</v>
+        <v>4</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
       <c r="B53" s="4"/>
-      <c r="C53" s="8" t="s">
-        <v>93</v>
+      <c r="C53" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D53" s="5">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
       <c r="B54" s="4"/>
-      <c r="C54" s="8" t="s">
-        <v>94</v>
+      <c r="C54" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D54" s="5">
-        <v>2.4500000000000002</v>
+        <v>4</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>54</v>
       </c>
       <c r="B55" s="4"/>
-      <c r="C55" s="8" t="s">
-        <v>95</v>
+      <c r="C55" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D55" s="5">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="4"/>
-      <c r="C56" s="8" t="s">
-        <v>96</v>
+      <c r="C56" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="D56" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1829,17 +1858,17 @@
         <v>56</v>
       </c>
       <c r="B57" s="4"/>
-      <c r="C57" s="8" t="s">
-        <v>97</v>
+      <c r="C57" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="D57" s="5">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1847,17 +1876,17 @@
         <v>57</v>
       </c>
       <c r="B58" s="4"/>
-      <c r="C58" s="8" t="s">
-        <v>98</v>
+      <c r="C58" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="D58" s="5">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1865,17 +1894,17 @@
         <v>58</v>
       </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="8" t="s">
-        <v>99</v>
+      <c r="C59" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="D59" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1883,17 +1912,17 @@
         <v>59</v>
       </c>
       <c r="B60" s="4"/>
-      <c r="C60" s="8" t="s">
-        <v>33</v>
+      <c r="C60" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="D60" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1901,17 +1930,17 @@
         <v>60</v>
       </c>
       <c r="B61" s="4"/>
-      <c r="C61" s="8" t="s">
-        <v>100</v>
+      <c r="C61" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="D61" s="5">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1919,17 +1948,17 @@
         <v>61</v>
       </c>
       <c r="B62" s="4"/>
-      <c r="C62" s="8" t="s">
-        <v>101</v>
+      <c r="C62" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="D62" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1937,17 +1966,17 @@
         <v>62</v>
       </c>
       <c r="B63" s="4"/>
-      <c r="C63" s="8" t="s">
-        <v>102</v>
+      <c r="C63" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="D63" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1955,8 +1984,8 @@
         <v>63</v>
       </c>
       <c r="B64" s="4"/>
-      <c r="C64" s="8" t="s">
-        <v>103</v>
+      <c r="C64" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="D64" s="5">
         <v>2</v>
@@ -1965,7 +1994,7 @@
         <v>6</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1973,29 +2002,29 @@
         <v>64</v>
       </c>
       <c r="B65" s="4"/>
-      <c r="C65" s="8" t="s">
-        <v>104</v>
+      <c r="C65" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="4"/>
-      <c r="C66" s="8" t="s">
-        <v>105</v>
+      <c r="C66" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>6</v>
@@ -2004,40 +2033,40 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>66</v>
       </c>
       <c r="B67" s="4"/>
-      <c r="C67" s="8" t="s">
-        <v>37</v>
+      <c r="C67" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="D67" s="5">
         <v>1</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
-      <c r="C68" s="8" t="s">
-        <v>40</v>
+      <c r="C68" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="D68" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2045,17 +2074,17 @@
         <v>68</v>
       </c>
       <c r="B69" s="4"/>
-      <c r="C69" s="8" t="s">
-        <v>106</v>
+      <c r="C69" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="D69" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2063,17 +2092,17 @@
         <v>69</v>
       </c>
       <c r="B70" s="4"/>
-      <c r="C70" s="8" t="s">
-        <v>107</v>
+      <c r="C70" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="D70" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2081,17 +2110,17 @@
         <v>70</v>
       </c>
       <c r="B71" s="4"/>
-      <c r="C71" s="8" t="s">
-        <v>108</v>
+      <c r="C71" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2099,17 +2128,17 @@
         <v>71</v>
       </c>
       <c r="B72" s="4"/>
-      <c r="C72" s="8" t="s">
-        <v>109</v>
+      <c r="C72" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D72" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2117,8 +2146,8 @@
         <v>72</v>
       </c>
       <c r="B73" s="4"/>
-      <c r="C73" s="8" t="s">
-        <v>110</v>
+      <c r="C73" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="D73" s="5">
         <v>2</v>
@@ -2127,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2135,17 +2164,17 @@
         <v>73</v>
       </c>
       <c r="B74" s="4"/>
-      <c r="C74" s="8" t="s">
-        <v>42</v>
+      <c r="C74" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="D74" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2153,17 +2182,17 @@
         <v>74</v>
       </c>
       <c r="B75" s="4"/>
-      <c r="C75" s="8" t="s">
-        <v>44</v>
+      <c r="C75" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="D75" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2171,35 +2200,35 @@
         <v>75</v>
       </c>
       <c r="B76" s="4"/>
-      <c r="C76" s="8" t="s">
-        <v>45</v>
+      <c r="C76" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="D76" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>76</v>
       </c>
       <c r="B77" s="4"/>
-      <c r="C77" s="8" t="s">
-        <v>46</v>
+      <c r="C77" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2207,53 +2236,413 @@
         <v>77</v>
       </c>
       <c r="B78" s="4"/>
-      <c r="C78" s="8" t="s">
-        <v>111</v>
+      <c r="C78" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="D78" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>78</v>
       </c>
       <c r="B79" s="4"/>
-      <c r="C79" s="8" t="s">
-        <v>112</v>
+      <c r="C79" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="D79" s="5">
-        <v>375</v>
+        <v>4</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>79</v>
       </c>
       <c r="B80" s="4"/>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D80" s="5">
+        <v>2</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" s="5">
+        <v>8</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D82" s="5">
+        <v>4</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D83" s="5">
+        <v>8</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D84" s="5">
+        <v>4</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D85" s="5">
+        <v>1</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D86" s="5">
+        <v>1</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" s="5">
+        <v>1</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4"/>
+      <c r="C88" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D80" s="5">
-        <v>250</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>49</v>
+      <c r="D88" s="5">
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="3">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4"/>
+      <c r="C89" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="3">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="C90" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D90" s="5">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="3">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4"/>
+      <c r="C91" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D91" s="5">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="3">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4"/>
+      <c r="C92" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D92" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="3">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4"/>
+      <c r="C93" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D93" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="3">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4"/>
+      <c r="C94" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="3">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D95" s="5">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="3">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" s="5">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="3">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4"/>
+      <c r="C97" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D97" s="5">
+        <v>2E-3</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="3">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D98" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="3">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D100" s="5">
+        <v>54</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Desktop\ruAstro\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E261F7C5-61A2-484D-93D7-88FAD4A52AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96ED0C70-2E18-488A-AA47-4777B29CD92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3720" yWindow="2235" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="215">
   <si>
     <t>№ п/п</t>
   </si>
@@ -45,90 +45,640 @@
     <t>Примечание</t>
   </si>
   <si>
+    <t>Плоскошлифовальный станок PLC USG 2063NC2, раб.стол 200х630</t>
+  </si>
+  <si>
+    <t>шт</t>
+  </si>
+  <si>
+    <t>ЛГУП-7246</t>
+  </si>
+  <si>
     <t>Станок лазерный резки B-power F3015 3000W, размер раб.стола 1500х3000,1500кг, скор. 2G</t>
   </si>
   <si>
-    <t>шт</t>
-  </si>
-  <si>
-    <t>ЛГУП-7246</t>
-  </si>
-  <si>
-    <t>Плоскошлифовальный станок PLC USG 2063NC2, раб.стол 200х630</t>
-  </si>
-  <si>
-    <t>Защитное стекло D18*2мм</t>
+    <t>Шайба М5 плоская увелич.цинк</t>
   </si>
   <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>ЛГУП-7254</t>
-  </si>
-  <si>
-    <t>Фокусирующая линза D20F800 СТ4,5мм (очистка)</t>
-  </si>
-  <si>
-    <t>Фокусирующая линза D20F150 СТ4,5мм (сварка)</t>
-  </si>
-  <si>
-    <t>Коллиматорная линза D16F60 СТ5,0мм (сварка)</t>
-  </si>
-  <si>
-    <t>Держатель сопла W-FT80 (трубка со шкалой) H80 d12 M16</t>
-  </si>
-  <si>
-    <t>Держатель сопла W-FT125 (трубка со шкалой) H125 d12 M16</t>
-  </si>
-  <si>
-    <t>Сопло для резки WNSUP-26 M16 (Тип-CUT)</t>
-  </si>
-  <si>
-    <t>Сопло направляющее WNR-17-12 1,2мм (Тип SS-004-012)</t>
-  </si>
-  <si>
-    <t>Уплотнительное кольцо для защитного стекла 21*15*2,7*2,2мм (артикул WR-21)</t>
-  </si>
-  <si>
-    <t>Зажимная гайка W-LN-SUP</t>
+    <t>ЛГУП-7271</t>
+  </si>
+  <si>
+    <t>Болт М5 (с внутр.шестигранником)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7273</t>
+  </si>
+  <si>
+    <t>ЛГУП-7276</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>Труба гофрированная ПВХ 16 мм с протяжкой</t>
+  </si>
+  <si>
+    <t>мм</t>
+  </si>
+  <si>
+    <t>Розетка 220 В IP55</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8</t>
+  </si>
+  <si>
+    <t>Настроечный образец НО Хордовый сталь (57х6, СП станд. в компл. с ПЭП, Ст.20,  Калибровка, Паспорт)</t>
+  </si>
+  <si>
+    <t>НТУП-017954</t>
+  </si>
+  <si>
+    <t>Настроечный образец НО Хордовый сталь (89х6, СП станд. в компл. с ПЭП, Ст.20,  Калибровка, Паспорт)</t>
+  </si>
+  <si>
+    <t>Настроечный образец НО зарубка-плоский (16-2,0х2,0, Ст.20, Калибровка, Паспорт)</t>
+  </si>
+  <si>
+    <t>Настроечный образец НО зарубка-плоский (14-2,0х2,0, Ст.20, Калибровка, Паспорт)</t>
+  </si>
+  <si>
+    <t>Настроечный образец НО зарубка-плоский (12-2,0х2,0, Ст.20, Калибровка, Паспорт)</t>
+  </si>
+  <si>
+    <t>Комплект мер СО-2 и СО-3 в соответствии с ГОСТ Р 55724-2013</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>ЛГУП-7282</t>
+  </si>
+  <si>
+    <t>л (дм3)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7283</t>
   </si>
   <si>
     <t>кг</t>
   </si>
   <si>
-    <t>ЛГУП-7266</t>
-  </si>
-  <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+    <t>ЛГУП-7284</t>
+  </si>
+  <si>
+    <t>Круг D165 09Г2С-8-ТО ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист S=0.5*300*600 Алюминий аннодированный матовый 2033-1 (черн/бел)</t>
+  </si>
+  <si>
+    <t>Лист S=8 ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>ЛГУП-7286</t>
+  </si>
+  <si>
+    <t>ЛГУП-7287</t>
+  </si>
+  <si>
+    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>ЛГУП-7289</t>
+  </si>
+  <si>
+    <t>ЛГУП-7297</t>
+  </si>
+  <si>
+    <t>Метчик М6х1-6Н машинно-ручной HSS-E VAP (глухой) DIN371</t>
+  </si>
+  <si>
+    <t>Гайка с насечкой М6 СМ100600</t>
+  </si>
+  <si>
+    <t>Гайка с насечкой, препятствующей откручиванию М8 арт. СМ100800</t>
+  </si>
+  <si>
+    <t>Гайка М5 для клеммных коробок</t>
+  </si>
+  <si>
+    <t>Болт оцинкованный, с частичной резьбой (М8х60) арт.СМ020870</t>
+  </si>
+  <si>
+    <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт. СМ 030508</t>
+  </si>
+  <si>
+    <t>Винт с квадратным подголовником ( М 6 х 10) -  арт. CM010610</t>
+  </si>
+  <si>
+    <t>Карта proximity стандартная ST-PC010EM</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внутренний CS 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Угол внутренний 10603 Legrand DPL</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Уплотнительная жировая смазка марки МКС, 50мл</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Электроконвектор с терморегулятором ЭВНБ 1кВт, 220В, 50 Гц.</t>
+  </si>
+  <si>
+    <t>Извещатель магнитоконтактный Smartec ST-DM146 IP66</t>
+  </si>
+  <si>
+    <t>Извещатель охранный точечный магнитоконтактный взрывозащ.И0102 В3 АТОН исп.21Ч СМД0000000490СМД</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный дымовой ИП-212-141</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный ручной взрывозащищенный ИП 535-07е 1ExdbIICT6Gb, IP67</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный ручной ИПР 535-25Г IP67</t>
+  </si>
+  <si>
+    <t>Кабель-канал 10453 Legrand DLP 195x65 (2м)</t>
+  </si>
+  <si>
+    <t>Кольцевой изолир. наконечник 4-6мм2 под винт М6</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Консоль с опорой ML 300мм (шт)</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х25(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р402(-60+40)2-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р403(-60+40) 2-3х20НК(А)-3х20НК(С)-4х10(П),1ЕхеLLCGbXT6, ip66, 160х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка распаячная КМ41242 IP55</t>
+  </si>
+  <si>
+    <t>Коробка соединительная К-СП 08.08.08</t>
+  </si>
+  <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Крышка (100х15х3000)</t>
+  </si>
+  <si>
+    <t>Крышка (50 х 15 х 3000) арт. 35520</t>
+  </si>
+  <si>
+    <t>Крышка (50х15х3000)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внешний CD 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 19-20</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>Светильник ЭРА SPB-202-0-40K-012 IP65 12Вт</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Разделитль 10582 Legrand DPL 50х80/105/150 (2м)</t>
+  </si>
+  <si>
+    <t>Профиль PSM (3000) арт. 34181</t>
+  </si>
+  <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
+  </si>
+  <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-15 IP65 2ExеdIIСТ6</t>
+  </si>
+  <si>
+    <t>Пост аварийной сигнализации загазованности в/защ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
+  </si>
+  <si>
+    <t>Пластина для заземления PTCE арт. 37501</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 120</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 4.1.1</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 2.1.1</t>
+  </si>
+  <si>
+    <t>Оповещатель светозвуковой Маяк-24К IP53</t>
+  </si>
+  <si>
+    <t>Оповещатель светозвуковой взрывозащ. ВС-07е-И 1ExdIICT6, IP66, 12-24В, -60..+70С</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный ТМЛ 25-8-7</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 4.1.1</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 2.1.1</t>
+  </si>
+  <si>
+    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
+  </si>
+  <si>
+    <t>Металлический лоток, неперфорированный (100х50х3000)</t>
+  </si>
+  <si>
+    <t>Металлический лоток , неперфорированный (50 х 50 х 3000) арт. 35020</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внутренний CS 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внешний CD90 (100х50)</t>
+  </si>
+  <si>
+    <t>Светильник взрывозащищенный ДБП 09-15-002 УХЛ1 ExdllBT6G IP65</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 2 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Заглушка для кабельных вводов M20</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт,Matrix-II IP20</t>
+  </si>
+  <si>
+    <t>Профиль PSM 3000</t>
+  </si>
+  <si>
+    <t>Трубка 305 ТВ-40-12 ГОСТ 19034-82</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМОУ d6-7 PR13.02394</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р405(-60+40)2-4х20НК(А)-4х20НК(С)-4х20(П), 1ЕхеLLCGbXT6, ip66, 190х75х75</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+  </si>
+  <si>
+    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 40х40 мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 100х60</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-FRLS 3х1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 2х2х0,75 d7,1мм</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Трубка ПВХ гибкая, гофрированная 16 мм</t>
+  </si>
+  <si>
+    <t>Трубка 305 ТВ-40-3,5 ГОСТ 19034-82</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
+  </si>
+  <si>
+    <t>Заглушка 10707 Legrand DPL 65х195</t>
+  </si>
+  <si>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
+  </si>
+  <si>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
+  </si>
+  <si>
+    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка к кабель-каналу 180мм (2м)10526 Legrand DLP</t>
+  </si>
+  <si>
+    <t>Отвод 90-159х10-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 45-89х8-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Растворитель Р-4 ГОСТ 7827-74</t>
+  </si>
+  <si>
+    <t>Разбавитель Procore Universal Thinner</t>
+  </si>
+  <si>
+    <t>Кольцо 020-025-30-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Краска-спрей SABOTAGE (желтая)</t>
+  </si>
+  <si>
+    <t>Краска-спрей SABOTAGE (красная)</t>
+  </si>
+  <si>
+    <t>Краска-спрей SABOTAGE 39(черный)</t>
+  </si>
+  <si>
+    <t>Грунт-эмаль PROCOAT AP 259 SC™ RAL 3020 (красный)</t>
+  </si>
+  <si>
+    <t>Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
+  </si>
+  <si>
+    <t>Грунт-эмаль Дюропокс ДТМ 80 (внутрянка)</t>
+  </si>
+  <si>
+    <t>Круг D32 Ст.20 ГОСТ1050-88</t>
+  </si>
+  <si>
+    <t>Круг D450 Ст.09Г2С ГОСТ 2590-2006</t>
+  </si>
+  <si>
+    <t>Круг D60 09Г2С-4 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист S=1 ст.09Г2С ГОСТ16523-89</t>
+  </si>
+  <si>
+    <t>Лист S=1 ст.3 ГОСТ16523-89</t>
+  </si>
+  <si>
+    <t>Лист S=12 ст.3 ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Лист S=2 ОК360В-4-III-Ст.3кп ГОСТ 16523-97</t>
+  </si>
+  <si>
+    <t>Лист S=4 ст.09Г2С ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Лист S=4 ст.3пс ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Лист S=6 Ст.3кп2 ГОСт 14637-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-12 ГОСТ 19903-74 / Ст. 09Г2С К52 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-4,0 ГОСТ 19903-74 / Ст.3пс4 ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-8,0 ГОСТ 19903-74/ Ст.3 ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Круг D40 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D32 30Х13 ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Круг ДКРН D48 НД БрАЖ9-4 ГОСТ 1628-78</t>
+  </si>
+  <si>
+    <t>Круг D240 ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг D22 Ст.3 ГОСТ 380-88</t>
+  </si>
+  <si>
+    <t>Круг D22 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D160 Ст.3 ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Круг D16 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D10 ГОСТ 2590-2006/ Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Днище 219х4-25 ст.20 ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 377-12-16ГС ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Уголок 40х40х3 ГОСТ 8509-93/ Ст3пс ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
+  </si>
+  <si>
+    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D34х4 Ст.09Г2С ГОСТ8733-75</t>
+  </si>
+  <si>
+    <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
+  </si>
+  <si>
+    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
   </si>
   <si>
     <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D89х10 ГОСТ 8732-78 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D45х9 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D34х4 Ст.09Г2С ГОСТ8733-75</t>
-  </si>
-  <si>
-    <t>Труба D25х3 09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Труба D57х6 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D89х12 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D720х12 Ст.09Г2С-К50 ГОСТ 20295-85</t>
+  </si>
+  <si>
+    <t>Труба D377х12 ст.09Г2С-К50 ГОСТ 8731-78</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 30.Ст3сп3.II.4.019 ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>Шайба 16 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Шайба 12 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Заклепка 4х8.31 ГОСТ 10299-80</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Болт М10-6gх35.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Гайка АМ30-6Н.20.III.4.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх40.58 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх16 56.35.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Сверло ГОСТ 10902-77 Ц/Х Ø5,2 Р6М5К5</t>
+  </si>
+  <si>
+    <t>Сверло ГОСТ 10902-77 Ц/Х Ø5,4 Р6М5К5</t>
+  </si>
+  <si>
+    <t>Сверло ГОСТ 10902-77 Ц/Х Ø5,3 Р6М5К5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -185,7 +735,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -204,6 +754,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -553,13 +1106,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -571,7 +1124,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -584,12 +1137,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5">
@@ -602,12 +1155,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="5">
@@ -620,16 +1173,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>11</v>
@@ -638,91 +1191,91 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="7" t="s">
-        <v>13</v>
+      <c r="C5" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="D5" s="5">
-        <v>5</v>
+        <v>240</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="7" t="s">
-        <v>14</v>
+      <c r="C6" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="D6" s="5">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="7" t="s">
-        <v>15</v>
+      <c r="C7" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="D7" s="5">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="7" t="s">
-        <v>16</v>
+      <c r="C8" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
+      <c r="C9" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="D9" s="5">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>12</v>
@@ -733,53 +1286,53 @@
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="7" t="s">
-        <v>18</v>
+      <c r="C10" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D10" s="5">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="7" t="s">
-        <v>19</v>
+      <c r="C11" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="D11" s="5">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="7" t="s">
-        <v>20</v>
+      <c r="C12" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D12" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -787,17 +1340,17 @@
         <v>12</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="7" t="s">
-        <v>21</v>
+      <c r="C13" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="D13" s="5">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -805,17 +1358,17 @@
         <v>13</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="7" t="s">
-        <v>24</v>
+      <c r="C14" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="D14" s="5">
-        <v>43.67</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -823,17 +1376,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="7" t="s">
-        <v>25</v>
+      <c r="C15" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="D15" s="5">
-        <v>19.440000000000001</v>
+        <v>16</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -841,17 +1394,17 @@
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="7" t="s">
-        <v>26</v>
+      <c r="C16" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="D16" s="5">
-        <v>909.38</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -859,17 +1412,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="7" t="s">
-        <v>27</v>
+      <c r="C17" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="D17" s="5">
-        <v>0.21</v>
+        <v>16</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -877,17 +1430,17 @@
         <v>17</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="7" t="s">
-        <v>28</v>
+      <c r="C18" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="D18" s="5">
-        <v>0.47</v>
+        <v>32</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -895,17 +1448,17 @@
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="7" t="s">
-        <v>29</v>
+      <c r="C19" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="D19" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -913,17 +1466,17 @@
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="7" t="s">
-        <v>30</v>
+      <c r="C20" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="D20" s="5">
-        <v>2.85</v>
+        <v>120</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -931,17 +1484,17 @@
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="7" t="s">
-        <v>31</v>
+      <c r="C21" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="D21" s="5">
-        <v>3.19</v>
+        <v>24</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -949,17 +1502,3059 @@
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="5">
+        <v>8</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="5">
+        <v>4</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="5">
+        <v>8</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="5">
+        <v>12</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="5">
+        <v>4</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="5">
+        <v>4</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="5">
+        <v>32</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="5">
+        <v>280</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="5">
+        <v>8</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="D22" s="5">
-        <v>13.42</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="5">
+        <v>56</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="5">
+        <v>3</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="5">
+        <v>4</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="5">
+        <v>8</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="5">
+        <v>4</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="5">
+        <v>4</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="5">
+        <v>4</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="5">
+        <v>4</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" s="5">
+        <v>160</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="5">
+        <v>25</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="5">
+        <v>9</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="5">
+        <v>63</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" s="5">
+        <v>16</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" s="5">
+        <v>4</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D47" s="5">
+        <v>255</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" s="5">
+        <v>285</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" s="5">
+        <v>20</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="5">
+        <v>174</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="5">
+        <v>136</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="5">
+        <v>32</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="5">
+        <v>20</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="5">
+        <v>8</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" s="5">
+        <v>8</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="5">
+        <v>4</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57" s="5">
+        <v>100</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" s="5">
+        <v>28</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="5">
+        <v>4</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D60" s="5">
+        <v>4</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D61" s="5">
+        <v>4</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D62" s="5">
+        <v>4</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D63" s="5">
+        <v>32</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D64" s="5">
+        <v>4</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D65" s="5">
+        <v>4</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" s="5">
+        <v>63</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D67" s="5">
+        <v>25</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D68" s="5">
+        <v>9</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D69" s="5">
+        <v>32</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D70" s="5">
+        <v>16</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D71" s="5">
+        <v>16</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" s="5">
+        <v>32</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D73" s="5">
+        <v>16</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" s="5">
+        <v>24</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D75" s="5">
+        <v>9</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D76" s="5">
+        <v>63</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D77" s="5">
+        <v>18</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D78" s="5">
+        <v>4</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="5">
+        <v>30</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D80" s="5">
+        <v>8</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="7">
+        <v>60000</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D82" s="5">
+        <v>225</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" s="5">
+        <v>4</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D84" s="5">
+        <v>508</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D85" s="5">
+        <v>520</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D86" s="5">
+        <v>8.4</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D87" s="5">
+        <v>32</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4"/>
+      <c r="C88" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D88" s="5">
+        <v>8</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="3">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4"/>
+      <c r="C89" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D89" s="5">
+        <v>24</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="3">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="C90" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D90" s="5">
+        <v>64</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="3">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4"/>
+      <c r="C91" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D91" s="5">
+        <v>52</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="3">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4"/>
+      <c r="C92" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D92" s="5">
+        <v>68</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="3">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4"/>
+      <c r="C93" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D93" s="5">
+        <v>7</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="3">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4"/>
+      <c r="C94" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D94" s="5">
+        <v>140</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="3">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D95" s="5">
+        <v>24</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="3">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D96" s="5">
+        <v>340.6</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="3">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4"/>
+      <c r="C97" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D97" s="5">
+        <v>34</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="3">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D98" s="5">
+        <v>112</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="3">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D99" s="5">
+        <v>160</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D100" s="5">
+        <v>60</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="3">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D101" s="5">
+        <v>120</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="3">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D102" s="5">
+        <v>16</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="3">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4"/>
+      <c r="C103" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D103" s="5">
+        <v>160</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="3">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D104" s="5">
+        <v>8</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="3">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4"/>
+      <c r="C105" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D105" s="5">
+        <v>200</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="3">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4"/>
+      <c r="C106" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D106" s="5">
+        <v>4</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="3">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4"/>
+      <c r="C107" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D107" s="5">
+        <v>4</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="3">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4"/>
+      <c r="C108" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D108" s="5">
+        <v>4</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="3">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4"/>
+      <c r="C109" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D109" s="5">
+        <v>16</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="3">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4"/>
+      <c r="C110" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="5">
+        <v>16</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="3">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4"/>
+      <c r="C111" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="5">
+        <v>12</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="3">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4"/>
+      <c r="C112" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D112" s="5">
+        <v>280</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="3">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D113" s="5">
+        <v>32</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="3">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D114" s="5">
+        <v>32</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="3">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="D115" s="5">
+        <v>1</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="3">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D116" s="5">
+        <v>1</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="3">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D117" s="5">
+        <v>1</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4"/>
+      <c r="C118" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D118" s="5">
+        <v>1</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="3">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D119" s="5">
+        <v>1</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4"/>
+      <c r="C120" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D120" s="5">
+        <v>1</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="3">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4"/>
+      <c r="C121" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D121" s="5">
+        <v>15</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="3">
+        <v>121</v>
+      </c>
+      <c r="B122" s="4"/>
+      <c r="C122" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D122" s="5">
+        <v>15</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="3">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4"/>
+      <c r="C123" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D123" s="5">
+        <v>22.5</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="3">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4"/>
+      <c r="C124" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D124" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="3">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4"/>
+      <c r="C125" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D125" s="5">
+        <v>120</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="3">
+        <v>125</v>
+      </c>
+      <c r="B126" s="4"/>
+      <c r="C126" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D126" s="5">
+        <v>60</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="3">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4"/>
+      <c r="C127" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D127" s="5">
+        <v>1</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="3">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4"/>
+      <c r="C128" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D128" s="5">
+        <v>4</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="3">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4"/>
+      <c r="C129" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D129" s="5">
+        <v>1</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="3">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4"/>
+      <c r="C130" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D130" s="5">
+        <v>6</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="3">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4"/>
+      <c r="C131" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D131" s="5">
+        <v>49.5</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="3">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4"/>
+      <c r="C132" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D132" s="5">
+        <v>102.75</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="3">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4"/>
+      <c r="C133" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D133" s="5">
+        <v>6</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="3">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4"/>
+      <c r="C134" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D134" s="5">
+        <v>837</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="3">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4"/>
+      <c r="C135" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D135" s="5">
+        <v>34.5</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="3">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4"/>
+      <c r="C136" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D136" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="3">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4"/>
+      <c r="C137" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D137" s="5">
+        <v>29.25</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="3">
+        <v>137</v>
+      </c>
+      <c r="B138" s="4"/>
+      <c r="C138" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D138" s="5">
+        <v>111</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="3">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4"/>
+      <c r="C139" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D139" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="3">
+        <v>139</v>
+      </c>
+      <c r="B140" s="4"/>
+      <c r="C140" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D140" s="5">
+        <v>406.5</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="3">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4"/>
+      <c r="C141" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D141" s="5">
+        <v>66</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="3">
+        <v>141</v>
+      </c>
+      <c r="B142" s="4"/>
+      <c r="C142" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D142" s="5">
+        <v>200.1</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="3">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4"/>
+      <c r="C143" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D143" s="7">
+        <v>1000</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="3">
+        <v>143</v>
+      </c>
+      <c r="B144" s="4"/>
+      <c r="C144" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D144" s="5">
+        <v>795.6</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="3">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4"/>
+      <c r="C145" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D145" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="3">
+        <v>145</v>
+      </c>
+      <c r="B146" s="4"/>
+      <c r="C146" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D146" s="5">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="3">
+        <v>146</v>
+      </c>
+      <c r="B147" s="4"/>
+      <c r="C147" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D147" s="5">
+        <v>43.5</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="3">
+        <v>147</v>
+      </c>
+      <c r="B148" s="4"/>
+      <c r="C148" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D148" s="5">
+        <v>137.55000000000001</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="3">
+        <v>148</v>
+      </c>
+      <c r="B149" s="4"/>
+      <c r="C149" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D149" s="5">
+        <v>20.7</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="3">
+        <v>149</v>
+      </c>
+      <c r="B150" s="4"/>
+      <c r="C150" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D150" s="5">
+        <v>495.15</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="3">
+        <v>150</v>
+      </c>
+      <c r="B151" s="4"/>
+      <c r="C151" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D151" s="5">
+        <v>12</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="3">
+        <v>151</v>
+      </c>
+      <c r="B152" s="4"/>
+      <c r="C152" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D152" s="5">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="3">
+        <v>152</v>
+      </c>
+      <c r="B153" s="4"/>
+      <c r="C153" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D153" s="5">
+        <v>199.8</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="3">
+        <v>153</v>
+      </c>
+      <c r="B154" s="4"/>
+      <c r="C154" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D154" s="5">
+        <v>27</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="3">
+        <v>154</v>
+      </c>
+      <c r="B155" s="4"/>
+      <c r="C155" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D155" s="5">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="3">
+        <v>155</v>
+      </c>
+      <c r="B156" s="4"/>
+      <c r="C156" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D156" s="5">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="3">
+        <v>156</v>
+      </c>
+      <c r="B157" s="4"/>
+      <c r="C157" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D157" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="3">
+        <v>157</v>
+      </c>
+      <c r="B158" s="4"/>
+      <c r="C158" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D158" s="5">
+        <v>30</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="3">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4"/>
+      <c r="C159" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D159" s="5">
+        <v>30</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="3">
+        <v>159</v>
+      </c>
+      <c r="B160" s="4"/>
+      <c r="C160" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D160" s="5">
+        <v>30</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="3">
+        <v>160</v>
+      </c>
+      <c r="B161" s="4"/>
+      <c r="C161" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D161" s="5">
+        <v>48.6</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="3">
+        <v>161</v>
+      </c>
+      <c r="B162" s="4"/>
+      <c r="C162" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D162" s="5">
+        <v>97.8</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="3">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4"/>
+      <c r="C163" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D163" s="5">
+        <v>57.15</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="3">
+        <v>163</v>
+      </c>
+      <c r="B164" s="4"/>
+      <c r="C164" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D164" s="5">
+        <v>33.75</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="3">
+        <v>164</v>
+      </c>
+      <c r="B165" s="4"/>
+      <c r="C165" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D165" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="3">
+        <v>165</v>
+      </c>
+      <c r="B166" s="4"/>
+      <c r="C166" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D166" s="5">
+        <v>7.05</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="3">
+        <v>166</v>
+      </c>
+      <c r="B167" s="4"/>
+      <c r="C167" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D167" s="5">
+        <v>193.2</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="3">
+        <v>167</v>
+      </c>
+      <c r="B168" s="4"/>
+      <c r="C168" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D168" s="5">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="3">
+        <v>168</v>
+      </c>
+      <c r="B169" s="4"/>
+      <c r="C169" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D169" s="5">
+        <v>95.25</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="3">
+        <v>169</v>
+      </c>
+      <c r="B170" s="4"/>
+      <c r="C170" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D170" s="5">
+        <v>291.60000000000002</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="3">
+        <v>170</v>
+      </c>
+      <c r="B171" s="4"/>
+      <c r="C171" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D171" s="5">
+        <v>233.85</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="3">
+        <v>171</v>
+      </c>
+      <c r="B172" s="4"/>
+      <c r="C172" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D172" s="7">
+        <v>4500</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="3">
+        <v>172</v>
+      </c>
+      <c r="B173" s="4"/>
+      <c r="C173" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D173" s="5">
+        <v>47.85</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="3">
+        <v>173</v>
+      </c>
+      <c r="B174" s="4"/>
+      <c r="C174" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D174" s="7">
+        <v>2000</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="3">
+        <v>174</v>
+      </c>
+      <c r="B175" s="4"/>
+      <c r="C175" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D175" s="5">
+        <v>180</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="3">
+        <v>175</v>
+      </c>
+      <c r="B176" s="4"/>
+      <c r="C176" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D176" s="5">
+        <v>30</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="3">
+        <v>176</v>
+      </c>
+      <c r="B177" s="4"/>
+      <c r="C177" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D177" s="5">
+        <v>15</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="3">
+        <v>177</v>
+      </c>
+      <c r="B178" s="4"/>
+      <c r="C178" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D178" s="5">
+        <v>360</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="3">
+        <v>178</v>
+      </c>
+      <c r="B179" s="4"/>
+      <c r="C179" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D179" s="5">
+        <v>15</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="3">
+        <v>179</v>
+      </c>
+      <c r="B180" s="4"/>
+      <c r="C180" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D180" s="5">
+        <v>15</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="3">
+        <v>180</v>
+      </c>
+      <c r="B181" s="4"/>
+      <c r="C181" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D181" s="5">
+        <v>60</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="3">
+        <v>181</v>
+      </c>
+      <c r="B182" s="4"/>
+      <c r="C182" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D182" s="5">
+        <v>45</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="3">
+        <v>182</v>
+      </c>
+      <c r="B183" s="4"/>
+      <c r="C183" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D183" s="5">
+        <v>15</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="3">
+        <v>183</v>
+      </c>
+      <c r="B184" s="4"/>
+      <c r="C184" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D184" s="5">
+        <v>360</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="3">
+        <v>184</v>
+      </c>
+      <c r="B185" s="4"/>
+      <c r="C185" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D185" s="5">
+        <v>30</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="3">
+        <v>185</v>
+      </c>
+      <c r="B186" s="4"/>
+      <c r="C186" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D186" s="5">
+        <v>15</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="3">
+        <v>186</v>
+      </c>
+      <c r="B187" s="4"/>
+      <c r="C187" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D187" s="5">
+        <v>15</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="3">
+        <v>187</v>
+      </c>
+      <c r="B188" s="4"/>
+      <c r="C188" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D188" s="5">
+        <v>5</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="3">
+        <v>188</v>
+      </c>
+      <c r="B189" s="4"/>
+      <c r="C189" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D189" s="5">
+        <v>5</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="3">
+        <v>189</v>
+      </c>
+      <c r="B190" s="4"/>
+      <c r="C190" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D190" s="5">
+        <v>5</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="3">
+        <v>190</v>
+      </c>
+      <c r="B191" s="4"/>
+      <c r="C191" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D191" s="5">
+        <v>5</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFA5116-58C0-4442-BA36-B6572F240477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141D86CA-40BA-49E4-AB5C-5D264E776348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2235" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="126">
   <si>
     <t>№ п/п</t>
   </si>
@@ -45,42 +45,21 @@
     <t>Примечание</t>
   </si>
   <si>
+    <t>кг</t>
+  </si>
+  <si>
+    <t>ЛГУП-7287</t>
+  </si>
+  <si>
+    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>АС 30, Гидравл. тележка 3000 кг, 1150х550 мм, полиурет.колесо, двойные полиурет.ролики, цвет красный</t>
+  </si>
+  <si>
     <t>шт</t>
   </si>
   <si>
-    <t>ЛГУП-7276</t>
-  </si>
-  <si>
-    <t>Розетка 220 В IP55</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
-  </si>
-  <si>
-    <t>Держатель проводника Rd8</t>
-  </si>
-  <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>Труба гофрированная ПВХ 16 мм с протяжкой</t>
-  </si>
-  <si>
-    <t>мм</t>
-  </si>
-  <si>
-    <t>кг</t>
-  </si>
-  <si>
-    <t>ЛГУП-7287</t>
-  </si>
-  <si>
-    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>АС 30, Гидравл. тележка 3000 кг, 1150х550 мм, полиурет.колесо, двойные полиурет.ролики, цвет красный</t>
-  </si>
-  <si>
     <t>ЛГУП-7313</t>
   </si>
   <si>
@@ -96,268 +75,196 @@
     <t>ЛГУП-7319</t>
   </si>
   <si>
-    <t>ЛГУП-7320</t>
-  </si>
-  <si>
-    <t>Пластина для заземления PTCE арт. 37501</t>
-  </si>
-  <si>
-    <t>Пластина анкерная 120</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Кабель-канал 10453 Legrand DLP 195x65 (2м)</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный ручной ИПР 535-25Г IP67</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный ручной взрывозащищенный ИП 535-07е 1ExdbIICT6Gb, IP67</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный дымовой ИП-212-141</t>
-  </si>
-  <si>
-    <t>Извещатель охранный точечный магнитоконтактный взрывозащ.И0102 В3 АТОН исп.21Ч СМД0000000490СМД</t>
-  </si>
-  <si>
-    <t>Извещатель магнитоконтактный Smartec ST-DM146 IP66</t>
-  </si>
-  <si>
-    <t>Заглушка 10707 Legrand DPL 65х195</t>
-  </si>
-  <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>Выключатель двухклавишный IP55</t>
-  </si>
-  <si>
-    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
-  </si>
-  <si>
-    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 4.1.1</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 2.1.1</t>
-  </si>
-  <si>
-    <t>Оповещатель светозвуковой Маяк-24К IP53</t>
-  </si>
-  <si>
-    <t>Оповещатель светозвуковой взрывозащ. ВС-07е-И 1ExdIICT6, IP66, 12-24В, -60..+70С</t>
-  </si>
-  <si>
-    <t>Наконечник кабельный ТМЛ 25-8-7</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 4.1.1</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 2.1.1</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (100х50х3000)</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
-  </si>
-  <si>
-    <t>Металлический лоток , неперфорированный (50 х 50 х 3000) арт. 35020</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внутренний CS 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка на угол вертикальный внешний CD90 (100х50)</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка (50х15х3000)</t>
-  </si>
-  <si>
-    <t>Крышка (50 х 15 х 3000) арт. 35520</t>
-  </si>
-  <si>
-    <t>Крышка (100х15х3000)</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
-    <t>Коробка распаячная КМ41242 IP55</t>
-  </si>
-  <si>
-    <t>Консоль с опорой ML 300мм (шт)</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Кольцевой изолир. наконечник 4-6мм2 под винт М6</t>
-  </si>
-  <si>
-    <t>Электроконвектор с терморегулятором ЭВНБ 1кВт, 220В, 50 Гц.</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
-  </si>
-  <si>
-    <t>Уплотнительная жировая смазка марки МКС, 50мл</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Угол внутренний 10603 Legrand DPL</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внутренний CS 90 100 х 50мм</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внутренний CS 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внешний CD 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 19-20</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>Светильник ЭРА SPB-202-0-40K-012 IP65 12Вт</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Профиль PSM (3000) арт. 34181</t>
-  </si>
-  <si>
-    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
-  </si>
-  <si>
-    <t>Пост кнопочный взрывозащищенный ПВК-15 IP65 2ExеdIIСТ6</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт,Matrix-II IP20</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМОУ d6-7 PR13.02394</t>
-  </si>
-  <si>
-    <t>Светильник взрывозащищенный ДБП 09-15-002 УХЛ1 ExdllBT6G IP65</t>
-  </si>
-  <si>
-    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
-  </si>
-  <si>
-    <t>Клемма WAGO 222-415, 2 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
-  </si>
-  <si>
-    <t>Заглушка для кабельных вводов M20</t>
-  </si>
-  <si>
-    <t>Профиль PSM 3000</t>
-  </si>
-  <si>
-    <t>Трубка 305 ТВ-40-12 ГОСТ 19034-82</t>
-  </si>
-  <si>
-    <t>Пост аварийной сигнализации загазованности в/защ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
-  </si>
-  <si>
-    <t>Трубка 305 ТВ-40-3,5 ГОСТ 19034-82</t>
-  </si>
-  <si>
-    <t>Трубка ПВХ гибкая, гофрированная 16 мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 2х2х0,75 d7,1мм</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
-  </si>
-  <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 100х60</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 40х40 мм</t>
-  </si>
-  <si>
-    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
-  </si>
-  <si>
-    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-FRLS 3х1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
-  </si>
-  <si>
-    <t>Провод Rd8</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
+    <t>Маркер  краска красный по металлу</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>ЛГУП-7331</t>
+  </si>
+  <si>
+    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
+  </si>
+  <si>
+    <t>пара</t>
+  </si>
+  <si>
+    <t>Перчатки с латесным покрытием</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
+    <t>Ветошь</t>
+  </si>
+  <si>
+    <t>Маркер белый</t>
+  </si>
+  <si>
+    <t>Каска строительная белая</t>
+  </si>
+  <si>
+    <t>Каска строительная оранжевая Исток</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Огнетушитель ОП-8</t>
+  </si>
+  <si>
+    <t>Резак</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Ножницы по металлу</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 24</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 30</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 36</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 41</t>
+  </si>
+  <si>
+    <t>Гайковерт</t>
+  </si>
+  <si>
+    <t>Кувалда 1 кг.</t>
+  </si>
+  <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>ЛГУП-7333</t>
+  </si>
+  <si>
+    <t>отвод 89х8, 09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 76х8, ст09г2с ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 57х6, 09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Эмаль ПФ-115 коричневая (25 кг), шт</t>
+  </si>
+  <si>
+    <t>ЛГУП-7334</t>
+  </si>
+  <si>
+    <t>Эмаль ПФ-115 серая 5,5 кг</t>
+  </si>
+  <si>
+    <t>Эмаль ПФ 115 красная 1,8кг STATUS /6</t>
+  </si>
+  <si>
+    <t>Эмаль ПФ-115 желтая (22кг)</t>
+  </si>
+  <si>
+    <t>Эмаль ПФ 115 черная 1,8кг STATUS /6</t>
+  </si>
+  <si>
+    <t>Паронит 3 мм</t>
+  </si>
+  <si>
+    <t>лист</t>
+  </si>
+  <si>
+    <t>Растворитель 646 (5л)</t>
+  </si>
+  <si>
+    <t>Паронит 2мм</t>
+  </si>
+  <si>
+    <t>Растворитель Р-4 /кг/</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х3 ГОСТ 8509-93/ст.20 ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>ЛГУП-7336</t>
+  </si>
+  <si>
+    <t>Опресовочный насос (ручной) на 60кг (6МПа)</t>
+  </si>
+  <si>
+    <t>Салфетки влажные SMART ЭКОНОМ для всей семьи 70шт</t>
+  </si>
+  <si>
+    <t>НТУП-017966</t>
+  </si>
+  <si>
+    <t>Грифель для карандаша механического 0,5мм, НВ</t>
+  </si>
+  <si>
+    <t>Грифель для карандаша механического 0,7мм, НВ</t>
+  </si>
+  <si>
+    <t>Папка-регистратор 50 мм</t>
+  </si>
+  <si>
+    <t>Папка-регистратор 75 мм</t>
+  </si>
+  <si>
+    <t>Мыло жидкое</t>
+  </si>
+  <si>
+    <t>Разделитель цветной картонный 240-105мм</t>
+  </si>
+  <si>
+    <t>Белизна-гель 3 в 1</t>
+  </si>
+  <si>
+    <t>Конверты А5, комплект 500шт</t>
+  </si>
+  <si>
+    <t>Скобы №10</t>
+  </si>
+  <si>
+    <t>Ручка шариковая синяя</t>
+  </si>
+  <si>
+    <t>Скобы №24/6</t>
+  </si>
+  <si>
+    <t>Бумага А4 500л.</t>
+  </si>
+  <si>
+    <t>Туалетная бумага</t>
+  </si>
+  <si>
+    <t>Мешки для мусора 30 л синие в рулоне 30шт. прочные,ПНД 10мкм 50*60 см, LAIMA</t>
+  </si>
+  <si>
+    <t>Батарейки GP Super, AA (LR6,15А), алкалиновые, пальч., КОМПЛЕКТ 10 шт., в пленке, 15A-2CRB10_АМК</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>Закладки клейкие неоновые STAFF "СТРЕЛКИ" 45х8 мм, 100шт (5 цв. х 20 л.) на пласт.основании, 111355</t>
+  </si>
+  <si>
+    <t>00УП-000005</t>
   </si>
   <si>
     <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
@@ -399,6 +306,42 @@
     <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
   </si>
   <si>
+    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D89х8 Ст.35 ГОСТ 1050-80</t>
+  </si>
+  <si>
+    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
+  </si>
+  <si>
+    <t>Труба D159х18 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D146х22 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D121х6 ГОСТ 8732-78 /Ст. 20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D180х25 ГОСТ 8732-78 / 09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D83*9 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>не исп. Труба D83х10 Ст20 ГОСТ 8731-74</t>
+  </si>
+  <si>
     <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
   </si>
   <si>
@@ -408,64 +351,58 @@
     <t>Труба D57х5 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
-  </si>
-  <si>
     <t>Труба D57х4 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
     <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D180х25 ГОСТ 8732-78 / 09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
     <t>Труба D14х2 09Г2С ГОСТ 8733-74</t>
   </si>
   <si>
-    <t>Труба D121х6 ГОСТ 8732-78 /Ст. 20 ГОСТ 8731-74</t>
-  </si>
-  <si>
     <t>Труба D108х11 Ст. 20Х13 ГОСТ 5632-72</t>
   </si>
   <si>
-    <t>Труба D146х22 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
-  </si>
-  <si>
-    <t>Труба D159х18 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
     <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
-    <t>не исп. Труба D83х10 Ст20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D83*9 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D89х8 Ст.35 ГОСТ 1050-80</t>
-  </si>
-  <si>
     <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
   </si>
   <si>
     <t>Труба 25х3,2 ГОСТ 3262-75 (D33,5)</t>
   </si>
   <si>
-    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
+    <t>Маркер черный</t>
+  </si>
+  <si>
+    <t>Фумлента</t>
+  </si>
+  <si>
+    <t>Переход 114х8-89х8 Ст.09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход 89х8-76х8 ст. 09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход 159х8-108х8 ст.09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Лист S=4 09Г2С</t>
+  </si>
+  <si>
+    <t>Швеллер №20У ГОСТ 8240-97/ 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Швеллер №5П ГОСТ 8240-97/ Ст.09Г2С ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
+  </si>
+  <si>
+    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
   </si>
 </sst>
 </file>
@@ -902,13 +839,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -939,10 +876,10 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D2" s="5">
-        <v>100</v>
+        <v>95.25</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>6</v>
@@ -957,10 +894,10 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="D3" s="5">
-        <v>28</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>6</v>
@@ -975,10 +912,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="D4" s="5">
-        <v>16</v>
+        <v>233.85</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>6</v>
@@ -996,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="5">
-        <v>16</v>
+        <v>47.85</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>6</v>
@@ -1005,16 +942,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="5">
-        <v>12</v>
+        <v>83</v>
+      </c>
+      <c r="D6" s="7">
+        <v>4500</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>6</v>
@@ -1029,10 +966,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5">
-        <v>280</v>
+        <v>84</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2000</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>6</v>
@@ -1047,10 +984,10 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D8" s="5">
-        <v>32</v>
+        <v>48.6</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>6</v>
@@ -1065,10 +1002,10 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="D9" s="5">
-        <v>4</v>
+        <v>97.8</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>6</v>
@@ -1077,16 +1014,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="D10" s="5">
-        <v>4</v>
+        <v>57.15</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>6</v>
@@ -1101,10 +1038,10 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D11" s="5">
-        <v>12</v>
+        <v>33.75</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>6</v>
@@ -1113,16 +1050,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D12" s="5">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>6</v>
@@ -1137,10 +1074,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="D13" s="5">
-        <v>4</v>
+        <v>7.05</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>6</v>
@@ -1155,10 +1092,10 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="D14" s="5">
-        <v>8</v>
+        <v>193.2</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>6</v>
@@ -1173,10 +1110,10 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D15" s="5">
-        <v>200</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>6</v>
@@ -1185,22 +1122,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D16" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1209,16 +1146,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="D17" s="5">
-        <v>4</v>
+        <v>36.6</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1227,16 +1164,16 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="D18" s="5">
-        <v>4</v>
+        <v>6.45</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1245,16 +1182,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="D19" s="5">
-        <v>4</v>
+        <v>5.16</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1263,16 +1200,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="D20" s="5">
-        <v>4</v>
+        <v>0.43</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1281,34 +1218,34 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="D21" s="5">
-        <v>4</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="D22" s="5">
-        <v>4</v>
+        <v>6.06</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1317,16 +1254,16 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="D23" s="5">
-        <v>32</v>
+        <v>2.87</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1335,16 +1272,16 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="D24" s="5">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1353,16 +1290,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="D25" s="5">
-        <v>4</v>
+        <v>5.35</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1371,16 +1308,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="D26" s="5">
-        <v>25</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1389,16 +1326,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="D27" s="5">
-        <v>63</v>
+        <v>2.04</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1407,16 +1344,16 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="D28" s="5">
-        <v>9</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1425,16 +1362,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="D29" s="5">
-        <v>32</v>
+        <v>43.48</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1443,16 +1380,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="D30" s="5">
-        <v>16</v>
+        <v>2.52</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1461,16 +1398,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="D31" s="5">
-        <v>16</v>
+        <v>5.68</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1479,16 +1416,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="D32" s="5">
-        <v>32</v>
+        <v>11.2</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1497,16 +1434,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="D33" s="5">
-        <v>16</v>
+        <v>1.52</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1515,16 +1452,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D34" s="5">
-        <v>32</v>
+        <v>146.4</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1533,16 +1470,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="D35" s="5">
-        <v>63</v>
+        <v>51.52</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1551,16 +1488,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="D36" s="5">
-        <v>9</v>
+        <v>0.84</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1569,16 +1506,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D37" s="5">
-        <v>25</v>
+        <v>26.52</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1587,16 +1524,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D38" s="5">
-        <v>160</v>
+        <v>13.76</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1605,16 +1542,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D39" s="5">
-        <v>4</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1623,16 +1560,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="D40" s="5">
-        <v>56</v>
+        <v>6.64</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1641,16 +1578,16 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D41" s="5">
-        <v>8</v>
+        <v>21.4</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1659,16 +1596,16 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="D42" s="5">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1677,16 +1614,16 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D43" s="5">
-        <v>8</v>
+        <v>10.8</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1695,16 +1632,16 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="D44" s="5">
-        <v>24</v>
+        <v>3.56</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1713,16 +1650,16 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D45" s="5">
-        <v>120</v>
+        <v>11.48</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1731,16 +1668,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D46" s="5">
-        <v>8</v>
+        <v>15.24</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1749,16 +1686,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="D47" s="5">
-        <v>32</v>
+        <v>24.24</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1767,16 +1704,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="D48" s="5">
-        <v>16</v>
+        <v>1.72</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1785,16 +1722,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D49" s="5">
-        <v>16</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1803,16 +1740,16 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="D50" s="5">
-        <v>16</v>
+        <v>17.84</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1821,16 +1758,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D51" s="5">
-        <v>32</v>
+        <v>7.72</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1839,16 +1776,16 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="D52" s="5">
-        <v>32</v>
+        <v>3.97</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1857,16 +1794,16 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="D53" s="5">
-        <v>16</v>
+        <v>1.1950000000000001</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1875,124 +1812,124 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D54" s="5">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="D54" s="7">
+        <v>1000</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>54</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="D55" s="5">
-        <v>255</v>
+        <v>40</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="D56" s="5">
-        <v>285</v>
+        <v>500</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>56</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="D57" s="5">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>57</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="D58" s="5">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>58</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D59" s="5">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>59</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="D60" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2001,88 +1938,88 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="D61" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>61</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="D62" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="D63" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>63</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D64" s="5">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>64</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="D65" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2091,16 +2028,16 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="D66" s="5">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2109,88 +2046,88 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="D67" s="5">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="D68" s="5">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>68</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="D69" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="D70" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>70</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D71" s="7">
-        <v>60000</v>
+        <v>35</v>
+      </c>
+      <c r="D71" s="5">
+        <v>10</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2199,196 +2136,196 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="D72" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="D73" s="5">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="D74" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>74</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D75" s="5">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>75</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="D76" s="5">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>76</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D77" s="5">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>77</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="D78" s="5">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>78</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D79" s="5">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>79</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="D80" s="5">
-        <v>340.6</v>
+        <v>100</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="D81" s="5">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="D82" s="5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2397,16 +2334,16 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="D83" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2415,16 +2352,16 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="D84" s="5">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2433,16 +2370,16 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="D85" s="5">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2451,16 +2388,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="D86" s="5">
-        <v>520</v>
+        <v>1</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2469,16 +2406,16 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="D87" s="5">
-        <v>508</v>
+        <v>17</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2487,16 +2424,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="D88" s="5">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2505,16 +2442,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="D89" s="5">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2523,16 +2460,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D90" s="5">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2541,286 +2478,286 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="D91" s="5">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>91</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="D92" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>92</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D93" s="5">
-        <v>95.25</v>
+        <v>120</v>
+      </c>
+      <c r="D93" s="7">
+        <v>1000</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="D94" s="5">
-        <v>291.60000000000002</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="D95" s="5">
-        <v>233.85</v>
+        <v>5</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D96" s="5">
-        <v>47.85</v>
+        <v>5</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D97" s="7">
-        <v>4500</v>
+        <v>63</v>
+      </c>
+      <c r="D97" s="5">
+        <v>5</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D98" s="7">
-        <v>2000</v>
+        <v>64</v>
+      </c>
+      <c r="D98" s="5">
+        <v>10</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="D99" s="5">
-        <v>48.6</v>
+        <v>10</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D100" s="5">
-        <v>97.8</v>
+        <v>1</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="D101" s="5">
-        <v>57.15</v>
+        <v>1</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="D102" s="5">
-        <v>33.75</v>
+        <v>5</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="D103" s="5">
-        <v>16.5</v>
+        <v>1</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="D104" s="5">
-        <v>7.05</v>
+        <v>20</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>104</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="D105" s="5">
-        <v>193.2</v>
+        <v>12</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="D106" s="5">
-        <v>20.399999999999999</v>
+        <v>40</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2829,16 +2766,16 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="D107" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2847,16 +2784,16 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="D108" s="5">
-        <v>5.68</v>
+        <v>10</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2865,16 +2802,16 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="D109" s="5">
-        <v>11.2</v>
+        <v>5</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2883,16 +2820,16 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="D110" s="5">
-        <v>1.52</v>
+        <v>6</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2901,16 +2838,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="D111" s="5">
-        <v>146.4</v>
+        <v>10</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2919,16 +2856,16 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D112" s="5">
-        <v>51.52</v>
+        <v>121</v>
+      </c>
+      <c r="D112" s="7">
+        <v>3757</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2937,16 +2874,16 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D113" s="5">
-        <v>0.84</v>
+        <v>372.6</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2955,16 +2892,16 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="D114" s="5">
-        <v>26.52</v>
+        <v>745.5</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2973,16 +2910,16 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D115" s="5">
-        <v>13.76</v>
+        <v>124</v>
+      </c>
+      <c r="D115" s="7">
+        <v>1712</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2991,556 +2928,16 @@
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D116" s="5">
-        <v>8.8000000000000007</v>
+        <v>125</v>
+      </c>
+      <c r="D116" s="7">
+        <v>1250.96</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="3">
-        <v>116</v>
-      </c>
-      <c r="B117" s="4"/>
-      <c r="C117" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D117" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="3">
-        <v>117</v>
-      </c>
-      <c r="B118" s="4"/>
-      <c r="C118" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="D118" s="5">
-        <v>21.4</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="3">
-        <v>118</v>
-      </c>
-      <c r="B119" s="4"/>
-      <c r="C119" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D119" s="5">
-        <v>4</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="3">
-        <v>119</v>
-      </c>
-      <c r="B120" s="4"/>
-      <c r="C120" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D120" s="5">
-        <v>10.8</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="3">
-        <v>120</v>
-      </c>
-      <c r="B121" s="4"/>
-      <c r="C121" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D121" s="5">
-        <v>3.56</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="3">
-        <v>121</v>
-      </c>
-      <c r="B122" s="4"/>
-      <c r="C122" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="D122" s="5">
-        <v>11.48</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="3">
-        <v>122</v>
-      </c>
-      <c r="B123" s="4"/>
-      <c r="C123" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D123" s="5">
-        <v>15.24</v>
-      </c>
-      <c r="E123" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="3">
-        <v>123</v>
-      </c>
-      <c r="B124" s="4"/>
-      <c r="C124" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D124" s="5">
-        <v>24.24</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="3">
-        <v>124</v>
-      </c>
-      <c r="B125" s="4"/>
-      <c r="C125" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D125" s="5">
-        <v>1.72</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="3">
-        <v>125</v>
-      </c>
-      <c r="B126" s="4"/>
-      <c r="C126" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D126" s="5">
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="3">
-        <v>126</v>
-      </c>
-      <c r="B127" s="4"/>
-      <c r="C127" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D127" s="5">
-        <v>17.84</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="3">
-        <v>127</v>
-      </c>
-      <c r="B128" s="4"/>
-      <c r="C128" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D128" s="5">
-        <v>2.52</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="3">
-        <v>128</v>
-      </c>
-      <c r="B129" s="4"/>
-      <c r="C129" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D129" s="5">
-        <v>43.48</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="3">
-        <v>129</v>
-      </c>
-      <c r="B130" s="4"/>
-      <c r="C130" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D130" s="5">
-        <v>77.760000000000005</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="3">
-        <v>130</v>
-      </c>
-      <c r="B131" s="4"/>
-      <c r="C131" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D131" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="3">
-        <v>131</v>
-      </c>
-      <c r="B132" s="4"/>
-      <c r="C132" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D132" s="5">
-        <v>19.440000000000001</v>
-      </c>
-      <c r="E132" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="3">
-        <v>132</v>
-      </c>
-      <c r="B133" s="4"/>
-      <c r="C133" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="D133" s="5">
-        <v>5.35</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="3">
-        <v>133</v>
-      </c>
-      <c r="B134" s="4"/>
-      <c r="C134" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D134" s="5">
-        <v>2.7</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="3">
-        <v>134</v>
-      </c>
-      <c r="B135" s="4"/>
-      <c r="C135" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="D135" s="5">
-        <v>2.87</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="3">
-        <v>135</v>
-      </c>
-      <c r="B136" s="4"/>
-      <c r="C136" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D136" s="5">
-        <v>6.06</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="3">
-        <v>136</v>
-      </c>
-      <c r="B137" s="4"/>
-      <c r="C137" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D137" s="5">
-        <v>7.72</v>
-      </c>
-      <c r="E137" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="3">
-        <v>137</v>
-      </c>
-      <c r="B138" s="4"/>
-      <c r="C138" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D138" s="5">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="3">
-        <v>138</v>
-      </c>
-      <c r="B139" s="4"/>
-      <c r="C139" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D139" s="5">
-        <v>0.43</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="3">
-        <v>139</v>
-      </c>
-      <c r="B140" s="4"/>
-      <c r="C140" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D140" s="5">
-        <v>36.6</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="3">
-        <v>140</v>
-      </c>
-      <c r="B141" s="4"/>
-      <c r="C141" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D141" s="5">
-        <v>5.16</v>
-      </c>
-      <c r="E141" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="3">
-        <v>141</v>
-      </c>
-      <c r="B142" s="4"/>
-      <c r="C142" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D142" s="5">
-        <v>6.45</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="3">
-        <v>142</v>
-      </c>
-      <c r="B143" s="4"/>
-      <c r="C143" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D143" s="5">
-        <v>3.97</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="3">
-        <v>143</v>
-      </c>
-      <c r="B144" s="4"/>
-      <c r="C144" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D144" s="5">
-        <v>1.1950000000000001</v>
-      </c>
-      <c r="E144" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="3">
-        <v>144</v>
-      </c>
-      <c r="B145" s="4"/>
-      <c r="C145" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D145" s="7">
-        <v>1000</v>
-      </c>
-      <c r="E145" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="3">
-        <v>145</v>
-      </c>
-      <c r="B146" s="4"/>
-      <c r="C146" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D146" s="5">
-        <v>7</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141D86CA-40BA-49E4-AB5C-5D264E776348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7475053D-1628-47ED-96A9-1CD5DA872060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="148">
   <si>
     <t>№ п/п</t>
   </si>
@@ -54,237 +54,219 @@
     <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
   </si>
   <si>
-    <t>АС 30, Гидравл. тележка 3000 кг, 1150х550 мм, полиурет.колесо, двойные полиурет.ролики, цвет красный</t>
+    <t>не исп. Труба D89х6 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>ЛГУП-7315</t>
   </si>
   <si>
     <t>шт</t>
   </si>
   <si>
-    <t>ЛГУП-7313</t>
-  </si>
-  <si>
-    <t>ЛГУП-7315</t>
-  </si>
-  <si>
-    <t>не исп. Труба D89х6 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Лист 3 ст 35</t>
-  </si>
-  <si>
-    <t>ЛГУП-7319</t>
+    <t>ЛГУП-7331</t>
+  </si>
+  <si>
+    <t>Каска строительная оранжевая Исток</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Ветошь</t>
+  </si>
+  <si>
+    <t>Маркер белый</t>
+  </si>
+  <si>
+    <t>Каска строительная белая</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Огнетушитель ОП-8</t>
+  </si>
+  <si>
+    <t>Перчатки с латесным покрытием</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
+    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
+  </si>
+  <si>
+    <t>пара</t>
   </si>
   <si>
     <t>Маркер  краска красный по металлу</t>
   </si>
   <si>
-    <t>шт.</t>
-  </si>
-  <si>
-    <t>ЛГУП-7331</t>
-  </si>
-  <si>
-    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
-  </si>
-  <si>
-    <t>пара</t>
-  </si>
-  <si>
-    <t>Перчатки с латесным покрытием</t>
-  </si>
-  <si>
-    <t>пар</t>
-  </si>
-  <si>
-    <t>Ветошь</t>
-  </si>
-  <si>
-    <t>Маркер белый</t>
-  </si>
-  <si>
-    <t>Каска строительная белая</t>
-  </si>
-  <si>
-    <t>Каска строительная оранжевая Исток</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Огнетушитель ОП-8</t>
+    <t>Гайковерт</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 41</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 36</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 30</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 24</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
+  </si>
+  <si>
+    <t>Ножницы по металлу</t>
+  </si>
+  <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>Кувалда 1 кг.</t>
   </si>
   <si>
     <t>Резак</t>
   </si>
   <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
-    <t>Ножницы по металлу</t>
-  </si>
-  <si>
-    <t>Трещетка ключ 1/2</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 24</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 30</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 36</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 41</t>
-  </si>
-  <si>
-    <t>Гайковерт</t>
-  </si>
-  <si>
-    <t>Кувалда 1 кг.</t>
-  </si>
-  <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
-    <t>ЛГУП-7333</t>
-  </si>
-  <si>
-    <t>отвод 89х8, 09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>Отвод 76х8, ст09г2с ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>Отвод 57х6, 09Г2С ГОСТ 17375-2001</t>
+    <t>Эмаль ПФ-115 желтая (22кг)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7334</t>
+  </si>
+  <si>
+    <t>Эмаль ПФ 115 красная 1,8кг STATUS /6</t>
+  </si>
+  <si>
+    <t>Растворитель 646 (5л)</t>
   </si>
   <si>
     <t>Эмаль ПФ-115 коричневая (25 кг), шт</t>
   </si>
   <si>
-    <t>ЛГУП-7334</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ-115 серая 5,5 кг</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ 115 красная 1,8кг STATUS /6</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ-115 желтая (22кг)</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ 115 черная 1,8кг STATUS /6</t>
-  </si>
-  <si>
-    <t>Паронит 3 мм</t>
-  </si>
-  <si>
-    <t>лист</t>
-  </si>
-  <si>
-    <t>Растворитель 646 (5л)</t>
-  </si>
-  <si>
-    <t>Паронит 2мм</t>
-  </si>
-  <si>
     <t>Растворитель Р-4 /кг/</t>
   </si>
   <si>
-    <t>Уголок 50х50х3 ГОСТ 8509-93/ст.20 ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>ЛГУП-7336</t>
-  </si>
-  <si>
-    <t>Опресовочный насос (ручной) на 60кг (6МПа)</t>
-  </si>
-  <si>
-    <t>Салфетки влажные SMART ЭКОНОМ для всей семьи 70шт</t>
-  </si>
-  <si>
-    <t>НТУП-017966</t>
-  </si>
-  <si>
-    <t>Грифель для карандаша механического 0,5мм, НВ</t>
-  </si>
-  <si>
-    <t>Грифель для карандаша механического 0,7мм, НВ</t>
-  </si>
-  <si>
-    <t>Папка-регистратор 50 мм</t>
-  </si>
-  <si>
-    <t>Папка-регистратор 75 мм</t>
-  </si>
-  <si>
-    <t>Мыло жидкое</t>
-  </si>
-  <si>
-    <t>Разделитель цветной картонный 240-105мм</t>
-  </si>
-  <si>
-    <t>Белизна-гель 3 в 1</t>
-  </si>
-  <si>
-    <t>Конверты А5, комплект 500шт</t>
-  </si>
-  <si>
-    <t>Скобы №10</t>
-  </si>
-  <si>
-    <t>Ручка шариковая синяя</t>
-  </si>
-  <si>
-    <t>Скобы №24/6</t>
-  </si>
-  <si>
-    <t>Бумага А4 500л.</t>
-  </si>
-  <si>
-    <t>Туалетная бумага</t>
-  </si>
-  <si>
-    <t>Мешки для мусора 30 л синие в рулоне 30шт. прочные,ПНД 10мкм 50*60 см, LAIMA</t>
-  </si>
-  <si>
-    <t>Батарейки GP Super, AA (LR6,15А), алкалиновые, пальч., КОМПЛЕКТ 10 шт., в пленке, 15A-2CRB10_АМК</t>
-  </si>
-  <si>
-    <t>компл</t>
-  </si>
-  <si>
-    <t>Закладки клейкие неоновые STAFF "СТРЕЛКИ" 45х8 мм, 100шт (5 цв. х 20 л.) на пласт.основании, 111355</t>
-  </si>
-  <si>
-    <t>00УП-000005</t>
+    <t>Дробемет для швеллера с конвейерной сеткой</t>
+  </si>
+  <si>
+    <t>ЛГУП-7338</t>
+  </si>
+  <si>
+    <t>Маркировка фланца</t>
+  </si>
+  <si>
+    <t>ЛГУП-7339</t>
+  </si>
+  <si>
+    <t>Шина</t>
+  </si>
+  <si>
+    <t>НТУП-017968</t>
+  </si>
+  <si>
+    <t>Строительство фундамента лестничной клетки(без учета материала)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7342</t>
+  </si>
+  <si>
+    <t>Строительство Промышленного пола(без учета материала)</t>
+  </si>
+  <si>
+    <t>Строительство Отмоски и цоколя(без учета материала)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7346</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>ЛГУП-7347</t>
+  </si>
+  <si>
+    <t>ЛГУП-7348</t>
+  </si>
+  <si>
+    <t>ЛГУП-7349</t>
+  </si>
+  <si>
+    <t>ЛГУП-7351</t>
+  </si>
+  <si>
+    <t>ЛГУП-7352</t>
+  </si>
+  <si>
+    <t>ЛГУП-7353</t>
+  </si>
+  <si>
+    <t>ЛГУП-7355</t>
+  </si>
+  <si>
+    <t>Фланец 25-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>ЛГУП-7356</t>
+  </si>
+  <si>
+    <t>ЛГУП-7357</t>
+  </si>
+  <si>
+    <t>Услуги по договору номер 7</t>
+  </si>
+  <si>
+    <t>АХУП-000649</t>
+  </si>
+  <si>
+    <t>ЛГУП-7365</t>
+  </si>
+  <si>
+    <t>ЛГУП-7366</t>
+  </si>
+  <si>
+    <t>л (дм3)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7367</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Уголок 40х40х3 ГОСТ 8509-93/ Ст3пс ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Труба D377х12 ст.09Г2С-К50 ГОСТ 8731-78</t>
+  </si>
+  <si>
+    <t>Труба D720х12 Ст.09Г2С-К50 ГОСТ 20295-85</t>
+  </si>
+  <si>
+    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
   </si>
   <si>
     <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
   </si>
   <si>
-    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D720х12 Ст.09Г2С-К50 ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>Труба D377х12 ст.09Г2С-К50 ГОСТ 8731-78</t>
-  </si>
-  <si>
-    <t>Уголок 40х40х3 ГОСТ 8509-93/ Ст3пс ГОСТ 535-88</t>
-  </si>
-  <si>
     <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
@@ -303,106 +285,190 @@
     <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
   </si>
   <si>
-    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
+    <t>Труба D57х4 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
     <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
   </si>
   <si>
+    <t>Труба D57х5 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D110х16 ГОСТ 8734-75/ Ст.20 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>не исп. Труба D83х10 Ст20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D159х18 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
+  </si>
+  <si>
     <t>Труба D89х8 Ст.35 ГОСТ 1050-80</t>
   </si>
   <si>
-    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
-  </si>
-  <si>
-    <t>Труба D159х18 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
+    <t>Труба 25х3,2 ГОСТ 3262-75 (D33,5)</t>
+  </si>
+  <si>
+    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
     <t>Труба D146х22 Ст.20 ГОСТ 8732-78</t>
   </si>
   <si>
+    <t>Труба D108х11 Ст. 20Х13 ГОСТ 5632-72</t>
+  </si>
+  <si>
     <t>Труба D121х6 ГОСТ 8732-78 /Ст. 20 ГОСТ 8731-74</t>
   </si>
   <si>
+    <t>Труба D14х2 09Г2С ГОСТ 8733-74</t>
+  </si>
+  <si>
     <t>Труба D180х25 ГОСТ 8732-78 / 09Г2С ГОСТ 19281-89</t>
   </si>
   <si>
+    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
+  </si>
+  <si>
     <t>Труба D83*9 Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
-    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>не исп. Труба D83х10 Ст20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D110х16 ГОСТ 8734-75/ Ст.20 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D57х5 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D57х4 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D14х2 09Г2С ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D108х11 Ст. 20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Труба 25х3,2 ГОСТ 3262-75 (D33,5)</t>
-  </si>
-  <si>
     <t>Маркер черный</t>
   </si>
   <si>
     <t>Фумлента</t>
   </si>
   <si>
-    <t>Переход 114х8-89х8 Ст.09Г2С ГОСТ 17378-01</t>
-  </si>
-  <si>
-    <t>Переход 89х8-76х8 ст. 09Г2С ГОСТ 17378-01</t>
-  </si>
-  <si>
-    <t>Переход 159х8-108х8 ст.09Г2С ГОСТ 17378-01</t>
-  </si>
-  <si>
-    <t>Лист S=4 09Г2С</t>
-  </si>
-  <si>
-    <t>Швеллер №20У ГОСТ 8240-97/ 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Швеллер №5П ГОСТ 8240-97/ Ст.09Г2С ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
-  </si>
-  <si>
-    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+    <t>Гайка М30х1,5-6Н.09Г2С.019 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Болт 1.2 М30х1000</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Гайка М16-6Н.09Г2С (оцинк.) ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Круг ДКРН D48 НД БрАЖ9-4 ГОСТ 1628-78</t>
+  </si>
+  <si>
+    <t>Круг D165 09Г2С-8-ТО ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг D450 Ст.09Г2С ГОСТ 2590-2006</t>
+  </si>
+  <si>
+    <t>Лист S=1 ст.09Г2С ГОСТ16523-89</t>
+  </si>
+  <si>
+    <t>Полоса 30х30 Ст.20Л</t>
+  </si>
+  <si>
+    <t>Шестигранник S=17 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=24 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=27 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=30 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=30 Ст.45 ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=46 Ст.09Г2С ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=46 Ст.45 ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Отвод 45-89х8-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Тройник 20х3-09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
+  </si>
+  <si>
+    <t>Труба D14х3 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D20х3 ГОСТ 8732-78/ 09Г2С  ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Заклепка 4х8.31 ГОСТ 10299-80</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька АМ16-6gx80 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 30.Ст3сп3.II.4.019 ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>Шайба 16 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Фланец х-300-40 (заготовка-поковка Ст.08Х18Н10 гр.IV КП195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Растворитель Р-4 ГОСТ 7827-74</t>
+  </si>
+  <si>
+    <t>Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
+  </si>
+  <si>
+    <t>Краска-спрей SABOTAGE (желтая)</t>
+  </si>
+  <si>
+    <t>Разбавитель Procore Universal Thinner</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Краска-спрей SABOTAGE 39(черный)</t>
   </si>
 </sst>
 </file>
@@ -839,13 +905,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="63.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -876,10 +942,10 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D2" s="5">
-        <v>95.25</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>6</v>
@@ -894,10 +960,10 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D3" s="5">
-        <v>291.60000000000002</v>
+        <v>48.6</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>6</v>
@@ -912,10 +978,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="5">
-        <v>233.85</v>
+        <v>75</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2000</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>6</v>
@@ -930,10 +996,10 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5">
-        <v>47.85</v>
+        <v>76</v>
+      </c>
+      <c r="D5" s="7">
+        <v>4500</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>6</v>
@@ -948,10 +1014,10 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="7">
-        <v>4500</v>
+        <v>8</v>
+      </c>
+      <c r="D6" s="5">
+        <v>47.85</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>6</v>
@@ -966,10 +1032,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2000</v>
+        <v>77</v>
+      </c>
+      <c r="D7" s="5">
+        <v>233.85</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>6</v>
@@ -984,10 +1050,10 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D8" s="5">
-        <v>48.6</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>6</v>
@@ -1002,10 +1068,10 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D9" s="5">
-        <v>97.8</v>
+        <v>95.25</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>6</v>
@@ -1020,10 +1086,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D10" s="5">
-        <v>57.15</v>
+        <v>97.8</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>6</v>
@@ -1038,10 +1104,10 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D11" s="5">
-        <v>33.75</v>
+        <v>57.15</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>6</v>
@@ -1056,10 +1122,10 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D12" s="5">
-        <v>16.5</v>
+        <v>33.75</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>6</v>
@@ -1074,10 +1140,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D13" s="5">
-        <v>7.05</v>
+        <v>16.5</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>6</v>
@@ -1092,10 +1158,10 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D14" s="5">
-        <v>193.2</v>
+        <v>7.05</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>6</v>
@@ -1110,10 +1176,10 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D15" s="5">
-        <v>20.399999999999999</v>
+        <v>193.2</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>6</v>
@@ -1122,7 +1188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1131,13 +1197,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="5">
-        <v>2</v>
+        <v>26.52</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1146,16 +1212,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D17" s="5">
-        <v>36.6</v>
+        <v>0.84</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1164,16 +1230,16 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D18" s="5">
-        <v>6.45</v>
+        <v>51.52</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1182,16 +1248,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D19" s="5">
-        <v>5.16</v>
+        <v>146.4</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1200,16 +1266,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D20" s="5">
-        <v>0.43</v>
+        <v>1.52</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1218,16 +1284,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D21" s="5">
-        <v>2.2400000000000002</v>
+        <v>11.2</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1236,16 +1302,16 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D22" s="5">
-        <v>6.06</v>
+        <v>5.68</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1254,16 +1320,16 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D23" s="5">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1272,16 +1338,16 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D24" s="5">
-        <v>2.7</v>
+        <v>13.76</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1290,16 +1356,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D25" s="5">
-        <v>5.35</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1308,16 +1374,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D26" s="5">
-        <v>19.440000000000001</v>
+        <v>6.06</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1326,16 +1392,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D27" s="5">
-        <v>2.04</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1344,16 +1410,16 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D28" s="5">
-        <v>77.760000000000005</v>
+        <v>0.43</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1362,16 +1428,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D29" s="5">
-        <v>43.48</v>
+        <v>5.16</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1380,16 +1446,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D30" s="5">
-        <v>2.52</v>
+        <v>6.45</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1398,16 +1464,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D31" s="5">
-        <v>5.68</v>
+        <v>36.6</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1416,16 +1482,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D32" s="5">
-        <v>11.2</v>
+        <v>1.1950000000000001</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1434,16 +1500,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D33" s="5">
-        <v>1.52</v>
+        <v>3.97</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1452,16 +1518,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D34" s="5">
-        <v>146.4</v>
+        <v>17.84</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1470,16 +1536,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D35" s="5">
-        <v>51.52</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1488,16 +1554,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D36" s="5">
-        <v>0.84</v>
+        <v>1.72</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1506,16 +1572,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="D37" s="5">
-        <v>26.52</v>
+        <v>24.24</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1524,16 +1590,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D38" s="5">
-        <v>13.76</v>
+        <v>15.24</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1542,16 +1608,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D39" s="5">
-        <v>8.8000000000000007</v>
+        <v>11.48</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1560,16 +1626,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D40" s="5">
-        <v>6.64</v>
+        <v>3.56</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1578,16 +1644,16 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D41" s="5">
-        <v>21.4</v>
+        <v>10.8</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1596,7 +1662,7 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D42" s="5">
         <v>4</v>
@@ -1605,7 +1671,7 @@
         <v>6</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1614,16 +1680,16 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D43" s="5">
-        <v>10.8</v>
+        <v>21.4</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1632,16 +1698,16 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D44" s="5">
-        <v>3.56</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1650,16 +1716,16 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D45" s="5">
-        <v>11.48</v>
+        <v>6.64</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1668,16 +1734,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D46" s="5">
-        <v>15.24</v>
+        <v>2.87</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1686,16 +1752,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D47" s="5">
-        <v>24.24</v>
+        <v>2.7</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1704,16 +1770,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D48" s="5">
-        <v>1.72</v>
+        <v>5.35</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1722,16 +1788,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D49" s="5">
-        <v>8.9600000000000009</v>
+        <v>43.48</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1740,16 +1806,16 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D50" s="5">
-        <v>17.84</v>
+        <v>7.72</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1758,16 +1824,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D51" s="5">
-        <v>7.72</v>
+        <v>2.04</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1776,31 +1842,31 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D52" s="5">
-        <v>3.97</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D53" s="5">
-        <v>1.1950000000000001</v>
+        <v>40</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>12</v>
@@ -1812,16 +1878,16 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="5">
+        <v>10</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="7">
-        <v>1000</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>6</v>
-      </c>
       <c r="F54" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1830,16 +1896,16 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D55" s="5">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1848,16 +1914,16 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D56" s="5">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1866,16 +1932,16 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D57" s="5">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1884,16 +1950,16 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="D58" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1902,16 +1968,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D59" s="5">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1920,16 +1986,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="D60" s="5">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1938,16 +2004,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="D61" s="5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1956,16 +2022,16 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D62" s="5">
-        <v>5</v>
+        <v>800</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1974,16 +2040,16 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D63" s="5">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1992,16 +2058,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D64" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2010,16 +2076,16 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D65" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2028,16 +2094,16 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D66" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2046,16 +2112,16 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D67" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2064,16 +2130,16 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D68" s="5">
         <v>10</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2082,16 +2148,16 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D69" s="5">
         <v>10</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2100,16 +2166,16 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D70" s="5">
         <v>10</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2118,16 +2184,16 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D71" s="5">
         <v>10</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2136,16 +2202,16 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D72" s="5">
         <v>10</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2154,16 +2220,16 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D73" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2172,37 +2238,37 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D74" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>74</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" s="5">
+        <v>1</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D75" s="5">
-        <v>6</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -2211,229 +2277,229 @@
         <v>40</v>
       </c>
       <c r="D76" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>76</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="D77" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>77</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="D78" s="5">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>78</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="D79" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>79</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D80" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D81" s="5">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D82" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>82</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D83" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D84" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>84</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D85" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>85</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>86</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D87" s="5">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>87</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="D88" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2442,16 +2508,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D89" s="5">
-        <v>10</v>
+        <v>113</v>
+      </c>
+      <c r="D89" s="7">
+        <v>13486</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2460,16 +2526,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="D90" s="5">
-        <v>30</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2478,28 +2544,28 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D91" s="5">
-        <v>20</v>
+        <v>27.51</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>91</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="D92" s="5">
-        <v>20</v>
+        <v>167.4</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>6</v>
@@ -2508,16 +2574,16 @@
         <v>58</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>92</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D93" s="7">
-        <v>1000</v>
+        <v>117</v>
+      </c>
+      <c r="D93" s="5">
+        <v>0.03</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>6</v>
@@ -2526,184 +2592,184 @@
         <v>58</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="D94" s="5">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="D95" s="5">
-        <v>5</v>
+        <v>0.21</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="D96" s="5">
-        <v>5</v>
+        <v>0.42</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="D97" s="5">
-        <v>5</v>
+        <v>0.33</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="D98" s="5">
-        <v>10</v>
+        <v>0.72</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="D99" s="5">
-        <v>10</v>
+        <v>1.62</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D100" s="5">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
+        <v>4.32</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="D102" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="D103" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2712,232 +2778,561 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="D104" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>104</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="D105" s="5">
-        <v>12</v>
+        <v>1.62</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="D106" s="5">
-        <v>40</v>
+        <v>2.5</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>106</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D107" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>107</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="D108" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>108</v>
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D109" s="5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D110" s="5">
-        <v>6</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>110</v>
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D111" s="5">
-        <v>10</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>111</v>
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D112" s="7">
-        <v>3757</v>
+        <v>81</v>
+      </c>
+      <c r="D112" s="5">
+        <v>11.43</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="D113" s="5">
-        <v>372.6</v>
+        <v>18</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="D114" s="5">
-        <v>745.5</v>
+        <v>3.3</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D115" s="7">
-        <v>1712</v>
+        <v>84</v>
+      </c>
+      <c r="D115" s="5">
+        <v>1.41</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D116" s="5">
+        <v>38.64</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="3">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D117" s="5">
+        <v>4.08</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4"/>
+      <c r="C118" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D118" s="5">
+        <v>58.32</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="3">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D119" s="5">
+        <v>5</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4"/>
+      <c r="C120" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D120" s="5">
+        <v>6</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="3">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4"/>
+      <c r="C121" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D121" s="5">
+        <v>12</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="3">
+        <v>121</v>
+      </c>
+      <c r="B122" s="4"/>
+      <c r="C122" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D122" s="5">
+        <v>36</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="3">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4"/>
+      <c r="C123" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D123" s="5">
+        <v>12</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="3">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4"/>
+      <c r="C124" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D124" s="5">
+        <v>6</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="3">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4"/>
+      <c r="C125" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D125" s="5">
+        <v>3</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="3">
         <v>125</v>
       </c>
-      <c r="D116" s="7">
-        <v>1250.96</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>79</v>
+      <c r="B126" s="4"/>
+      <c r="C126" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D126" s="5">
+        <v>72</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="3">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4"/>
+      <c r="C127" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D127" s="5">
+        <v>3</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="3">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4"/>
+      <c r="C128" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D128" s="5">
+        <v>4</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="3">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4"/>
+      <c r="C129" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D129" s="5">
+        <v>5</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="3">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4"/>
+      <c r="C130" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D130" s="5">
+        <v>9.9</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="3">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4"/>
+      <c r="C131" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D131" s="5">
+        <v>1</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="3">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4"/>
+      <c r="C132" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D132" s="5">
+        <v>3</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="3">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4"/>
+      <c r="C133" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D133" s="5">
+        <v>3</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="3">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4"/>
+      <c r="C134" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D134" s="5">
+        <v>1</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C139" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7475053D-1628-47ED-96A9-1CD5DA872060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7ADDF4-5CE3-44B5-817A-59A9D04ACD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="170">
   <si>
     <t>№ п/п</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
   </si>
   <si>
-    <t>не исп. Труба D89х6 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-87</t>
-  </si>
-  <si>
     <t>ЛГУП-7315</t>
   </si>
   <si>
@@ -66,24 +63,24 @@
     <t>ЛГУП-7331</t>
   </si>
   <si>
+    <t>Каска строительная белая</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
     <t>Каска строительная оранжевая Исток</t>
   </si>
   <si>
-    <t>шт.</t>
+    <t>Ветошь</t>
+  </si>
+  <si>
+    <t>Маркер белый</t>
   </si>
   <si>
     <t>Маркер по металлу черный тонкий</t>
   </si>
   <si>
-    <t>Ветошь</t>
-  </si>
-  <si>
-    <t>Маркер белый</t>
-  </si>
-  <si>
-    <t>Каска строительная белая</t>
-  </si>
-  <si>
     <t>Маркер по металлу белый</t>
   </si>
   <si>
@@ -105,30 +102,33 @@
     <t>Маркер  краска красный по металлу</t>
   </si>
   <si>
+    <t>Ключ комбинированные омедненные 41</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 36</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 30</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 24</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
+  </si>
+  <si>
     <t>Гайковерт</t>
   </si>
   <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 41</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 36</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 30</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 24</t>
-  </si>
-  <si>
-    <t>Трещетка ключ 1/2</t>
-  </si>
-  <si>
     <t>Ножницы по металлу</t>
   </si>
   <si>
+    <t>Резак</t>
+  </si>
+  <si>
     <t>Ключи обмедненные</t>
   </si>
   <si>
@@ -138,9 +138,6 @@
     <t>Кувалда 1 кг.</t>
   </si>
   <si>
-    <t>Резак</t>
-  </si>
-  <si>
     <t>Эмаль ПФ-115 желтая (22кг)</t>
   </si>
   <si>
@@ -150,12 +147,12 @@
     <t>Эмаль ПФ 115 красная 1,8кг STATUS /6</t>
   </si>
   <si>
+    <t>Эмаль ПФ-115 коричневая (25 кг), шт</t>
+  </si>
+  <si>
     <t>Растворитель 646 (5л)</t>
   </si>
   <si>
-    <t>Эмаль ПФ-115 коричневая (25 кг), шт</t>
-  </si>
-  <si>
     <t>Растворитель Р-4 /кг/</t>
   </si>
   <si>
@@ -177,73 +174,109 @@
     <t>НТУП-017968</t>
   </si>
   <si>
+    <t>Строительство Отмоски и цоколя(без учета материала)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7342</t>
+  </si>
+  <si>
+    <t>Строительство Промышленного пола(без учета материала)</t>
+  </si>
+  <si>
     <t>Строительство фундамента лестничной клетки(без учета материала)</t>
   </si>
   <si>
-    <t>ЛГУП-7342</t>
-  </si>
-  <si>
-    <t>Строительство Промышленного пола(без учета материала)</t>
-  </si>
-  <si>
-    <t>Строительство Отмоски и цоколя(без учета материала)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7346</t>
-  </si>
-  <si>
     <t>м</t>
   </si>
   <si>
     <t>ЛГУП-7347</t>
   </si>
   <si>
-    <t>ЛГУП-7348</t>
-  </si>
-  <si>
     <t>ЛГУП-7349</t>
   </si>
   <si>
-    <t>ЛГУП-7351</t>
-  </si>
-  <si>
-    <t>ЛГУП-7352</t>
-  </si>
-  <si>
-    <t>ЛГУП-7353</t>
-  </si>
-  <si>
-    <t>ЛГУП-7355</t>
+    <t>ЛГУП-7356</t>
   </si>
   <si>
     <t>Фланец 25-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
   </si>
   <si>
-    <t>ЛГУП-7356</t>
-  </si>
-  <si>
     <t>ЛГУП-7357</t>
   </si>
   <si>
-    <t>Услуги по договору номер 7</t>
-  </si>
-  <si>
-    <t>АХУП-000649</t>
-  </si>
-  <si>
     <t>ЛГУП-7365</t>
   </si>
   <si>
-    <t>ЛГУП-7366</t>
+    <t>ЛГУП-7367</t>
   </si>
   <si>
     <t>л (дм3)</t>
   </si>
   <si>
-    <t>ЛГУП-7367</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>ЛГУП-7374</t>
+  </si>
+  <si>
+    <t>ЛГУП-7375</t>
+  </si>
+  <si>
+    <t>ЛГУП-7378</t>
+  </si>
+  <si>
+    <t>Окно 1100х900 мм /шт/ (ПВХ-профили морозостойкого исп) рал9016 белый</t>
+  </si>
+  <si>
+    <t>Бордюры тротуарные</t>
+  </si>
+  <si>
+    <t>ЛГУП-7380</t>
+  </si>
+  <si>
+    <t>Бетон М-250</t>
+  </si>
+  <si>
+    <t>м3</t>
+  </si>
+  <si>
+    <t>Туя Смарагд высота 1,5 м</t>
+  </si>
+  <si>
+    <t>ЛГУП-7381</t>
+  </si>
+  <si>
+    <t>Укладка бордюрного камня 340 м</t>
+  </si>
+  <si>
+    <t>ед</t>
+  </si>
+  <si>
+    <t>ЛГУП-7382</t>
+  </si>
+  <si>
+    <t>Наконечник НКИ 6,0-6</t>
+  </si>
+  <si>
+    <t>ЛГУП-7384</t>
+  </si>
+  <si>
+    <t>Труба 377х10, 09Г2с / тн</t>
+  </si>
+  <si>
+    <t>т</t>
+  </si>
+  <si>
+    <t>НТУП-017990</t>
+  </si>
+  <si>
+    <t>Труба 720х12 ст.09Г2С/кг</t>
+  </si>
+  <si>
+    <t>Костюм москитный</t>
+  </si>
+  <si>
+    <t>ЛГУП-7386</t>
+  </si>
+  <si>
+    <t>Спрей от комаров "Москитол"</t>
   </si>
   <si>
     <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
@@ -285,90 +318,45 @@
     <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
   </si>
   <si>
-    <t>Труба D57х4 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+    <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D146х22 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D57х5 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
     <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D57х5 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D110х16 ГОСТ 8734-75/ Ст.20 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>не исп. Труба D83х10 Ст20 ГОСТ 8731-74</t>
-  </si>
-  <si>
     <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
   </si>
   <si>
-    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D159х18 Ст.20 ГОСТ 8732-78</t>
+    <t>Труба D108х11 Ст. 20Х13 ГОСТ 5632-72</t>
   </si>
   <si>
     <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
   </si>
   <si>
-    <t>Труба D89х8 Ст.35 ГОСТ 1050-80</t>
-  </si>
-  <si>
-    <t>Труба 25х3,2 ГОСТ 3262-75 (D33,5)</t>
+    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
   </si>
   <si>
     <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
   </si>
   <si>
-    <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D146х22 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D108х11 Ст. 20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Труба D121х6 ГОСТ 8732-78 /Ст. 20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D14х2 09Г2С ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D180х25 ГОСТ 8732-78 / 09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D83*9 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
     <t>Маркер черный</t>
   </si>
   <si>
     <t>Фумлента</t>
   </si>
   <si>
-    <t>Гайка М30х1,5-6Н.09Г2С.019 ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Болт 1.2 М30х1000</t>
-  </si>
-  <si>
     <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
   </si>
   <si>
-    <t>Гайка М16-6Н.09Г2С (оцинк.) ГОСТ 9064-75</t>
-  </si>
-  <si>
     <t>Круг ДКРН D48 НД БрАЖ9-4 ГОСТ 1628-78</t>
   </si>
   <si>
@@ -405,70 +393,148 @@
     <t>Шестигранник S=46 Ст.45 ГОСТ 535-88</t>
   </si>
   <si>
-    <t>Отвод 45-89х8-09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>Тройник 20х3-09Г2С ГОСТ 17376-2001</t>
-  </si>
-  <si>
-    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
-  </si>
-  <si>
-    <t>Труба D14х3 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D20х3 ГОСТ 8732-78/ 09Г2С  ГОСТ 8731-74</t>
-  </si>
-  <si>
     <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
   </si>
   <si>
     <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
   </si>
   <si>
+    <t>Шпилька АМ16-6gx80 ГОСТ 9066-75</t>
+  </si>
+  <si>
     <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
   </si>
   <si>
+    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
     <t>Заклепка 4х8.31 ГОСТ 10299-80</t>
   </si>
   <si>
-    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька АМ16-6gx80 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
+    <t>Шайба 16 ГОСТ 6958-78</t>
   </si>
   <si>
     <t>Шайба 30.Ст3сп3.II.4.019 ГОСТ 9065-75</t>
   </si>
   <si>
-    <t>Шайба 16 ГОСТ 6958-78</t>
-  </si>
-  <si>
-    <t>Фланец х-300-40 (заготовка-поковка Ст.08Х18Н10 гр.IV КП195 ГОСТ 8479-70)</t>
+    <t>Краска-спрей SABOTAGE (желтая)</t>
+  </si>
+  <si>
+    <t>Краска-спрей SABOTAGE 39(черный)</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Разбавитель Procore Universal Thinner</t>
+  </si>
+  <si>
+    <t>Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
   </si>
   <si>
     <t>Растворитель Р-4 ГОСТ 7827-74</t>
   </si>
   <si>
-    <t>Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
-  </si>
-  <si>
-    <t>Краска-спрей SABOTAGE (желтая)</t>
-  </si>
-  <si>
-    <t>Разбавитель Procore Universal Thinner</t>
-  </si>
-  <si>
-    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>Краска-спрей SABOTAGE 39(черный)</t>
+    <t>Шпилька резьбовая оцинкованная M12 DIN 975</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х10</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х8 оцинкованная</t>
+  </si>
+  <si>
+    <t>Саморез для сэндвич панелей 5,5х25</t>
+  </si>
+  <si>
+    <t>Болт М20х50 ГОСТ15591-70</t>
+  </si>
+  <si>
+    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>Гайка М20-6Н ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х19 RAL9016 (белый)</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х25 RAL 2007(оранж)</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х25 RAL9016 (белый)</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 6,3*70</t>
+  </si>
+  <si>
+    <t>Саморез металл/металл 4,2х19</t>
+  </si>
+  <si>
+    <t>Шпилька 2М16х1,5-6gx120.109.40Х.26 ГОСТ 22034-76</t>
+  </si>
+  <si>
+    <t>Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
+  </si>
+  <si>
+    <t>Труба профильная 50х25х3 Ст.3сп5 ГОСТ 8645-68</t>
+  </si>
+  <si>
+    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
+  </si>
+  <si>
+    <t>Труба профильная 60х60х5 ГОСТ 8639-82/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Профиль 50х25х3 ст.09Г2С ГОСТ 30245-2012</t>
+  </si>
+  <si>
+    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 63х63х4 ГОСТ 8509-93 / 09Г2С ГОСТ5521-93</t>
+  </si>
+  <si>
+    <t>Уголок 63х63х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
+  </si>
+  <si>
+    <t>Дверь левая с доводчиком 1900х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
+  </si>
+  <si>
+    <t>Дверь левая с доводчиком 2000х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
+  </si>
+  <si>
+    <t>Эмаль ПФ-115 белая</t>
+  </si>
+  <si>
+    <t>Сольвент ГОСТ 10214-78</t>
+  </si>
+  <si>
+    <t>Гайка с насечкой М6 СМ100600</t>
+  </si>
+  <si>
+    <t>Газоанализатор взрывозащищенный СГОЭС (метан) 1Ex d IIC T4 Gb, IP67 Ур1. 10%, ур.2 50% НКПР</t>
+  </si>
+  <si>
+    <t>Провод ПУГВ 1х6,0 ЖЗ ГОСТ 31947-2012</t>
   </si>
 </sst>
 </file>
@@ -905,13 +971,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="63.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="56.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -942,7 +1008,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D2" s="5">
         <v>20.399999999999999</v>
@@ -960,7 +1026,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D3" s="5">
         <v>48.6</v>
@@ -978,7 +1044,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D4" s="7">
         <v>2000</v>
@@ -996,7 +1062,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D5" s="7">
         <v>4500</v>
@@ -1032,7 +1098,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D7" s="5">
         <v>233.85</v>
@@ -1050,7 +1116,7 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D8" s="5">
         <v>291.60000000000002</v>
@@ -1068,7 +1134,7 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D9" s="5">
         <v>95.25</v>
@@ -1086,7 +1152,7 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D10" s="5">
         <v>97.8</v>
@@ -1104,7 +1170,7 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D11" s="5">
         <v>57.15</v>
@@ -1122,7 +1188,7 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D12" s="5">
         <v>33.75</v>
@@ -1140,7 +1206,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D13" s="5">
         <v>16.5</v>
@@ -1158,7 +1224,7 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D14" s="5">
         <v>7.05</v>
@@ -1176,7 +1242,7 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D15" s="5">
         <v>193.2</v>
@@ -1194,16 +1260,16 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="5">
+        <v>17.84</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D16" s="5">
-        <v>26.52</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1212,16 +1278,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D17" s="5">
-        <v>0.84</v>
+        <v>24.24</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1230,16 +1296,16 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D18" s="5">
-        <v>51.52</v>
+        <v>11.48</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1248,16 +1314,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D19" s="5">
-        <v>146.4</v>
+        <v>2.87</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1266,7 +1332,7 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D20" s="5">
         <v>1.52</v>
@@ -1275,7 +1341,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1284,16 +1350,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D21" s="5">
-        <v>11.2</v>
+        <v>36.6</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1302,16 +1368,16 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D22" s="5">
-        <v>5.68</v>
+        <v>146.4</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1320,16 +1386,16 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D23" s="5">
-        <v>2.52</v>
+        <v>5.16</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1338,16 +1404,16 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D24" s="5">
-        <v>13.76</v>
+        <v>3.56</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1356,16 +1422,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D25" s="5">
-        <v>19.440000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1374,16 +1440,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D26" s="5">
-        <v>6.06</v>
+        <v>6.64</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1392,16 +1458,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D27" s="5">
-        <v>2.2400000000000002</v>
+        <v>13.76</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1410,412 +1476,412 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D28" s="5">
-        <v>0.43</v>
+        <v>3.97</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D29" s="5">
-        <v>5.16</v>
+        <v>40</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="D30" s="5">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="D31" s="5">
-        <v>36.6</v>
+        <v>10</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D32" s="5">
-        <v>1.1950000000000001</v>
+        <v>10</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="D33" s="5">
-        <v>3.97</v>
+        <v>40</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D34" s="5">
-        <v>17.84</v>
+        <v>5</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D35" s="5">
-        <v>8.9600000000000009</v>
+        <v>20</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="D36" s="5">
-        <v>1.72</v>
+        <v>20</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="D37" s="5">
-        <v>24.24</v>
+        <v>15</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="D38" s="5">
-        <v>15.24</v>
+        <v>800</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="D39" s="5">
-        <v>11.48</v>
+        <v>500</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="D40" s="5">
-        <v>3.56</v>
+        <v>40</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="D41" s="5">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D42" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="D43" s="5">
-        <v>21.4</v>
+        <v>10</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="D44" s="5">
-        <v>8.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="D45" s="5">
-        <v>6.64</v>
+        <v>10</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="D46" s="5">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="D47" s="5">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="D48" s="5">
-        <v>5.35</v>
+        <v>4</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>48</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="D49" s="5">
-        <v>43.48</v>
+        <v>10</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="D50" s="5">
-        <v>7.72</v>
+        <v>6</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1824,16 +1890,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="D51" s="5">
-        <v>2.04</v>
+        <v>1</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1842,124 +1908,124 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="D52" s="5">
-        <v>77.760000000000005</v>
+        <v>12</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="D53" s="5">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D54" s="5">
         <v>10</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>54</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D55" s="5">
         <v>20</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D56" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>56</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D57" s="5">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>57</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="D58" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1968,16 +2034,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D59" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1986,16 +2052,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D60" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2004,16 +2070,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D61" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2022,232 +2088,232 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="D62" s="5">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="D63" s="5">
-        <v>500</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>63</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="D64" s="5">
-        <v>40</v>
+        <v>27.51</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>64</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>167.4</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="D66" s="5">
-        <v>10</v>
+        <v>0.03</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>66</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="D67" s="5">
-        <v>10</v>
+        <v>1.59</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D68" s="5">
-        <v>10</v>
+        <v>0.21</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>68</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="D69" s="5">
-        <v>10</v>
+        <v>0.42</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="D70" s="5">
-        <v>10</v>
+        <v>0.33</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>70</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="D71" s="5">
-        <v>10</v>
+        <v>0.72</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>71</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="D72" s="5">
-        <v>10</v>
+        <v>1.62</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="D73" s="5">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="D74" s="5">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2256,16 +2322,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="D75" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2274,16 +2340,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="D76" s="5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2292,16 +2358,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D77" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2310,16 +2376,16 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D78" s="5">
-        <v>4</v>
+        <v>58.32</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2328,16 +2394,16 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="D79" s="5">
-        <v>20</v>
+        <v>4.08</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2346,16 +2412,16 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D80" s="5">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2364,16 +2430,16 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="D81" s="5">
-        <v>400</v>
+        <v>11.43</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2382,124 +2448,124 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D82" s="5">
-        <v>4</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>82</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="D83" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="D84" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>84</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="D85" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>85</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D86" s="5">
-        <v>256</v>
+        <v>36</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>86</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D87" s="5">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>87</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D88" s="5">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2508,16 +2574,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D89" s="7">
-        <v>13486</v>
+        <v>130</v>
+      </c>
+      <c r="D89" s="5">
+        <v>3</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2526,250 +2592,250 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D90" s="5">
-        <v>4.1399999999999997</v>
+        <v>72</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>90</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D91" s="5">
-        <v>27.51</v>
+        <v>1</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>91</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D92" s="5">
-        <v>167.4</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>92</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D93" s="5">
-        <v>0.03</v>
+        <v>3</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D94" s="5">
-        <v>1.59</v>
+        <v>3</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D95" s="5">
-        <v>0.21</v>
+        <v>9.9</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D96" s="5">
-        <v>0.42</v>
+        <v>5</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D97" s="5">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D98" s="5">
-        <v>0.72</v>
+        <v>30</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D99" s="5">
-        <v>1.62</v>
+        <v>30</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D100" s="5">
-        <v>3.6</v>
+        <v>416</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D101" s="5">
-        <v>4.32</v>
+        <v>6</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D102" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D103" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2778,430 +2844,430 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D104" s="5">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>104</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D105" s="5">
-        <v>1.62</v>
+        <v>146</v>
+      </c>
+      <c r="D105" s="7">
+        <v>1100</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="D106" s="5">
-        <v>2.5</v>
+        <v>400</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>106</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="D107" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>107</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="D108" s="5">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>108</v>
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="D109" s="5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="D110" s="5">
-        <v>9.7200000000000006</v>
+        <v>2</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>110</v>
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="D111" s="5">
-        <v>19.559999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>111</v>
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="D112" s="5">
-        <v>11.43</v>
+        <v>32.659999999999997</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="D113" s="5">
-        <v>18</v>
+        <v>279.08</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="D114" s="5">
-        <v>3.3</v>
+        <v>50.8</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="D115" s="5">
-        <v>1.41</v>
+        <v>7.8</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="D116" s="5">
-        <v>38.64</v>
+        <v>916.44</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="D117" s="5">
-        <v>4.08</v>
+        <v>12</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="D118" s="5">
-        <v>58.32</v>
+        <v>21</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>118</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="D119" s="5">
-        <v>5</v>
+        <v>55.64</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>119</v>
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D120" s="5">
-        <v>6</v>
+        <v>41.21</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>120</v>
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="D121" s="5">
-        <v>12</v>
+        <v>308.89</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>121</v>
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="D122" s="5">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>122</v>
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="D123" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>123</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="D124" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>124</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="D125" s="5">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>125</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="D126" s="5">
-        <v>72</v>
+        <v>0.7</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="D127" s="5">
-        <v>3</v>
+        <v>340</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3210,16 +3276,16 @@
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="D128" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3228,34 +3294,34 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="D129" s="5">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="D130" s="5">
-        <v>9.9</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3264,16 +3330,16 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D131" s="5">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="D131" s="7">
+        <v>1200</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3282,16 +3348,16 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D132" s="5">
-        <v>3</v>
+        <v>167</v>
+      </c>
+      <c r="D132" s="7">
+        <v>1280</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3300,16 +3366,16 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="D133" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3318,21 +3384,88 @@
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="D134" s="5">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C139" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="3">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4"/>
+      <c r="C135" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D135" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="3">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4"/>
+      <c r="C136" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D136" s="7">
+        <v>1000</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="3">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4"/>
+      <c r="C137" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D137" s="5">
+        <v>3</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="3">
+        <v>137</v>
+      </c>
+      <c r="B138" s="4"/>
+      <c r="C138" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D138" s="5">
+        <v>30</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7ADDF4-5CE3-44B5-817A-59A9D04ACD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF9D92-EBF0-45FF-9580-1FA8D10B55AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="193">
   <si>
     <t>№ п/п</t>
   </si>
@@ -57,57 +57,60 @@
     <t>ЛГУП-7315</t>
   </si>
   <si>
+    <t>Огнетушитель ОП-8</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>ЛГУП-7331</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Каска строительная белая</t>
+  </si>
+  <si>
+    <t>Маркер белый</t>
+  </si>
+  <si>
+    <t>Ветошь</t>
+  </si>
+  <si>
+    <t>Перчатки с латесным покрытием</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
+    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
+  </si>
+  <si>
+    <t>пара</t>
+  </si>
+  <si>
+    <t>Каска строительная оранжевая Исток</t>
+  </si>
+  <si>
     <t>шт</t>
   </si>
   <si>
-    <t>ЛГУП-7331</t>
-  </si>
-  <si>
-    <t>Каска строительная белая</t>
-  </si>
-  <si>
-    <t>шт.</t>
-  </si>
-  <si>
-    <t>Каска строительная оранжевая Исток</t>
-  </si>
-  <si>
-    <t>Ветошь</t>
-  </si>
-  <si>
-    <t>Маркер белый</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Огнетушитель ОП-8</t>
-  </si>
-  <si>
-    <t>Перчатки с латесным покрытием</t>
-  </si>
-  <si>
-    <t>пар</t>
-  </si>
-  <si>
-    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
-  </si>
-  <si>
-    <t>пара</t>
-  </si>
-  <si>
     <t>Маркер  краска красный по металлу</t>
   </si>
   <si>
+    <t>Гайковерт</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
     <t>Ключ комбинированные омедненные 41</t>
   </si>
   <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
     <t>Ключ комбинированные омедненные 36</t>
   </si>
   <si>
@@ -117,24 +120,21 @@
     <t>Ключ комбинированные омедненные 24</t>
   </si>
   <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
     <t>Трещетка ключ 1/2</t>
   </si>
   <si>
-    <t>Гайковерт</t>
-  </si>
-  <si>
     <t>Ножницы по металлу</t>
   </si>
   <si>
     <t>Резак</t>
   </si>
   <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
     <t>Кувалда 1 кг.</t>
   </si>
   <si>
@@ -147,15 +147,15 @@
     <t>Эмаль ПФ 115 красная 1,8кг STATUS /6</t>
   </si>
   <si>
+    <t>Растворитель 646 (5л)</t>
+  </si>
+  <si>
+    <t>Растворитель Р-4 /кг/</t>
+  </si>
+  <si>
     <t>Эмаль ПФ-115 коричневая (25 кг), шт</t>
   </si>
   <si>
-    <t>Растворитель 646 (5л)</t>
-  </si>
-  <si>
-    <t>Растворитель Р-4 /кг/</t>
-  </si>
-  <si>
     <t>Дробемет для швеллера с конвейерной сеткой</t>
   </si>
   <si>
@@ -195,24 +195,24 @@
     <t>ЛГУП-7349</t>
   </si>
   <si>
+    <t>Фланец 25-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
     <t>ЛГУП-7356</t>
   </si>
   <si>
-    <t>Фланец 25-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
     <t>ЛГУП-7357</t>
   </si>
   <si>
     <t>ЛГУП-7365</t>
   </si>
   <si>
+    <t>л (дм3)</t>
+  </si>
+  <si>
     <t>ЛГУП-7367</t>
   </si>
   <si>
-    <t>л (дм3)</t>
-  </si>
-  <si>
     <t>ЛГУП-7374</t>
   </si>
   <si>
@@ -225,18 +225,6 @@
     <t>Окно 1100х900 мм /шт/ (ПВХ-профили морозостойкого исп) рал9016 белый</t>
   </si>
   <si>
-    <t>Бордюры тротуарные</t>
-  </si>
-  <si>
-    <t>ЛГУП-7380</t>
-  </si>
-  <si>
-    <t>Бетон М-250</t>
-  </si>
-  <si>
-    <t>м3</t>
-  </si>
-  <si>
     <t>Туя Смарагд высота 1,5 м</t>
   </si>
   <si>
@@ -252,10 +240,10 @@
     <t>ЛГУП-7382</t>
   </si>
   <si>
-    <t>Наконечник НКИ 6,0-6</t>
-  </si>
-  <si>
-    <t>ЛГУП-7384</t>
+    <t>Труба 720х12 ст.09Г2С/кг</t>
+  </si>
+  <si>
+    <t>НТУП-017990</t>
   </si>
   <si>
     <t>Труба 377х10, 09Г2с / тн</t>
@@ -264,19 +252,46 @@
     <t>т</t>
   </si>
   <si>
-    <t>НТУП-017990</t>
-  </si>
-  <si>
-    <t>Труба 720х12 ст.09Г2С/кг</t>
-  </si>
-  <si>
-    <t>Костюм москитный</t>
-  </si>
-  <si>
-    <t>ЛГУП-7386</t>
-  </si>
-  <si>
-    <t>Спрей от комаров "Москитол"</t>
+    <t>Панель стеновая ПТСМ 2537х1000х100 снаружи RAL 9016/ внутри RAL 9016</t>
+  </si>
+  <si>
+    <t>ЛГУП-7391</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 438х1000х100мм Ral 9016(белый)</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2526х1000х100 снаружи RAL 9016/ внутри RAL 9016</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2337х1000х100 снаружи RAL 9016/ внутри RAL 9016</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2232х1000х100 снаружи RAL 9016/ внутри RAL 9016</t>
+  </si>
+  <si>
+    <t>Панель кровельная 3205х1000х150,внутри RAL9016(белый)/снаружи Ral 2007</t>
+  </si>
+  <si>
+    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 2007(оранж)</t>
+  </si>
+  <si>
+    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 9016(белый)</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН 2,0 ГОСТ 19903-80/ 20 ГОСТ 16523-89</t>
+  </si>
+  <si>
+    <t>Услуги связи</t>
+  </si>
+  <si>
+    <t>00УП-000005</t>
+  </si>
+  <si>
+    <t>Услуга автокрана</t>
+  </si>
+  <si>
+    <t>АМУП-000091</t>
   </si>
   <si>
     <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
@@ -291,6 +306,12 @@
     <t>Труба D720х12 Ст.09Г2С-К50 ГОСТ 20295-85</t>
   </si>
   <si>
+    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
+  </si>
+  <si>
     <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
@@ -300,12 +321,6 @@
     <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
   </si>
   <si>
-    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
-  </si>
-  <si>
     <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
   </si>
   <si>
@@ -318,42 +333,42 @@
     <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
   </si>
   <si>
+    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
+  </si>
+  <si>
+    <t>Труба D108х11 Ст. 20Х13 ГОСТ 5632-72</t>
+  </si>
+  <si>
+    <t>Труба D146х22 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
     <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
-    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D146х22 Ст.20 ГОСТ 8732-78</t>
+    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
   </si>
   <si>
     <t>Труба D57х5 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D108х11 Ст. 20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
-  </si>
-  <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+    <t>Фумлента</t>
   </si>
   <si>
     <t>Маркер черный</t>
   </si>
   <si>
-    <t>Фумлента</t>
-  </si>
-  <si>
     <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
   </si>
   <si>
@@ -375,52 +390,58 @@
     <t>Шестигранник S=17 Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
+    <t>Шестигранник S=46 Ст.45 ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=46 Ст.09Г2С ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=30 Ст.45 ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=30 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=27 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
     <t>Шестигранник S=24 Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
-    <t>Шестигранник S=27 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=30 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=30 Ст.45 ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=46 Ст.09Г2С ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=46 Ст.45 ГОСТ 535-88</t>
-  </si>
-  <si>
     <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
   </si>
   <si>
     <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
   </si>
   <si>
+    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 30.Ст3сп3.II.4.019 ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба 16 ГОСТ 6958-78</t>
+  </si>
+  <si>
     <t>Шпилька АМ16-6gx80 ГОСТ 9066-75</t>
   </si>
   <si>
+    <t>Заклепка 4х8.31 ГОСТ 10299-80</t>
+  </si>
+  <si>
     <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
   </si>
   <si>
-    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
-  </si>
-  <si>
     <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
   </si>
   <si>
-    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Заклепка 4х8.31 ГОСТ 10299-80</t>
-  </si>
-  <si>
-    <t>Шайба 16 ГОСТ 6958-78</t>
-  </si>
-  <si>
-    <t>Шайба 30.Ст3сп3.II.4.019 ГОСТ 9065-75</t>
+    <t>Растворитель Р-4 ГОСТ 7827-74</t>
+  </si>
+  <si>
+    <t>Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
   </si>
   <si>
     <t>Краска-спрей SABOTAGE (желтая)</t>
@@ -435,75 +456,69 @@
     <t>Разбавитель Procore Universal Thinner</t>
   </si>
   <si>
-    <t>Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
-  </si>
-  <si>
-    <t>Растворитель Р-4 ГОСТ 7827-74</t>
+    <t>Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
+  </si>
+  <si>
+    <t>Шпилька 2М16х1,5-6gx120.109.40Х.26 ГОСТ 22034-76</t>
+  </si>
+  <si>
+    <t>Саморез металл/металл 4,2х19</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 6,3*70</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х25 RAL9016 (белый)</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х25 RAL 2007(оранж)</t>
+  </si>
+  <si>
+    <t>Гайка М20-6Н ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>Болт М20х50 ГОСТ15591-70</t>
+  </si>
+  <si>
+    <t>Саморез для сэндвич панелей 5,5х25</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х8 оцинкованная</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х10</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х19 RAL9016 (белый)</t>
   </si>
   <si>
     <t>Шпилька резьбовая оцинкованная M12 DIN 975</t>
   </si>
   <si>
-    <t>Заклепка 4,8х10</t>
-  </si>
-  <si>
-    <t>Заклепка 4,8х8 оцинкованная</t>
-  </si>
-  <si>
-    <t>Саморез для сэндвич панелей 5,5х25</t>
-  </si>
-  <si>
-    <t>Болт М20х50 ГОСТ15591-70</t>
-  </si>
-  <si>
-    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
-  </si>
-  <si>
-    <t>Гайка М20-6Н ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Саморез кровельный 5,5х19 RAL9016 (белый)</t>
-  </si>
-  <si>
-    <t>Саморез кровельный 5,5х25 RAL 2007(оранж)</t>
-  </si>
-  <si>
-    <t>Саморез кровельный 5,5х25 RAL9016 (белый)</t>
-  </si>
-  <si>
-    <t>Саморез кровельный 6,3*70</t>
-  </si>
-  <si>
-    <t>Саморез металл/металл 4,2х19</t>
-  </si>
-  <si>
-    <t>Шпилька 2М16х1,5-6gx120.109.40Х.26 ГОСТ 22034-76</t>
-  </si>
-  <si>
-    <t>Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
+    <t>Профиль 50х25х3 ст.09Г2С ГОСТ 30245-2012</t>
+  </si>
+  <si>
+    <t>Труба профильная 60х60х5 ГОСТ 8639-82/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
+  </si>
+  <si>
+    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
   </si>
   <si>
     <t>Труба профильная 50х25х3 Ст.3сп5 ГОСТ 8645-68</t>
   </si>
   <si>
-    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
-  </si>
-  <si>
-    <t>Труба профильная 60х60х5 ГОСТ 8639-82/09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Профиль 50х25х3 ст.09Г2С ГОСТ 30245-2012</t>
-  </si>
-  <si>
-    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
     <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
   </si>
   <si>
@@ -516,25 +531,79 @@
     <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
   </si>
   <si>
+    <t>Эмаль ПФ-115 белая</t>
+  </si>
+  <si>
+    <t>Дверь левая с доводчиком 2000х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
+  </si>
+  <si>
     <t>Дверь левая с доводчиком 1900х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
   </si>
   <si>
-    <t>Дверь левая с доводчиком 2000х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ-115 белая</t>
-  </si>
-  <si>
     <t>Сольвент ГОСТ 10214-78</t>
   </si>
   <si>
-    <t>Гайка с насечкой М6 СМ100600</t>
-  </si>
-  <si>
-    <t>Газоанализатор взрывозащищенный СГОЭС (метан) 1Ex d IIC T4 Gb, IP67 Ур1. 10%, ур.2 50% НКПР</t>
-  </si>
-  <si>
-    <t>Провод ПУГВ 1х6,0 ЖЗ ГОСТ 31947-2012</t>
+    <t>Круг D10 ГОСТ 2590-2006/ Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D20 09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 3100х1000х100 RAL 9016/9016</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2450х1000х80 RAL 9016 (бел) снаружи/ RAL 9016 (белый) внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2270х1000х80 RAL 9016 снаружи/ RAL 9016 (бел.) внутри</t>
+  </si>
+  <si>
+    <t>Лист профилированный С21-1000-0,7 L=650мм RAL 2007 (оранжевый)</t>
+  </si>
+  <si>
+    <t>Лист профилированный С21-1000-0,7 L=2600 мм RAL2007 (оранж)</t>
+  </si>
+  <si>
+    <t>Лист профилированный С21-1000-0,7 L=1600мм RAL 2007(Оранжевый)</t>
+  </si>
+  <si>
+    <t>Лист профилированный С21-1000-0,7 L=1015мм RAL 1021 (желт)</t>
+  </si>
+  <si>
+    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 7036(Серый)</t>
+  </si>
+  <si>
+    <t>Круг D25 ГОСТ 2590-06/ 345-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лента ПВХ облицовочная декоративн самоклеющаяся, шириной 19мм</t>
+  </si>
+  <si>
+    <t>Лист S=2 ГОСТ 19903-74/ Ст.09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист S=4 ст.09Г2С ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Лист S=5 Ст.3 ГОСТ 380-2005</t>
+  </si>
+  <si>
+    <t>Лист оцинкованный ОЦ Б-ПН-НО-0,5 ГОСТ 19904-90/ОН-КР ГОСТ 14918-80 (кг)</t>
+  </si>
+  <si>
+    <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-2,0 ГОСТ 19903-74 / Ст3 ГОСТ 14637-89</t>
   </si>
 </sst>
 </file>
@@ -971,13 +1040,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="56.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -1008,7 +1077,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D2" s="5">
         <v>20.399999999999999</v>
@@ -1026,7 +1095,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D3" s="5">
         <v>48.6</v>
@@ -1044,7 +1113,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D4" s="7">
         <v>2000</v>
@@ -1062,7 +1131,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D5" s="7">
         <v>4500</v>
@@ -1080,10 +1149,10 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="D6" s="5">
-        <v>47.85</v>
+        <v>97.8</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>6</v>
@@ -1098,10 +1167,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D7" s="5">
-        <v>233.85</v>
+        <v>57.15</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>6</v>
@@ -1116,10 +1185,10 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="D8" s="5">
-        <v>291.60000000000002</v>
+        <v>47.85</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>6</v>
@@ -1134,10 +1203,10 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D9" s="5">
-        <v>95.25</v>
+        <v>233.85</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>6</v>
@@ -1152,10 +1221,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D10" s="5">
-        <v>97.8</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>6</v>
@@ -1170,10 +1239,10 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D11" s="5">
-        <v>57.15</v>
+        <v>95.25</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>6</v>
@@ -1188,7 +1257,7 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D12" s="5">
         <v>33.75</v>
@@ -1206,7 +1275,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D13" s="5">
         <v>16.5</v>
@@ -1224,7 +1293,7 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D14" s="5">
         <v>7.05</v>
@@ -1242,7 +1311,7 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D15" s="5">
         <v>193.2</v>
@@ -1260,10 +1329,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D16" s="5">
-        <v>17.84</v>
+        <v>6.64</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>6</v>
@@ -1278,10 +1347,10 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D17" s="5">
-        <v>24.24</v>
+        <v>13.76</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>6</v>
@@ -1296,10 +1365,10 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D18" s="5">
-        <v>11.48</v>
+        <v>0.43</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>6</v>
@@ -1314,10 +1383,10 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D19" s="5">
-        <v>2.87</v>
+        <v>3.56</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>6</v>
@@ -1332,10 +1401,10 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D20" s="5">
-        <v>1.52</v>
+        <v>2.87</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>6</v>
@@ -1350,10 +1419,10 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D21" s="5">
-        <v>36.6</v>
+        <v>11.48</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>6</v>
@@ -1368,10 +1437,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D22" s="5">
-        <v>146.4</v>
+        <v>24.24</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>6</v>
@@ -1386,10 +1455,10 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D23" s="5">
-        <v>5.16</v>
+        <v>17.84</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>6</v>
@@ -1404,10 +1473,10 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D24" s="5">
-        <v>3.56</v>
+        <v>3.97</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>6</v>
@@ -1422,10 +1491,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" s="5">
-        <v>0.43</v>
+        <v>5.16</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>6</v>
@@ -1440,10 +1509,10 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D26" s="5">
-        <v>6.64</v>
+        <v>146.4</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>6</v>
@@ -1458,10 +1527,10 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D27" s="5">
-        <v>13.76</v>
+        <v>36.6</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>6</v>
@@ -1476,10 +1545,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D28" s="5">
-        <v>3.97</v>
+        <v>1.52</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>6</v>
@@ -1494,16 +1563,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="D29" s="5">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1512,16 +1581,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="5">
+        <v>20</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="D30" s="5">
-        <v>5</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1533,13 +1602,13 @@
         <v>14</v>
       </c>
       <c r="D31" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1551,13 +1620,13 @@
         <v>15</v>
       </c>
       <c r="D32" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1566,16 +1635,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="D33" s="5">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1584,16 +1653,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="D34" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1605,13 +1674,13 @@
         <v>17</v>
       </c>
       <c r="D35" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1623,13 +1692,13 @@
         <v>18</v>
       </c>
       <c r="D36" s="5">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1638,16 +1707,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" s="5">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1656,16 +1725,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D38" s="5">
-        <v>800</v>
+        <v>10</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1674,16 +1743,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="D39" s="5">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1698,10 +1767,10 @@
         <v>40</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1713,10 +1782,10 @@
         <v>25</v>
       </c>
       <c r="D41" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>26</v>
@@ -1734,7 +1803,7 @@
         <v>10</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>26</v>
@@ -1752,7 +1821,7 @@
         <v>10</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>26</v>
@@ -1770,7 +1839,7 @@
         <v>10</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>26</v>
@@ -1788,7 +1857,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>26</v>
@@ -1803,10 +1872,10 @@
         <v>31</v>
       </c>
       <c r="D46" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>26</v>
@@ -1818,13 +1887,13 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D47" s="5">
         <v>10</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>26</v>
@@ -1836,13 +1905,13 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D48" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>26</v>
@@ -1854,13 +1923,13 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D49" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>26</v>
@@ -1878,7 +1947,7 @@
         <v>6</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>26</v>
@@ -1896,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>38</v>
@@ -1914,7 +1983,7 @@
         <v>12</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>38</v>
@@ -1929,10 +1998,10 @@
         <v>40</v>
       </c>
       <c r="D53" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>38</v>
@@ -1947,10 +2016,10 @@
         <v>41</v>
       </c>
       <c r="D54" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>38</v>
@@ -1965,10 +2034,10 @@
         <v>42</v>
       </c>
       <c r="D55" s="5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>38</v>
@@ -1986,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>44</v>
@@ -2004,7 +2073,7 @@
         <v>400</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>46</v>
@@ -2022,7 +2091,7 @@
         <v>4</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>48</v>
@@ -2040,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>50</v>
@@ -2058,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>50</v>
@@ -2076,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>50</v>
@@ -2088,7 +2157,7 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D62" s="5">
         <v>40</v>
@@ -2106,7 +2175,7 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D63" s="5">
         <v>4.1399999999999997</v>
@@ -2124,7 +2193,7 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D64" s="5">
         <v>27.51</v>
@@ -2142,7 +2211,7 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D65" s="5">
         <v>167.4</v>
@@ -2160,7 +2229,7 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D66" s="5">
         <v>0.03</v>
@@ -2178,7 +2247,7 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D67" s="5">
         <v>1.59</v>
@@ -2196,7 +2265,7 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D68" s="5">
         <v>0.21</v>
@@ -2214,10 +2283,10 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D69" s="5">
-        <v>0.42</v>
+        <v>4.32</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>6</v>
@@ -2232,10 +2301,10 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D70" s="5">
-        <v>0.33</v>
+        <v>3.6</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>6</v>
@@ -2250,10 +2319,10 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D71" s="5">
-        <v>0.72</v>
+        <v>1.62</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>6</v>
@@ -2268,10 +2337,10 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D72" s="5">
-        <v>1.62</v>
+        <v>0.72</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>6</v>
@@ -2286,10 +2355,10 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D73" s="5">
-        <v>3.6</v>
+        <v>0.33</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>6</v>
@@ -2304,10 +2373,10 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D74" s="5">
-        <v>4.32</v>
+        <v>0.42</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>6</v>
@@ -2322,16 +2391,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="D75" s="5">
         <v>3</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2340,16 +2409,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D76" s="5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2358,16 +2427,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="5">
+        <v>15</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="D77" s="5">
-        <v>3</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2376,10 +2445,10 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D78" s="5">
-        <v>58.32</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>6</v>
@@ -2394,10 +2463,10 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D79" s="5">
-        <v>4.08</v>
+        <v>11.43</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>6</v>
@@ -2412,7 +2481,7 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D80" s="5">
         <v>18</v>
@@ -2430,10 +2499,10 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D81" s="5">
-        <v>11.43</v>
+        <v>4.08</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>6</v>
@@ -2448,10 +2517,10 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D82" s="5">
-        <v>19.559999999999999</v>
+        <v>58.32</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>6</v>
@@ -2466,13 +2535,13 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D83" s="5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>59</v>
@@ -2484,13 +2553,13 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D84" s="5">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>59</v>
@@ -2502,13 +2571,13 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D85" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>59</v>
@@ -2520,13 +2589,13 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D86" s="5">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>59</v>
@@ -2538,13 +2607,13 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D87" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>59</v>
@@ -2556,13 +2625,13 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D88" s="5">
         <v>12</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>59</v>
@@ -2574,13 +2643,13 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D89" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>59</v>
@@ -2592,13 +2661,13 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D90" s="5">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>59</v>
@@ -2610,16 +2679,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D91" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2628,16 +2697,16 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D92" s="5">
-        <v>1</v>
+        <v>9.9</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2646,16 +2715,16 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D93" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2664,16 +2733,16 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D94" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F94" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2682,16 +2751,16 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D95" s="5">
-        <v>9.9</v>
+        <v>3</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2700,16 +2769,16 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D96" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E96" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2718,13 +2787,13 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D97" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>62</v>
@@ -2736,13 +2805,13 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D98" s="5">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>62</v>
@@ -2754,13 +2823,13 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D99" s="5">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>62</v>
@@ -2772,13 +2841,13 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D100" s="5">
-        <v>416</v>
+        <v>8</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>62</v>
@@ -2790,13 +2859,13 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D101" s="5">
-        <v>6</v>
+        <v>400</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>62</v>
@@ -2808,13 +2877,13 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D102" s="5">
-        <v>2</v>
+        <v>148</v>
+      </c>
+      <c r="D102" s="7">
+        <v>1100</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>62</v>
@@ -2826,13 +2895,13 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D103" s="5">
         <v>6</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>62</v>
@@ -2844,13 +2913,13 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D104" s="5">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>62</v>
@@ -2862,13 +2931,13 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D105" s="7">
-        <v>1100</v>
+        <v>151</v>
+      </c>
+      <c r="D105" s="5">
+        <v>6</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>62</v>
@@ -2880,13 +2949,13 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D106" s="5">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>62</v>
@@ -2898,13 +2967,13 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D107" s="5">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>62</v>
@@ -2916,13 +2985,13 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D108" s="5">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>62</v>
@@ -2934,13 +3003,13 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D109" s="5">
-        <v>4</v>
+        <v>250</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>62</v>
@@ -2952,13 +3021,13 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D110" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>62</v>
@@ -2970,10 +3039,10 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D111" s="5">
-        <v>79.44</v>
+        <v>50.8</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>6</v>
@@ -2988,10 +3057,10 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D112" s="5">
-        <v>32.659999999999997</v>
+        <v>279.08</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>6</v>
@@ -3006,10 +3075,10 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D113" s="5">
-        <v>279.08</v>
+        <v>32.659999999999997</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>6</v>
@@ -3024,10 +3093,10 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D114" s="5">
-        <v>50.8</v>
+        <v>7.8</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>6</v>
@@ -3042,10 +3111,10 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D115" s="5">
-        <v>7.8</v>
+        <v>916.44</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>6</v>
@@ -3060,10 +3129,10 @@
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D116" s="5">
-        <v>916.44</v>
+        <v>12</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>6</v>
@@ -3078,10 +3147,10 @@
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D117" s="5">
-        <v>12</v>
+        <v>79.44</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>6</v>
@@ -3096,7 +3165,7 @@
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D118" s="5">
         <v>21</v>
@@ -3114,7 +3183,7 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D119" s="5">
         <v>55.64</v>
@@ -3132,7 +3201,7 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D120" s="5">
         <v>41.21</v>
@@ -3150,7 +3219,7 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D121" s="5">
         <v>308.89</v>
@@ -3168,13 +3237,13 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D122" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>64</v>
@@ -3186,13 +3255,13 @@
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="D123" s="5">
         <v>2</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>64</v>
@@ -3204,13 +3273,13 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D124" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>64</v>
@@ -3222,13 +3291,13 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="D125" s="5">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>64</v>
@@ -3240,13 +3309,13 @@
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D126" s="5">
         <v>0.7</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>64</v>
@@ -3261,16 +3330,16 @@
         <v>66</v>
       </c>
       <c r="D127" s="5">
-        <v>340</v>
+        <v>150</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -3279,13 +3348,13 @@
         <v>68</v>
       </c>
       <c r="D128" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>69</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3294,34 +3363,34 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D129" s="5">
-        <v>150</v>
+        <v>71</v>
+      </c>
+      <c r="D129" s="7">
+        <v>1000</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D130" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F130" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="D130" s="5">
-        <v>1</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3332,29 +3401,29 @@
       <c r="C131" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D131" s="7">
-        <v>1200</v>
+      <c r="D131" s="5">
+        <v>6</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D132" s="7">
-        <v>1280</v>
+        <v>77</v>
+      </c>
+      <c r="D132" s="5">
+        <v>2</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>76</v>
@@ -3366,13 +3435,13 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="D133" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>76</v>
@@ -3384,13 +3453,13 @@
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="D134" s="5">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>76</v>
@@ -3402,16 +3471,16 @@
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D135" s="5">
-        <v>2.2999999999999998</v>
+        <v>6</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3420,52 +3489,484 @@
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D136" s="7">
-        <v>1000</v>
+        <v>81</v>
+      </c>
+      <c r="D136" s="5">
+        <v>6</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>136</v>
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D137" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>137</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D138" s="5">
+        <v>16</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="3">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4"/>
+      <c r="C139" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D139" s="5">
+        <v>6.52</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="3">
+        <v>139</v>
+      </c>
+      <c r="B140" s="4"/>
+      <c r="C140" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D140" s="5">
+        <v>1</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="3">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4"/>
+      <c r="C141" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D141" s="5">
+        <v>3</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="3">
+        <v>141</v>
+      </c>
+      <c r="B142" s="4"/>
+      <c r="C142" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D142" s="5">
+        <v>5</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="3">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4"/>
+      <c r="C143" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D143" s="5">
+        <v>7</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="3">
+        <v>143</v>
+      </c>
+      <c r="B144" s="4"/>
+      <c r="C144" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D144" s="5">
+        <v>4</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="3">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4"/>
+      <c r="C145" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D145" s="5">
+        <v>2</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="3">
+        <v>145</v>
+      </c>
+      <c r="B146" s="4"/>
+      <c r="C146" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D146" s="5">
+        <v>7</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="3">
+        <v>146</v>
+      </c>
+      <c r="B147" s="4"/>
+      <c r="C147" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D147" s="5">
+        <v>2</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="3">
+        <v>147</v>
+      </c>
+      <c r="B148" s="4"/>
+      <c r="C148" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D138" s="5">
-        <v>30</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>82</v>
+      <c r="D148" s="5">
+        <v>14</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="3">
+        <v>148</v>
+      </c>
+      <c r="B149" s="4"/>
+      <c r="C149" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D149" s="5">
+        <v>4</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="3">
+        <v>149</v>
+      </c>
+      <c r="B150" s="4"/>
+      <c r="C150" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D150" s="5">
+        <v>26.84</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="3">
+        <v>150</v>
+      </c>
+      <c r="B151" s="4"/>
+      <c r="C151" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D151" s="5">
+        <v>6</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="3">
+        <v>151</v>
+      </c>
+      <c r="B152" s="4"/>
+      <c r="C152" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D152" s="5">
+        <v>24.14</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="3">
+        <v>152</v>
+      </c>
+      <c r="B153" s="4"/>
+      <c r="C153" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D153" s="5">
+        <v>2.15</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="3">
+        <v>153</v>
+      </c>
+      <c r="B154" s="4"/>
+      <c r="C154" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D154" s="5">
+        <v>3.41</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="3">
+        <v>154</v>
+      </c>
+      <c r="B155" s="4"/>
+      <c r="C155" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D155" s="5">
+        <v>212.17</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="3">
+        <v>155</v>
+      </c>
+      <c r="B156" s="4"/>
+      <c r="C156" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D156" s="5">
+        <v>49</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="3">
+        <v>156</v>
+      </c>
+      <c r="B157" s="4"/>
+      <c r="C157" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D157" s="5">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="3">
+        <v>157</v>
+      </c>
+      <c r="B158" s="4"/>
+      <c r="C158" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D158" s="5">
+        <v>5</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="3">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4"/>
+      <c r="C159" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D159" s="5">
+        <v>411</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="3">
+        <v>159</v>
+      </c>
+      <c r="B160" s="4"/>
+      <c r="C160" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D160" s="5">
+        <v>4.01</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="3">
+        <v>160</v>
+      </c>
+      <c r="B161" s="4"/>
+      <c r="C161" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D161" s="5">
+        <v>4</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="3">
+        <v>161</v>
+      </c>
+      <c r="B162" s="4"/>
+      <c r="C162" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D162" s="5">
+        <v>16</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF9D92-EBF0-45FF-9580-1FA8D10B55AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D235D03F-DE49-4340-8B94-92219173260F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="140">
   <si>
     <t>№ п/п</t>
   </si>
@@ -54,244 +54,226 @@
     <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
   </si>
   <si>
-    <t>ЛГУП-7315</t>
+    <t>Каска строительная оранжевая Исток</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>ЛГУП-7331</t>
+  </si>
+  <si>
+    <t>шт</t>
+  </si>
+  <si>
+    <t>Ветошь</t>
+  </si>
+  <si>
+    <t>Маркер белый</t>
+  </si>
+  <si>
+    <t>Каска строительная белая</t>
+  </si>
+  <si>
+    <t>Маркер  краска красный по металлу</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
+  </si>
+  <si>
+    <t>пара</t>
+  </si>
+  <si>
+    <t>Перчатки с латесным покрытием</t>
+  </si>
+  <si>
+    <t>пар</t>
   </si>
   <si>
     <t>Огнетушитель ОП-8</t>
   </si>
   <si>
-    <t>шт.</t>
-  </si>
-  <si>
-    <t>ЛГУП-7331</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Каска строительная белая</t>
-  </si>
-  <si>
-    <t>Маркер белый</t>
-  </si>
-  <si>
-    <t>Ветошь</t>
-  </si>
-  <si>
-    <t>Перчатки с латесным покрытием</t>
-  </si>
-  <si>
-    <t>пар</t>
-  </si>
-  <si>
-    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
-  </si>
-  <si>
-    <t>пара</t>
-  </si>
-  <si>
-    <t>Каска строительная оранжевая Исток</t>
-  </si>
-  <si>
-    <t>шт</t>
-  </si>
-  <si>
-    <t>Маркер  краска красный по металлу</t>
+    <t>Кувалда 1 кг.</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Резак</t>
+  </si>
+  <si>
+    <t>Ножницы по металлу</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 24</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 30</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 36</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 41</t>
   </si>
   <si>
     <t>Гайковерт</t>
   </si>
   <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 41</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 36</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 30</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 24</t>
-  </si>
-  <si>
     <t>Ключи обмедненные</t>
   </si>
   <si>
     <t>набор</t>
   </si>
   <si>
-    <t>Трещетка ключ 1/2</t>
-  </si>
-  <si>
-    <t>Ножницы по металлу</t>
-  </si>
-  <si>
-    <t>Резак</t>
-  </si>
-  <si>
-    <t>Кувалда 1 кг.</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ-115 желтая (22кг)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7334</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ 115 красная 1,8кг STATUS /6</t>
-  </si>
-  <si>
-    <t>Растворитель 646 (5л)</t>
-  </si>
-  <si>
-    <t>Растворитель Р-4 /кг/</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ-115 коричневая (25 кг), шт</t>
-  </si>
-  <si>
     <t>Дробемет для швеллера с конвейерной сеткой</t>
   </si>
   <si>
     <t>ЛГУП-7338</t>
   </si>
   <si>
-    <t>Маркировка фланца</t>
-  </si>
-  <si>
-    <t>ЛГУП-7339</t>
-  </si>
-  <si>
-    <t>Шина</t>
-  </si>
-  <si>
-    <t>НТУП-017968</t>
+    <t>Строительство фундамента лестничной клетки(без учета материала)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7342</t>
+  </si>
+  <si>
+    <t>Строительство Промышленного пола(без учета материала)</t>
   </si>
   <si>
     <t>Строительство Отмоски и цоколя(без учета материала)</t>
   </si>
   <si>
-    <t>ЛГУП-7342</t>
-  </si>
-  <si>
-    <t>Строительство Промышленного пола(без учета материала)</t>
-  </si>
-  <si>
-    <t>Строительство фундамента лестничной клетки(без учета материала)</t>
+    <t>ЛГУП-7357</t>
+  </si>
+  <si>
+    <t>л (дм3)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7367</t>
+  </si>
+  <si>
+    <t>ЛГУП-7375</t>
+  </si>
+  <si>
+    <t>ЛГУП-7378</t>
+  </si>
+  <si>
+    <t>Окно 1100х900 мм /шт/ (ПВХ-профили морозостойкого исп) рал9016 белый</t>
+  </si>
+  <si>
+    <t>Труба 377х10, 09Г2с / тн</t>
+  </si>
+  <si>
+    <t>т</t>
+  </si>
+  <si>
+    <t>НТУП-017990</t>
+  </si>
+  <si>
+    <t>Труба 720х12 ст.09Г2С/кг</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН 2,0 ГОСТ 19903-80/ 20 ГОСТ 16523-89</t>
+  </si>
+  <si>
+    <t>ЛГУП-7391</t>
   </si>
   <si>
     <t>м</t>
   </si>
   <si>
-    <t>ЛГУП-7347</t>
-  </si>
-  <si>
-    <t>ЛГУП-7349</t>
-  </si>
-  <si>
-    <t>Фланец 25-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>ЛГУП-7356</t>
-  </si>
-  <si>
-    <t>ЛГУП-7357</t>
-  </si>
-  <si>
-    <t>ЛГУП-7365</t>
-  </si>
-  <si>
-    <t>л (дм3)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7367</t>
-  </si>
-  <si>
-    <t>ЛГУП-7374</t>
-  </si>
-  <si>
-    <t>ЛГУП-7375</t>
-  </si>
-  <si>
-    <t>ЛГУП-7378</t>
-  </si>
-  <si>
-    <t>Окно 1100х900 мм /шт/ (ПВХ-профили морозостойкого исп) рал9016 белый</t>
-  </si>
-  <si>
-    <t>Туя Смарагд высота 1,5 м</t>
-  </si>
-  <si>
-    <t>ЛГУП-7381</t>
-  </si>
-  <si>
-    <t>Укладка бордюрного камня 340 м</t>
-  </si>
-  <si>
-    <t>ед</t>
-  </si>
-  <si>
-    <t>ЛГУП-7382</t>
-  </si>
-  <si>
-    <t>Труба 720х12 ст.09Г2С/кг</t>
-  </si>
-  <si>
-    <t>НТУП-017990</t>
-  </si>
-  <si>
-    <t>Труба 377х10, 09Г2с / тн</t>
-  </si>
-  <si>
-    <t>т</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2537х1000х100 снаружи RAL 9016/ внутри RAL 9016</t>
-  </si>
-  <si>
-    <t>ЛГУП-7391</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 438х1000х100мм Ral 9016(белый)</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2526х1000х100 снаружи RAL 9016/ внутри RAL 9016</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2337х1000х100 снаружи RAL 9016/ внутри RAL 9016</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2232х1000х100 снаружи RAL 9016/ внутри RAL 9016</t>
-  </si>
-  <si>
-    <t>Панель кровельная 3205х1000х150,внутри RAL9016(белый)/снаружи Ral 2007</t>
-  </si>
-  <si>
-    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 2007(оранж)</t>
-  </si>
-  <si>
-    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 9016(белый)</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН 2,0 ГОСТ 19903-80/ 20 ГОСТ 16523-89</t>
-  </si>
-  <si>
-    <t>Услуги связи</t>
-  </si>
-  <si>
-    <t>00УП-000005</t>
-  </si>
-  <si>
-    <t>Услуга автокрана</t>
-  </si>
-  <si>
-    <t>АМУП-000091</t>
+    <t>Средство для чистки сантехники Антиржавчина Grass WC-gel 0,75 л</t>
+  </si>
+  <si>
+    <t>ЛГУП-7408</t>
+  </si>
+  <si>
+    <t>Средство чистящее для стекол Grass Clean Glass голубая лагуна 600мл</t>
+  </si>
+  <si>
+    <t>Метла</t>
+  </si>
+  <si>
+    <t>Средство для чистки универсальное Пемоксоль санитарный 500г.</t>
+  </si>
+  <si>
+    <t>Туалетная бумага</t>
+  </si>
+  <si>
+    <t>Средство для мытья пола 5 л</t>
+  </si>
+  <si>
+    <t>Салфетка для уборки и полировки микрофибра 25х25см 5шт</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>Карандаш</t>
+  </si>
+  <si>
+    <t>ЛГУП-7409</t>
+  </si>
+  <si>
+    <t>Ручка</t>
+  </si>
+  <si>
+    <t>Папка-вкладыш с расширением (на 250 листов) ПВХ 180мкм</t>
+  </si>
+  <si>
+    <t>Файл-вкладыш А4 прозрачный гладкий 100 шт. в упаковке</t>
+  </si>
+  <si>
+    <t>Фланец 100-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>ЛГУП-7410</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 50-40-11-1-Е 09ГСФ-IV ГОСТ 33259-2015 (п/ф)</t>
+  </si>
+  <si>
+    <t>Фланец 150-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 50-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 150-40-11-1-Е-09Г2С-IV ГОСТ 33259-2015 (п/ф из поковки)</t>
+  </si>
+  <si>
+    <t>Фланец 100-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Валик велюр тканный беж. 6х15х60мм ворс 4мм (2шт/уп) 1190062</t>
+  </si>
+  <si>
+    <t>АХУП-000663</t>
+  </si>
+  <si>
+    <t>ЛГУП-7413</t>
+  </si>
+  <si>
+    <t>ЛГУП-7415</t>
+  </si>
+  <si>
+    <t>м2</t>
   </si>
   <si>
     <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
@@ -306,21 +288,21 @@
     <t>Труба D720х12 Ст.09Г2С-К50 ГОСТ 20295-85</t>
   </si>
   <si>
+    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
+  </si>
+  <si>
     <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
     <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
   </si>
   <si>
-    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
-  </si>
-  <si>
     <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
   </si>
   <si>
@@ -333,277 +315,136 @@
     <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
   </si>
   <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
-  </si>
-  <si>
-    <t>Труба D108х11 Ст. 20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Труба D146х22 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D140х25 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D57х5 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
+    <t>Маркер черный</t>
   </si>
   <si>
     <t>Фумлента</t>
   </si>
   <si>
-    <t>Маркер черный</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Круг ДКРН D48 НД БрАЖ9-4 ГОСТ 1628-78</t>
-  </si>
-  <si>
-    <t>Круг D165 09Г2С-8-ТО ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Круг D450 Ст.09Г2С ГОСТ 2590-2006</t>
-  </si>
-  <si>
-    <t>Лист S=1 ст.09Г2С ГОСТ16523-89</t>
-  </si>
-  <si>
-    <t>Полоса 30х30 Ст.20Л</t>
-  </si>
-  <si>
-    <t>Шестигранник S=17 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=46 Ст.45 ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=46 Ст.09Г2С ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=30 Ст.45 ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=30 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=27 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=24 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
-    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
-    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
-  </si>
-  <si>
-    <t>Шайба 30.Ст3сп3.II.4.019 ГОСТ 9065-75</t>
-  </si>
-  <si>
-    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Шайба 16 ГОСТ 6958-78</t>
-  </si>
-  <si>
-    <t>Шпилька АМ16-6gx80 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Заклепка 4х8.31 ГОСТ 10299-80</t>
-  </si>
-  <si>
-    <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+    <t>Разбавитель Procore Universal Thinner</t>
   </si>
   <si>
     <t>Растворитель Р-4 ГОСТ 7827-74</t>
   </si>
   <si>
+    <t>Краска-спрей SABOTAGE (желтая)</t>
+  </si>
+  <si>
+    <t>Краска-спрей SABOTAGE 39(черный)</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
     <t>Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
   </si>
   <si>
-    <t>Краска-спрей SABOTAGE (желтая)</t>
-  </si>
-  <si>
-    <t>Краска-спрей SABOTAGE 39(черный)</t>
-  </si>
-  <si>
-    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>Разбавитель Procore Universal Thinner</t>
-  </si>
-  <si>
-    <t>Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
-  </si>
-  <si>
-    <t>Шпилька 2М16х1,5-6gx120.109.40Х.26 ГОСТ 22034-76</t>
-  </si>
-  <si>
-    <t>Саморез металл/металл 4,2х19</t>
-  </si>
-  <si>
-    <t>Саморез кровельный 6,3*70</t>
-  </si>
-  <si>
-    <t>Саморез кровельный 5,5х25 RAL9016 (белый)</t>
-  </si>
-  <si>
-    <t>Саморез кровельный 5,5х25 RAL 2007(оранж)</t>
-  </si>
-  <si>
-    <t>Гайка М20-6Н ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
-  </si>
-  <si>
-    <t>Болт М20х50 ГОСТ15591-70</t>
-  </si>
-  <si>
-    <t>Саморез для сэндвич панелей 5,5х25</t>
-  </si>
-  <si>
-    <t>Заклепка 4,8х8 оцинкованная</t>
-  </si>
-  <si>
-    <t>Заклепка 4,8х10</t>
-  </si>
-  <si>
-    <t>Саморез кровельный 5,5х19 RAL9016 (белый)</t>
-  </si>
-  <si>
-    <t>Шпилька резьбовая оцинкованная M12 DIN 975</t>
+    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
+  </si>
+  <si>
+    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба профильная 50х25х3 Ст.3сп5 ГОСТ 8645-68</t>
+  </si>
+  <si>
+    <t>Труба профильная 60х60х5 ГОСТ 8639-82/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 63х63х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Уголок 63х63х4 ГОСТ 8509-93 / 09Г2С ГОСТ5521-93</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
   </si>
   <si>
     <t>Профиль 50х25х3 ст.09Г2С ГОСТ 30245-2012</t>
   </si>
   <si>
-    <t>Труба профильная 60х60х5 ГОСТ 8639-82/09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
-  </si>
-  <si>
-    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
   </si>
   <si>
     <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
   </si>
   <si>
-    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Труба профильная 50х25х3 Ст.3сп5 ГОСТ 8645-68</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 63х63х4 ГОСТ 8509-93 / 09Г2С ГОСТ5521-93</t>
-  </si>
-  <si>
-    <t>Уголок 63х63х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
+    <t>Сольвент ГОСТ 10214-78</t>
   </si>
   <si>
     <t>Эмаль ПФ-115 белая</t>
   </si>
   <si>
+    <t>Дверь левая с доводчиком 1900х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
+  </si>
+  <si>
     <t>Дверь левая с доводчиком 2000х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
   </si>
   <si>
-    <t>Дверь левая с доводчиком 1900х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
-  </si>
-  <si>
-    <t>Сольвент ГОСТ 10214-78</t>
+    <t>Лента ПВХ облицовочная декоративн самоклеющаяся, шириной 19мм</t>
+  </si>
+  <si>
+    <t>Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
+  </si>
+  <si>
+    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 7036(Серый)</t>
+  </si>
+  <si>
+    <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
+  </si>
+  <si>
+    <t>Лист оцинкованный ОЦ Б-ПН-НО-0,5 ГОСТ 19904-90/ОН-КР ГОСТ 14918-80 (кг)</t>
+  </si>
+  <si>
+    <t>Лист S=5 Ст.3 ГОСТ 380-2005</t>
+  </si>
+  <si>
+    <t>Лист S=4 ст.09Г2С ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист S=2 ГОСТ 19903-74/ Ст.09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг D25 ГОСТ 2590-06/ 345-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Круг D20 09Г2С ГОСТ 19281-2014</t>
   </si>
   <si>
     <t>Круг D10 ГОСТ 2590-2006/ Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
-    <t>Круг D20 09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 3100х1000х100 RAL 9016/9016</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2450х1000х80 RAL 9016 (бел) снаружи/ RAL 9016 (белый) внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2270х1000х80 RAL 9016 снаружи/ RAL 9016 (бел.) внутри</t>
-  </si>
-  <si>
-    <t>Лист профилированный С21-1000-0,7 L=650мм RAL 2007 (оранжевый)</t>
-  </si>
-  <si>
-    <t>Лист профилированный С21-1000-0,7 L=2600 мм RAL2007 (оранж)</t>
-  </si>
-  <si>
-    <t>Лист профилированный С21-1000-0,7 L=1600мм RAL 2007(Оранжевый)</t>
-  </si>
-  <si>
-    <t>Лист профилированный С21-1000-0,7 L=1015мм RAL 1021 (желт)</t>
-  </si>
-  <si>
-    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 7036(Серый)</t>
-  </si>
-  <si>
-    <t>Круг D25 ГОСТ 2590-06/ 345-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Лента ПВХ облицовочная декоративн самоклеющаяся, шириной 19мм</t>
-  </si>
-  <si>
-    <t>Лист S=2 ГОСТ 19903-74/ Ст.09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Лист S=4 ст.09Г2С ГОСТ 14637-89</t>
-  </si>
-  <si>
-    <t>Лист S=5 Ст.3 ГОСТ 380-2005</t>
-  </si>
-  <si>
-    <t>Лист оцинкованный ОЦ Б-ПН-НО-0,5 ГОСТ 19904-90/ОН-КР ГОСТ 14918-80 (кг)</t>
-  </si>
-  <si>
-    <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
-  </si>
-  <si>
     <t>Лист Б-ПН-2,0 ГОСТ 19903-74 / Ст3 ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Кольцо 080-090-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Пружина №467 НТ.200.000.029.0</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
+  </si>
+  <si>
+    <t>Кольцо 350-360-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
+  </si>
+  <si>
+    <t>Круг D90 Ст.20Х13 ГОСТ 5632-72</t>
+  </si>
+  <si>
+    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
   </si>
 </sst>
 </file>
@@ -1040,12 +881,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="56.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
@@ -1077,7 +918,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D2" s="5">
         <v>20.399999999999999</v>
@@ -1095,7 +936,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D3" s="5">
         <v>48.6</v>
@@ -1113,7 +954,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D4" s="7">
         <v>2000</v>
@@ -1131,7 +972,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D5" s="7">
         <v>4500</v>
@@ -1149,10 +990,10 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5">
-        <v>97.8</v>
+        <v>47.85</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>6</v>
@@ -1167,10 +1008,10 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D7" s="5">
-        <v>57.15</v>
+        <v>233.85</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>6</v>
@@ -1185,10 +1026,10 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="D8" s="5">
-        <v>47.85</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>6</v>
@@ -1203,10 +1044,10 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D9" s="5">
-        <v>233.85</v>
+        <v>95.25</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>6</v>
@@ -1221,10 +1062,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D10" s="5">
-        <v>291.60000000000002</v>
+        <v>97.8</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>6</v>
@@ -1239,10 +1080,10 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D11" s="5">
-        <v>95.25</v>
+        <v>57.15</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>6</v>
@@ -1257,7 +1098,7 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D12" s="5">
         <v>33.75</v>
@@ -1275,7 +1116,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D13" s="5">
         <v>16.5</v>
@@ -1293,7 +1134,7 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D14" s="5">
         <v>7.05</v>
@@ -1311,7 +1152,7 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D15" s="5">
         <v>193.2</v>
@@ -1323,238 +1164,238 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="D16" s="5">
-        <v>6.64</v>
+        <v>10</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D17" s="5">
-        <v>13.76</v>
+        <v>40</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D18" s="5">
-        <v>0.43</v>
+        <v>10</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="D19" s="5">
-        <v>3.56</v>
+        <v>40</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D20" s="5">
-        <v>2.87</v>
+        <v>5</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="D21" s="5">
-        <v>11.48</v>
+        <v>5</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="D22" s="5">
-        <v>24.24</v>
+        <v>40</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="D23" s="5">
-        <v>17.84</v>
+        <v>20</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5">
-        <v>3.97</v>
+        <v>20</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="D25" s="5">
-        <v>5.16</v>
+        <v>500</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="D26" s="5">
-        <v>146.4</v>
+        <v>800</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="D27" s="5">
-        <v>36.6</v>
+        <v>15</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="D28" s="5">
-        <v>1.52</v>
+        <v>6</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1563,16 +1404,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D29" s="5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1581,16 +1422,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D30" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1599,16 +1440,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D31" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1617,16 +1458,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D32" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1635,16 +1476,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="D33" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1653,16 +1494,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D34" s="5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1671,16 +1512,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D35" s="5">
         <v>10</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1689,16 +1530,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D36" s="5">
-        <v>800</v>
+        <v>2</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1707,34 +1548,34 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D37" s="5">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D38" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1743,16 +1584,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D39" s="5">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1761,16 +1602,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D40" s="5">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1779,106 +1620,106 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D41" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="D42" s="5">
-        <v>10</v>
+        <v>11.43</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="D43" s="5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="D44" s="5">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D45" s="5">
-        <v>10</v>
+        <v>58.32</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="D46" s="5">
-        <v>10</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1887,16 +1728,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D47" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1905,16 +1746,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D48" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1923,16 +1764,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D49" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1941,160 +1782,160 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D50" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D51" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="D52" s="5">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="D53" s="5">
-        <v>10</v>
+        <v>32.659999999999997</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="D54" s="5">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>54</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="D55" s="5">
-        <v>4</v>
+        <v>79.44</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="D56" s="5">
-        <v>1</v>
+        <v>279.08</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>56</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" s="5">
+        <v>308.89</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D57" s="5">
-        <v>400</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>57</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="D58" s="5">
-        <v>4</v>
+        <v>41.21</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2103,16 +1944,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="D59" s="5">
-        <v>1</v>
+        <v>55.64</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2121,16 +1962,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D60" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2139,16 +1980,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="D61" s="5">
-        <v>1</v>
+        <v>50.8</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2157,160 +1998,160 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D62" s="5">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D63" s="5">
-        <v>4.1399999999999997</v>
+        <v>916.44</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>63</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D64" s="5">
-        <v>27.51</v>
+        <v>0.7</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>64</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="D65" s="5">
-        <v>167.4</v>
+        <v>2</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D66" s="5">
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>66</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D67" s="5">
-        <v>1.59</v>
+        <v>1</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D68" s="5">
-        <v>0.21</v>
+        <v>2</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>68</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="D69" s="5">
-        <v>4.32</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D70" s="5">
-        <v>3.6</v>
+        <v>51</v>
+      </c>
+      <c r="D70" s="7">
+        <v>1000</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2319,16 +2160,16 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="D71" s="5">
-        <v>1.62</v>
+        <v>26.84</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2337,16 +2178,16 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D72" s="5">
-        <v>0.72</v>
+        <v>2.15</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2355,16 +2196,16 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D73" s="5">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2373,16 +2214,16 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D74" s="5">
-        <v>0.42</v>
+        <v>4</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2391,16 +2232,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="D75" s="5">
-        <v>3</v>
+        <v>411</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2409,16 +2250,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D76" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2427,16 +2268,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D77" s="5">
-        <v>15</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2445,16 +2286,16 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="D78" s="5">
-        <v>19.559999999999999</v>
+        <v>49</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2463,16 +2304,16 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="D79" s="5">
-        <v>11.43</v>
+        <v>212.17</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2481,16 +2322,16 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="D80" s="5">
-        <v>18</v>
+        <v>3.41</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2499,16 +2340,16 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="D81" s="5">
-        <v>4.08</v>
+        <v>24.14</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2517,16 +2358,16 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="D82" s="5">
-        <v>58.32</v>
+        <v>6</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2535,16 +2376,16 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D83" s="5">
-        <v>3</v>
+        <v>6.52</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2553,16 +2394,16 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D84" s="5">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2571,16 +2412,16 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D85" s="5">
-        <v>6</v>
+        <v>4.01</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2589,16 +2430,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="D86" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2607,16 +2448,16 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="D87" s="5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2625,16 +2466,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="D88" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2643,16 +2484,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="D89" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2661,286 +2502,286 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="D90" s="5">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>90</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="D91" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>91</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="D92" s="5">
-        <v>9.9</v>
+        <v>4</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>92</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="D94" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="D95" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>142</v>
+        <v>68</v>
       </c>
       <c r="D96" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="D97" s="5">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="D98" s="5">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="D99" s="5">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="D100" s="5">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="D101" s="5">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D102" s="7">
-        <v>1100</v>
+        <v>75</v>
+      </c>
+      <c r="D102" s="5">
+        <v>100</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="D103" s="5">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="D104" s="5">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>104</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="D105" s="5">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2949,16 +2790,16 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="D106" s="5">
-        <v>416</v>
+        <v>50</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2967,16 +2808,16 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="D107" s="5">
         <v>30</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2985,16 +2826,16 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="D108" s="5">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3003,16 +2844,16 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D109" s="5">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3021,16 +2862,16 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D110" s="5">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3039,16 +2880,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D111" s="5">
-        <v>50.8</v>
+        <v>31.7</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3057,916 +2898,16 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="D112" s="5">
-        <v>279.08</v>
+        <v>0.15</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
-        <v>112</v>
-      </c>
-      <c r="B113" s="4"/>
-      <c r="C113" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D113" s="5">
-        <v>32.659999999999997</v>
-      </c>
-      <c r="E113" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="3">
-        <v>113</v>
-      </c>
-      <c r="B114" s="4"/>
-      <c r="C114" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D114" s="5">
-        <v>7.8</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="3">
-        <v>114</v>
-      </c>
-      <c r="B115" s="4"/>
-      <c r="C115" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D115" s="5">
-        <v>916.44</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="3">
-        <v>115</v>
-      </c>
-      <c r="B116" s="4"/>
-      <c r="C116" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D116" s="5">
-        <v>12</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="3">
-        <v>116</v>
-      </c>
-      <c r="B117" s="4"/>
-      <c r="C117" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D117" s="5">
-        <v>79.44</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="3">
-        <v>117</v>
-      </c>
-      <c r="B118" s="4"/>
-      <c r="C118" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D118" s="5">
-        <v>21</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="3">
-        <v>118</v>
-      </c>
-      <c r="B119" s="4"/>
-      <c r="C119" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D119" s="5">
-        <v>55.64</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="3">
-        <v>119</v>
-      </c>
-      <c r="B120" s="4"/>
-      <c r="C120" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D120" s="5">
-        <v>41.21</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="3">
-        <v>120</v>
-      </c>
-      <c r="B121" s="4"/>
-      <c r="C121" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D121" s="5">
-        <v>308.89</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="3">
-        <v>121</v>
-      </c>
-      <c r="B122" s="4"/>
-      <c r="C122" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D122" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="3">
-        <v>122</v>
-      </c>
-      <c r="B123" s="4"/>
-      <c r="C123" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D123" s="5">
-        <v>2</v>
-      </c>
-      <c r="E123" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="3">
-        <v>123</v>
-      </c>
-      <c r="B124" s="4"/>
-      <c r="C124" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D124" s="5">
-        <v>1</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="3">
-        <v>124</v>
-      </c>
-      <c r="B125" s="4"/>
-      <c r="C125" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D125" s="5">
-        <v>2</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="3">
-        <v>125</v>
-      </c>
-      <c r="B126" s="4"/>
-      <c r="C126" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D126" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="3">
-        <v>126</v>
-      </c>
-      <c r="B127" s="4"/>
-      <c r="C127" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D127" s="5">
-        <v>150</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="3">
-        <v>127</v>
-      </c>
-      <c r="B128" s="4"/>
-      <c r="C128" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D128" s="5">
-        <v>1</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="3">
-        <v>128</v>
-      </c>
-      <c r="B129" s="4"/>
-      <c r="C129" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D129" s="7">
-        <v>1000</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="3">
-        <v>129</v>
-      </c>
-      <c r="B130" s="4"/>
-      <c r="C130" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D130" s="5">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="3">
-        <v>130</v>
-      </c>
-      <c r="B131" s="4"/>
-      <c r="C131" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D131" s="5">
-        <v>6</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="3">
-        <v>131</v>
-      </c>
-      <c r="B132" s="4"/>
-      <c r="C132" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D132" s="5">
-        <v>2</v>
-      </c>
-      <c r="E132" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="3">
-        <v>132</v>
-      </c>
-      <c r="B133" s="4"/>
-      <c r="C133" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D133" s="5">
-        <v>2</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="3">
-        <v>133</v>
-      </c>
-      <c r="B134" s="4"/>
-      <c r="C134" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D134" s="5">
-        <v>2</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="3">
-        <v>134</v>
-      </c>
-      <c r="B135" s="4"/>
-      <c r="C135" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D135" s="5">
-        <v>6</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="3">
-        <v>135</v>
-      </c>
-      <c r="B136" s="4"/>
-      <c r="C136" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="D136" s="5">
-        <v>6</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="3">
-        <v>136</v>
-      </c>
-      <c r="B137" s="4"/>
-      <c r="C137" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D137" s="5">
-        <v>10</v>
-      </c>
-      <c r="E137" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="3">
-        <v>137</v>
-      </c>
-      <c r="B138" s="4"/>
-      <c r="C138" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D138" s="5">
-        <v>16</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="3">
-        <v>138</v>
-      </c>
-      <c r="B139" s="4"/>
-      <c r="C139" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D139" s="5">
-        <v>6.52</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="3">
-        <v>139</v>
-      </c>
-      <c r="B140" s="4"/>
-      <c r="C140" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D140" s="5">
-        <v>1</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="3">
-        <v>140</v>
-      </c>
-      <c r="B141" s="4"/>
-      <c r="C141" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D141" s="5">
-        <v>3</v>
-      </c>
-      <c r="E141" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="3">
-        <v>141</v>
-      </c>
-      <c r="B142" s="4"/>
-      <c r="C142" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D142" s="5">
-        <v>5</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="3">
-        <v>142</v>
-      </c>
-      <c r="B143" s="4"/>
-      <c r="C143" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="D143" s="5">
-        <v>7</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="3">
-        <v>143</v>
-      </c>
-      <c r="B144" s="4"/>
-      <c r="C144" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D144" s="5">
-        <v>4</v>
-      </c>
-      <c r="E144" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="3">
-        <v>144</v>
-      </c>
-      <c r="B145" s="4"/>
-      <c r="C145" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D145" s="5">
-        <v>2</v>
-      </c>
-      <c r="E145" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="3">
-        <v>145</v>
-      </c>
-      <c r="B146" s="4"/>
-      <c r="C146" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D146" s="5">
-        <v>7</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="3">
-        <v>146</v>
-      </c>
-      <c r="B147" s="4"/>
-      <c r="C147" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="D147" s="5">
-        <v>2</v>
-      </c>
-      <c r="E147" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="3">
-        <v>147</v>
-      </c>
-      <c r="B148" s="4"/>
-      <c r="C148" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D148" s="5">
-        <v>14</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F148" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="3">
-        <v>148</v>
-      </c>
-      <c r="B149" s="4"/>
-      <c r="C149" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D149" s="5">
-        <v>4</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="3">
-        <v>149</v>
-      </c>
-      <c r="B150" s="4"/>
-      <c r="C150" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D150" s="5">
-        <v>26.84</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="3">
-        <v>150</v>
-      </c>
-      <c r="B151" s="4"/>
-      <c r="C151" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D151" s="5">
-        <v>6</v>
-      </c>
-      <c r="E151" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="3">
-        <v>151</v>
-      </c>
-      <c r="B152" s="4"/>
-      <c r="C152" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D152" s="5">
-        <v>24.14</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="3">
-        <v>152</v>
-      </c>
-      <c r="B153" s="4"/>
-      <c r="C153" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D153" s="5">
-        <v>2.15</v>
-      </c>
-      <c r="E153" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F153" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="3">
-        <v>153</v>
-      </c>
-      <c r="B154" s="4"/>
-      <c r="C154" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D154" s="5">
-        <v>3.41</v>
-      </c>
-      <c r="E154" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F154" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="3">
-        <v>154</v>
-      </c>
-      <c r="B155" s="4"/>
-      <c r="C155" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D155" s="5">
-        <v>212.17</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="3">
-        <v>155</v>
-      </c>
-      <c r="B156" s="4"/>
-      <c r="C156" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D156" s="5">
-        <v>49</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F156" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="3">
-        <v>156</v>
-      </c>
-      <c r="B157" s="4"/>
-      <c r="C157" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D157" s="5">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F157" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="3">
-        <v>157</v>
-      </c>
-      <c r="B158" s="4"/>
-      <c r="C158" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D158" s="5">
-        <v>5</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F158" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="3">
-        <v>158</v>
-      </c>
-      <c r="B159" s="4"/>
-      <c r="C159" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D159" s="5">
-        <v>411</v>
-      </c>
-      <c r="E159" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="3">
-        <v>159</v>
-      </c>
-      <c r="B160" s="4"/>
-      <c r="C160" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D160" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F160" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="3">
-        <v>160</v>
-      </c>
-      <c r="B161" s="4"/>
-      <c r="C161" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D161" s="5">
-        <v>4</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F161" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="3">
-        <v>161</v>
-      </c>
-      <c r="B162" s="4"/>
-      <c r="C162" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D162" s="5">
-        <v>16</v>
-      </c>
-      <c r="E162" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D235D03F-DE49-4340-8B94-92219173260F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C15226-ACA9-414C-A703-D16BBC0C5C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="162">
   <si>
     <t>№ п/п</t>
   </si>
@@ -45,274 +45,181 @@
     <t>Примечание</t>
   </si>
   <si>
+    <t>шт</t>
+  </si>
+  <si>
+    <t>ЛГУП-7413</t>
+  </si>
+  <si>
     <t>кг</t>
   </si>
   <si>
-    <t>ЛГУП-7287</t>
-  </si>
-  <si>
-    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
+    <t>Маркер  краска красный по металлу</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>ЛГУП-7331</t>
+  </si>
+  <si>
+    <t>Каска строительная белая</t>
+  </si>
+  <si>
+    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
+  </si>
+  <si>
+    <t>пара</t>
+  </si>
+  <si>
+    <t>Перчатки с латесным покрытием</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
+    <t>Маркер белый</t>
+  </si>
+  <si>
+    <t>Ветошь</t>
   </si>
   <si>
     <t>Каска строительная оранжевая Исток</t>
   </si>
   <si>
-    <t>шт.</t>
-  </si>
-  <si>
-    <t>ЛГУП-7331</t>
-  </si>
-  <si>
-    <t>шт</t>
-  </si>
-  <si>
-    <t>Ветошь</t>
-  </si>
-  <si>
-    <t>Маркер белый</t>
-  </si>
-  <si>
-    <t>Каска строительная белая</t>
-  </si>
-  <si>
-    <t>Маркер  краска красный по металлу</t>
-  </si>
-  <si>
     <t>Маркер по металлу черный тонкий</t>
   </si>
   <si>
     <t>Маркер по металлу белый</t>
   </si>
   <si>
-    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
-  </si>
-  <si>
-    <t>пара</t>
-  </si>
-  <si>
-    <t>Перчатки с латесным покрытием</t>
-  </si>
-  <si>
-    <t>пар</t>
-  </si>
-  <si>
     <t>Огнетушитель ОП-8</t>
   </si>
   <si>
+    <t>Гайковерт</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 41</t>
+  </si>
+  <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 36</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 30</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 24</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
+  </si>
+  <si>
     <t>Кувалда 1 кг.</t>
   </si>
   <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
     <t>Резак</t>
   </si>
   <si>
     <t>Ножницы по металлу</t>
   </si>
   <si>
-    <t>Трещетка ключ 1/2</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 24</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 30</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 36</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 41</t>
-  </si>
-  <si>
-    <t>Гайковерт</t>
-  </si>
-  <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
-    <t>Дробемет для швеллера с конвейерной сеткой</t>
-  </si>
-  <si>
-    <t>ЛГУП-7338</t>
-  </si>
-  <si>
-    <t>Строительство фундамента лестничной клетки(без учета материала)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7342</t>
-  </si>
-  <si>
-    <t>Строительство Промышленного пола(без учета материала)</t>
-  </si>
-  <si>
-    <t>Строительство Отмоски и цоколя(без учета материала)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7357</t>
-  </si>
-  <si>
-    <t>л (дм3)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7367</t>
-  </si>
-  <si>
-    <t>ЛГУП-7375</t>
-  </si>
-  <si>
-    <t>ЛГУП-7378</t>
-  </si>
-  <si>
-    <t>Окно 1100х900 мм /шт/ (ПВХ-профили морозостойкого исп) рал9016 белый</t>
-  </si>
-  <si>
-    <t>Труба 377х10, 09Г2с / тн</t>
-  </si>
-  <si>
-    <t>т</t>
-  </si>
-  <si>
-    <t>НТУП-017990</t>
-  </si>
-  <si>
-    <t>Труба 720х12 ст.09Г2С/кг</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН 2,0 ГОСТ 19903-80/ 20 ГОСТ 16523-89</t>
-  </si>
-  <si>
-    <t>ЛГУП-7391</t>
+    <t>ЛГУП-7428</t>
+  </si>
+  <si>
+    <t>Днище 820х14-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 720х12 ст09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 377х10 09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Распылитель Тесла Трибо</t>
+  </si>
+  <si>
+    <t>ЛГУП-7429</t>
+  </si>
+  <si>
+    <t>ЛГУП-7445</t>
+  </si>
+  <si>
+    <t>ЛГУП-7446</t>
+  </si>
+  <si>
+    <t>ЛГУП-7447</t>
   </si>
   <si>
     <t>м</t>
   </si>
   <si>
-    <t>Средство для чистки сантехники Антиржавчина Grass WC-gel 0,75 л</t>
-  </si>
-  <si>
-    <t>ЛГУП-7408</t>
-  </si>
-  <si>
-    <t>Средство чистящее для стекол Grass Clean Glass голубая лагуна 600мл</t>
-  </si>
-  <si>
-    <t>Метла</t>
-  </si>
-  <si>
-    <t>Средство для чистки универсальное Пемоксоль санитарный 500г.</t>
-  </si>
-  <si>
-    <t>Туалетная бумага</t>
-  </si>
-  <si>
-    <t>Средство для мытья пола 5 л</t>
-  </si>
-  <si>
-    <t>Салфетка для уборки и полировки микрофибра 25х25см 5шт</t>
-  </si>
-  <si>
-    <t>компл</t>
-  </si>
-  <si>
-    <t>Карандаш</t>
-  </si>
-  <si>
-    <t>ЛГУП-7409</t>
-  </si>
-  <si>
-    <t>Ручка</t>
-  </si>
-  <si>
-    <t>Папка-вкладыш с расширением (на 250 листов) ПВХ 180мкм</t>
-  </si>
-  <si>
-    <t>Файл-вкладыш А4 прозрачный гладкий 100 шт. в упаковке</t>
-  </si>
-  <si>
-    <t>Фланец 100-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>ЛГУП-7410</t>
-  </si>
-  <si>
-    <t>Фланец 80-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 80-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 50-40-11-1-Е 09ГСФ-IV ГОСТ 33259-2015 (п/ф)</t>
-  </si>
-  <si>
-    <t>Фланец 150-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 50-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 150-40-11-1-Е-09Г2С-IV ГОСТ 33259-2015 (п/ф из поковки)</t>
-  </si>
-  <si>
-    <t>Фланец 100-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Валик велюр тканный беж. 6х15х60мм ворс 4мм (2шт/уп) 1190062</t>
-  </si>
-  <si>
-    <t>АХУП-000663</t>
-  </si>
-  <si>
-    <t>ЛГУП-7413</t>
-  </si>
-  <si>
-    <t>ЛГУП-7415</t>
-  </si>
-  <si>
-    <t>м2</t>
-  </si>
-  <si>
-    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Уголок 40х40х3 ГОСТ 8509-93/ Ст3пс ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Труба D377х12 ст.09Г2С-К50 ГОСТ 8731-78</t>
-  </si>
-  <si>
-    <t>Труба D720х12 Ст.09Г2С-К50 ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
-  </si>
-  <si>
-    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D34х4 Ст.09Г2С ГОСТ8733-75</t>
-  </si>
-  <si>
-    <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
+    <t>ЛГУП-7448</t>
+  </si>
+  <si>
+    <t>Перемычка и наконечник НКИ 6-0-6</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8</t>
+  </si>
+  <si>
+    <t>МИП-24 исп.20 (МИП-24-2/П5-Р-RS), до двух АКБ 12 В 17 Ач</t>
+  </si>
+  <si>
+    <t>Блок коммутации 24В БК-24-RS485-01</t>
+  </si>
+  <si>
+    <t>Индикатор положения поплавка ИПП 01.00.000</t>
+  </si>
+  <si>
+    <t>ЛГУП-7450</t>
+  </si>
+  <si>
+    <t>ЛГУП-7451</t>
+  </si>
+  <si>
+    <t>Обогреватель взрывозащищенный ОВЭ-4 ТК-1.0 1 кВт, 220В, 50 Гц.</t>
+  </si>
+  <si>
+    <t>Коробка клеммная К-СП 16.18.09 24/20П 4КВе-Л-М20(А)-4КВе-Л-М20(В) 1ЕхеLLCGbXT6, ip66, 160х180х90</t>
+  </si>
+  <si>
+    <t>Коробка соед взрывозащК-СП 16.26.09 24/31 П 8КВе-Л-М20(А) 8КВе-Л-М20(В) 1ЕхеLLCGb ip66, 160х260х90</t>
+  </si>
+  <si>
+    <t>К-СП 16.26.09 32/26П 6КВе-Л-М20(А)-6КВе-Л-М20(В)-1КВе-Л-М20(D) 1ExeLLCGbXT6 ip66 120х260х90</t>
+  </si>
+  <si>
+    <t>Газоанализатор взрывозащищенный СГОЭС 1Ex d IIC T4 Gb, IP67</t>
+  </si>
+  <si>
+    <t>Палитра цветов</t>
+  </si>
+  <si>
+    <t>ЛГУП-7454</t>
+  </si>
+  <si>
+    <t>ЛГУП-7457</t>
+  </si>
+  <si>
+    <t>ЛГУП-7460</t>
+  </si>
+  <si>
+    <t>ЛГУП-7462</t>
+  </si>
+  <si>
+    <t>Кольцо 350-360-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Смола ЭД-20 ГОСТ 10587-84</t>
   </si>
   <si>
     <t>Маркер черный</t>
@@ -321,130 +228,289 @@
     <t>Фумлента</t>
   </si>
   <si>
-    <t>Разбавитель Procore Universal Thinner</t>
-  </si>
-  <si>
-    <t>Растворитель Р-4 ГОСТ 7827-74</t>
-  </si>
-  <si>
-    <t>Краска-спрей SABOTAGE (желтая)</t>
-  </si>
-  <si>
-    <t>Краска-спрей SABOTAGE 39(черный)</t>
-  </si>
-  <si>
-    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>Грунт-эмаль Дюропокс ДТМ 70 цвет серый (наружка)</t>
-  </si>
-  <si>
-    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
-  </si>
-  <si>
-    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба профильная 50х25х3 Ст.3сп5 ГОСТ 8645-68</t>
-  </si>
-  <si>
-    <t>Труба профильная 60х60х5 ГОСТ 8639-82/09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 63х63х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Уголок 63х63х4 ГОСТ 8509-93 / 09Г2С ГОСТ5521-93</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Профиль 50х25х3 ст.09Г2С ГОСТ 30245-2012</t>
-  </si>
-  <si>
-    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Сольвент ГОСТ 10214-78</t>
-  </si>
-  <si>
-    <t>Эмаль ПФ-115 белая</t>
-  </si>
-  <si>
-    <t>Дверь левая с доводчиком 1900х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
-  </si>
-  <si>
-    <t>Дверь левая с доводчиком 2000х1000 мм(ВхШ) полотно RAL 7036 (серый)/ коробка (RAL 7036) (серый)</t>
-  </si>
-  <si>
-    <t>Лента ПВХ облицовочная декоративн самоклеющаяся, шириной 19мм</t>
-  </si>
-  <si>
-    <t>Плита П-А,I,М,Ш,Е1(600х450х19) ГОСТ 10632-89</t>
-  </si>
-  <si>
-    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 7036(Серый)</t>
-  </si>
-  <si>
-    <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
-  </si>
-  <si>
-    <t>Лист оцинкованный ОЦ Б-ПН-НО-0,5 ГОСТ 19904-90/ОН-КР ГОСТ 14918-80 (кг)</t>
-  </si>
-  <si>
-    <t>Лист S=5 Ст.3 ГОСТ 380-2005</t>
-  </si>
-  <si>
-    <t>Лист S=4 ст.09Г2С ГОСТ 14637-89</t>
-  </si>
-  <si>
-    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Лист S=2 ГОСТ 19903-74/ Ст.09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Круг D25 ГОСТ 2590-06/ 345-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Круг D20 09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Круг D10 ГОСТ 2590-2006/ Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-2,0 ГОСТ 19903-74 / Ст3 ГОСТ 14637-89</t>
+    <t>Днище 219х4-25 ст.20 ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Шайба 16 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Труба ГКРХХ 110х17,5 БрАЖН 10-4-4 ГОСТ 1208-90</t>
+  </si>
+  <si>
+    <t>Труба 10х1,0 М3-ПТ ГОСТ 617-90</t>
+  </si>
+  <si>
+    <t>Фланец х-80-40 ГОСТ12821 (заготовка-поковка ст.20 гр.IV КП 195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Труба D89х6 ГОСТ 8732-78 Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>Труба D108х16 ГОСТ 8732-78/ Ст.40Х  ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
+  </si>
+  <si>
+    <t>Зажим клеммный винтовой 2,5 мм2 (50/1500/36000) Б0033416 ЭРА арт. Б0033416</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Заглушка NO-550-07 для винтовых клемм 2,5мм2 арт. Б0035737</t>
+  </si>
+  <si>
+    <t>Фиксатор ФК-102-01 на DIN-рейку 32057DEK Dekraft 2 арт. 32057DEK</t>
+  </si>
+  <si>
+    <t>DIN-рейка 50см перфорированная adr-50 EKF арт. adr-50</t>
+  </si>
+  <si>
+    <t>Разъем РпИм 1.25-5-0.8 плоский</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный НШвИ 0,75мм</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный НШвИ 1,5мм</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный НШвИ 2,5мм</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внешний CD 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внешний CD90 (100х50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 4.1.1</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 4.1.1</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 120</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 40х40 мм</t>
+  </si>
+  <si>
+    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Провод ПуГВнг(А)-LS 1x1,5</t>
+  </si>
+  <si>
+    <t>Провод ПуГВнг(А)-LS 1x0,75</t>
+  </si>
+  <si>
+    <t>Кабель-канал 40х40 перфорированный Plast kk40-40 EKF</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Шина заземления на DIN-изолятор ШНИ-6х9-8</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический двухполюсный 3А B ВА47-29 4.5кА MVA20-2-003-B IEK</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
+  </si>
+  <si>
+    <t>Коробка клеммная К-СП 08.13.09 24/11П 2КВе-Л-М20(А)-2КВе-Л-М20(В) 1ExeLLCGbXT6 ip66,80х130х90</t>
+  </si>
+  <si>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический двухполюсный IEK ARMAT M10N 2P B 10А AR-M10N-2-B010</t>
+  </si>
+  <si>
+    <t>Контроллер доступа "С2000-2"</t>
+  </si>
+  <si>
+    <t>Корпус металлический ЩМП-3-0 (650х500х220мм) У2 IP54 YKM40-03-54 IEK арт. YKM40-03-54</t>
+  </si>
+  <si>
+    <t>Карта proximity стандартная ST-PC010EM</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внутренний CS 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внутренний CS 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Прокладка медная 8х11-II ГОСТ 19752-84</t>
   </si>
   <si>
     <t>Кольцо 080-090-58 ГОСТ 9833-73</t>
   </si>
   <si>
-    <t>Пружина №467 НТ.200.000.029.0</t>
-  </si>
-  <si>
-    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
-  </si>
-  <si>
-    <t>Кольцо 350-360-58-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
-  </si>
-  <si>
-    <t>Круг D90 Ст.20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
+    <t>Кольцо 112-118-36 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 055-060-30-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.030</t>
+  </si>
+  <si>
+    <t>Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 065-075-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Уплотнение ПСМНТ.001.022.002</t>
+  </si>
+  <si>
+    <t>Обогреватель взрывозащищенный ОВЭ-4-УХЛ3 1,8 кВт, 380В IExdIIАТ3, IP54</t>
+  </si>
+  <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-15 IP65 2ExеdIIСТ6</t>
+  </si>
+  <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
+  </si>
+  <si>
+    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
+  </si>
+  <si>
+    <t>Датчик давления взрывозащ. СТИ775Ц-E-1-M-D-B-H-T-1</t>
+  </si>
+  <si>
+    <t>Лист Б-ПР-1,0 ГОСТ 19904-74/ 4-III-Ст3кп ГОСТ 16523-89</t>
+  </si>
+  <si>
+    <t>Шестигранник S=14 Ст.45 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D370 Ст.20 ГОСТ1050-88</t>
+  </si>
+  <si>
+    <t>Круг D45 Ст.40Х ГОСТ 4543-71</t>
+  </si>
+  <si>
+    <t>Круг D70 Ст.40Х ГОСТ 4543-71</t>
+  </si>
+  <si>
+    <t>Круг D430 Ст.16ГС ГОСТ 19281-14</t>
+  </si>
+  <si>
+    <t>Круг D195 Ст.16ГС-3 ГОСТ 5520-79</t>
+  </si>
+  <si>
+    <t>Шарик 25,4-100 ГОСТ 3722-81</t>
+  </si>
+  <si>
+    <t>Шпилька М18х40.56.019 ГОСТ 22034-76</t>
+  </si>
+  <si>
+    <t>Заклепка 2х4х37 Ан.Окс.хр. ГОСТ10299-80</t>
+  </si>
+  <si>
+    <t>Винт М16х50.56.019 ГОСТ 1481-84</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Оповещатель светозвуковой Маяк-24К IP53</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный дымовой ИП 212-141М</t>
   </si>
 </sst>
 </file>
@@ -881,12 +947,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
@@ -912,16 +978,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="D2" s="5">
-        <v>20.399999999999999</v>
+        <v>120</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>6</v>
@@ -930,19 +996,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D3" s="5">
-        <v>48.6</v>
+        <v>0.25</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>7</v>
@@ -954,16 +1020,16 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="7">
-        <v>2000</v>
+        <v>9</v>
+      </c>
+      <c r="D4" s="5">
+        <v>40</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -972,16 +1038,16 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="7">
-        <v>4500</v>
+        <v>12</v>
+      </c>
+      <c r="D5" s="5">
+        <v>5</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -990,16 +1056,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D6" s="5">
-        <v>47.85</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1008,16 +1074,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5">
-        <v>233.85</v>
+        <v>500</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1026,16 +1092,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5">
-        <v>291.60000000000002</v>
+        <v>800</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1044,16 +1110,16 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D9" s="5">
-        <v>95.25</v>
+        <v>5</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1062,16 +1128,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="D10" s="5">
-        <v>97.8</v>
+        <v>40</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1080,16 +1146,16 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5">
-        <v>57.15</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1098,16 +1164,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="D12" s="5">
-        <v>33.75</v>
+        <v>10</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1116,16 +1182,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1134,16 +1200,16 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="D14" s="5">
-        <v>7.05</v>
+        <v>20</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1152,304 +1218,304 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="D15" s="5">
-        <v>193.2</v>
+        <v>15</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D16" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="D17" s="5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D18" s="5">
         <v>10</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="D20" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D21" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D22" s="5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D23" s="5">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D24" s="5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D25" s="5">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D26" s="5">
-        <v>800</v>
+        <v>10</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D27" s="5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D28" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D29" s="5">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D30" s="5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D31" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1458,16 +1524,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="D32" s="5">
-        <v>10</v>
+        <v>53.25</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,16 +1542,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D33" s="5">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1494,16 +1560,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="D34" s="5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1512,16 +1578,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D35" s="5">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1530,16 +1596,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D36" s="5">
-        <v>2</v>
+        <v>99.25</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1548,34 +1614,34 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D37" s="5">
-        <v>10</v>
+        <v>18.25</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" s="5">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="D38" s="7">
+        <v>4286.5</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1584,16 +1650,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D39" s="5">
-        <v>1</v>
+        <v>148.5</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1602,16 +1668,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="D40" s="5">
-        <v>1</v>
+        <v>37.35</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1620,106 +1686,106 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="D41" s="5">
-        <v>1</v>
+        <v>271.75</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D42" s="5">
-        <v>11.43</v>
+        <v>2.1</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D43" s="5">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D44" s="5">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D45" s="5">
-        <v>58.32</v>
+        <v>20</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D46" s="5">
-        <v>19.559999999999999</v>
+        <v>2</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1728,16 +1794,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D47" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1746,16 +1812,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D48" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1764,16 +1830,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D49" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1782,16 +1848,16 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D50" s="5">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1800,16 +1866,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D51" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1818,16 +1884,16 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D52" s="5">
-        <v>9.9</v>
+        <v>20</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1836,10 +1902,10 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D53" s="5">
-        <v>32.659999999999997</v>
+        <v>4</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>6</v>
@@ -1854,10 +1920,10 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D54" s="5">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>6</v>
@@ -1872,10 +1938,10 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D55" s="5">
-        <v>79.44</v>
+        <v>4</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>6</v>
@@ -1890,10 +1956,10 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D56" s="5">
-        <v>279.08</v>
+        <v>4</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>6</v>
@@ -1908,10 +1974,10 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D57" s="5">
-        <v>308.89</v>
+        <v>4</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>6</v>
@@ -1926,10 +1992,10 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D58" s="5">
-        <v>41.21</v>
+        <v>1</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>6</v>
@@ -1944,10 +2010,10 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D59" s="5">
-        <v>55.64</v>
+        <v>1</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>6</v>
@@ -1962,10 +2028,10 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D60" s="5">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>6</v>
@@ -1980,10 +2046,10 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D61" s="5">
-        <v>50.8</v>
+        <v>30</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>6</v>
@@ -1998,10 +2064,10 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D62" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>6</v>
@@ -2016,10 +2082,10 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D63" s="5">
-        <v>916.44</v>
+        <v>7</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>6</v>
@@ -2034,16 +2100,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D64" s="5">
-        <v>0.7</v>
+        <v>15</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2052,16 +2118,16 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2070,16 +2136,16 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D66" s="5">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2088,16 +2154,16 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2106,16 +2172,16 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D68" s="5">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2124,16 +2190,16 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="D69" s="5">
-        <v>2.2999999999999998</v>
+        <v>8</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2142,646 +2208,646 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D70" s="7">
-        <v>1000</v>
+        <v>106</v>
+      </c>
+      <c r="D70" s="5">
+        <v>2</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>70</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="D71" s="5">
-        <v>26.84</v>
+        <v>1</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>71</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D72" s="5">
-        <v>2.15</v>
+        <v>16</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D74" s="5">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>74</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D75" s="5">
-        <v>411</v>
+        <v>112</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>75</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D76" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>76</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D77" s="5">
-        <v>8.1999999999999993</v>
+        <v>1</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>77</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D78" s="5">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>78</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D79" s="5">
-        <v>212.17</v>
+        <v>4</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>79</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D80" s="5">
-        <v>3.41</v>
+        <v>48</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D81" s="5">
-        <v>24.14</v>
+        <v>39</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D82" s="5">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>82</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D83" s="5">
-        <v>6.52</v>
+        <v>135</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D84" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>84</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="D85" s="5">
-        <v>4.01</v>
+        <v>70</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>85</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="D86" s="5">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>86</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="D87" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>87</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="D88" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>88</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="D89" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>89</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D90" s="5">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>90</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D91" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>91</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="D92" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>92</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="D93" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="D94" s="5">
         <v>10</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="D95" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="D96" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="D97" s="5">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="D98" s="5">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="D99" s="5">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="D100" s="5">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D101" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="D102" s="5">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="D103" s="5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="D104" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>104</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="D105" s="5">
         <v>50</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2790,16 +2856,16 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D106" s="5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2808,16 +2874,16 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D107" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2826,16 +2892,16 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D108" s="5">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2844,16 +2910,16 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D109" s="5">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2862,16 +2928,16 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D110" s="5">
-        <v>0.3</v>
+        <v>25</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2880,16 +2946,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D111" s="5">
-        <v>31.7</v>
+        <v>2</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2898,16 +2964,484 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="D112" s="5">
-        <v>0.15</v>
+        <v>2</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>81</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="3">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D113" s="5">
+        <v>2</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="3">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D114" s="5">
+        <v>2</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="3">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D115" s="5">
+        <v>2</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="3">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D116" s="5">
+        <v>1</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="3">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D117" s="5">
+        <v>1</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4"/>
+      <c r="C118" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D118" s="5">
+        <v>6</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="3">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D119" s="5">
+        <v>4</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4"/>
+      <c r="C120" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D120" s="5">
+        <v>1</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="3">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4"/>
+      <c r="C121" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D121" s="5">
+        <v>1</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="3">
+        <v>121</v>
+      </c>
+      <c r="B122" s="4"/>
+      <c r="C122" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D122" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="3">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4"/>
+      <c r="C123" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D123" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="3">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4"/>
+      <c r="C124" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D124" s="5">
+        <v>950</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="3">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4"/>
+      <c r="C125" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D125" s="5">
+        <v>131</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="3">
+        <v>125</v>
+      </c>
+      <c r="B126" s="4"/>
+      <c r="C126" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D126" s="5">
+        <v>26.5</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="3">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4"/>
+      <c r="C127" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D127" s="7">
+        <v>1415.25</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="3">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4"/>
+      <c r="C128" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D128" s="5">
+        <v>291</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="3">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4"/>
+      <c r="C129" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D129" s="5">
+        <v>25</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="3">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4"/>
+      <c r="C130" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D130" s="5">
+        <v>500</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="3">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4"/>
+      <c r="C131" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D131" s="5">
+        <v>50</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="3">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4"/>
+      <c r="C132" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D132" s="5">
+        <v>100</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="3">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4"/>
+      <c r="C133" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D133" s="5">
+        <v>36</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="3">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4"/>
+      <c r="C134" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D134" s="5">
+        <v>24</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="3">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4"/>
+      <c r="C135" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D135" s="5">
+        <v>2</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="3">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4"/>
+      <c r="C136" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D136" s="5">
+        <v>2</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="3">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4"/>
+      <c r="C137" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D137" s="5">
+        <v>30</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="3">
+        <v>137</v>
+      </c>
+      <c r="B138" s="4"/>
+      <c r="C138" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D138" s="5">
+        <v>6</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C15226-ACA9-414C-A703-D16BBC0C5C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899FF701-B3E4-4D5E-B966-3ED39BF75F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="166">
   <si>
     <t>№ п/п</t>
   </si>
@@ -54,63 +54,75 @@
     <t>кг</t>
   </si>
   <si>
+    <t>ЛГУП-7331</t>
+  </si>
+  <si>
     <t>Маркер  краска красный по металлу</t>
   </si>
   <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>ЛГУП-7331</t>
+    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
+  </si>
+  <si>
+    <t>пара</t>
+  </si>
+  <si>
+    <t>Перчатки с латесным покрытием</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
+    <t>Каска строительная оранжевая Исток</t>
+  </si>
+  <si>
+    <t>Огнетушитель ОП-8</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
   </si>
   <si>
     <t>Каска строительная белая</t>
   </si>
   <si>
-    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
-  </si>
-  <si>
-    <t>пара</t>
-  </si>
-  <si>
-    <t>Перчатки с латесным покрытием</t>
-  </si>
-  <si>
-    <t>пар</t>
-  </si>
-  <si>
     <t>Маркер белый</t>
   </si>
   <si>
     <t>Ветошь</t>
   </si>
   <si>
-    <t>Каска строительная оранжевая Исток</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Огнетушитель ОП-8</t>
+    <t>Резак</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Кувалда 1 кг.</t>
+  </si>
+  <si>
+    <t>Ножницы по металлу</t>
+  </si>
+  <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
   </si>
   <si>
     <t>Гайковерт</t>
   </si>
   <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
     <t>Ключ комбинированные омедненные 41</t>
   </si>
   <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
     <t>Ключ комбинированные омедненные 36</t>
   </si>
   <si>
@@ -120,27 +132,15 @@
     <t>Ключ комбинированные омедненные 24</t>
   </si>
   <si>
-    <t>Трещетка ключ 1/2</t>
-  </si>
-  <si>
-    <t>Кувалда 1 кг.</t>
-  </si>
-  <si>
-    <t>Резак</t>
-  </si>
-  <si>
-    <t>Ножницы по металлу</t>
-  </si>
-  <si>
     <t>ЛГУП-7428</t>
   </si>
   <si>
+    <t>Днище 720х12 ст09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
     <t>Днище 820х14-09Г2С ГОСТ 6533-78</t>
   </si>
   <si>
-    <t>Днище 720х12 ст09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
     <t>Днище 377х10 09Г2С ГОСТ 6533-78</t>
   </si>
   <si>
@@ -171,49 +171,67 @@
     <t>Держатель проводника Rd8</t>
   </si>
   <si>
+    <t>Индикатор положения поплавка ИПП 01.00.000</t>
+  </si>
+  <si>
     <t>МИП-24 исп.20 (МИП-24-2/П5-Р-RS), до двух АКБ 12 В 17 Ач</t>
   </si>
   <si>
     <t>Блок коммутации 24В БК-24-RS485-01</t>
   </si>
   <si>
-    <t>Индикатор положения поплавка ИПП 01.00.000</t>
-  </si>
-  <si>
     <t>ЛГУП-7450</t>
   </si>
   <si>
-    <t>ЛГУП-7451</t>
-  </si>
-  <si>
-    <t>Обогреватель взрывозащищенный ОВЭ-4 ТК-1.0 1 кВт, 220В, 50 Гц.</t>
-  </si>
-  <si>
-    <t>Коробка клеммная К-СП 16.18.09 24/20П 4КВе-Л-М20(А)-4КВе-Л-М20(В) 1ЕхеLLCGbXT6, ip66, 160х180х90</t>
-  </si>
-  <si>
-    <t>Коробка соед взрывозащК-СП 16.26.09 24/31 П 8КВе-Л-М20(А) 8КВе-Л-М20(В) 1ЕхеLLCGb ip66, 160х260х90</t>
-  </si>
-  <si>
-    <t>К-СП 16.26.09 32/26П 6КВе-Л-М20(А)-6КВе-Л-М20(В)-1КВе-Л-М20(D) 1ExeLLCGbXT6 ip66 120х260х90</t>
+    <t>Палитра цветов</t>
+  </si>
+  <si>
+    <t>ЛГУП-7454</t>
+  </si>
+  <si>
+    <t>ЛГУП-7457</t>
+  </si>
+  <si>
+    <t>ЛГУП-7460</t>
   </si>
   <si>
     <t>Газоанализатор взрывозащищенный СГОЭС 1Ex d IIC T4 Gb, IP67</t>
   </si>
   <si>
-    <t>Палитра цветов</t>
-  </si>
-  <si>
-    <t>ЛГУП-7454</t>
-  </si>
-  <si>
-    <t>ЛГУП-7457</t>
-  </si>
-  <si>
-    <t>ЛГУП-7460</t>
-  </si>
-  <si>
-    <t>ЛГУП-7462</t>
+    <t>ЛГУП-7475</t>
+  </si>
+  <si>
+    <t>Наконечник штыревой втулочный изолированный НШВИ 0.5-8 79435</t>
+  </si>
+  <si>
+    <t>ЛГУП-7477</t>
+  </si>
+  <si>
+    <t>Провод силовой ПуГВнг(А)-LS 1х0.5 белый</t>
+  </si>
+  <si>
+    <t>ЛГУП-7478</t>
+  </si>
+  <si>
+    <t>ЛГУП-7480</t>
+  </si>
+  <si>
+    <t>00УП-000005</t>
+  </si>
+  <si>
+    <t>Дюбель-молли М6х50</t>
+  </si>
+  <si>
+    <t>ЛГУП-7485</t>
+  </si>
+  <si>
+    <t>Контргайка 20 ГОСТ 8968-75 (12Х18Н10Т)</t>
+  </si>
+  <si>
+    <t>Удалитель наклеек Lavr Антискотч</t>
+  </si>
+  <si>
+    <t>ЛГУП-7486</t>
   </si>
   <si>
     <t>Кольцо 350-360-58-2-2 ГОСТ 9833-73</t>
@@ -228,61 +246,145 @@
     <t>Фумлента</t>
   </si>
   <si>
+    <t>Шайба 16 ГОСТ 6958-78</t>
+  </si>
+  <si>
     <t>Днище 219х4-25 ст.20 ГОСТ 6533-78</t>
   </si>
   <si>
-    <t>Шайба 16 ГОСТ 6958-78</t>
+    <t>Труба 10х1,0 М3-ПТ ГОСТ 617-90</t>
   </si>
   <si>
     <t>Труба ГКРХХ 110х17,5 БрАЖН 10-4-4 ГОСТ 1208-90</t>
   </si>
   <si>
-    <t>Труба 10х1,0 М3-ПТ ГОСТ 617-90</t>
-  </si>
-  <si>
     <t>Фланец х-80-40 ГОСТ12821 (заготовка-поковка ст.20 гр.IV КП 195 ГОСТ 8479-70)</t>
   </si>
   <si>
+    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D108х16 ГОСТ 8732-78/ Ст.40Х  ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+  </si>
+  <si>
     <t>Труба D89х6 ГОСТ 8732-78 Ст.20 ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Труба D108х16 ГОСТ 8732-78/ Ст.40Х  ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
+    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
   </si>
   <si>
     <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
+    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 120</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 4.1.1</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 4.1.1</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
+  </si>
+  <si>
+    <t>Коробка клеммная К-СП 08.13.09 24/11П 2КВе-Л-М20(А)-2КВе-Л-М20(В) 1ExeLLCGbXT6 ip66,80х130х90</t>
+  </si>
+  <si>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>Разъем РпИм 1.25-5-0.8 плоский</t>
+  </si>
+  <si>
+    <t>DIN-рейка 50см перфорированная adr-50 EKF арт. adr-50</t>
+  </si>
+  <si>
+    <t>Фиксатор ФК-102-01 на DIN-рейку 32057DEK Dekraft 2 арт. 32057DEK</t>
+  </si>
+  <si>
+    <t>Заглушка NO-550-07 для винтовых клемм 2,5мм2 арт. Б0035737</t>
+  </si>
+  <si>
+    <t>Зажим клеммный винтовой 2,5 мм2 (50/1500/36000) Б0033416 ЭРА арт. Б0033416</t>
+  </si>
+  <si>
+    <t>Шина заземления на DIN-изолятор ШНИ-6х9-8</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 40х40 мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
   </si>
   <si>
     <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
   </si>
   <si>
-    <t>Зажим клеммный винтовой 2,5 мм2 (50/1500/36000) Б0033416 ЭРА арт. Б0033416</t>
-  </si>
-  <si>
-    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
-  </si>
-  <si>
-    <t>Заглушка NO-550-07 для винтовых клемм 2,5мм2 арт. Б0035737</t>
-  </si>
-  <si>
-    <t>Фиксатор ФК-102-01 на DIN-рейку 32057DEK Dekraft 2 арт. 32057DEK</t>
-  </si>
-  <si>
-    <t>DIN-рейка 50см перфорированная adr-50 EKF арт. adr-50</t>
-  </si>
-  <si>
-    <t>Разъем РпИм 1.25-5-0.8 плоский</t>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
+  </si>
+  <si>
+    <t>Кабель-канал 40х40 перфорированный Plast kk40-40 EKF</t>
+  </si>
+  <si>
+    <t>Провод ПуГВнг(А)-LS 1x0,75</t>
+  </si>
+  <si>
+    <t>Провод ПуГВнг(А)-LS 1x1,5</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
   </si>
   <si>
     <t>Наконечник кабельный НШвИ 0,75мм</t>
@@ -294,6 +396,18 @@
     <t>Наконечник кабельный НШвИ 2,5мм</t>
   </si>
   <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
     <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
   </si>
   <si>
@@ -303,102 +417,12 @@
     <t>Крышка на угол вертикальный внешний CD90 (100х50)</t>
   </si>
   <si>
-    <t>Угол вертикальный внутренний CS 90 100 х 50мм</t>
-  </si>
-  <si>
-    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 4.1.1</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 4.1.1</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Пластина анкерная 120</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
-  </si>
-  <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 40х40 мм</t>
-  </si>
-  <si>
-    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
-  </si>
-  <si>
-    <t>Провод Rd8</t>
-  </si>
-  <si>
-    <t>Провод ПуГВнг(А)-LS 1x1,5</t>
-  </si>
-  <si>
-    <t>Провод ПуГВнг(А)-LS 1x0,75</t>
-  </si>
-  <si>
-    <t>Кабель-канал 40х40 перфорированный Plast kk40-40 EKF</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Шина заземления на DIN-изолятор ШНИ-6х9-8</t>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
   </si>
   <si>
     <t>Выключатель автоматический двухполюсный 3А B ВА47-29 4.5кА MVA20-2-003-B IEK</t>
   </si>
   <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>Коробка клеммная К-СП 08.13.09 24/11П 2КВе-Л-М20(А)-2КВе-Л-М20(В) 1ExeLLCGbXT6 ip66,80х130х90</t>
-  </si>
-  <si>
-    <t>Выключатель двухклавишный IP55</t>
-  </si>
-  <si>
     <t>Выключатель автоматический двухполюсный IEK ARMAT M10N 2P B 10А AR-M10N-2-B010</t>
   </si>
   <si>
@@ -426,10 +450,16 @@
     <t>Угол вертикальный внешний CD 90 (50 х 50)</t>
   </si>
   <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+    <t>Кольцо 055-060-30-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 065-075-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.030</t>
   </si>
   <si>
     <t>Прокладка медная 8х11-II ГОСТ 19752-84</t>
@@ -441,76 +471,58 @@
     <t>Кольцо 112-118-36 ГОСТ 9833-73</t>
   </si>
   <si>
-    <t>Кольцо 055-060-30-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Пружина ПСМНТ.001.000.030</t>
-  </si>
-  <si>
-    <t>Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 065-075-58 ГОСТ 9833-73</t>
-  </si>
-  <si>
     <t>Уплотнение ПСМНТ.001.022.002</t>
   </si>
   <si>
-    <t>Обогреватель взрывозащищенный ОВЭ-4-УХЛ3 1,8 кВт, 380В IExdIIАТ3, IP54</t>
-  </si>
-  <si>
-    <t>Пост кнопочный взрывозащищенный ПВК-15 IP65 2ExеdIIСТ6</t>
-  </si>
-  <si>
-    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
-  </si>
-  <si>
-    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
-  </si>
-  <si>
-    <t>Датчик давления взрывозащ. СТИ775Ц-E-1-M-D-B-H-T-1</t>
+    <t>Круг D195 Ст.16ГС-3 ГОСТ 5520-79</t>
+  </si>
+  <si>
+    <t>Круг D430 Ст.16ГС ГОСТ 19281-14</t>
+  </si>
+  <si>
+    <t>Круг D70 Ст.40Х ГОСТ 4543-71</t>
+  </si>
+  <si>
+    <t>Круг D45 Ст.40Х ГОСТ 4543-71</t>
+  </si>
+  <si>
+    <t>Круг D370 Ст.20 ГОСТ1050-88</t>
+  </si>
+  <si>
+    <t>Шестигранник S=14 Ст.45 ГОСТ 1050-88</t>
   </si>
   <si>
     <t>Лист Б-ПР-1,0 ГОСТ 19904-74/ 4-III-Ст3кп ГОСТ 16523-89</t>
   </si>
   <si>
-    <t>Шестигранник S=14 Ст.45 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D370 Ст.20 ГОСТ1050-88</t>
-  </si>
-  <si>
-    <t>Круг D45 Ст.40Х ГОСТ 4543-71</t>
-  </si>
-  <si>
-    <t>Круг D70 Ст.40Х ГОСТ 4543-71</t>
-  </si>
-  <si>
-    <t>Круг D430 Ст.16ГС ГОСТ 19281-14</t>
-  </si>
-  <si>
-    <t>Круг D195 Ст.16ГС-3 ГОСТ 5520-79</t>
-  </si>
-  <si>
     <t>Шарик 25,4-100 ГОСТ 3722-81</t>
   </si>
   <si>
+    <t>Винт М16х50.56.019 ГОСТ 1481-84</t>
+  </si>
+  <si>
+    <t>Заклепка 2х4х37 Ан.Окс.хр. ГОСТ10299-80</t>
+  </si>
+  <si>
     <t>Шпилька М18х40.56.019 ГОСТ 22034-76</t>
   </si>
   <si>
-    <t>Заклепка 2х4х37 Ан.Окс.хр. ГОСТ10299-80</t>
-  </si>
-  <si>
-    <t>Винт М16х50.56.019 ГОСТ 1481-84</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Оповещатель светозвуковой Маяк-24К IP53</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный дымовой ИП 212-141М</t>
+    <t>Розетка для реле 2 СО</t>
+  </si>
+  <si>
+    <t>Промежуточное реле 2 CO контакта 24в DC</t>
+  </si>
+  <si>
+    <t>Клемма пружинная Push-in CP-ML 2 ур. 4мм2 серая IEK YCT23-00-2-K03-004 IEK</t>
+  </si>
+  <si>
+    <t>Заглушка для CP-ML 2 ур. 4мм2 серая IEK YCT23-00-2-K03-004-ZGL IEK</t>
+  </si>
+  <si>
+    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Сгон ДУ20 L-120 12Х18Н10Т</t>
   </si>
 </sst>
 </file>
@@ -947,12 +959,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="75" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
@@ -984,7 +996,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D2" s="5">
         <v>120</v>
@@ -1002,7 +1014,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D3" s="5">
         <v>0.25</v>
@@ -1020,16 +1032,16 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="D4" s="5">
         <v>40</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1038,16 +1050,16 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1056,16 +1068,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1074,16 +1086,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1092,16 +1104,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="5">
-        <v>800</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1110,16 +1122,16 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="D9" s="5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1128,16 +1140,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="5">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1146,16 +1158,16 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1164,16 +1176,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1182,16 +1194,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D13" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1203,13 +1215,13 @@
         <v>21</v>
       </c>
       <c r="D14" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1221,13 +1233,13 @@
         <v>22</v>
       </c>
       <c r="D15" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1239,10 +1251,10 @@
         <v>23</v>
       </c>
       <c r="D16" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>24</v>
@@ -1257,10 +1269,10 @@
         <v>25</v>
       </c>
       <c r="D17" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>24</v>
@@ -1278,7 +1290,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>24</v>
@@ -1290,13 +1302,13 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" s="5">
         <v>10</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>24</v>
@@ -1314,7 +1326,7 @@
         <v>10</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>24</v>
@@ -1329,10 +1341,10 @@
         <v>30</v>
       </c>
       <c r="D21" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>24</v>
@@ -1350,7 +1362,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>24</v>
@@ -1365,10 +1377,10 @@
         <v>32</v>
       </c>
       <c r="D23" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>24</v>
@@ -1383,10 +1395,10 @@
         <v>33</v>
       </c>
       <c r="D24" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>24</v>
@@ -1404,7 +1416,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>24</v>
@@ -1416,10 +1428,10 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D26" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>6</v>
@@ -1434,10 +1446,10 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D27" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>6</v>
@@ -1455,10 +1467,10 @@
         <v>36</v>
       </c>
       <c r="D28" s="5">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>35</v>
@@ -1473,10 +1485,10 @@
         <v>37</v>
       </c>
       <c r="D29" s="5">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>35</v>
@@ -1494,7 +1506,7 @@
         <v>18</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>35</v>
@@ -1524,10 +1536,10 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D32" s="5">
-        <v>53.25</v>
+        <v>0.2</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>8</v>
@@ -1542,10 +1554,10 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D33" s="5">
-        <v>0.2</v>
+        <v>53.25</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>8</v>
@@ -1560,7 +1572,7 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D34" s="5">
         <v>25</v>
@@ -1578,10 +1590,10 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D35" s="5">
-        <v>49</v>
+        <v>271.75</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>8</v>
@@ -1596,10 +1608,10 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="5">
-        <v>99.25</v>
+        <v>79</v>
+      </c>
+      <c r="D36" s="7">
+        <v>4286.5</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>8</v>
@@ -1614,7 +1626,7 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D37" s="5">
         <v>18.25</v>
@@ -1632,10 +1644,10 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" s="7">
-        <v>4286.5</v>
+        <v>81</v>
+      </c>
+      <c r="D38" s="5">
+        <v>99.25</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>8</v>
@@ -1650,10 +1662,10 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D39" s="5">
-        <v>148.5</v>
+        <v>49</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>8</v>
@@ -1668,7 +1680,7 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D40" s="5">
         <v>37.35</v>
@@ -1686,10 +1698,10 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D41" s="5">
-        <v>271.75</v>
+        <v>148.5</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>8</v>
@@ -1704,10 +1716,10 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D42" s="5">
-        <v>2.1</v>
+        <v>130</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>44</v>
@@ -1722,10 +1734,10 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D43" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
@@ -1740,10 +1752,10 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="D44" s="5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>6</v>
@@ -1758,10 +1770,10 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="D45" s="5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>6</v>
@@ -1776,7 +1788,7 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D46" s="5">
         <v>2</v>
@@ -1794,10 +1806,10 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D47" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>6</v>
@@ -1812,10 +1824,10 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D48" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>6</v>
@@ -1830,10 +1842,10 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D49" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>6</v>
@@ -1848,10 +1860,10 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D50" s="5">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>6</v>
@@ -1866,10 +1878,10 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D51" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>6</v>
@@ -1884,10 +1896,10 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D52" s="5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>6</v>
@@ -1902,10 +1914,10 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D53" s="5">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>6</v>
@@ -1920,7 +1932,7 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D54" s="5">
         <v>4</v>
@@ -1938,10 +1950,10 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="D55" s="5">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>6</v>
@@ -1956,10 +1968,10 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D56" s="5">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>6</v>
@@ -1974,10 +1986,10 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D57" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>6</v>
@@ -1992,7 +2004,7 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D58" s="5">
         <v>1</v>
@@ -2010,10 +2022,10 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D59" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>6</v>
@@ -2028,10 +2040,10 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D60" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>6</v>
@@ -2046,10 +2058,10 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D61" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>6</v>
@@ -2064,7 +2076,7 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D62" s="5">
         <v>2</v>
@@ -2082,10 +2094,10 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D63" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>6</v>
@@ -2100,13 +2112,13 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D64" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>45</v>
@@ -2118,10 +2130,10 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D65" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>44</v>
@@ -2136,10 +2148,10 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D66" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>44</v>
@@ -2154,10 +2166,10 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D67" s="5">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>44</v>
@@ -2172,10 +2184,10 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D68" s="5">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>44</v>
@@ -2190,10 +2202,10 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D69" s="5">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>44</v>
@@ -2208,10 +2220,10 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D70" s="5">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>44</v>
@@ -2226,10 +2238,10 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>44</v>
@@ -2244,10 +2256,10 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D72" s="5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>44</v>
@@ -2262,10 +2274,10 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D73" s="5">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>44</v>
@@ -2280,10 +2292,10 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D74" s="5">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>44</v>
@@ -2298,10 +2310,10 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D75" s="5">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>44</v>
@@ -2316,10 +2328,10 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D76" s="5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>44</v>
@@ -2334,13 +2346,13 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>45</v>
@@ -2352,7 +2364,7 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="D78" s="5">
         <v>1</v>
@@ -2370,10 +2382,10 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D79" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>6</v>
@@ -2388,10 +2400,10 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D80" s="5">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>6</v>
@@ -2406,10 +2418,10 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D81" s="5">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>6</v>
@@ -2424,10 +2436,10 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D82" s="5">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>6</v>
@@ -2442,10 +2454,10 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D83" s="5">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>6</v>
@@ -2460,10 +2472,10 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D84" s="5">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>6</v>
@@ -2478,10 +2490,10 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="D85" s="5">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>6</v>
@@ -2496,10 +2508,10 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D86" s="5">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>6</v>
@@ -2514,10 +2526,10 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D87" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>6</v>
@@ -2532,10 +2544,10 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D88" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>6</v>
@@ -2550,10 +2562,10 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D89" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>6</v>
@@ -2568,10 +2580,10 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="D90" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>6</v>
@@ -2586,7 +2598,7 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="D91" s="5">
         <v>1</v>
@@ -2604,7 +2616,7 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D92" s="5">
         <v>1</v>
@@ -2622,7 +2634,7 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="D93" s="5">
         <v>1</v>
@@ -2640,10 +2652,10 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="D94" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>6</v>
@@ -2658,7 +2670,7 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D95" s="5">
         <v>1</v>
@@ -2676,10 +2688,10 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D96" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>6</v>
@@ -2694,10 +2706,10 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D97" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>6</v>
@@ -2712,10 +2724,10 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D98" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>6</v>
@@ -2730,7 +2742,7 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D99" s="5">
         <v>8</v>
@@ -2748,7 +2760,7 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D100" s="5">
         <v>8</v>
@@ -2766,10 +2778,10 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>6</v>
@@ -2784,7 +2796,7 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D102" s="5">
         <v>8</v>
@@ -2802,10 +2814,10 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D103" s="5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>6</v>
@@ -2820,10 +2832,10 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D104" s="5">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>6</v>
@@ -2838,10 +2850,10 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D105" s="5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>6</v>
@@ -2856,7 +2868,7 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D106" s="5">
         <v>25</v>
@@ -2874,10 +2886,10 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D107" s="5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>6</v>
@@ -2892,10 +2904,10 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D108" s="5">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>6</v>
@@ -2910,10 +2922,10 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D109" s="5">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>6</v>
@@ -2928,160 +2940,160 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D110" s="5">
         <v>25</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>110</v>
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="D111" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>111</v>
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="D112" s="5">
-        <v>2</v>
+        <v>291</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D113" s="5">
-        <v>2</v>
+        <v>150</v>
+      </c>
+      <c r="D113" s="7">
+        <v>1415.25</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D114" s="5">
-        <v>2</v>
+        <v>26.5</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D115" s="5">
+        <v>131</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D115" s="5">
-        <v>2</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="D116" s="5">
-        <v>1</v>
+        <v>950</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="D117" s="5">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D118" s="5">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3090,16 +3102,16 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D119" s="5">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3108,160 +3120,160 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>120</v>
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="D121" s="5">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>121</v>
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D122" s="5">
-        <v>1.5</v>
+        <v>500</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>122</v>
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="D123" s="5">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>123</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="D124" s="5">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>124</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D125" s="5">
-        <v>131</v>
+        <v>3</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>125</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D126" s="5">
-        <v>26.5</v>
+        <v>3</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D127" s="7">
-        <v>1415.25</v>
+        <v>162</v>
+      </c>
+      <c r="D127" s="5">
+        <v>16</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>127</v>
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D128" s="5">
-        <v>291</v>
+        <v>6</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3270,16 +3282,16 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="D129" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3288,10 +3300,10 @@
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D130" s="5">
-        <v>500</v>
+        <v>9</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>6</v>
@@ -3306,10 +3318,10 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D131" s="5">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>6</v>
@@ -3324,10 +3336,10 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D132" s="5">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>6</v>
@@ -3336,70 +3348,70 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>132</v>
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="D133" s="5">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>44</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>133</v>
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D134" s="5">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D135" s="5">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D136" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>6</v>
@@ -3408,40 +3420,184 @@
         <v>62</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>136</v>
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="D137" s="5">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>137</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D138" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="3">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4"/>
+      <c r="C139" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D139" s="5">
+        <v>12</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="3">
+        <v>139</v>
+      </c>
+      <c r="B140" s="4"/>
+      <c r="C140" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D140" s="5">
+        <v>64</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="3">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4"/>
+      <c r="C141" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D141" s="5">
+        <v>24</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="3">
+        <v>141</v>
+      </c>
+      <c r="B142" s="4"/>
+      <c r="C142" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D142" s="5">
+        <v>80</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="3">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4"/>
+      <c r="C143" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D143" s="5">
+        <v>250</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="3">
+        <v>143</v>
+      </c>
+      <c r="B144" s="4"/>
+      <c r="C144" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D144" s="5">
+        <v>150</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="3">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4"/>
+      <c r="C145" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D145" s="5">
+        <v>300</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="3">
+        <v>145</v>
+      </c>
+      <c r="B146" s="4"/>
+      <c r="C146" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D146" s="5">
+        <v>5</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899FF701-B3E4-4D5E-B966-3ED39BF75F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E8650F-B0FA-43C8-AEFE-246D339F49B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="210">
   <si>
     <t>№ п/п</t>
   </si>
@@ -48,108 +48,99 @@
     <t>шт</t>
   </si>
   <si>
-    <t>ЛГУП-7413</t>
+    <t>ЛГУП-7331</t>
+  </si>
+  <si>
+    <t>Маркер  краска красный по металлу</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
+  </si>
+  <si>
+    <t>пара</t>
+  </si>
+  <si>
+    <t>Перчатки с латесным покрытием</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
+    <t>Огнетушитель ОП-8</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Каска строительная оранжевая Исток</t>
+  </si>
+  <si>
+    <t>Ветошь</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Каска строительная белая</t>
+  </si>
+  <si>
+    <t>Маркер белый</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 30</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 36</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 41</t>
+  </si>
+  <si>
+    <t>Гайковерт</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 24</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
+  </si>
+  <si>
+    <t>Ножницы по металлу</t>
+  </si>
+  <si>
+    <t>Резак</t>
+  </si>
+  <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>Кувалда 1 кг.</t>
+  </si>
+  <si>
+    <t>Днище 377х10 09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>ЛГУП-7428</t>
+  </si>
+  <si>
+    <t>Днище 720х12 ст09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 820х14-09Г2С ГОСТ 6533-78</t>
   </si>
   <si>
     <t>кг</t>
   </si>
   <si>
-    <t>ЛГУП-7331</t>
-  </si>
-  <si>
-    <t>Маркер  краска красный по металлу</t>
-  </si>
-  <si>
-    <t>шт.</t>
-  </si>
-  <si>
-    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
-  </si>
-  <si>
-    <t>пара</t>
-  </si>
-  <si>
-    <t>Перчатки с латесным покрытием</t>
-  </si>
-  <si>
-    <t>пар</t>
-  </si>
-  <si>
-    <t>Каска строительная оранжевая Исток</t>
-  </si>
-  <si>
-    <t>Огнетушитель ОП-8</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Каска строительная белая</t>
-  </si>
-  <si>
-    <t>Маркер белый</t>
-  </si>
-  <si>
-    <t>Ветошь</t>
-  </si>
-  <si>
-    <t>Резак</t>
-  </si>
-  <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
-    <t>Кувалда 1 кг.</t>
-  </si>
-  <si>
-    <t>Ножницы по металлу</t>
-  </si>
-  <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
-    <t>Трещетка ключ 1/2</t>
-  </si>
-  <si>
-    <t>Гайковерт</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 41</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 36</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 30</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 24</t>
-  </si>
-  <si>
-    <t>ЛГУП-7428</t>
-  </si>
-  <si>
-    <t>Днище 720х12 ст09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 820х14-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 377х10 09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Распылитель Тесла Трибо</t>
-  </si>
-  <si>
-    <t>ЛГУП-7429</t>
-  </si>
-  <si>
     <t>ЛГУП-7445</t>
   </si>
   <si>
@@ -159,27 +150,27 @@
     <t>ЛГУП-7447</t>
   </si>
   <si>
+    <t>ЛГУП-7448</t>
+  </si>
+  <si>
+    <t>Блок коммутации 24В БК-24-RS485-01</t>
+  </si>
+  <si>
+    <t>МИП-24 исп.20 (МИП-24-2/П5-Р-RS), до двух АКБ 12 В 17 Ач</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8</t>
+  </si>
+  <si>
+    <t>Индикатор положения поплавка ИПП 01.00.000</t>
+  </si>
+  <si>
+    <t>Перемычка и наконечник НКИ 6-0-6</t>
+  </si>
+  <si>
     <t>м</t>
   </si>
   <si>
-    <t>ЛГУП-7448</t>
-  </si>
-  <si>
-    <t>Перемычка и наконечник НКИ 6-0-6</t>
-  </si>
-  <si>
-    <t>Держатель проводника Rd8</t>
-  </si>
-  <si>
-    <t>Индикатор положения поплавка ИПП 01.00.000</t>
-  </si>
-  <si>
-    <t>МИП-24 исп.20 (МИП-24-2/П5-Р-RS), до двух АКБ 12 В 17 Ач</t>
-  </si>
-  <si>
-    <t>Блок коммутации 24В БК-24-RS485-01</t>
-  </si>
-  <si>
     <t>ЛГУП-7450</t>
   </si>
   <si>
@@ -216,28 +207,82 @@
     <t>ЛГУП-7480</t>
   </si>
   <si>
-    <t>00УП-000005</t>
+    <t>ЛГУП-7485</t>
   </si>
   <si>
     <t>Дюбель-молли М6х50</t>
   </si>
   <si>
-    <t>ЛГУП-7485</t>
-  </si>
-  <si>
     <t>Контргайка 20 ГОСТ 8968-75 (12Х18Н10Т)</t>
   </si>
   <si>
-    <t>Удалитель наклеек Lavr Антискотч</t>
-  </si>
-  <si>
-    <t>ЛГУП-7486</t>
-  </si>
-  <si>
-    <t>Кольцо 350-360-58-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Смола ЭД-20 ГОСТ 10587-84</t>
+    <t>ЛГУП-7489</t>
+  </si>
+  <si>
+    <t>ЛГУП-7490</t>
+  </si>
+  <si>
+    <t>Сапоги летние</t>
+  </si>
+  <si>
+    <t>НТУП-018048</t>
+  </si>
+  <si>
+    <t>спец одежда летняя</t>
+  </si>
+  <si>
+    <t>ЛГУП-7491</t>
+  </si>
+  <si>
+    <t>м2</t>
+  </si>
+  <si>
+    <t>ЛГУП-7492</t>
+  </si>
+  <si>
+    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 9016(белый)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7493</t>
+  </si>
+  <si>
+    <t>ЛГУП-7496</t>
+  </si>
+  <si>
+    <t>ЛГУП-7497</t>
+  </si>
+  <si>
+    <t>ЛГУП-7498</t>
+  </si>
+  <si>
+    <t>Вал ПСМНТ.001.015.000 св.загот (нормализация "стоя" при темп-ре 350-400 град 30 мин и отпуск в печи)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7499</t>
+  </si>
+  <si>
+    <t>Корпус ПСМНТ.001.018.001 (14 скв) - наплавка ПНЖ</t>
+  </si>
+  <si>
+    <t>Крышка ПСМНТ.001.000.001 (заготовка-отливка СЧ14-18 ГОСТ 1412-85)</t>
+  </si>
+  <si>
+    <t>Сегмент ПСМНТ.001.014.000</t>
+  </si>
+  <si>
+    <t>Оцинкование шпилек М16х80 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>ЛГУП-7500</t>
+  </si>
+  <si>
+    <t>Оцинкование шпилек М24х130 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>ЛГУП-7501</t>
+  </si>
+  <si>
+    <t>ЛГУП-7502</t>
   </si>
   <si>
     <t>Маркер черный</t>
@@ -261,219 +306,219 @@
     <t>Фланец х-80-40 ГОСТ12821 (заготовка-поковка ст.20 гр.IV КП 195 ГОСТ 8479-70)</t>
   </si>
   <si>
+    <t>Труба D89х6 ГОСТ 8732-78 Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D108х16 ГОСТ 8732-78/ Ст.40Х  ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
     <t>Труба D194х14 В20 ГОСТ 8732-78</t>
   </si>
   <si>
-    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D108х16 ГОСТ 8732-78/ Ст.40Х  ГОСТ 8731-74</t>
-  </si>
-  <si>
     <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
   </si>
   <si>
-    <t>Труба D89х6 ГОСТ 8732-78 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
+    <t>Корпус металлический ЩМП-3-0 (650х500х220мм) У2 IP54 YKM40-03-54 IEK арт. YKM40-03-54</t>
+  </si>
+  <si>
+    <t>Контроллер доступа "С2000-2"</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический двухполюсный IEK ARMAT M10N 2P B 10А AR-M10N-2-B010</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический двухполюсный 3А B ВА47-29 4.5кА MVA20-2-003-B IEK</t>
+  </si>
+  <si>
+    <t>Шина заземления на DIN-изолятор ШНИ-6х9-8</t>
+  </si>
+  <si>
+    <t>Зажим клеммный винтовой 2,5 мм2 (50/1500/36000) Б0033416 ЭРА арт. Б0033416</t>
+  </si>
+  <si>
+    <t>Заглушка NO-550-07 для винтовых клемм 2,5мм2 арт. Б0035737</t>
+  </si>
+  <si>
+    <t>Фиксатор ФК-102-01 на DIN-рейку 32057DEK Dekraft 2 арт. 32057DEK</t>
+  </si>
+  <si>
+    <t>DIN-рейка 50см перфорированная adr-50 EKF арт. adr-50</t>
+  </si>
+  <si>
+    <t>Разъем РпИм 1.25-5-0.8 плоский</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный НШвИ 0,75мм</t>
+  </si>
+  <si>
+    <t>Коробка клеммная К-СП 08.13.09 24/11П 2КВе-Л-М20(А)-2КВе-Л-М20(В) 1ExeLLCGbXT6 ip66,80х130х90</t>
+  </si>
+  <si>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 4.1.1</t>
+  </si>
+  <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 4.1.1</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 120</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
   </si>
   <si>
     <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
   </si>
   <si>
-    <t>Пластина анкерная 120</t>
-  </si>
-  <si>
-    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 4.1.1</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 4.1.1</t>
-  </si>
-  <si>
-    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
+    <t>Короб ПВХ 40х40 мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
+  </si>
+  <si>
+    <t>Кабель-канал 40х40 перфорированный Plast kk40-40 EKF</t>
+  </si>
+  <si>
+    <t>Провод ПуГВнг(А)-LS 1x0,75</t>
+  </si>
+  <si>
+    <t>Провод ПуГВнг(А)-LS 1x1,5</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный НШвИ 1,5мм</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный НШвИ 2,5мм</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внешний CD 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внешний CD90 (100х50)</t>
   </si>
   <si>
     <t>Угол вертикальный внутренний CS 90 100 х 50мм</t>
   </si>
   <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>Коробка клеммная К-СП 08.13.09 24/11П 2КВе-Л-М20(А)-2КВе-Л-М20(В) 1ExeLLCGbXT6 ip66,80х130х90</t>
-  </si>
-  <si>
-    <t>Выключатель двухклавишный IP55</t>
-  </si>
-  <si>
-    <t>Разъем РпИм 1.25-5-0.8 плоский</t>
-  </si>
-  <si>
-    <t>DIN-рейка 50см перфорированная adr-50 EKF арт. adr-50</t>
-  </si>
-  <si>
-    <t>Фиксатор ФК-102-01 на DIN-рейку 32057DEK Dekraft 2 арт. 32057DEK</t>
-  </si>
-  <si>
-    <t>Заглушка NO-550-07 для винтовых клемм 2,5мм2 арт. Б0035737</t>
-  </si>
-  <si>
-    <t>Зажим клеммный винтовой 2,5 мм2 (50/1500/36000) Б0033416 ЭРА арт. Б0033416</t>
-  </si>
-  <si>
-    <t>Шина заземления на DIN-изолятор ШНИ-6х9-8</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 40х40 мм</t>
-  </si>
-  <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
-  </si>
-  <si>
-    <t>Кабель-канал 40х40 перфорированный Plast kk40-40 EKF</t>
-  </si>
-  <si>
-    <t>Провод ПуГВнг(А)-LS 1x0,75</t>
-  </si>
-  <si>
-    <t>Провод ПуГВнг(А)-LS 1x1,5</t>
-  </si>
-  <si>
-    <t>Провод Rd8</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Наконечник кабельный НШвИ 0,75мм</t>
-  </si>
-  <si>
-    <t>Наконечник кабельный НШвИ 1,5мм</t>
-  </si>
-  <si>
-    <t>Наконечник кабельный НШвИ 2,5мм</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внешний CD 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Крышка на угол вертикальный внешний CD90 (100х50)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Выключатель автоматический двухполюсный 3А B ВА47-29 4.5кА MVA20-2-003-B IEK</t>
-  </si>
-  <si>
-    <t>Выключатель автоматический двухполюсный IEK ARMAT M10N 2P B 10А AR-M10N-2-B010</t>
-  </si>
-  <si>
-    <t>Контроллер доступа "С2000-2"</t>
-  </si>
-  <si>
-    <t>Корпус металлический ЩМП-3-0 (650х500х220мм) У2 IP54 YKM40-03-54 IEK арт. YKM40-03-54</t>
+    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внутренний CS 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внутренний CS 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
   </si>
   <si>
     <t>Карта proximity стандартная ST-PC010EM</t>
   </si>
   <si>
-    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внутренний CS 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внутренний CS 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внешний CD 90 (50 х 50)</t>
+    <t>Кольцо 112-118-36 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-090-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Прокладка медная 8х11-II ГОСТ 19752-84</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.030</t>
+  </si>
+  <si>
+    <t>Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 065-075-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Уплотнение ПСМНТ.001.022.002</t>
   </si>
   <si>
     <t>Кольцо 055-060-30-2-2 ГОСТ 9833-73</t>
   </si>
   <si>
-    <t>Кольцо 065-075-58 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Пружина ПСМНТ.001.000.030</t>
-  </si>
-  <si>
-    <t>Прокладка медная 8х11-II ГОСТ 19752-84</t>
-  </si>
-  <si>
-    <t>Кольцо 080-090-58 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 112-118-36 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Уплотнение ПСМНТ.001.022.002</t>
-  </si>
-  <si>
     <t>Круг D195 Ст.16ГС-3 ГОСТ 5520-79</t>
   </si>
   <si>
@@ -507,22 +552,109 @@
     <t>Шпилька М18х40.56.019 ГОСТ 22034-76</t>
   </si>
   <si>
+    <t>Заглушка для CP-ML 2 ур. 4мм2 серая IEK YCT23-00-2-K03-004-ZGL IEK</t>
+  </si>
+  <si>
+    <t>Клемма пружинная Push-in CP-ML 2 ур. 4мм2 серая IEK YCT23-00-2-K03-004 IEK</t>
+  </si>
+  <si>
+    <t>Промежуточное реле 2 CO контакта 24в DC</t>
+  </si>
+  <si>
     <t>Розетка для реле 2 СО</t>
   </si>
   <si>
-    <t>Промежуточное реле 2 CO контакта 24в DC</t>
-  </si>
-  <si>
-    <t>Клемма пружинная Push-in CP-ML 2 ур. 4мм2 серая IEK YCT23-00-2-K03-004 IEK</t>
-  </si>
-  <si>
-    <t>Заглушка для CP-ML 2 ур. 4мм2 серая IEK YCT23-00-2-K03-004-ZGL IEK</t>
-  </si>
-  <si>
     <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
   </si>
   <si>
     <t>Сгон ДУ20 L-120 12Х18Н10Т</t>
+  </si>
+  <si>
+    <t>Гайка 2М14х1,5 ГОСТ 15522-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх25.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Гайка М14х1,5 ГОСТ 15522-70</t>
+  </si>
+  <si>
+    <t>Шайба 8 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба А8 ГОСТ 10450-78</t>
+  </si>
+  <si>
+    <t>Шайба А14 ГОСТ 10450-78</t>
+  </si>
+  <si>
+    <t>Труба D102х5 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Труба ДКРПТ 8х1 М2 ГОСТ 617-90 (отгружать L кратно 2,5м, либо бухтами)</t>
+  </si>
+  <si>
+    <t>Круг D160 Ст.3 ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Круг D265 ст.20 ГОСТ 1050-13</t>
+  </si>
+  <si>
+    <t>Круг D26 Ст.3 ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
+  </si>
+  <si>
+    <t>Круг D6-h10 ГОСТ 7417-75/ Ст.10 ГОСТ 1051-73</t>
+  </si>
+  <si>
+    <t>Сетка П160 ГОСТ 3187-76</t>
+  </si>
+  <si>
+    <t>Двигатель АИМЛ 63 В4IM3081</t>
+  </si>
+  <si>
+    <t>Полумуфта насоса НТ.3.00.00.00.002 (изготовление шлицов)</t>
+  </si>
+  <si>
+    <t>Полумуфта привода НТ.3.00.00.00.003 (изготовление паза)</t>
+  </si>
+  <si>
+    <t>Картонная коробка - 400 (Д) х 400 (Ш) х 610 (В) мм (картон Т23 ГОСТ 7376-89)</t>
+  </si>
+  <si>
+    <t>Лист А0.М1(анод) 0,5 ГОСТ 21631-76 (черный)</t>
+  </si>
+  <si>
+    <t>Скотч 50мм*120м PROFITTO /6/54 прозрачн</t>
+  </si>
+  <si>
+    <t>Круг D170 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Тройник 89х6 ст.09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Газоанализатор взрывозащищенный СГОЭС (метан) 1Ex d IIC T4 Gb, IP67 Ур1. 10%, ур.2 50% НКПР</t>
+  </si>
+  <si>
+    <t>Шпилька А1М36-6gx220.09Г2С (оцинк.) ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Гайка М36-6Н ст.09Г2С (оцинк.) ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Кольцо 210-220-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Грунт-эмаль 2К ПУ, RAL 9003 (белый)</t>
+  </si>
+  <si>
+    <t>Паронит ПОН-Б 1мм</t>
   </si>
 </sst>
 </file>
@@ -959,13 +1091,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -990,16 +1122,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D2" s="5">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>6</v>
@@ -1008,19 +1140,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>0.25</v>
+        <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>7</v>
@@ -1032,16 +1164,16 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1050,16 +1182,16 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>40</v>
+        <v>800</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1068,16 +1200,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1086,16 +1218,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5">
-        <v>800</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1110,10 +1242,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1125,13 +1257,13 @@
         <v>17</v>
       </c>
       <c r="D9" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1146,10 +1278,10 @@
         <v>20</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1161,13 +1293,13 @@
         <v>19</v>
       </c>
       <c r="D11" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1176,16 +1308,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="D12" s="5">
         <v>5</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1194,16 +1326,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1215,13 +1347,13 @@
         <v>21</v>
       </c>
       <c r="D14" s="5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1230,16 +1362,16 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="5">
         <v>10</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1248,16 +1380,16 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1269,13 +1401,13 @@
         <v>25</v>
       </c>
       <c r="D17" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1290,10 +1422,10 @@
         <v>10</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1308,10 +1440,10 @@
         <v>10</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1320,16 +1452,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" s="5">
         <v>10</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1338,16 +1470,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1356,16 +1488,16 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" s="5">
         <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1377,13 +1509,13 @@
         <v>32</v>
       </c>
       <c r="D23" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1395,13 +1527,13 @@
         <v>33</v>
       </c>
       <c r="D24" s="5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1410,16 +1542,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="5">
+        <v>23</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="D25" s="5">
-        <v>10</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1428,16 +1560,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="D26" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1446,16 +1578,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D27" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1464,70 +1596,70 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="D28" s="5">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="5">
-        <v>4</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="5">
+        <v>53.25</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="5">
-        <v>18</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="5">
+        <v>25</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="D31" s="5">
-        <v>1</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1536,16 +1668,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D32" s="5">
-        <v>0.2</v>
+        <v>49</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1554,16 +1686,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D33" s="5">
-        <v>53.25</v>
+        <v>18.25</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1572,16 +1704,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="5">
-        <v>25</v>
+        <v>95</v>
+      </c>
+      <c r="D34" s="7">
+        <v>4286.5</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1590,16 +1722,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D35" s="5">
-        <v>271.75</v>
+        <v>148.5</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1608,16 +1740,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" s="7">
-        <v>4286.5</v>
+        <v>97</v>
+      </c>
+      <c r="D36" s="5">
+        <v>37.35</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1626,16 +1758,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D37" s="5">
-        <v>18.25</v>
+        <v>271.75</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1644,16 +1776,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D38" s="5">
         <v>99.25</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1662,16 +1794,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D39" s="5">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1680,16 +1812,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D40" s="5">
-        <v>37.35</v>
+        <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1698,16 +1830,16 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="D41" s="5">
-        <v>148.5</v>
+        <v>1</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1716,16 +1848,16 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D42" s="5">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1734,16 +1866,16 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D43" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1752,16 +1884,16 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="D44" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1770,16 +1902,16 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D45" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1788,16 +1920,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D46" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1806,16 +1938,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D47" s="5">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1824,16 +1956,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D48" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1842,16 +1974,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D49" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1860,16 +1992,16 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D50" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1878,16 +2010,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D51" s="5">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1896,16 +2028,16 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D52" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1914,16 +2046,16 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D53" s="5">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1932,16 +2064,16 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D54" s="5">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1950,16 +2082,16 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D55" s="5">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1968,16 +2100,16 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D56" s="5">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1986,16 +2118,16 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D57" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2004,7 +2136,7 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D58" s="5">
         <v>1</v>
@@ -2013,7 +2145,7 @@
         <v>6</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2022,16 +2154,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="D59" s="5">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2040,16 +2172,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D60" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2058,16 +2190,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D61" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2076,16 +2208,16 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="D62" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2094,16 +2226,16 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="D63" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2112,16 +2244,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D64" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2130,16 +2262,16 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D65" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2148,16 +2280,16 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D66" s="5">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2166,16 +2298,16 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="D67" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2184,16 +2316,16 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D68" s="5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2202,16 +2334,16 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D69" s="5">
-        <v>2.1</v>
+        <v>130</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2220,16 +2352,16 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D70" s="5">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2238,16 +2370,16 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D71" s="5">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2256,16 +2388,16 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="D72" s="5">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2274,16 +2406,16 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D73" s="5">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2292,16 +2424,16 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D74" s="5">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2310,16 +2442,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D75" s="5">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2328,16 +2460,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D76" s="5">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2346,16 +2478,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D77" s="5">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2364,16 +2496,16 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="D78" s="5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2382,16 +2514,16 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D79" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2400,16 +2532,16 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D80" s="5">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2418,16 +2550,16 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D81" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2436,16 +2568,16 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D82" s="5">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2454,16 +2586,16 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D83" s="5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2472,16 +2604,16 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D84" s="5">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2490,16 +2622,16 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D85" s="5">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2508,16 +2640,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D86" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2526,16 +2658,16 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="D87" s="5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2544,16 +2676,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="D88" s="5">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2562,16 +2694,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="D89" s="5">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2580,16 +2712,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D90" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2598,16 +2730,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="D91" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2616,16 +2748,16 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D92" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2634,16 +2766,16 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2652,16 +2784,16 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D94" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2670,16 +2802,16 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D95" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2688,16 +2820,16 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D96" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2706,16 +2838,16 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="D97" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2724,7 +2856,7 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="D98" s="5">
         <v>1</v>
@@ -2733,7 +2865,7 @@
         <v>6</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2742,16 +2874,16 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="D99" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2760,16 +2892,16 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D100" s="5">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2778,16 +2910,16 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="D101" s="5">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2796,16 +2928,16 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D102" s="5">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2814,7 +2946,7 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="D103" s="5">
         <v>25</v>
@@ -2823,7 +2955,7 @@
         <v>6</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2832,16 +2964,16 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="D104" s="5">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2850,16 +2982,16 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="D105" s="5">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2868,16 +3000,16 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D106" s="5">
         <v>25</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2886,67 +3018,67 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="D107" s="5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>107</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="D108" s="5">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>108</v>
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D109" s="5">
-        <v>50</v>
+        <v>291</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D110" s="5">
-        <v>25</v>
+        <v>165</v>
+      </c>
+      <c r="D110" s="7">
+        <v>1415.25</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>51</v>
@@ -2958,16 +3090,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>52</v>
+        <v>166</v>
       </c>
       <c r="D111" s="5">
-        <v>1</v>
+        <v>26.5</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2976,16 +3108,16 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D112" s="5">
-        <v>291</v>
+        <v>131</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2994,16 +3126,16 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D113" s="7">
-        <v>1415.25</v>
+        <v>168</v>
+      </c>
+      <c r="D113" s="5">
+        <v>950</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3012,16 +3144,16 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D114" s="5">
-        <v>26.5</v>
+        <v>2.5</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3030,70 +3162,70 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D115" s="5">
-        <v>131</v>
+        <v>1.5</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D116" s="5">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D117" s="5">
-        <v>2.5</v>
+        <v>100</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D118" s="5">
-        <v>1.5</v>
+        <v>50</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3102,16 +3234,16 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D119" s="5">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3120,16 +3252,16 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D120" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3138,16 +3270,16 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="D121" s="5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3156,16 +3288,16 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="D122" s="5">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3174,16 +3306,16 @@
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D123" s="5">
+        <v>6</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F123" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D123" s="5">
-        <v>1</v>
-      </c>
-      <c r="E123" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3192,16 +3324,16 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="D124" s="5">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3210,7 +3342,7 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D125" s="5">
         <v>3</v>
@@ -3219,7 +3351,7 @@
         <v>6</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3228,7 +3360,7 @@
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="D126" s="5">
         <v>3</v>
@@ -3237,7 +3369,7 @@
         <v>6</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3246,16 +3378,16 @@
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="D127" s="5">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3264,16 +3396,16 @@
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>163</v>
+        <v>55</v>
       </c>
       <c r="D128" s="5">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3282,16 +3414,16 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="D129" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3300,16 +3432,16 @@
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D130" s="5">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3318,7 +3450,7 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D131" s="5">
         <v>9</v>
@@ -3327,7 +3459,7 @@
         <v>6</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3336,16 +3468,16 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D132" s="5">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3354,16 +3486,16 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>60</v>
+        <v>179</v>
       </c>
       <c r="D133" s="5">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3372,16 +3504,16 @@
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="D134" s="5">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3390,16 +3522,16 @@
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="D135" s="5">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3408,28 +3540,28 @@
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="D136" s="5">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>136</v>
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="D137" s="5">
-        <v>160</v>
+        <v>9</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>6</v>
@@ -3438,16 +3570,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>137</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="D138" s="5">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>6</v>
@@ -3456,16 +3588,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>138</v>
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D139" s="5">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>6</v>
@@ -3474,16 +3606,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>139</v>
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="D140" s="5">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>6</v>
@@ -3492,16 +3624,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>140</v>
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="D141" s="5">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>6</v>
@@ -3510,94 +3642,616 @@
         <v>63</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>141</v>
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="D142" s="5">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>142</v>
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D143" s="5">
+        <v>5.76</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F143" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D143" s="5">
-        <v>250</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>143</v>
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="D144" s="5">
-        <v>150</v>
+        <v>40.14</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>144</v>
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="D145" s="5">
-        <v>300</v>
+        <v>4.41</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>145</v>
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D146" s="5">
+        <v>1</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="3">
+        <v>146</v>
+      </c>
+      <c r="B147" s="4"/>
+      <c r="C147" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D146" s="5">
-        <v>5</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F146" s="4" t="s">
+      <c r="D147" s="5">
+        <v>1</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="3">
+        <v>147</v>
+      </c>
+      <c r="B148" s="4"/>
+      <c r="C148" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D148" s="5">
+        <v>28.44</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F148" s="4" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="3">
+        <v>148</v>
+      </c>
+      <c r="B149" s="4"/>
+      <c r="C149" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D149" s="5">
+        <v>99</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="3">
+        <v>149</v>
+      </c>
+      <c r="B150" s="4"/>
+      <c r="C150" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D150" s="5">
+        <v>1.71</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="3">
+        <v>150</v>
+      </c>
+      <c r="B151" s="4"/>
+      <c r="C151" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D151" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="3">
+        <v>151</v>
+      </c>
+      <c r="B152" s="4"/>
+      <c r="C152" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D152" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="3">
+        <v>152</v>
+      </c>
+      <c r="B153" s="4"/>
+      <c r="C153" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D153" s="5">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="3">
+        <v>153</v>
+      </c>
+      <c r="B154" s="4"/>
+      <c r="C154" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D154" s="5">
+        <v>9</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="3">
+        <v>154</v>
+      </c>
+      <c r="B155" s="4"/>
+      <c r="C155" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D155" s="5">
+        <v>9</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="3">
+        <v>155</v>
+      </c>
+      <c r="B156" s="4"/>
+      <c r="C156" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D156" s="5">
+        <v>9</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="3">
+        <v>156</v>
+      </c>
+      <c r="B157" s="4"/>
+      <c r="C157" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D157" s="5">
+        <v>9</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="3">
+        <v>157</v>
+      </c>
+      <c r="B158" s="4"/>
+      <c r="C158" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D158" s="5">
+        <v>1</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="3">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4"/>
+      <c r="C159" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D159" s="5">
+        <v>9</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="3">
+        <v>159</v>
+      </c>
+      <c r="B160" s="4"/>
+      <c r="C160" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D160" s="5">
+        <v>29.72</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="3">
+        <v>160</v>
+      </c>
+      <c r="B161" s="4"/>
+      <c r="C161" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D161" s="5">
+        <v>8</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="3">
+        <v>161</v>
+      </c>
+      <c r="B162" s="4"/>
+      <c r="C162" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D162" s="5">
+        <v>3</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="3">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4"/>
+      <c r="C163" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D163" s="5">
+        <v>10</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="3">
+        <v>163</v>
+      </c>
+      <c r="B164" s="4"/>
+      <c r="C164" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D164" s="5">
+        <v>18</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="3">
+        <v>164</v>
+      </c>
+      <c r="B165" s="4"/>
+      <c r="C165" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D165" s="5">
+        <v>80</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="3">
+        <v>165</v>
+      </c>
+      <c r="B166" s="4"/>
+      <c r="C166" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D166" s="5">
+        <v>160</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="3">
+        <v>166</v>
+      </c>
+      <c r="B167" s="4"/>
+      <c r="C167" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D167" s="5">
+        <v>10</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="3">
+        <v>167</v>
+      </c>
+      <c r="B168" s="4"/>
+      <c r="C168" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D168" s="5">
+        <v>10</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="3">
+        <v>168</v>
+      </c>
+      <c r="B169" s="4"/>
+      <c r="C169" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D169" s="5">
+        <v>10</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="3">
+        <v>169</v>
+      </c>
+      <c r="B170" s="4"/>
+      <c r="C170" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D170" s="5">
+        <v>10</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="3">
+        <v>170</v>
+      </c>
+      <c r="B171" s="4"/>
+      <c r="C171" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D171" s="5">
+        <v>932</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="3">
+        <v>171</v>
+      </c>
+      <c r="B172" s="4"/>
+      <c r="C172" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D172" s="7">
+        <v>1192</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="3">
+        <v>172</v>
+      </c>
+      <c r="B173" s="4"/>
+      <c r="C173" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D173" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="3">
+        <v>173</v>
+      </c>
+      <c r="B174" s="4"/>
+      <c r="C174" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D174" s="5">
+        <v>27</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="3">
+        <v>174</v>
+      </c>
+      <c r="B175" s="4"/>
+      <c r="C175" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D175" s="5">
+        <v>30</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E8650F-B0FA-43C8-AEFE-246D339F49B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265810E7-253B-4CDA-8348-1474619741FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="3270" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="304">
   <si>
     <t>№ п/п</t>
   </si>
@@ -48,54 +48,138 @@
     <t>шт</t>
   </si>
   <si>
+    <t>ЛГУП-7428</t>
+  </si>
+  <si>
+    <t>Днище 377х10 09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>Днище 720х12 ст09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 820х14-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>ЛГУП-7491</t>
+  </si>
+  <si>
+    <t>м2</t>
+  </si>
+  <si>
+    <t>кг</t>
+  </si>
+  <si>
+    <t>ЛГУП-7492</t>
+  </si>
+  <si>
+    <t>Вал ПСМНТ.001.015.000 св.загот (нормализация "стоя" при темп-ре 350-400 град 30 мин и отпуск в печи)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7499</t>
+  </si>
+  <si>
+    <t>Корпус ПСМНТ.001.018.001 (14 скв) - наплавка ПНЖ</t>
+  </si>
+  <si>
+    <t>Крышка ПСМНТ.001.000.001 (заготовка-отливка СЧ14-18 ГОСТ 1412-85)</t>
+  </si>
+  <si>
+    <t>Сегмент ПСМНТ.001.014.000</t>
+  </si>
+  <si>
+    <t>ЛГУП-7516</t>
+  </si>
+  <si>
+    <t>Краскопульт для труб</t>
+  </si>
+  <si>
+    <t>ЛГУП-7525</t>
+  </si>
+  <si>
+    <t>Шуроповерт Макита</t>
+  </si>
+  <si>
+    <t>ЛГУП-7534</t>
+  </si>
+  <si>
+    <t>Биты крестовая РН-2</t>
+  </si>
+  <si>
+    <t>Бита для кровельных саморезов 8мм</t>
+  </si>
+  <si>
+    <t>Бита для кровельных саморезов10мм</t>
+  </si>
+  <si>
+    <t>Система контроля каротажа СКК</t>
+  </si>
+  <si>
+    <t>ЛГУП-7535</t>
+  </si>
+  <si>
+    <t>Перчатки с латесным покрытием</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
     <t>ЛГУП-7331</t>
   </si>
   <si>
+    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
+  </si>
+  <si>
+    <t>пара</t>
+  </si>
+  <si>
     <t>Маркер  краска красный по металлу</t>
   </si>
   <si>
-    <t>шт.</t>
-  </si>
-  <si>
-    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
-  </si>
-  <si>
-    <t>пара</t>
-  </si>
-  <si>
-    <t>Перчатки с латесным покрытием</t>
-  </si>
-  <si>
-    <t>пар</t>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Каска строительная оранжевая Исток</t>
+  </si>
+  <si>
+    <t>Каска строительная белая</t>
+  </si>
+  <si>
+    <t>Маркер белый</t>
+  </si>
+  <si>
+    <t>Ветошь</t>
   </si>
   <si>
     <t>Огнетушитель ОП-8</t>
   </si>
   <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Каска строительная оранжевая Исток</t>
-  </si>
-  <si>
-    <t>Ветошь</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Каска строительная белая</t>
-  </si>
-  <si>
-    <t>Маркер белый</t>
+    <t>Кувалда 1 кг.</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Резак</t>
+  </si>
+  <si>
+    <t>Ножницы по металлу</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 24</t>
   </si>
   <si>
     <t>Ключ комбинированные омедненные 30</t>
   </si>
   <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
     <t>Ключ комбинированные омедненные 36</t>
   </si>
   <si>
@@ -105,184 +189,169 @@
     <t>Гайковерт</t>
   </si>
   <si>
-    <t>Ключ комбинированные омедненные 24</t>
-  </si>
-  <si>
-    <t>Трещетка ключ 1/2</t>
-  </si>
-  <si>
-    <t>Ножницы по металлу</t>
-  </si>
-  <si>
-    <t>Резак</t>
-  </si>
-  <si>
     <t>Ключи обмедненные</t>
   </si>
   <si>
     <t>набор</t>
   </si>
   <si>
-    <t>Кувалда 1 кг.</t>
-  </si>
-  <si>
-    <t>Днище 377х10 09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>ЛГУП-7428</t>
-  </si>
-  <si>
-    <t>Днище 720х12 ст09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 820х14-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>кг</t>
-  </si>
-  <si>
-    <t>ЛГУП-7445</t>
-  </si>
-  <si>
-    <t>ЛГУП-7446</t>
-  </si>
-  <si>
-    <t>ЛГУП-7447</t>
+    <t>Перемычка и наконечник НКИ 6-0-6</t>
   </si>
   <si>
     <t>ЛГУП-7448</t>
   </si>
   <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>Индикатор положения поплавка ИПП 01.00.000</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8</t>
+  </si>
+  <si>
     <t>Блок коммутации 24В БК-24-RS485-01</t>
   </si>
   <si>
     <t>МИП-24 исп.20 (МИП-24-2/П5-Р-RS), до двух АКБ 12 В 17 Ач</t>
   </si>
   <si>
-    <t>Держатель проводника Rd8</t>
-  </si>
-  <si>
-    <t>Индикатор положения поплавка ИПП 01.00.000</t>
-  </si>
-  <si>
-    <t>Перемычка и наконечник НКИ 6-0-6</t>
-  </si>
-  <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>ЛГУП-7450</t>
-  </si>
-  <si>
     <t>Палитра цветов</t>
   </si>
   <si>
-    <t>ЛГУП-7454</t>
-  </si>
-  <si>
-    <t>ЛГУП-7457</t>
-  </si>
-  <si>
-    <t>ЛГУП-7460</t>
-  </si>
-  <si>
-    <t>Газоанализатор взрывозащищенный СГОЭС 1Ex d IIC T4 Gb, IP67</t>
-  </si>
-  <si>
-    <t>ЛГУП-7475</t>
-  </si>
-  <si>
-    <t>Наконечник штыревой втулочный изолированный НШВИ 0.5-8 79435</t>
-  </si>
-  <si>
-    <t>ЛГУП-7477</t>
-  </si>
-  <si>
-    <t>Провод силовой ПуГВнг(А)-LS 1х0.5 белый</t>
-  </si>
-  <si>
-    <t>ЛГУП-7478</t>
-  </si>
-  <si>
-    <t>ЛГУП-7480</t>
-  </si>
-  <si>
-    <t>ЛГУП-7485</t>
-  </si>
-  <si>
-    <t>Дюбель-молли М6х50</t>
-  </si>
-  <si>
-    <t>Контргайка 20 ГОСТ 8968-75 (12Х18Н10Т)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7489</t>
-  </si>
-  <si>
-    <t>ЛГУП-7490</t>
-  </si>
-  <si>
-    <t>Сапоги летние</t>
-  </si>
-  <si>
-    <t>НТУП-018048</t>
-  </si>
-  <si>
-    <t>спец одежда летняя</t>
-  </si>
-  <si>
-    <t>ЛГУП-7491</t>
-  </si>
-  <si>
-    <t>м2</t>
-  </si>
-  <si>
-    <t>ЛГУП-7492</t>
-  </si>
-  <si>
-    <t>Лист гладкий 0,5 1250х2500мм RAL полиуретан 9016(белый)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7493</t>
-  </si>
-  <si>
-    <t>ЛГУП-7496</t>
-  </si>
-  <si>
-    <t>ЛГУП-7497</t>
-  </si>
-  <si>
-    <t>ЛГУП-7498</t>
-  </si>
-  <si>
-    <t>Вал ПСМНТ.001.015.000 св.загот (нормализация "стоя" при темп-ре 350-400 град 30 мин и отпуск в печи)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7499</t>
-  </si>
-  <si>
-    <t>Корпус ПСМНТ.001.018.001 (14 скв) - наплавка ПНЖ</t>
-  </si>
-  <si>
-    <t>Крышка ПСМНТ.001.000.001 (заготовка-отливка СЧ14-18 ГОСТ 1412-85)</t>
-  </si>
-  <si>
-    <t>Сегмент ПСМНТ.001.014.000</t>
-  </si>
-  <si>
-    <t>Оцинкование шпилек М16х80 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>ЛГУП-7500</t>
-  </si>
-  <si>
-    <t>Оцинкование шпилек М24х130 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>ЛГУП-7501</t>
-  </si>
-  <si>
-    <t>ЛГУП-7502</t>
+    <t>ЛГУП-7511</t>
+  </si>
+  <si>
+    <t>ЛГУП-7542</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 8.03.016 ГОСТ 13463-77</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 6.02.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>ЛГУП-7543</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 12 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 8.02.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шибер НТ.512.000.005.02 (лазер)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7545</t>
+  </si>
+  <si>
+    <t>Шибер НТ.512.000.005.02 (шлифовка)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7547</t>
+  </si>
+  <si>
+    <t>Хомут для воздуховода 250 М8</t>
+  </si>
+  <si>
+    <t>Хомут для воздуховода 350 М8</t>
+  </si>
+  <si>
+    <t>Хомут соединительный 125</t>
+  </si>
+  <si>
+    <t>Сетка защитная на всас VR-200</t>
+  </si>
+  <si>
+    <t>Сетка защитная VR-250</t>
+  </si>
+  <si>
+    <t>Решетка гравитационная D200</t>
+  </si>
+  <si>
+    <t>Клапан обратный взрывозащищенный 150х150 АЗЕ 102.000-00</t>
+  </si>
+  <si>
+    <t>Вентилятор осевой накладной Ровен VC-125  IP54 0,15 кВт, 220V, 50Гц</t>
+  </si>
+  <si>
+    <t>Вентилятор взрывозащищенный ВР 300-45-2; исп.1(В1) Пр270; 0,37 кВт; 1330 об/мин</t>
+  </si>
+  <si>
+    <t>ЛГУП-7548</t>
+  </si>
+  <si>
+    <t>Саморез с пресс шайбой 4,2х13</t>
+  </si>
+  <si>
+    <t>ЛГУП-7550</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Шайба 16 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Днище 219х4-25 ст.20 ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Двигатель АИМЛ 63 В4IM3081</t>
+  </si>
+  <si>
+    <t>Сетка П160 ГОСТ 3187-76</t>
+  </si>
+  <si>
+    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
+  </si>
+  <si>
+    <t>Полумуфта насоса НТ.3.00.00.00.002 (изготовление шлицов)</t>
+  </si>
+  <si>
+    <t>Полумуфта привода НТ.3.00.00.00.003 (изготовление паза)</t>
+  </si>
+  <si>
+    <t>Круг D265 ст.20 ГОСТ 1050-13</t>
+  </si>
+  <si>
+    <t>Круг D160 Ст.3 ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Круг D26 Ст.3 ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Круг D6-h10 ГОСТ 7417-75/ Ст.10 ГОСТ 1051-73</t>
+  </si>
+  <si>
+    <t>Картонная коробка - 400 (Д) х 400 (Ш) х 610 (В) мм (картон Т23 ГОСТ 7376-89)</t>
+  </si>
+  <si>
+    <t>Скотч 50мм*120м PROFITTO /6/54 прозрачн</t>
+  </si>
+  <si>
+    <t>Лист А0.М1(анод) 0,5 ГОСТ 21631-76 (черный)</t>
+  </si>
+  <si>
+    <t>Круг D170 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Прокладка медная 8х11-II ГОСТ 19752-84</t>
+  </si>
+  <si>
+    <t>Труба D60*13 ГКРХ БРКМц3-1 ГОСТ1628-78</t>
+  </si>
+  <si>
+    <t>Труба ГКРХХ 110х17,5 БрАЖН 10-4-4 ГОСТ 1208-90</t>
+  </si>
+  <si>
+    <t>Труба D20х5 БрКМц 3-1 ГОСТ 1208-2014</t>
+  </si>
+  <si>
+    <t>Труба 10х1,0 М3-ПТ ГОСТ 617-90</t>
+  </si>
+  <si>
+    <t>Труба ГКРНх D60х13 БрАЖ9-4 ГОСТ 1628-78</t>
   </si>
   <si>
     <t>Маркер черный</t>
@@ -291,40 +360,88 @@
     <t>Фумлента</t>
   </si>
   <si>
-    <t>Шайба 16 ГОСТ 6958-78</t>
-  </si>
-  <si>
-    <t>Днище 219х4-25 ст.20 ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Труба 10х1,0 М3-ПТ ГОСТ 617-90</t>
-  </si>
-  <si>
-    <t>Труба ГКРХХ 110х17,5 БрАЖН 10-4-4 ГОСТ 1208-90</t>
-  </si>
-  <si>
-    <t>Фланец х-80-40 ГОСТ12821 (заготовка-поковка ст.20 гр.IV КП 195 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Труба D89х6 ГОСТ 8732-78 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D108х16 ГОСТ 8732-78/ Ст.40Х  ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D194х14 В20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+    <t>Наконечник кабельный НШвИ 2,5мм</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный НШвИ 1,5мм</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный НШвИ 0,75мм</t>
+  </si>
+  <si>
+    <t>Разъем РпИм 1.25-5-0.8 плоский</t>
+  </si>
+  <si>
+    <t>DIN-рейка 50см перфорированная adr-50 EKF арт. adr-50</t>
+  </si>
+  <si>
+    <t>Фиксатор ФК-102-01 на DIN-рейку 32057DEK Dekraft 2 арт. 32057DEK</t>
+  </si>
+  <si>
+    <t>Заглушка NO-550-07 для винтовых клемм 2,5мм2 арт. Б0035737</t>
+  </si>
+  <si>
+    <t>Зажим клеммный винтовой 2,5 мм2 (50/1500/36000) Б0033416 ЭРА арт. Б0033416</t>
+  </si>
+  <si>
+    <t>Шина заземления на DIN-изолятор ШНИ-6х9-8</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 4.1.1</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 4.1.1</t>
+  </si>
+  <si>
+    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внутренний CS 90 100 х 50мм</t>
+  </si>
+  <si>
+    <t>Крышка на угол вертикальный внешний CD90 (100х50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внешний CD 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический двухполюсный IEK ARMAT M10N 2P B 10А AR-M10N-2-B010</t>
+  </si>
+  <si>
+    <t>Выключатель автоматический двухполюсный 3А B ВА47-29 4.5кА MVA20-2-003-B IEK</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Угол вертикальный внутренний CS 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внутренний CS 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
+  </si>
+  <si>
+    <t>Карта proximity стандартная ST-PC010EM</t>
   </si>
   <si>
     <t>Корпус металлический ЩМП-3-0 (650х500х220мм) У2 IP54 YKM40-03-54 IEK арт. YKM40-03-54</t>
@@ -333,328 +450,493 @@
     <t>Контроллер доступа "С2000-2"</t>
   </si>
   <si>
-    <t>Выключатель автоматический двухполюсный IEK ARMAT M10N 2P B 10А AR-M10N-2-B010</t>
-  </si>
-  <si>
-    <t>Выключатель автоматический двухполюсный 3А B ВА47-29 4.5кА MVA20-2-003-B IEK</t>
-  </si>
-  <si>
-    <t>Шина заземления на DIN-изолятор ШНИ-6х9-8</t>
-  </si>
-  <si>
-    <t>Зажим клеммный винтовой 2,5 мм2 (50/1500/36000) Б0033416 ЭРА арт. Б0033416</t>
-  </si>
-  <si>
-    <t>Заглушка NO-550-07 для винтовых клемм 2,5мм2 арт. Б0035737</t>
-  </si>
-  <si>
-    <t>Фиксатор ФК-102-01 на DIN-рейку 32057DEK Dekraft 2 арт. 32057DEK</t>
-  </si>
-  <si>
-    <t>DIN-рейка 50см перфорированная adr-50 EKF арт. adr-50</t>
-  </si>
-  <si>
-    <t>Разъем РпИм 1.25-5-0.8 плоский</t>
-  </si>
-  <si>
-    <t>Наконечник кабельный НШвИ 0,75мм</t>
+    <t>Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 120</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
   </si>
   <si>
     <t>Коробка клеммная К-СП 08.13.09 24/11П 2КВе-Л-М20(А)-2КВе-Л-М20(В) 1ExeLLCGbXT6 ip66,80х130х90</t>
   </si>
   <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>Крышка на угол вертикальный внутренний CS 90 100 х 50мм</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 4.1.1</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 4.1.1</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
-  </si>
-  <si>
-    <t>Пластина анкерная 120</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/Ø 5-14 мм</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Провод ПуГВнг(А)-LS 1x1,5</t>
+  </si>
+  <si>
+    <t>Провод ПуГВнг(А)-LS 1x0,75</t>
+  </si>
+  <si>
+    <t>Кабель-канал 40х40 перфорированный Plast kk40-40 EKF</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
   </si>
   <si>
     <t>Короб ПВХ 40х40 мм</t>
   </si>
   <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
-  </si>
-  <si>
-    <t>Кабель-канал 40х40 перфорированный Plast kk40-40 EKF</t>
-  </si>
-  <si>
-    <t>Провод ПуГВнг(А)-LS 1x0,75</t>
-  </si>
-  <si>
-    <t>Провод ПуГВнг(А)-LS 1x1,5</t>
-  </si>
-  <si>
-    <t>Провод Rd8</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Выключатель двухклавишный IP55</t>
-  </si>
-  <si>
-    <t>Наконечник кабельный НШвИ 1,5мм</t>
-  </si>
-  <si>
-    <t>Наконечник кабельный НШвИ 2,5мм</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внешний CD 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Крышка на угол вертикальный внешний CD90 (100х50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внутренний CS 90 100 х 50мм</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Угол вертикальный внутренний CS 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внутренний CS 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
-  </si>
-  <si>
-    <t>Карта proximity стандартная ST-PC010EM</t>
-  </si>
-  <si>
-    <t>Кольцо 112-118-36 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 080-090-58 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Прокладка медная 8х11-II ГОСТ 19752-84</t>
-  </si>
-  <si>
-    <t>Пружина ПСМНТ.001.000.030</t>
-  </si>
-  <si>
-    <t>Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 065-075-58 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Уплотнение ПСМНТ.001.022.002</t>
-  </si>
-  <si>
-    <t>Кольцо 055-060-30-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Круг D195 Ст.16ГС-3 ГОСТ 5520-79</t>
-  </si>
-  <si>
-    <t>Круг D430 Ст.16ГС ГОСТ 19281-14</t>
-  </si>
-  <si>
-    <t>Круг D70 Ст.40Х ГОСТ 4543-71</t>
-  </si>
-  <si>
-    <t>Круг D45 Ст.40Х ГОСТ 4543-71</t>
-  </si>
-  <si>
-    <t>Круг D370 Ст.20 ГОСТ1050-88</t>
-  </si>
-  <si>
-    <t>Шестигранник S=14 Ст.45 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Лист Б-ПР-1,0 ГОСТ 19904-74/ 4-III-Ст3кп ГОСТ 16523-89</t>
-  </si>
-  <si>
-    <t>Шарик 25,4-100 ГОСТ 3722-81</t>
+    <t>Шпонка 6х6х20 ГОСТ 23360-78</t>
+  </si>
+  <si>
+    <t>Шплинт 3,2х25.3.019 ГОСТ 397-79</t>
+  </si>
+  <si>
+    <t>Шплинт 2х20 ГОСТ 397</t>
+  </si>
+  <si>
+    <t>Шайба С.20 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба С.16.05.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба С 10.019 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Шайба М4.02.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба А.12.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба А.10.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Винт М4-6g*55.33 ГОСТ 1491-80</t>
   </si>
   <si>
     <t>Винт М16х50.56.019 ГОСТ 1481-84</t>
   </si>
   <si>
+    <t>Винт ВМ 6-6gх12.56.019 ГОСТ 1491-84</t>
+  </si>
+  <si>
+    <t>Винт ВМ 6-6gх10.56.019 ГОСТ 1491-84</t>
+  </si>
+  <si>
+    <t>Винт ВМ 4-6gх12.56.019 ГОСТ1491-84</t>
+  </si>
+  <si>
+    <t>Винт В2.М6-6gх8.48.016 ГОСТ 17475-80</t>
+  </si>
+  <si>
+    <t>Винт В1.М4-6gх16.56.019 ГОСТ 17473-80</t>
+  </si>
+  <si>
+    <t>Винт А.М10-6gх10  ГОСТ 1476-93</t>
+  </si>
+  <si>
+    <t>Болт М8х75.019 ГОСТ 15589-70</t>
+  </si>
+  <si>
+    <t>Болт М8х20.58.019 ГОСТ 7805-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх45.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх40.58 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх35.66.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх25.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх16 56.35.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М6х16.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М6-6gх12.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М6-6gx25.56.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М20х50 ГОСТ15591-70</t>
+  </si>
+  <si>
+    <t>Болт М16х90.58.019 ГОСТ 7805-70</t>
+  </si>
+  <si>
+    <t>Болт М12х50 (S18) ГОСТ 15589-70</t>
+  </si>
+  <si>
+    <t>Болт М12х30.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М12x65 ГОСТ 15589-70</t>
+  </si>
+  <si>
+    <t>Болт М10-6gх35.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Шплинт 6,3х50.4 ГОСТ 397-79</t>
+  </si>
+  <si>
+    <t>Заклепка вытяжная 3,2х8-NiCu/SSt ISO 16584</t>
+  </si>
+  <si>
+    <t>Шпонка 12х8х28 ГОСТ 23360-78</t>
+  </si>
+  <si>
+    <t>Винт М4-6gх16.58.019 ГОСТ 17473-80</t>
+  </si>
+  <si>
+    <t>Винт М4х12.68.019 ГОСТ 1491-80</t>
+  </si>
+  <si>
+    <t>Шайба 4 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 5 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 5.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба 6 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 6.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Винт М6-6gх16.58.019 ГОСТ 17475-80</t>
+  </si>
+  <si>
+    <t>Винт М8-6gх25.68 ГОСТ 11738-84</t>
+  </si>
+  <si>
+    <t>Гайка 2М16.5.056 ГОСТ 5918-73</t>
+  </si>
+  <si>
+    <t>Гайка АМ30-6Н.20.III.4.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка АМ36-6Н.20lll.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
+  </si>
+  <si>
+    <t>Гайка М14х1,5 ГОСТ 15522-70</t>
+  </si>
+  <si>
+    <t>Гайка М16 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
+  </si>
+  <si>
+    <t>Гайка М20 ГОСТ 9064 -75</t>
+  </si>
+  <si>
+    <t>Гайка М20-6Н ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Гайка М24 оцинк. ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка М4-7Н.019 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Гайка М5-7Н.5.019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>Гайка М6-6Н.5.019 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Гайка М8-6H.5 ГОСТ 2524-70</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.016 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Заклепка 4х8.31 ГОСТ 10299-80</t>
+  </si>
+  <si>
+    <t>Саморез для сэндвич панелей 5,5х100</t>
+  </si>
+  <si>
+    <t>Саморез для сэндвич панелей 5,5х130</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х19 RAL1021 (желт)</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х25 RAL1021 (желт)</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х25 RAL9003 (белый)</t>
+  </si>
+  <si>
+    <t>Саморез металл/металл 4,2х19</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 10 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 10.02.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 12.02 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 16 65Г 05 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 16.Ст3сп3.II.4.019 ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>Шайба 30.Ст3сп3.II.4.019 ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>Шайба 36 ГОСТ 9065-75 (шт.)</t>
+  </si>
+  <si>
+    <t>Саморез кровельный 5,5х25 RAL9016 (белый)</t>
+  </si>
+  <si>
     <t>Заклепка 2х4х37 Ан.Окс.хр. ГОСТ10299-80</t>
   </si>
   <si>
+    <t>Болт М16-6gх110.58 ГОСТ 7805-70</t>
+  </si>
+  <si>
+    <t>Болт М10x30 (S16) ГОСТ 15589-70</t>
+  </si>
+  <si>
+    <t>Шпилька АМ20х1,5-6gx130.40.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька М16-6gx220 ГОСТ 22042-76</t>
+  </si>
+  <si>
+    <t>Шпилька АМ20х1,5-6gх110.40.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Болт М8-6gx12 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Гайка М12-6Н.019 ГОСТ 15521-70</t>
+  </si>
+  <si>
+    <t>Шпилька М8х350, кл.пр. 8.8, оц</t>
+  </si>
+  <si>
+    <t>Шайба 8Л ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба нажимная ПСМНТ.001.000.026</t>
+  </si>
+  <si>
+    <t>Шпилька М24х130 ГОСТ 9066-75</t>
+  </si>
+  <si>
     <t>Шпилька М18х40.56.019 ГОСТ 22034-76</t>
   </si>
   <si>
-    <t>Заглушка для CP-ML 2 ур. 4мм2 серая IEK YCT23-00-2-K03-004-ZGL IEK</t>
-  </si>
-  <si>
-    <t>Клемма пружинная Push-in CP-ML 2 ур. 4мм2 серая IEK YCT23-00-2-K03-004 IEK</t>
-  </si>
-  <si>
-    <t>Промежуточное реле 2 CO контакта 24в DC</t>
-  </si>
-  <si>
-    <t>Розетка для реле 2 СО</t>
-  </si>
-  <si>
-    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Сгон ДУ20 L-120 12Х18Н10Т</t>
+    <t>Шпилька М16х90 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька АМ16-6gx80 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька А1М20-6gх120.48.40Х.IV.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька А1М36-6gx220.09Г2С (оцинк.) ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шайба усиленная М16 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Шайба А8 ГОСТ 10450-78</t>
+  </si>
+  <si>
+    <t>Шайба А14 ГОСТ 10450-78</t>
+  </si>
+  <si>
+    <t>Шайба А10.01.019 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Шайба А 16.37 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Шайба 6Л ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 10.65Г.019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>не исп. Шайба 10 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Саморез для сэндвич панелей 5,5х25</t>
+  </si>
+  <si>
+    <t>не исп. Саморез для сэндвич панелей 5,5х180</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х8 оцинкованная</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х10</t>
+  </si>
+  <si>
+    <t>Гвозди П1,6х25 ГОСТ 4028-63</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.5 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Гайка М16-6Н ГОСТ 5916-70</t>
+  </si>
+  <si>
+    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>Гайка 2М18.5.019 ГОСТ 5915-70</t>
   </si>
   <si>
     <t>Гайка 2М14х1,5 ГОСТ 15522-70</t>
   </si>
   <si>
-    <t>Болт М8-6gх25.58.019 ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Гайка М14х1,5 ГОСТ 15522-70</t>
-  </si>
-  <si>
-    <t>Шайба 8 ГОСТ 6402-70</t>
-  </si>
-  <si>
-    <t>Шайба А8 ГОСТ 10450-78</t>
-  </si>
-  <si>
-    <t>Шайба А14 ГОСТ 10450-78</t>
-  </si>
-  <si>
-    <t>Труба D102х5 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D219х5 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба ДКРПТ 8х1 М2 ГОСТ 617-90 (отгружать L кратно 2,5м, либо бухтами)</t>
-  </si>
-  <si>
-    <t>Круг D160 Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Круг D265 ст.20 ГОСТ 1050-13</t>
-  </si>
-  <si>
-    <t>Круг D26 Ст.3 ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
-  </si>
-  <si>
-    <t>Круг D6-h10 ГОСТ 7417-75/ Ст.10 ГОСТ 1051-73</t>
-  </si>
-  <si>
-    <t>Сетка П160 ГОСТ 3187-76</t>
-  </si>
-  <si>
-    <t>Двигатель АИМЛ 63 В4IM3081</t>
-  </si>
-  <si>
-    <t>Полумуфта насоса НТ.3.00.00.00.002 (изготовление шлицов)</t>
-  </si>
-  <si>
-    <t>Полумуфта привода НТ.3.00.00.00.003 (изготовление паза)</t>
-  </si>
-  <si>
-    <t>Картонная коробка - 400 (Д) х 400 (Ш) х 610 (В) мм (картон Т23 ГОСТ 7376-89)</t>
-  </si>
-  <si>
-    <t>Лист А0.М1(анод) 0,5 ГОСТ 21631-76 (черный)</t>
-  </si>
-  <si>
-    <t>Скотч 50мм*120м PROFITTO /6/54 прозрачн</t>
-  </si>
-  <si>
-    <t>Круг D170 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Тройник 89х6 ст.09Г2С ГОСТ 17376-2001</t>
-  </si>
-  <si>
-    <t>Газоанализатор взрывозащищенный СГОЭС (метан) 1Ex d IIC T4 Gb, IP67 Ур1. 10%, ур.2 50% НКПР</t>
-  </si>
-  <si>
-    <t>Шпилька А1М36-6gx220.09Г2С (оцинк.) ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Гайка М36-6Н ст.09Г2С (оцинк.) ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Кольцо 210-220-58-2-2 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Грунт-эмаль 2К ПУ, RAL 9003 (белый)</t>
-  </si>
-  <si>
-    <t>Паронит ПОН-Б 1мм</t>
+    <t>Рычаг НТ.510.000.003.0 (лазер)</t>
+  </si>
+  <si>
+    <t>Круг D65 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D4 Ст.10 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
+  </si>
+  <si>
+    <t>Круг D145 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D85 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Воздуховод 160-1700-оц.-0.5-г.г</t>
+  </si>
+  <si>
+    <t>Воздуховод 200-оц.0,5 L=500</t>
+  </si>
+  <si>
+    <t>Воздуховод 250-3000-оц.-0.5-г.г</t>
+  </si>
+  <si>
+    <t>Воздуховод 250-оц.-0.5-н.ф L=210</t>
+  </si>
+  <si>
+    <t>Воздуховод 250-оц.0,5 L=800</t>
+  </si>
+  <si>
+    <t>Воздуховод прямошовный (Ф125-110 оц.0.5)</t>
+  </si>
+  <si>
+    <t>Врезка прямоугольная воротниковая 145х145/250-100-20-оц.-0,5</t>
+  </si>
+  <si>
+    <t>Вставка гибкая ВГ-250-У-О-ф.ф</t>
+  </si>
+  <si>
+    <t>Дефлектор (Ф250 оц.0.5)</t>
+  </si>
+  <si>
+    <t>Заглушка 250-50-оц.-0.5-н</t>
+  </si>
+  <si>
+    <t>Отвод-90 оцинкованный 200-200-35-35-оц.-0.5-ф.ф</t>
+  </si>
+  <si>
+    <t>Отвод-90 оцинкованный 250-250-35-35-оц.-0.5-н.н</t>
+  </si>
+  <si>
+    <t>Переход 250/160-154-50-50-оц.-0.5-н.н</t>
+  </si>
+  <si>
+    <t>Виброизолятор взрывозащищенный ВР-201</t>
+  </si>
+  <si>
+    <t>Обогреватель взрывозащищенный ОВЭ-4-УХЛ3 1,8 кВт, 380В IExdIIАТ3, IP54</t>
+  </si>
+  <si>
+    <t>Электроконвектор с терморегулятором ЭВНБ 1кВт, 220В, 50 Гц.</t>
+  </si>
+  <si>
+    <t>Лист 1,0 ГОСТ 19903-2015 08кп ГОСТ 16523-97</t>
+  </si>
+  <si>
+    <t>Болт М6-6gх16 ГОСТ 7798-70</t>
   </si>
 </sst>
 </file>
@@ -1091,13 +1373,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -1128,10 +1410,10 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="5">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>6</v>
@@ -1146,13 +1428,13 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="D3" s="5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>7</v>
@@ -1164,13 +1446,13 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>7</v>
@@ -1182,13 +1464,13 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5">
-        <v>800</v>
+        <v>23</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>7</v>
@@ -1200,10 +1482,10 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D6" s="5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>9</v>
@@ -1212,328 +1494,328 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="D7" s="5">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="D8" s="5">
-        <v>10</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D9" s="5">
-        <v>10</v>
+        <v>0.09</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="D10" s="5">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="D11" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D12" s="5">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D13" s="5">
-        <v>40</v>
+        <v>28.44</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D14" s="5">
-        <v>10</v>
+        <v>1.71</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="D15" s="5">
-        <v>10</v>
+        <v>0.36</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D16" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D17" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="D18" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="D19" s="5">
-        <v>10</v>
+        <v>29.72</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D20" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D21" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D22" s="5">
         <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D23" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D24" s="5">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1542,16 +1824,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D25" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1560,16 +1842,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="D26" s="5">
-        <v>4</v>
+        <v>53.25</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1578,16 +1860,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D27" s="5">
-        <v>5</v>
+        <v>21.3</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1596,142 +1878,142 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D28" s="5">
-        <v>10</v>
+        <v>23.43</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D29" s="5">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D30" s="5">
-        <v>53.25</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D31" s="5">
-        <v>25</v>
+        <v>0.2</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D32" s="5">
-        <v>49</v>
+        <v>0.08</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D33" s="5">
-        <v>18.25</v>
+        <v>6.8</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D34" s="7">
-        <v>4286.5</v>
+        <v>108</v>
+      </c>
+      <c r="D34" s="5">
+        <v>7.48</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D35" s="5">
-        <v>148.5</v>
+        <v>14.62</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1740,16 +2022,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D36" s="5">
-        <v>37.35</v>
+        <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1758,16 +2040,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="D37" s="5">
-        <v>271.75</v>
+        <v>2</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1776,16 +2058,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="D38" s="5">
-        <v>99.25</v>
+        <v>2</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1794,16 +2076,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="D39" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1812,16 +2094,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="D40" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1830,235 +2112,235 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D42" s="5">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="D43" s="5">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D44" s="5">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="D45" s="5">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="D46" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="D47" s="5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="D48" s="5">
         <v>10</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>48</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="D49" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D50" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="D51" s="5">
         <v>40</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="D52" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="D53" s="5">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -2067,319 +2349,319 @@
         <v>44</v>
       </c>
       <c r="D54" s="5">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>54</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="D55" s="5">
         <v>4</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="D56" s="5">
-        <v>135</v>
+        <v>10</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>56</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="D57" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>57</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="D58" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>58</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="D59" s="5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>59</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="D60" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>60</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="D61" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>61</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="D62" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D63" s="5">
+        <v>10</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D63" s="5">
-        <v>1</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>63</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="D64" s="5">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>64</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D66" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>66</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="D67" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D68" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>68</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D69" s="5">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D70" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>70</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D71" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2388,88 +2670,88 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D72" s="5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D73" s="5">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D74" s="5">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>74</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D75" s="5">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>75</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D76" s="5">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2478,160 +2760,160 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D77" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>77</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D78" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>78</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D79" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>79</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D80" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D81" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D82" s="5">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>82</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D83" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D84" s="5">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>84</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D85" s="5">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2640,16 +2922,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D86" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2658,106 +2940,106 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D87" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>87</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D88" s="5">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>88</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D89" s="5">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>89</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D90" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>90</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D91" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>91</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D92" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2766,43 +3048,43 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D93" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D94" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D95" s="5">
         <v>8</v>
@@ -2811,16 +3093,16 @@
         <v>6</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D96" s="5">
         <v>8</v>
@@ -2829,16 +3111,16 @@
         <v>6</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D97" s="5">
         <v>8</v>
@@ -2847,16 +3129,16 @@
         <v>6</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="D98" s="5">
         <v>1</v>
@@ -2865,187 +3147,187 @@
         <v>6</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D99" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D100" s="5">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D101" s="5">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D102" s="5">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D103" s="5">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D104" s="5">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>104</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D105" s="5">
-        <v>170</v>
+        <v>4</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="D106" s="5">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>106</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D107" s="5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>107</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="D108" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3054,16 +3336,16 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D109" s="5">
-        <v>291</v>
+        <v>1</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3072,16 +3354,16 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D110" s="7">
-        <v>1415.25</v>
+        <v>154</v>
+      </c>
+      <c r="D110" s="5">
+        <v>35</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3090,16 +3372,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D111" s="5">
-        <v>26.5</v>
+        <v>8</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3108,16 +3390,16 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D112" s="5">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3126,16 +3408,16 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D113" s="5">
-        <v>950</v>
+        <v>1</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3144,16 +3426,16 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D114" s="5">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3162,394 +3444,394 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D115" s="5">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="D116" s="5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="D117" s="5">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D118" s="5">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>118</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D119" s="5">
-        <v>500</v>
+        <v>112</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>119</v>
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>120</v>
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="D121" s="5">
         <v>40</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>121</v>
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D122" s="5">
+        <v>15</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F122" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D122" s="5">
-        <v>20</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>122</v>
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D123" s="5">
         <v>6</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>123</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D124" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>124</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="D125" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>125</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="D126" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>57</v>
+        <v>168</v>
       </c>
       <c r="D127" s="5">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>127</v>
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="D128" s="5">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>128</v>
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D129" s="5">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D130" s="5">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>130</v>
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D131" s="5">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D132" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>132</v>
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D133" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>133</v>
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D134" s="5">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D135" s="5">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>62</v>
+        <v>176</v>
       </c>
       <c r="D136" s="5">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3558,16 +3840,16 @@
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D137" s="5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3576,16 +3858,16 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D138" s="5">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3594,16 +3876,16 @@
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D139" s="5">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3612,16 +3894,16 @@
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D140" s="5">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3630,16 +3912,16 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D141" s="5">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3648,16 +3930,16 @@
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D142" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3666,16 +3948,16 @@
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D143" s="5">
-        <v>5.76</v>
+        <v>4</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3684,16 +3966,16 @@
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D144" s="5">
-        <v>40.14</v>
+        <v>4</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3702,16 +3984,16 @@
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D145" s="5">
-        <v>4.41</v>
+        <v>16</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3720,16 +4002,16 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="D146" s="5">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3738,466 +4020,466 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="D147" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>147</v>
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D148" s="5">
-        <v>28.44</v>
+        <v>24</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>148</v>
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D149" s="5">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>149</v>
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D150" s="5">
-        <v>1.71</v>
+        <v>4</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>150</v>
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D151" s="5">
-        <v>0.09</v>
+        <v>4</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>151</v>
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D152" s="5">
-        <v>0.36</v>
+        <v>16</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>152</v>
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D153" s="5">
-        <v>1.7999999999999999E-2</v>
+        <v>32</v>
       </c>
       <c r="E153" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>153</v>
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D154" s="5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="3">
         <v>154</v>
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D155" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
         <v>155</v>
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D156" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>156</v>
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D157" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>157</v>
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D158" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>158</v>
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D159" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>159</v>
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D160" s="5">
-        <v>29.72</v>
+        <v>4</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>160</v>
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="D161" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>161</v>
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>71</v>
+        <v>303</v>
       </c>
       <c r="D162" s="5">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>162</v>
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D163" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>163</v>
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D164" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>164</v>
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D165" s="5">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="E165" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>165</v>
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D166" s="5">
-        <v>160</v>
+        <v>12</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>166</v>
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="D167" s="5">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>167</v>
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="D168" s="5">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="3">
         <v>168</v>
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="D169" s="5">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>169</v>
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="D170" s="5">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
         <v>170</v>
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D171" s="5">
-        <v>932</v>
+        <v>16</v>
       </c>
       <c r="E171" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>171</v>
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D172" s="7">
-        <v>1192</v>
+        <v>210</v>
+      </c>
+      <c r="D172" s="5">
+        <v>92</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4206,16 +4488,16 @@
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D173" s="5">
-        <v>0.18</v>
+        <v>56</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4224,16 +4506,16 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D174" s="5">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4242,16 +4524,3243 @@
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D175" s="5">
+        <v>32</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="3">
+        <v>175</v>
+      </c>
+      <c r="B176" s="4"/>
+      <c r="C176" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D176" s="5">
+        <v>4</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="3">
+        <v>176</v>
+      </c>
+      <c r="B177" s="4"/>
+      <c r="C177" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D177" s="5">
+        <v>96</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="3">
+        <v>177</v>
+      </c>
+      <c r="B178" s="4"/>
+      <c r="C178" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D178" s="5">
+        <v>160</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="3">
+        <v>178</v>
+      </c>
+      <c r="B179" s="4"/>
+      <c r="C179" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D179" s="5">
+        <v>16</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="3">
+        <v>179</v>
+      </c>
+      <c r="B180" s="4"/>
+      <c r="C180" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D180" s="5">
+        <v>12</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="3">
+        <v>180</v>
+      </c>
+      <c r="B181" s="4"/>
+      <c r="C181" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D181" s="7">
+        <v>7328</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="3">
+        <v>181</v>
+      </c>
+      <c r="B182" s="4"/>
+      <c r="C182" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D182" s="5">
+        <v>124</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="3">
+        <v>182</v>
+      </c>
+      <c r="B183" s="4"/>
+      <c r="C183" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D183" s="5">
+        <v>288</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="3">
+        <v>183</v>
+      </c>
+      <c r="B184" s="4"/>
+      <c r="C184" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D184" s="5">
+        <v>16</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="3">
+        <v>184</v>
+      </c>
+      <c r="B185" s="4"/>
+      <c r="C185" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D185" s="5">
+        <v>672</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="3">
+        <v>185</v>
+      </c>
+      <c r="B186" s="4"/>
+      <c r="C186" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D186" s="5">
+        <v>12</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="3">
+        <v>186</v>
+      </c>
+      <c r="B187" s="4"/>
+      <c r="C187" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D187" s="5">
+        <v>40</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="3">
+        <v>187</v>
+      </c>
+      <c r="B188" s="4"/>
+      <c r="C188" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D188" s="5">
+        <v>16</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="3">
+        <v>188</v>
+      </c>
+      <c r="B189" s="4"/>
+      <c r="C189" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D189" s="5">
+        <v>24</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="3">
+        <v>189</v>
+      </c>
+      <c r="B190" s="4"/>
+      <c r="C190" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D190" s="5">
+        <v>236</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="3">
+        <v>190</v>
+      </c>
+      <c r="B191" s="4"/>
+      <c r="C191" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D191" s="5">
+        <v>16</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="3">
+        <v>191</v>
+      </c>
+      <c r="B192" s="4"/>
+      <c r="C192" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D192" s="5">
+        <v>200</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="3">
+        <v>192</v>
+      </c>
+      <c r="B193" s="4"/>
+      <c r="C193" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D193" s="5">
+        <v>680</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="3">
+        <v>193</v>
+      </c>
+      <c r="B194" s="4"/>
+      <c r="C194" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D194" s="7">
+        <v>1000</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="3">
+        <v>194</v>
+      </c>
+      <c r="B195" s="4"/>
+      <c r="C195" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D195" s="7">
+        <v>5600</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="3">
+        <v>195</v>
+      </c>
+      <c r="B196" s="4"/>
+      <c r="C196" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D196" s="7">
+        <v>2400</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="3">
+        <v>196</v>
+      </c>
+      <c r="B197" s="4"/>
+      <c r="C197" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D197" s="5">
+        <v>480</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="3">
+        <v>197</v>
+      </c>
+      <c r="B198" s="4"/>
+      <c r="C198" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D198" s="5">
+        <v>144</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="3">
+        <v>198</v>
+      </c>
+      <c r="B199" s="4"/>
+      <c r="C199" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D199" s="5">
+        <v>140</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="3">
+        <v>199</v>
+      </c>
+      <c r="B200" s="4"/>
+      <c r="C200" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D200" s="5">
+        <v>4</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="3">
+        <v>200</v>
+      </c>
+      <c r="B201" s="4"/>
+      <c r="C201" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D201" s="5">
+        <v>8</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="3">
+        <v>201</v>
+      </c>
+      <c r="B202" s="4"/>
+      <c r="C202" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D202" s="5">
+        <v>4</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="3">
+        <v>202</v>
+      </c>
+      <c r="B203" s="4"/>
+      <c r="C203" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D203" s="5">
+        <v>96</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="3">
+        <v>203</v>
+      </c>
+      <c r="B204" s="4"/>
+      <c r="C204" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D204" s="5">
+        <v>160</v>
+      </c>
+      <c r="E204" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="3">
+        <v>204</v>
+      </c>
+      <c r="B205" s="4"/>
+      <c r="C205" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D205" s="5">
+        <v>1</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="3">
+        <v>205</v>
+      </c>
+      <c r="B206" s="4"/>
+      <c r="C206" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D206" s="5">
+        <v>3</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="3">
+        <v>206</v>
+      </c>
+      <c r="B207" s="4"/>
+      <c r="C207" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D207" s="5">
+        <v>600</v>
+      </c>
+      <c r="E207" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="3">
+        <v>207</v>
+      </c>
+      <c r="B208" s="4"/>
+      <c r="C208" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D208" s="5">
+        <v>4</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="3">
         <v>208</v>
       </c>
-      <c r="D175" s="5">
+      <c r="B209" s="4"/>
+      <c r="C209" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D209" s="5">
+        <v>2</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="3">
+        <v>209</v>
+      </c>
+      <c r="B210" s="4"/>
+      <c r="C210" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D210" s="5">
+        <v>2</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="3">
+        <v>210</v>
+      </c>
+      <c r="B211" s="4"/>
+      <c r="C211" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D211" s="5">
+        <v>1</v>
+      </c>
+      <c r="E211" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="3">
+        <v>211</v>
+      </c>
+      <c r="B212" s="4"/>
+      <c r="C212" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D212" s="5">
+        <v>4</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="3">
+        <v>212</v>
+      </c>
+      <c r="B213" s="4"/>
+      <c r="C213" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D213" s="5">
+        <v>1</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="3">
+        <v>213</v>
+      </c>
+      <c r="B214" s="4"/>
+      <c r="C214" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D214" s="5">
+        <v>6</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="3">
+        <v>214</v>
+      </c>
+      <c r="B215" s="4"/>
+      <c r="C215" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D215" s="5">
+        <v>1</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="3">
+        <v>215</v>
+      </c>
+      <c r="B216" s="4"/>
+      <c r="C216" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D216" s="5">
+        <v>1</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="3">
+        <v>216</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D217" s="5">
+        <v>8</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="3">
+        <v>217</v>
+      </c>
+      <c r="B218" s="4"/>
+      <c r="C218" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D218" s="5">
+        <v>4</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="3">
+        <v>218</v>
+      </c>
+      <c r="B219" s="4"/>
+      <c r="C219" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D219" s="5">
+        <v>3</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="3">
+        <v>219</v>
+      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D220" s="5">
+        <v>4</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="3">
+        <v>220</v>
+      </c>
+      <c r="B221" s="4"/>
+      <c r="C221" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D221" s="5">
+        <v>1</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="3">
+        <v>221</v>
+      </c>
+      <c r="B222" s="4"/>
+      <c r="C222" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D222" s="5">
+        <v>6</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="3">
+        <v>222</v>
+      </c>
+      <c r="B223" s="4"/>
+      <c r="C223" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D223" s="5">
+        <v>4</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="3">
+        <v>223</v>
+      </c>
+      <c r="B224" s="4"/>
+      <c r="C224" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D224" s="5">
+        <v>40</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="3">
+        <v>224</v>
+      </c>
+      <c r="B225" s="4"/>
+      <c r="C225" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D225" s="5">
+        <v>1</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="3">
+        <v>225</v>
+      </c>
+      <c r="B226" s="4"/>
+      <c r="C226" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D226" s="5">
+        <v>1</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="3">
+        <v>226</v>
+      </c>
+      <c r="B227" s="4"/>
+      <c r="C227" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D227" s="5">
+        <v>3</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="3">
+        <v>227</v>
+      </c>
+      <c r="B228" s="4"/>
+      <c r="C228" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D228" s="5">
+        <v>2</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="3">
+        <v>228</v>
+      </c>
+      <c r="B229" s="4"/>
+      <c r="C229" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D229" s="5">
+        <v>4</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="3">
+        <v>229</v>
+      </c>
+      <c r="B230" s="4"/>
+      <c r="C230" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D230" s="5">
+        <v>8</v>
+      </c>
+      <c r="E230" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="3">
+        <v>230</v>
+      </c>
+      <c r="B231" s="4"/>
+      <c r="C231" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D231" s="5">
+        <v>8</v>
+      </c>
+      <c r="E231" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="3">
+        <v>231</v>
+      </c>
+      <c r="B232" s="4"/>
+      <c r="C232" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D232" s="5">
+        <v>16</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="3">
+        <v>232</v>
+      </c>
+      <c r="B233" s="4"/>
+      <c r="C233" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D233" s="5">
+        <v>90</v>
+      </c>
+      <c r="E233" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="3">
+        <v>233</v>
+      </c>
+      <c r="B234" s="4"/>
+      <c r="C234" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D234" s="5">
+        <v>2</v>
+      </c>
+      <c r="E234" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="3">
+        <v>234</v>
+      </c>
+      <c r="B235" s="4"/>
+      <c r="C235" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D235" s="5">
+        <v>3</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="3">
+        <v>235</v>
+      </c>
+      <c r="B236" s="4"/>
+      <c r="C236" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D236" s="5">
+        <v>250</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="3">
+        <v>236</v>
+      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D237" s="7">
+        <v>1400</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="3">
+        <v>237</v>
+      </c>
+      <c r="B238" s="4"/>
+      <c r="C238" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D238" s="5">
+        <v>1</v>
+      </c>
+      <c r="E238" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="3">
+        <v>238</v>
+      </c>
+      <c r="B239" s="4"/>
+      <c r="C239" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D239" s="5">
+        <v>1</v>
+      </c>
+      <c r="E239" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="3">
+        <v>239</v>
+      </c>
+      <c r="B240" s="4"/>
+      <c r="C240" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="D240" s="5">
+        <v>8</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="3">
+        <v>240</v>
+      </c>
+      <c r="B241" s="4"/>
+      <c r="C241" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D241" s="5">
+        <v>1</v>
+      </c>
+      <c r="E241" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="3">
+        <v>241</v>
+      </c>
+      <c r="B242" s="4"/>
+      <c r="C242" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D242" s="5">
+        <v>1</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="3">
+        <v>242</v>
+      </c>
+      <c r="B243" s="4"/>
+      <c r="C243" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D243" s="5">
+        <v>3</v>
+      </c>
+      <c r="E243" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="3">
+        <v>243</v>
+      </c>
+      <c r="B244" s="4"/>
+      <c r="C244" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D244" s="5">
+        <v>4</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="3">
+        <v>244</v>
+      </c>
+      <c r="B245" s="4"/>
+      <c r="C245" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D245" s="5">
+        <v>6</v>
+      </c>
+      <c r="E245" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="3">
+        <v>245</v>
+      </c>
+      <c r="B246" s="4"/>
+      <c r="C246" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D246" s="5">
+        <v>4</v>
+      </c>
+      <c r="E246" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="3">
+        <v>246</v>
+      </c>
+      <c r="B247" s="4"/>
+      <c r="C247" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D247" s="5">
+        <v>14</v>
+      </c>
+      <c r="E247" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="3">
+        <v>247</v>
+      </c>
+      <c r="B248" s="4"/>
+      <c r="C248" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D248" s="5">
+        <v>1</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="3">
+        <v>248</v>
+      </c>
+      <c r="B249" s="4"/>
+      <c r="C249" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D249" s="5">
+        <v>1</v>
+      </c>
+      <c r="E249" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="3">
+        <v>249</v>
+      </c>
+      <c r="B250" s="4"/>
+      <c r="C250" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D250" s="5">
+        <v>3</v>
+      </c>
+      <c r="E250" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="3">
+        <v>250</v>
+      </c>
+      <c r="B251" s="4"/>
+      <c r="C251" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D251" s="5">
+        <v>2</v>
+      </c>
+      <c r="E251" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="3">
+        <v>251</v>
+      </c>
+      <c r="B252" s="4"/>
+      <c r="C252" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D252" s="5">
+        <v>72</v>
+      </c>
+      <c r="E252" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="3">
+        <v>252</v>
+      </c>
+      <c r="B253" s="4"/>
+      <c r="C253" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D253" s="5">
+        <v>20</v>
+      </c>
+      <c r="E253" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="3">
+        <v>253</v>
+      </c>
+      <c r="B254" s="4"/>
+      <c r="C254" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="D254" s="5">
+        <v>447</v>
+      </c>
+      <c r="E254" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="3">
+        <v>254</v>
+      </c>
+      <c r="B255" s="4"/>
+      <c r="C255" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D255" s="5">
+        <v>12</v>
+      </c>
+      <c r="E255" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="3">
+        <v>255</v>
+      </c>
+      <c r="B256" s="4"/>
+      <c r="C256" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D256" s="5">
+        <v>60</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="3">
+        <v>256</v>
+      </c>
+      <c r="B257" s="4"/>
+      <c r="C257" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="D257" s="5">
+        <v>16</v>
+      </c>
+      <c r="E257" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="3">
+        <v>257</v>
+      </c>
+      <c r="B258" s="4"/>
+      <c r="C258" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D258" s="5">
+        <v>20</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="3">
+        <v>258</v>
+      </c>
+      <c r="B259" s="4"/>
+      <c r="C259" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D259" s="5">
+        <v>1</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="3">
+        <v>259</v>
+      </c>
+      <c r="B260" s="4"/>
+      <c r="C260" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D260" s="5">
+        <v>8</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="3">
+        <v>260</v>
+      </c>
+      <c r="B261" s="4"/>
+      <c r="C261" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D261" s="5">
+        <v>3</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F261" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="3">
+        <v>261</v>
+      </c>
+      <c r="B262" s="4"/>
+      <c r="C262" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D262" s="5">
+        <v>1</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="3">
+        <v>262</v>
+      </c>
+      <c r="B263" s="4"/>
+      <c r="C263" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D263" s="5">
+        <v>14</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="3">
+        <v>263</v>
+      </c>
+      <c r="B264" s="4"/>
+      <c r="C264" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D264" s="5">
+        <v>20</v>
+      </c>
+      <c r="E264" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" s="3">
+        <v>264</v>
+      </c>
+      <c r="B265" s="4"/>
+      <c r="C265" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="D265" s="5">
+        <v>3</v>
+      </c>
+      <c r="E265" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" s="3">
+        <v>265</v>
+      </c>
+      <c r="B266" s="4"/>
+      <c r="C266" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D266" s="5">
+        <v>4</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="3">
+        <v>266</v>
+      </c>
+      <c r="B267" s="4"/>
+      <c r="C267" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D267" s="5">
+        <v>16</v>
+      </c>
+      <c r="E267" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="3">
+        <v>267</v>
+      </c>
+      <c r="B268" s="4"/>
+      <c r="C268" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D268" s="5">
+        <v>2</v>
+      </c>
+      <c r="E268" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="3">
+        <v>268</v>
+      </c>
+      <c r="B269" s="4"/>
+      <c r="C269" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D269" s="5">
+        <v>2</v>
+      </c>
+      <c r="E269" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" s="3">
+        <v>269</v>
+      </c>
+      <c r="B270" s="4"/>
+      <c r="C270" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D270" s="5">
+        <v>4</v>
+      </c>
+      <c r="E270" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="3">
+        <v>270</v>
+      </c>
+      <c r="B271" s="4"/>
+      <c r="C271" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D271" s="5">
+        <v>9</v>
+      </c>
+      <c r="E271" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="3">
+        <v>271</v>
+      </c>
+      <c r="B272" s="4"/>
+      <c r="C272" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D272" s="5">
+        <v>8</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" s="3">
+        <v>272</v>
+      </c>
+      <c r="B273" s="4"/>
+      <c r="C273" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D273" s="5">
+        <v>2</v>
+      </c>
+      <c r="E273" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" s="3">
+        <v>273</v>
+      </c>
+      <c r="B274" s="4"/>
+      <c r="C274" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D274" s="5">
+        <v>10</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" s="3">
+        <v>274</v>
+      </c>
+      <c r="B275" s="4"/>
+      <c r="C275" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D275" s="5">
+        <v>10</v>
+      </c>
+      <c r="E275" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" s="3">
+        <v>275</v>
+      </c>
+      <c r="B276" s="4"/>
+      <c r="C276" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D276" s="5">
+        <v>3</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" s="3">
+        <v>276</v>
+      </c>
+      <c r="B277" s="4"/>
+      <c r="C277" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D277" s="5">
+        <v>40</v>
+      </c>
+      <c r="E277" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="3">
+        <v>277</v>
+      </c>
+      <c r="B278" s="4"/>
+      <c r="C278" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D278" s="5">
+        <v>24</v>
+      </c>
+      <c r="E278" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="3">
+        <v>278</v>
+      </c>
+      <c r="B279" s="4"/>
+      <c r="C279" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D279" s="5">
+        <v>1</v>
+      </c>
+      <c r="E279" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" s="3">
+        <v>279</v>
+      </c>
+      <c r="B280" s="4"/>
+      <c r="C280" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D280" s="5">
+        <v>2</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" s="3">
+        <v>280</v>
+      </c>
+      <c r="B281" s="4"/>
+      <c r="C281" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D281" s="5">
+        <v>1</v>
+      </c>
+      <c r="E281" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="3">
+        <v>281</v>
+      </c>
+      <c r="B282" s="4"/>
+      <c r="C282" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D282" s="5">
+        <v>2</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" s="3">
+        <v>282</v>
+      </c>
+      <c r="B283" s="4"/>
+      <c r="C283" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D283" s="5">
+        <v>43</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="3">
+        <v>283</v>
+      </c>
+      <c r="B284" s="4"/>
+      <c r="C284" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D284" s="5">
+        <v>40</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" s="3">
+        <v>284</v>
+      </c>
+      <c r="B285" s="4"/>
+      <c r="C285" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D285" s="5">
+        <v>2</v>
+      </c>
+      <c r="E285" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" s="3">
+        <v>285</v>
+      </c>
+      <c r="B286" s="4"/>
+      <c r="C286" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D286" s="5">
+        <v>120</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" s="3">
+        <v>286</v>
+      </c>
+      <c r="B287" s="4"/>
+      <c r="C287" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D287" s="5">
+        <v>36</v>
+      </c>
+      <c r="E287" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" s="3">
+        <v>287</v>
+      </c>
+      <c r="B288" s="4"/>
+      <c r="C288" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D288" s="5">
+        <v>100</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289" s="3">
+        <v>288</v>
+      </c>
+      <c r="B289" s="4"/>
+      <c r="C289" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D289" s="5">
+        <v>170</v>
+      </c>
+      <c r="E289" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="3">
+        <v>289</v>
+      </c>
+      <c r="B290" s="4"/>
+      <c r="C290" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D290" s="5">
+        <v>50</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="3">
+        <v>290</v>
+      </c>
+      <c r="B291" s="4"/>
+      <c r="C291" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D291" s="5">
         <v>30</v>
       </c>
-      <c r="E175" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F175" s="4" t="s">
+      <c r="E291" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" s="3">
+        <v>291</v>
+      </c>
+      <c r="B292" s="4"/>
+      <c r="C292" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D292" s="5">
+        <v>30</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="3">
+        <v>292</v>
+      </c>
+      <c r="B293" s="4"/>
+      <c r="C293" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="D293" s="5">
+        <v>80</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" s="3">
+        <v>293</v>
+      </c>
+      <c r="B294" s="4"/>
+      <c r="C294" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D294" s="5">
+        <v>127</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="3">
+        <v>294</v>
+      </c>
+      <c r="B295" s="4"/>
+      <c r="C295" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D295" s="5">
+        <v>6</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="3">
+        <v>295</v>
+      </c>
+      <c r="B296" s="4"/>
+      <c r="C296" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D296" s="5">
+        <v>4</v>
+      </c>
+      <c r="E296" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="3">
+        <v>296</v>
+      </c>
+      <c r="B297" s="4"/>
+      <c r="C297" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D297" s="5">
+        <v>10</v>
+      </c>
+      <c r="E297" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="3">
+        <v>297</v>
+      </c>
+      <c r="B298" s="4"/>
+      <c r="C298" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D298" s="5">
+        <v>3</v>
+      </c>
+      <c r="E298" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="3">
+        <v>298</v>
+      </c>
+      <c r="B299" s="4"/>
+      <c r="C299" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D299" s="5">
+        <v>144</v>
+      </c>
+      <c r="E299" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="3">
+        <v>299</v>
+      </c>
+      <c r="B300" s="4"/>
+      <c r="C300" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D300" s="5">
+        <v>4</v>
+      </c>
+      <c r="E300" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="3">
+        <v>300</v>
+      </c>
+      <c r="B301" s="4"/>
+      <c r="C301" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D301" s="5">
+        <v>72</v>
+      </c>
+      <c r="E301" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="3">
+        <v>301</v>
+      </c>
+      <c r="B302" s="4"/>
+      <c r="C302" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D302" s="5">
+        <v>11</v>
+      </c>
+      <c r="E302" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="3">
+        <v>302</v>
+      </c>
+      <c r="B303" s="4"/>
+      <c r="C303" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D303" s="5">
+        <v>16</v>
+      </c>
+      <c r="E303" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" s="3">
+        <v>303</v>
+      </c>
+      <c r="B304" s="4"/>
+      <c r="C304" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D304" s="5">
+        <v>3</v>
+      </c>
+      <c r="E304" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="3">
+        <v>304</v>
+      </c>
+      <c r="B305" s="4"/>
+      <c r="C305" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D305" s="7">
+        <v>1034</v>
+      </c>
+      <c r="E305" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="3">
+        <v>305</v>
+      </c>
+      <c r="B306" s="4"/>
+      <c r="C306" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D306" s="5">
+        <v>51</v>
+      </c>
+      <c r="E306" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="3">
+        <v>306</v>
+      </c>
+      <c r="B307" s="4"/>
+      <c r="C307" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D307" s="5">
+        <v>40</v>
+      </c>
+      <c r="E307" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="3">
+        <v>307</v>
+      </c>
+      <c r="B308" s="4"/>
+      <c r="C308" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D308" s="5">
+        <v>24</v>
+      </c>
+      <c r="E308" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309" s="3">
+        <v>308</v>
+      </c>
+      <c r="B309" s="4"/>
+      <c r="C309" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D309" s="5">
+        <v>20</v>
+      </c>
+      <c r="E309" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="3">
+        <v>309</v>
+      </c>
+      <c r="B310" s="4"/>
+      <c r="C310" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D310" s="5">
+        <v>1</v>
+      </c>
+      <c r="E310" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311" s="3">
+        <v>310</v>
+      </c>
+      <c r="B311" s="4"/>
+      <c r="C311" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D311" s="5">
+        <v>1</v>
+      </c>
+      <c r="E311" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A312" s="3">
+        <v>311</v>
+      </c>
+      <c r="B312" s="4"/>
+      <c r="C312" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D312" s="5">
+        <v>8</v>
+      </c>
+      <c r="E312" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A313" s="3">
+        <v>312</v>
+      </c>
+      <c r="B313" s="4"/>
+      <c r="C313" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D313" s="5">
+        <v>4</v>
+      </c>
+      <c r="E313" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="3">
+        <v>313</v>
+      </c>
+      <c r="B314" s="4"/>
+      <c r="C314" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D314" s="5">
+        <v>2</v>
+      </c>
+      <c r="E314" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="3">
+        <v>314</v>
+      </c>
+      <c r="B315" s="4"/>
+      <c r="C315" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D315" s="5">
+        <v>4</v>
+      </c>
+      <c r="E315" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="3">
+        <v>315</v>
+      </c>
+      <c r="B316" s="4"/>
+      <c r="C316" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D316" s="5">
+        <v>4</v>
+      </c>
+      <c r="E316" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="3">
+        <v>316</v>
+      </c>
+      <c r="B317" s="4"/>
+      <c r="C317" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D317" s="5">
+        <v>18</v>
+      </c>
+      <c r="E317" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318" s="3">
+        <v>317</v>
+      </c>
+      <c r="B318" s="4"/>
+      <c r="C318" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="D318" s="5">
+        <v>18</v>
+      </c>
+      <c r="E318" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="3">
+        <v>318</v>
+      </c>
+      <c r="B319" s="4"/>
+      <c r="C319" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D319" s="5">
+        <v>16.38</v>
+      </c>
+      <c r="E319" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A320" s="3">
+        <v>319</v>
+      </c>
+      <c r="B320" s="4"/>
+      <c r="C320" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="D320" s="5">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="E320" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="3">
+        <v>320</v>
+      </c>
+      <c r="B321" s="4"/>
+      <c r="C321" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D321" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="E321" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="3">
+        <v>321</v>
+      </c>
+      <c r="B322" s="4"/>
+      <c r="C322" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D322" s="5">
+        <v>60.66</v>
+      </c>
+      <c r="E322" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="3">
+        <v>322</v>
+      </c>
+      <c r="B323" s="4"/>
+      <c r="C323" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="D323" s="5">
+        <v>53.28</v>
+      </c>
+      <c r="E323" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A324" s="3">
+        <v>323</v>
+      </c>
+      <c r="B324" s="4"/>
+      <c r="C324" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D324" s="5">
+        <v>18</v>
+      </c>
+      <c r="E324" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="3">
+        <v>324</v>
+      </c>
+      <c r="B325" s="4"/>
+      <c r="C325" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D325" s="5">
+        <v>4</v>
+      </c>
+      <c r="E325" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326" s="3">
+        <v>325</v>
+      </c>
+      <c r="B326" s="4"/>
+      <c r="C326" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D326" s="5">
+        <v>4</v>
+      </c>
+      <c r="E326" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="3">
+        <v>326</v>
+      </c>
+      <c r="B327" s="4"/>
+      <c r="C327" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D327" s="5">
+        <v>4</v>
+      </c>
+      <c r="E327" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="3">
+        <v>327</v>
+      </c>
+      <c r="B328" s="4"/>
+      <c r="C328" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D328" s="5">
+        <v>4</v>
+      </c>
+      <c r="E328" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="3">
+        <v>328</v>
+      </c>
+      <c r="B329" s="4"/>
+      <c r="C329" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D329" s="5">
+        <v>4</v>
+      </c>
+      <c r="E329" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330" s="3">
+        <v>329</v>
+      </c>
+      <c r="B330" s="4"/>
+      <c r="C330" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D330" s="5">
+        <v>4</v>
+      </c>
+      <c r="E330" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331" s="3">
+        <v>330</v>
+      </c>
+      <c r="B331" s="4"/>
+      <c r="C331" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D331" s="5">
+        <v>8</v>
+      </c>
+      <c r="E331" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332" s="3">
+        <v>331</v>
+      </c>
+      <c r="B332" s="4"/>
+      <c r="C332" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D332" s="5">
+        <v>8</v>
+      </c>
+      <c r="E332" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="3">
+        <v>332</v>
+      </c>
+      <c r="B333" s="4"/>
+      <c r="C333" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D333" s="5">
+        <v>4</v>
+      </c>
+      <c r="E333" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="3">
+        <v>333</v>
+      </c>
+      <c r="B334" s="4"/>
+      <c r="C334" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D334" s="5">
+        <v>4</v>
+      </c>
+      <c r="E334" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A335" s="3">
+        <v>334</v>
+      </c>
+      <c r="B335" s="4"/>
+      <c r="C335" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D335" s="5">
+        <v>4</v>
+      </c>
+      <c r="E335" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A336" s="3">
+        <v>335</v>
+      </c>
+      <c r="B336" s="4"/>
+      <c r="C336" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D336" s="5">
+        <v>4</v>
+      </c>
+      <c r="E336" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A337" s="3">
+        <v>336</v>
+      </c>
+      <c r="B337" s="4"/>
+      <c r="C337" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D337" s="5">
+        <v>4</v>
+      </c>
+      <c r="E337" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338" s="3">
+        <v>337</v>
+      </c>
+      <c r="B338" s="4"/>
+      <c r="C338" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D338" s="5">
+        <v>8</v>
+      </c>
+      <c r="E338" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F338" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A339" s="3">
+        <v>338</v>
+      </c>
+      <c r="B339" s="4"/>
+      <c r="C339" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D339" s="5">
+        <v>4</v>
+      </c>
+      <c r="E339" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F339" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A340" s="3">
+        <v>339</v>
+      </c>
+      <c r="B340" s="4"/>
+      <c r="C340" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D340" s="5">
+        <v>4</v>
+      </c>
+      <c r="E340" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F340" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="3">
+        <v>340</v>
+      </c>
+      <c r="B341" s="4"/>
+      <c r="C341" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D341" s="5">
+        <v>32</v>
+      </c>
+      <c r="E341" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A342" s="3">
+        <v>341</v>
+      </c>
+      <c r="B342" s="4"/>
+      <c r="C342" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D342" s="5">
+        <v>8</v>
+      </c>
+      <c r="E342" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F342" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="3">
+        <v>342</v>
+      </c>
+      <c r="B343" s="4"/>
+      <c r="C343" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D343" s="5">
+        <v>4</v>
+      </c>
+      <c r="E343" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F343" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="3">
+        <v>343</v>
+      </c>
+      <c r="B344" s="4"/>
+      <c r="C344" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D344" s="5">
+        <v>4</v>
+      </c>
+      <c r="E344" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A345" s="3">
+        <v>344</v>
+      </c>
+      <c r="B345" s="4"/>
+      <c r="C345" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D345" s="5">
+        <v>8</v>
+      </c>
+      <c r="E345" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F345" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A346" s="3">
+        <v>345</v>
+      </c>
+      <c r="B346" s="4"/>
+      <c r="C346" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D346" s="5">
+        <v>4</v>
+      </c>
+      <c r="E346" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F346" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A347" s="3">
+        <v>346</v>
+      </c>
+      <c r="B347" s="4"/>
+      <c r="C347" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D347" s="5">
+        <v>8</v>
+      </c>
+      <c r="E347" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F347" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A348" s="3">
+        <v>347</v>
+      </c>
+      <c r="B348" s="4"/>
+      <c r="C348" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D348" s="5">
+        <v>8</v>
+      </c>
+      <c r="E348" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F348" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A349" s="3">
+        <v>348</v>
+      </c>
+      <c r="B349" s="4"/>
+      <c r="C349" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D349" s="5">
+        <v>8</v>
+      </c>
+      <c r="E349" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F349" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A350" s="3">
+        <v>349</v>
+      </c>
+      <c r="B350" s="4"/>
+      <c r="C350" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D350" s="5">
+        <v>4.96</v>
+      </c>
+      <c r="E350" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F350" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A351" s="3">
+        <v>350</v>
+      </c>
+      <c r="B351" s="4"/>
+      <c r="C351" s="8" t="s">
         <v>85</v>
+      </c>
+      <c r="D351" s="5">
+        <v>96</v>
+      </c>
+      <c r="E351" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F351" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A352" s="3">
+        <v>351</v>
+      </c>
+      <c r="B352" s="4"/>
+      <c r="C352" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D352" s="5">
+        <v>360</v>
+      </c>
+      <c r="E352" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F352" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A353" s="3">
+        <v>352</v>
+      </c>
+      <c r="B353" s="4"/>
+      <c r="C353" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D353" s="5">
+        <v>384</v>
+      </c>
+      <c r="E353" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F353" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A354" s="3">
+        <v>353</v>
+      </c>
+      <c r="B354" s="4"/>
+      <c r="C354" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D354" s="5">
+        <v>12</v>
+      </c>
+      <c r="E354" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B355" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE25E10-E917-4B14-B12A-A163F3754BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36433B96-F7A6-44A2-B7A2-E99BF8B9CA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3570" yWindow="3180" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="394">
   <si>
     <t>№ п/п</t>
   </si>
@@ -69,985 +69,1144 @@
     <t>ЛГУП-6943</t>
   </si>
   <si>
-    <t>Ветошь</t>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 24</t>
   </si>
   <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>ЛГУП-7331</t>
-  </si>
-  <si>
-    <t>Перчатки с латесным покрытием</t>
+    <t>Ключ комбинированные омедненные 30</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 36</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 41</t>
+  </si>
+  <si>
+    <t>Гайковерт</t>
+  </si>
+  <si>
+    <t>Кувалда 1 кг.</t>
+  </si>
+  <si>
+    <t>Резак</t>
+  </si>
+  <si>
+    <t>Ножницы по металлу</t>
+  </si>
+  <si>
+    <t>Трещетка ключ 1/2</t>
+  </si>
+  <si>
+    <t>пог. м</t>
+  </si>
+  <si>
+    <t>ЛГУП-7653</t>
+  </si>
+  <si>
+    <t>ЛГУП-7654</t>
+  </si>
+  <si>
+    <t>Комплект кабельной проходки МКС</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>мм</t>
+  </si>
+  <si>
+    <t>г</t>
+  </si>
+  <si>
+    <t>Пломба 1-6х10-АД-1М ГОСТ 18677-73</t>
+  </si>
+  <si>
+    <t>Электроприв четвер.взры. ГЗ-ОФВ-300/28М 1х220 DN80PN63 L=452 УХЛ (исп. фл. J)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-20 У2 IP54 ЗЭТА</t>
+  </si>
+  <si>
+    <t>Лампа индикации ADDS D22 LED белая 220В AC/DC ЛK-22 IP55 25152DEK Dekraft</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
+  </si>
+  <si>
+    <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт.CM030508</t>
+  </si>
+  <si>
+    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
+  </si>
+  <si>
+    <t>ЛГУП-7657</t>
+  </si>
+  <si>
+    <t>ЛГУП-7661</t>
+  </si>
+  <si>
+    <t>кг</t>
+  </si>
+  <si>
+    <t>ЛГУП-7663</t>
+  </si>
+  <si>
+    <t>Труба D89х8 Ст. 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D720х12 09Г2С ГОСТ 10705-80</t>
+  </si>
+  <si>
+    <t>ЛГУП-7664</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.3сп ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>ЛГУП-7665</t>
+  </si>
+  <si>
+    <t>ЛГУП-7666</t>
+  </si>
+  <si>
+    <t>ЛГУП-7667</t>
+  </si>
+  <si>
+    <t>Палитра цветов</t>
+  </si>
+  <si>
+    <t>ЛГУП-7511</t>
+  </si>
+  <si>
+    <t>ЛГУП-7593</t>
+  </si>
+  <si>
+    <t>Набор ударных торцовых головок Makita Impact Black 1/2", 9 шт. (арт. E-16564)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7646</t>
+  </si>
+  <si>
+    <t>Борфреза твердосплавная F 1225/6</t>
+  </si>
+  <si>
+    <t>Борфреза твердосплавная сфероцилиндрическая C1225-M06</t>
+  </si>
+  <si>
+    <t>Удостоверение по электробезопасности</t>
+  </si>
+  <si>
+    <t>НТУП-018086</t>
+  </si>
+  <si>
+    <t>Угол 90° ⌀25 мм полипропилен</t>
+  </si>
+  <si>
+    <t>ЛГУП-7647</t>
+  </si>
+  <si>
+    <t>Труба ПП армированная стекловолокном, ф 32</t>
+  </si>
+  <si>
+    <t>Гайка для циркуляционного насоса 11/4", черная AV Engineering AVE183010 (код. 27874394 "ВИ")</t>
+  </si>
+  <si>
+    <t>Тройник ⌀32 x 25 x 32 мм полипропилен</t>
+  </si>
+  <si>
+    <t>Кран шаровой ГАЛЛОП 11/4'' ,внутр/наружн резьба, рукоятка 11б27п1 Стандарт 221 (Код 41070227 "ВИ")</t>
+  </si>
+  <si>
+    <t>Кран ПП 32</t>
+  </si>
+  <si>
+    <t>ЛГУП-7671</t>
+  </si>
+  <si>
+    <t>ЛГУП-7674</t>
+  </si>
+  <si>
+    <t>Шайба стопорная НТ.002.004.002 (плазма)</t>
+  </si>
+  <si>
+    <t>Сетка арматурная сварная легкая из арматурной проволки (класса Вр-1 тип 4)</t>
+  </si>
+  <si>
+    <t>т</t>
+  </si>
+  <si>
+    <t>ЛГУП-7677</t>
+  </si>
+  <si>
+    <t>ЛГУП-7679</t>
+  </si>
+  <si>
+    <t>Шкаф ПС и ОС АГЗУ 14-1500 АО Оренбургнефтегаз</t>
+  </si>
+  <si>
+    <t>Шкаф ПС и ОС АГЗУ 14-400 АО Оренбургнефтегаз</t>
+  </si>
+  <si>
+    <t>Саморез  кровельный 5,5х60 С пресс-шайбой со сверлом (мет/мет)</t>
+  </si>
+  <si>
+    <t>100 шт</t>
+  </si>
+  <si>
+    <t>НТУП-018112</t>
+  </si>
+  <si>
+    <t>Профлист С-8(Желтый) 1,2*6м</t>
+  </si>
+  <si>
+    <t>Вал ПСМНТ.001.015.000 св.загот (нормализация "стоя" при темп-ре 350-400 град 30 мин и отпуск в печи)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7680</t>
+  </si>
+  <si>
+    <t>Сегмент ПСМНТ.001.014.000</t>
+  </si>
+  <si>
+    <t>ЛГУП-7683</t>
+  </si>
+  <si>
+    <t>Сетка армированная С1 диам. 12 мм размер яч. 200х200 мм</t>
+  </si>
+  <si>
+    <t>ЛГУП-7685</t>
+  </si>
+  <si>
+    <t>ЛГ00-000043</t>
+  </si>
+  <si>
+    <t>ЛГУП-7686</t>
+  </si>
+  <si>
+    <t>Кран шаровой штуцерный 11лс01пп PN63 DN15 КОФ</t>
+  </si>
+  <si>
+    <t>ЛГУП-7687</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая фланцевая с руч. прив. 30лс76нж PN63 DN150 КОФ</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая фланцевая с ручным приводом 30лс76нж PN63 DN150 КОФ с контр.протечек</t>
+  </si>
+  <si>
+    <t>Кран шаровой фланцевый 11лс01 пф PN1,6 DN50 КОФ</t>
+  </si>
+  <si>
+    <t>Кран шаровой фланцевый 11лс01 пф PN63 DN50 КОФ</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-10 ГОСТ 19903-74/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>ЛГУП-7688</t>
+  </si>
+  <si>
+    <t>Круг 50-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Круг 38-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Круг 28-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-5,0 ГОСТ 19903-2015/ 09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Круг 22-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-6 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-4 ГОСТ 19903-74/09Г2С ГОСТ 5520-79</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-10 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Шестиграник 27-h12 ГОСТ 8560-78/(ст.13ХФА)</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-8 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>ЛГУП-7689</t>
+  </si>
+  <si>
+    <t>Гайка М36.7Н.09Г2С ОСТ 26-2041-96</t>
+  </si>
+  <si>
+    <t>ЛГУП-7691</t>
+  </si>
+  <si>
+    <t>Гайка М30.7H.09Г2С.05 ОСТ 26-2038-96</t>
+  </si>
+  <si>
+    <t>Шпильки 1-М30-8gx160.09Г2С.05 ОСТ 26-2038-96</t>
+  </si>
+  <si>
+    <t>Шпильки 1-М36-8gx190.09Г2С.05 ОСТ 26-2038-96</t>
+  </si>
+  <si>
+    <t>Болт М10-6gx40.56.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М14-6gx45.10Г2.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Заклепочник (2,4 - 4,8мм)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7699</t>
+  </si>
+  <si>
+    <t>Сверло по металлу   5,0мм</t>
+  </si>
+  <si>
+    <t>Шуроповерт Макита</t>
+  </si>
+  <si>
+    <t>Набор ключей ударных 17-55</t>
+  </si>
+  <si>
+    <t>Батарейка Camelion Plus Alkaline LR03-BP4, алкалиновая, LR03 AAA (4 шт.)</t>
+  </si>
+  <si>
+    <t>НТУП-018116</t>
+  </si>
+  <si>
+    <t>ЛГУП-7703</t>
+  </si>
+  <si>
+    <t>ЛГУП-7705</t>
+  </si>
+  <si>
+    <t>Гайка М16.7Н.09Г2С.019 ОСТ 26-2041-96</t>
+  </si>
+  <si>
+    <t>Гайка М12.7Н.09Г2С.019 ОСТ 26-2041-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М12-8gx60.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М12-8gx80.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М16-8gx80.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М30-8gx160.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М20-8gx130.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М16-8gx90.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М16-8g x100.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Крестики для кафеля 2мм</t>
+  </si>
+  <si>
+    <t>ЛГУП-7707</t>
+  </si>
+  <si>
+    <t>Шпатель зубчатый Интек 10108-350-010 350 мм, нержавеющая сталь, зуб 10x10 мм</t>
+  </si>
+  <si>
+    <t>Шпатель зубчатый Интек 10108-150-006 150 мм, нержавеющая сталь, зуб 6x6 мм</t>
+  </si>
+  <si>
+    <t>Перчатки  х/б двойной облив латексный зеленый 13кл</t>
   </si>
   <si>
     <t>пар</t>
   </si>
   <si>
-    <t>Маркер белый</t>
-  </si>
-  <si>
-    <t>Каска строительная белая</t>
-  </si>
-  <si>
-    <t>Огнетушитель ОП-8</t>
-  </si>
-  <si>
-    <t>Маркер  краска красный по металлу</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Перчатки х/б трикотажные 5 нитей 10 класс с ПВХ -Камаз 426</t>
-  </si>
-  <si>
-    <t>пара</t>
-  </si>
-  <si>
-    <t>Каска строительная оранжевая Исток</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Резак</t>
-  </si>
-  <si>
-    <t>ЛГУП-7332</t>
-  </si>
-  <si>
-    <t>Ножницы по металлу</t>
-  </si>
-  <si>
-    <t>Трещетка ключ 1/2</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 24</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 30</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 36</t>
-  </si>
-  <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 41</t>
-  </si>
-  <si>
-    <t>Кувалда 1 кг.</t>
-  </si>
-  <si>
-    <t>Гайковерт</t>
-  </si>
-  <si>
-    <t>Палитра цветов</t>
-  </si>
-  <si>
-    <t>ЛГУП-7511</t>
-  </si>
-  <si>
-    <t>Бита для кровельных саморезов10мм</t>
-  </si>
-  <si>
-    <t>ЛГУП-7534</t>
-  </si>
-  <si>
-    <t>Шуроповерт Макита</t>
-  </si>
-  <si>
-    <t>Бита для кровельных саморезов 8мм</t>
-  </si>
-  <si>
-    <t>Биты крестовая РН-2</t>
-  </si>
-  <si>
-    <t>Угловая шлифмашина Makita GA5030R, ф125мм, 720Вт, 11000об\м</t>
-  </si>
-  <si>
-    <t>ЛГУП-7645</t>
-  </si>
-  <si>
-    <t>Аккумуляторный ударный гайковерт Makita DTW190RME (LXT)</t>
-  </si>
-  <si>
-    <t>Набор ударных торцовых головок Makita Impact Black 1/2", 9 шт. (арт. E-16564)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7646</t>
-  </si>
-  <si>
-    <t>Борфреза твердосплавная F 1225/6</t>
-  </si>
-  <si>
-    <t>Борфреза твердосплавная сфероцилиндрическая C1225-M06</t>
-  </si>
-  <si>
-    <t>Удостоверение по электробезопасности</t>
-  </si>
-  <si>
-    <t>НТУП-018086</t>
-  </si>
-  <si>
-    <t>Кран ПП 32</t>
-  </si>
-  <si>
-    <t>ЛГУП-7647</t>
-  </si>
-  <si>
-    <t>Кран шаровой ГАЛЛОП 11/4'' ,внутр/наружн резьба, рукоятка 11б27п1 Стандарт 221 (Код 41070227 "ВИ")</t>
-  </si>
-  <si>
-    <t>Труба ПП армированная стекловолокном, ф 32</t>
-  </si>
-  <si>
-    <t>мм</t>
-  </si>
-  <si>
-    <t>Угол 90° ⌀25 мм полипропилен</t>
-  </si>
-  <si>
-    <t>Гайка для циркуляционного насоса 11/4", черная AV Engineering AVE183010 (код. 27874394 "ВИ")</t>
-  </si>
-  <si>
-    <t>компл</t>
-  </si>
-  <si>
-    <t>Тройник ⌀32 x 25 x 32 мм полипропилен</t>
-  </si>
-  <si>
-    <t>ЛГУП-7650</t>
-  </si>
-  <si>
-    <t>ЛГУП-7652</t>
-  </si>
-  <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>ЛГУП-7653</t>
-  </si>
-  <si>
-    <t>пог. м</t>
-  </si>
-  <si>
-    <t>ЛГУП-7654</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-20 У2 IP54 ЗЭТА</t>
-  </si>
-  <si>
-    <t>Лампа индикации ADDS D22 LED белая 220В AC/DC ЛK-22 IP55 25152DEK Dekraft</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
-  </si>
-  <si>
-    <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт.CM030508</t>
-  </si>
-  <si>
-    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
-  </si>
-  <si>
-    <t>Электроприв четвер.взры. ГЗ-ОФВ-300/28М 1х220 DN80PN63 L=452 УХЛ (исп. фл. J)</t>
-  </si>
-  <si>
-    <t>Комплект кабельной проходки МКС</t>
-  </si>
-  <si>
-    <t>г</t>
-  </si>
-  <si>
-    <t>Пломба 1-6х10-АД-1М ГОСТ 18677-73</t>
-  </si>
-  <si>
-    <t>ЛГУП-7657</t>
-  </si>
-  <si>
-    <t>ЛГУП-7658</t>
-  </si>
-  <si>
-    <t>ЛГУП-7661</t>
-  </si>
-  <si>
-    <t>кг</t>
-  </si>
-  <si>
-    <t>ЛГУП-7663</t>
-  </si>
-  <si>
-    <t>Труба D89х8 Ст. 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D720х12 09Г2С ГОСТ 10705-80</t>
-  </si>
-  <si>
-    <t>ЛГУП-7664</t>
-  </si>
-  <si>
-    <t>ЛГУП-7665</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.3сп ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>ЛГУП-7666</t>
-  </si>
-  <si>
-    <t>ЛГУП-7667</t>
-  </si>
-  <si>
-    <t>Жалюзи "День-Ночь" 1500х700</t>
-  </si>
-  <si>
-    <t>ЛГУП-7670</t>
-  </si>
-  <si>
-    <t>ЛГУП-7671</t>
-  </si>
-  <si>
-    <t>ЛГУП-7674</t>
-  </si>
-  <si>
-    <t>Шайба стопорная НТ.002.004.002 (плазма)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7676</t>
-  </si>
-  <si>
-    <t>КИ00-000003</t>
-  </si>
-  <si>
-    <t>Сетка арматурная сварная легкая из арматурной проволки (класса Вр-1 тип 4)</t>
-  </si>
-  <si>
-    <t>т</t>
-  </si>
-  <si>
-    <t>ЛГУП-7677</t>
-  </si>
-  <si>
-    <t>Краска-спрей (эмаль) универсальная RAL 1021 Рапсово-желтая 520мл аэрозоль</t>
-  </si>
-  <si>
-    <t>ЛГУП-7678</t>
-  </si>
-  <si>
-    <t>Шкаф ПС и ОС АГЗУ 14-400 АО Оренбургнефтегаз</t>
-  </si>
-  <si>
-    <t>ЛГУП-7679</t>
-  </si>
-  <si>
-    <t>Шкаф ПС и ОС АГЗУ 14-1500 АО Оренбургнефтегаз</t>
-  </si>
-  <si>
-    <t>Саморез  кровельный 5,5х60 С пресс-шайбой со сверлом (мет/мет)</t>
-  </si>
-  <si>
-    <t>100 шт</t>
-  </si>
-  <si>
-    <t>НТУП-018112</t>
-  </si>
-  <si>
-    <t>Профлист С-8(Желтый) 1,2*6м</t>
-  </si>
-  <si>
-    <t>Вал ПСМНТ.001.015.000 св.загот (нормализация "стоя" при темп-ре 350-400 град 30 мин и отпуск в печи)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7680</t>
-  </si>
-  <si>
-    <t>Сегмент ПСМНТ.001.014.000</t>
-  </si>
-  <si>
-    <t>ЛГУП-7683</t>
-  </si>
-  <si>
-    <t>Бетон В-25 М350</t>
-  </si>
-  <si>
-    <t>м3</t>
-  </si>
-  <si>
-    <t>ЛГУП-7684</t>
-  </si>
-  <si>
-    <t>Бетон В 7.5</t>
-  </si>
-  <si>
-    <t>Сетка армированная С1 диам. 12 мм размер яч. 200х200 мм</t>
-  </si>
-  <si>
-    <t>ЛГУП-7685</t>
-  </si>
-  <si>
-    <t>ЛГ00-000043</t>
-  </si>
-  <si>
-    <t>Фумлента</t>
-  </si>
-  <si>
-    <t>Маркер черный</t>
+    <t>Лист шлифовальный на бумажной основе DILWIS P40 230x280 мм</t>
+  </si>
+  <si>
+    <t>Лист шлифовальный на бумажной основе DILWIS P120 230x280 мм</t>
+  </si>
+  <si>
+    <t>Лист шлифовальный на бумажной основе DILWIS P180 93x230 мм, 5 шт.</t>
+  </si>
+  <si>
+    <t>Грунтовка глубокого проникновения Церезит CT17 10 л</t>
+  </si>
+  <si>
+    <t>Набор малярный Dexter валик 100 мм и кисть 40 мм, ручка, кювета, скотч</t>
+  </si>
+  <si>
+    <t>Набор малярный  для фасадных работ</t>
+  </si>
+  <si>
+    <t>Серпянка</t>
+  </si>
+  <si>
+    <t>Набор малярный валик и кювета</t>
+  </si>
+  <si>
+    <t>Дюбель+шуруп 6*40</t>
+  </si>
+  <si>
+    <t>Пленка BEGINIA 100 мкм 3x10 м прозрачный полиэтилен</t>
+  </si>
+  <si>
+    <t>Крестики для кафеля 1,5 мм</t>
+  </si>
+  <si>
+    <t>Пескобетон М-300 (25 кг)</t>
+  </si>
+  <si>
+    <t>Перчатки</t>
+  </si>
+  <si>
+    <t>Саморез полусфера-прессшайба со сверлом 4,2*19мм оцинк.</t>
+  </si>
+  <si>
+    <t>Саморез по дереву 3,5*3,8х35 мм черный</t>
+  </si>
+  <si>
+    <t>Профиль потолочный 60х2 7мм 3м 0,6мм КНАУФ</t>
+  </si>
+  <si>
+    <t>Профиль потолочный П28х27-3000 (3м) КНАУФ</t>
+  </si>
+  <si>
+    <t>Гипсокартон</t>
+  </si>
+  <si>
+    <t>Ведро 12л пластиковое</t>
+  </si>
+  <si>
+    <t>Ведро 20л пластик.</t>
+  </si>
+  <si>
+    <t>Шпатель 350мм, н/ж ст., пласт.ручка</t>
+  </si>
+  <si>
+    <t>Шпатель 100мм</t>
+  </si>
+  <si>
+    <t>Шпаклевка полимер. финишная VETONIT KR 20 кг</t>
+  </si>
+  <si>
+    <t>Клей монтажный</t>
+  </si>
+  <si>
+    <t>Затирка</t>
+  </si>
+  <si>
+    <t>Клей для плитки 25 кг</t>
+  </si>
+  <si>
+    <t>Подвес прямой Knauf Шт</t>
+  </si>
+  <si>
+    <t>Мешки п/п 50 кг 55*95</t>
+  </si>
+  <si>
+    <t>Отлив нижний Лист Б-ПН-0-0,55 ГОСТ 19904-90 ОН-КР-1 ГОСТ 14918-80 RAL 7036 (платиново-серый)</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2500х1000х80 RAL 1021 (желт) снаружи/ RAL 9003 (белый) внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2300х1000х80,  снаружи RAL 1021 / внутри RAL 9003</t>
+  </si>
+  <si>
+    <t>Лист профилированный С21-1000-0,7 L=1600мм RAL 1021 (желтый)</t>
+  </si>
+  <si>
+    <t>Лист профилированный С21-1000-0,7 L=1350мм RAL 1021 (желтый)</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2600х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 3100х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2800х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2900х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2900х1000х150 мм RAL 9003 (белый)</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 3100х1000х100 9003/9003</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка (50х15х3000)</t>
+  </si>
+  <si>
+    <t>Крышка (100х15х3000)</t>
+  </si>
+  <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Коробка распаячная КМ41242 IP55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
+  </si>
+  <si>
+    <t>Провод НВМ 0,35 IV 500 ГОСТ 17515-72</t>
+  </si>
+  <si>
+    <t>Трубка 3.31 ТВ-40 ГОСТ 19034-82</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(А)-FRLS 2*2*0,75</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 100х60</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 40х40 мм</t>
+  </si>
+  <si>
+    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
+  </si>
+  <si>
+    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
+  </si>
+  <si>
+    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS- 3х2,50</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
+  </si>
+  <si>
+    <t>Трубка для фильтра 1/4" Гейзер</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
+  </si>
+  <si>
+    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
+  </si>
+  <si>
+    <t>Консоль с опорой ML 300мм (шт)</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
+  </si>
+  <si>
+    <t>Заглушка 10707 Legrand DPL 65х195</t>
+  </si>
+  <si>
+    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
+  </si>
+  <si>
+    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
+  </si>
+  <si>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
+  </si>
+  <si>
+    <t>Геркон КЭМ-2</t>
+  </si>
+  <si>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>Аварийное освещение Вега 60 2Ex Тех  IP65</t>
+  </si>
+  <si>
+    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Профиль PSM (3000) арт. 34181</t>
+  </si>
+  <si>
+    <t>Плата питания ПСМ.11.00.00.01-02</t>
+  </si>
+  <si>
+    <t>Плата печатная ПСМ.11.00.01.01-02</t>
+  </si>
+  <si>
+    <t>Пластина для заземления PTCE арт. 37501</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 120</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 4.1.1</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 2.1.1</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 4.1.1</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 2.1.1</t>
+  </si>
+  <si>
+    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
+  </si>
+  <si>
+    <t>Металлический лоток, неперфорированный (100х50х3000)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Автолак акриловый бесцветный Auton спрей 520мл</t>
+  </si>
+  <si>
+    <t>Фланец 150-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Труба D1020х26 ст.09Г2С-К52 ГОСТ 20295-85</t>
+  </si>
+  <si>
+    <t>Труба D110х16 ГОСТ 8734-75/ Ст.20 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D34х4 Ст.09Г2С ГОСТ8733-75</t>
+  </si>
+  <si>
+    <t>Труба D34х3,5 Ст.09Г2С ГОСТ10705-80</t>
+  </si>
+  <si>
+    <t>Труба D32х4 Ст.09Г2С ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D32х3 Ст.09Г2С ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D273х16 Ст.09Г2С-3 ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D57х4 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
+  </si>
+  <si>
+    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D720х20 Ст.09Г2С-К50 ГОСТ 20295-85</t>
+  </si>
+  <si>
+    <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D83х12 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D93х4-В-20 ГОСТ32528</t>
+  </si>
+  <si>
+    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D14х2 09Г2С ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D152х5 09Г2С ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D159х14 ГОСТ 8732-78/ Ст.09Г2С-3 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D219х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
+  </si>
+  <si>
+    <t>Труба D219х12 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
+  </si>
+  <si>
+    <t>Днище 1020х26 09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 219х4-25 16ГС-3 ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 720х20-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Профиль 50х25х5 Ст3сп-ГОСТ 30245-2012 L=125мм</t>
+  </si>
+  <si>
+    <t>Труба профильная 25х25х1,5 ГОСТ 8639-82/ В 20 ГОСТ 13663-86</t>
+  </si>
+  <si>
+    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
+  </si>
+  <si>
+    <t>Уголок 30х30х3-В ГОСТ 8509-93/ Ст.3сп3-1 ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Уголок 40х40х3 ГОСТ 8509-93/ Ст3пс ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.3пс5-св ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Уголок 63х63х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Уголок 75х75х5 ГОСТ 8509-93/ 09Г2С 535-88</t>
+  </si>
+  <si>
+    <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
+  </si>
+  <si>
+    <t>Швеллер 16У ГОСТ 8240-97 / 09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Швеллер 20У ГОСТ 8240-97 / Ст3сп ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Швеллер 8П ГОСТ 8240-97/Ст3сп ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Швеллер №20У ГОСТ 8240-97/ 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Швеллер №5П ГОСТ 8240-97/ Ст.09Г2С ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Труба ДКРПТ 8х1 М2 ГОСТ 617-90 (отгружать L кратно 2,5м, либо бухтами)</t>
+  </si>
+  <si>
+    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
+  </si>
+  <si>
+    <t>Труба D20х5 БрКМц 3-1 ГОСТ 1208-2014</t>
+  </si>
+  <si>
+    <t>Фланец 150-63-11-1-J-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 150-40-11-1-Е-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 200-63-11-1-J 09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 3-250-63 Ст.09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Фланец 3-500-63 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 50-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 50-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 50-63-11-1-J 09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-63-11-1-J-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец ANSI CL300-3'' Ду80 - заготовка поковка ст.09Г2С</t>
+  </si>
+  <si>
+    <t>Фланец х-50-63 ГОСТ 12821 (заготовка-поковка Ст.13ХФА гр.IV КП195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Узел барабана DК-1150 (c двухслойным ракелем) для Kyocera</t>
+  </si>
+  <si>
+    <t>Печка FK-1150</t>
+  </si>
+  <si>
+    <t>Кассета подачи бумаги в сборе CT-1150 для Kyocera</t>
+  </si>
+  <si>
+    <t>Картридж Standart TK-1170 7,2k 750</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+  </si>
+  <si>
+    <t>Шайба 12 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба 30.4.019 ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>Шайба 36 ГОСТ 9065-75 (шт.)</t>
+  </si>
+  <si>
+    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба А 16.37 ГОСТ 6958-78</t>
+  </si>
+  <si>
+    <t>Шайба А.12.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шайба С.16.05.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шпилька А1М20-6gх120.48.40Х.IV.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шайба 12 65Г 06 ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>Шайба 10.02.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Шпилька А1М30-6gx180.09Г2С (оцинк.) ГОСТ 9066-75</t>
   </si>
   <si>
     <t>Шпилька АМ20-6gx120.40. 20 IV.2. ГОСТ 9066-75</t>
   </si>
   <si>
-    <t>Шпилька АМ16х1,5-6gx90.32.1 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Муфта вводная для труб гофрированных D=16 мм ТУ 2248-007-57453845-2009</t>
-  </si>
-  <si>
-    <t>Провод ПУВ 1х0,75 ТУ16-705.501-2010</t>
-  </si>
-  <si>
-    <t>Дисплей МТ-6464В-2FLB-3V3 (МЭЛТ)</t>
-  </si>
-  <si>
-    <t>Геркон КЭМ-2а</t>
-  </si>
-  <si>
-    <t>Разъем: вилка на панель, крепление гайкой Weipu SF1012/P2 и розетка кабельная Weipu SF1010/S2I</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 3100х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 3100х1000х100 9003/9003</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2900х1000х150 мм RAL 9003 (белый)</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2900х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2800х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2600х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2500х1000х80 RAL 1021 (желт) снаружи/ RAL 9003 (белый) внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2300х1000х80,  снаружи RAL 1021 / внутри RAL 9003</t>
-  </si>
-  <si>
-    <t>Лист профилированный С21-1000-0,7 L=1600мм RAL 1021 (желтый)</t>
-  </si>
-  <si>
-    <t>Лист профилированный С21-1000-0,7 L=1350мм RAL 1021 (желтый)</t>
-  </si>
-  <si>
-    <t>Отлив нижний Лист Б-ПН-0-0,55 ГОСТ 19904-90 ОН-КР-1 ГОСТ 14918-80 RAL 7036 (платиново-серый)</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 2.1.1</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 4.1.1</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 2.1.1</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 4.1.1</t>
-  </si>
-  <si>
-    <t>Крышка (100х15х3000)</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
-    <t>Коробка распаячная КМ41242 IP55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
-  </si>
-  <si>
-    <t>Консоль с опорой ML 300мм (шт)</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
-  </si>
-  <si>
-    <t>Заглушка 10707 Legrand DPL 65х195</t>
-  </si>
-  <si>
-    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
-  </si>
-  <si>
-    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
-  </si>
-  <si>
-    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
-  </si>
-  <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>Пластина анкерная 120</t>
-  </si>
-  <si>
-    <t>Пластина для заземления PTCE арт. 37501</t>
-  </si>
-  <si>
-    <t>Геркон КЭМ-2</t>
-  </si>
-  <si>
-    <t>Выключатель двухклавишный IP55</t>
-  </si>
-  <si>
-    <t>Аварийное освещение Вега 60 2Ex Тех  IP65</t>
-  </si>
-  <si>
-    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Плата печатная ПСМ.11.00.01.01-02</t>
-  </si>
-  <si>
-    <t>Плата питания ПСМ.11.00.00.01-02</t>
-  </si>
-  <si>
-    <t>Профиль PSM (3000) арт. 34181</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Крышка (50х15х3000)</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Трубка для фильтра 1/4" Гейзер</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
-  </si>
-  <si>
-    <t>Провод НВМ 0,35 IV 500 ГОСТ 17515-72</t>
-  </si>
-  <si>
-    <t>Трубка 3.31 ТВ-40 ГОСТ 19034-82</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(А)-FRLS 2*2*0,75</t>
-  </si>
-  <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 100х60</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 40х40 мм</t>
-  </si>
-  <si>
-    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
-  </si>
-  <si>
-    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
-  </si>
-  <si>
-    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
-  </si>
-  <si>
-    <t>Провод Rd8</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS- 3х2,50</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
-  </si>
-  <si>
-    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (100х50х3000)</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
-  </si>
-  <si>
-    <t>Автолак акриловый бесцветный Auton спрей 520мл</t>
-  </si>
-  <si>
-    <t>Обогреватель взрывозащищенный ОВЭ-4-УХЛ3 1,8 кВт, 380В IExdIIАТ3, IP54</t>
-  </si>
-  <si>
-    <t>Двигатель АИМЛ 63 В4IM3081</t>
-  </si>
-  <si>
-    <t>Фланец 150-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Труба D110х16 ГОСТ 8734-75/ Ст.20 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
-  </si>
-  <si>
-    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D219х12 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D219х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
-  </si>
-  <si>
-    <t>Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D159х14 ГОСТ 8732-78/ Ст.09Г2С-3 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D152х5 09Г2С ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D14х2 09Г2С ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D93х4-В-20 ГОСТ32528</t>
-  </si>
-  <si>
-    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Труба D83х12 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D720х20 Ст.09Г2С-К50 ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
-  </si>
-  <si>
-    <t>Труба D57х4 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D34х4 Ст.09Г2С ГОСТ8733-75</t>
-  </si>
-  <si>
-    <t>Труба D34х3,5 Ст.09Г2С ГОСТ10705-80</t>
-  </si>
-  <si>
-    <t>Труба D32х4 Ст.09Г2С ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D32х3 Ст.09Г2С ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D273х16 Ст.09Г2С-3 ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Труба D1020х26 ст.09Г2С-К52 ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>Днище 1020х26 09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 219х4-25 16ГС-3 ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 720х20-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Уголок 30х30х3-В ГОСТ 8509-93/ Ст.3сп3-1 ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Уголок 40х40х3 ГОСТ 8509-93/ Ст3пс ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.3пс5-св ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Уголок 63х63х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Уголок 75х75х5 ГОСТ 8509-93/ 09Г2С 535-88</t>
-  </si>
-  <si>
-    <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
-  </si>
-  <si>
-    <t>Швеллер 16У ГОСТ 8240-97 / 09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Швеллер 20У ГОСТ 8240-97 / Ст3сп ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Швеллер 8П ГОСТ 8240-97/Ст3сп ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Швеллер №20У ГОСТ 8240-97/ 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Швеллер №5П ГОСТ 8240-97/ Ст.09Г2С ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Профиль 50х25х5 Ст3сп-ГОСТ 30245-2012 L=125мм</t>
-  </si>
-  <si>
-    <t>Труба профильная 25х25х1,5 ГОСТ 8639-82/ В 20 ГОСТ 13663-86</t>
-  </si>
-  <si>
-    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
-  </si>
-  <si>
-    <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Труба D20х5 БрКМц 3-1 ГОСТ 1208-2014</t>
-  </si>
-  <si>
-    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
-  </si>
-  <si>
-    <t>Труба ДКРПТ 8х1 М2 ГОСТ 617-90 (отгружать L кратно 2,5м, либо бухтами)</t>
-  </si>
-  <si>
-    <t>Фланец х-50-63 ГОСТ 12821 (заготовка-поковка Ст.13ХФА гр.IV КП195 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Фланец ANSI CL300-3'' Ду80 - заготовка поковка ст.09Г2С</t>
-  </si>
-  <si>
-    <t>Фланец 80-63-11-1-J-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 80-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 80-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 50-63-11-1-J 09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 50-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 50-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 3-500-63 09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
-    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Фланец 3-250-63 Ст.09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
-    <t>Фланец 200-63-11-1-J 09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
-    <t>Фланец 150-63-11-1-J-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 150-40-11-1-Е-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+    <t>Шпилька АМ36-6gх190.48.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Заклепка вытяжная Al 4,0х8 din 7337</t>
+  </si>
+  <si>
+    <t>Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
+  </si>
+  <si>
+    <t>Заклепка вытяжная 3,2х8-NiCu/SSt ISO 16584</t>
+  </si>
+  <si>
+    <t>Шпилька М20х110 ГОСТ 9066-75 ст 40Х</t>
+  </si>
+  <si>
+    <t>Шпилька М20х130 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х8 оцинкованная</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х10</t>
+  </si>
+  <si>
+    <t>Гвозди П1,6х25 ГОСТ 4028-63</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Гайка М30 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка М24 оцинк. ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка М20 ГОСТ 9064 -75</t>
+  </si>
+  <si>
+    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>Шпилька М24х130 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька М30-6gх160.30.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх160.60.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Гайка АМ30-6Н.20.III.4.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка М48 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Шайба 48.1 ГОСТ 9065-75</t>
+  </si>
+  <si>
+    <t>Шпилька М48х260 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Винт М6-6gх16.58.019 ГОСТ 17475-80</t>
+  </si>
+  <si>
+    <t>Винт М4-6gх16.58.019 ГОСТ 17473-80</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх40.58 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх16 56.35.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М16-6gх110.58 ГОСТ 7805-70</t>
+  </si>
+  <si>
+    <t>Саморез 4,2х19 оцинк. со сверлом</t>
   </si>
   <si>
     <t>Гайка М16.5.019 ГОСТ 5915-70</t>
   </si>
   <si>
-    <t>Шпилька АМ30-6gх160.60.1 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька М30-6gх160.30.35.III.4.019 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька М24х130 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька М20х130 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька М20х110 ГОСТ 9066-75 ст 40Х</t>
-  </si>
-  <si>
-    <t>Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
-  </si>
-  <si>
-    <t>Шпилька АМ36-6gх190.48.35.III.4.019 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька А1М30-6gx180.09Г2С (оцинк.) ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька А1М20-6gх120.48.40Х.IV.1 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шайба С.16.05.019 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Шайба А.12.019 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Шайба А 16.37 ГОСТ 6958-78</t>
-  </si>
-  <si>
-    <t>Гайка М48 ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Шпилька М48х260 ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Шайба 48.1 ГОСТ 9065-75</t>
-  </si>
-  <si>
-    <t>Шайба 8.01.019 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Шайба 8 65Г 019 ГОСТ 6402-70</t>
-  </si>
-  <si>
-    <t>Шайба 36 ГОСТ 9065-75 (шт.)</t>
-  </si>
-  <si>
-    <t>Шайба 30.4.019 ГОСТ 9065-75</t>
-  </si>
-  <si>
-    <t>Шайба 12 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Шайба 12 65Г 06 ГОСТ 6402-70</t>
-  </si>
-  <si>
-    <t>Шайба 10.02.019 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Заклепка вытяжная Al 4,0х8 din 7337</t>
-  </si>
-  <si>
-    <t>Заклепка вытяжная 3,2х8-NiCu/SSt ISO 16584</t>
-  </si>
-  <si>
-    <t>Гайка АМ30-6Н.20.III.4.019 ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Заклепка 4,8х8 оцинкованная</t>
-  </si>
-  <si>
-    <t>Заклепка 4,8х10</t>
-  </si>
-  <si>
-    <t>Гвозди П1,6х25 ГОСТ 4028-63</t>
-  </si>
-  <si>
-    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Гайка М30 ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Гайка М24 оцинк. ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Гайка М20 ГОСТ 9064 -75</t>
-  </si>
-  <si>
-    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
-  </si>
-  <si>
     <t>Гайка АМ36-6Н.20lll.019 ГОСТ 9064-75</t>
   </si>
   <si>
-    <t>Винт М6-6gх16.58.019 ГОСТ 17475-80</t>
-  </si>
-  <si>
-    <t>Винт М4-6gх16.58.019 ГОСТ 17473-80</t>
-  </si>
-  <si>
-    <t>Саморез 4,2х19 оцинк. со сверлом</t>
-  </si>
-  <si>
-    <t>Болт М16-6gх110.58 ГОСТ 7805-70</t>
-  </si>
-  <si>
-    <t>Болт М8-6gх40.58 ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Болт М8-6gх16 56.35.019 ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Насос НШ 4-ГЗ</t>
-  </si>
-  <si>
-    <t>Лист алюм. анод. сатин (черн/бел) 1,0</t>
-  </si>
-  <si>
-    <t>Лист А0.М1(анод) 0,5 ГОСТ 21631-76 (черный)</t>
+    <t>Шкаф управления</t>
   </si>
   <si>
     <t>Шкаф силовой</t>
   </si>
   <si>
-    <t>Шкаф управления</t>
+    <t>Гайка АМ24-6Н.09Г2С (оцинк.) ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка АМ20х1,5-6Н.1 ГОСТ 9064-75</t>
   </si>
   <si>
     <t>Гайка АМ16-6Н.20.III.4 ГОСТ 9064-75</t>
   </si>
   <si>
-    <t>Гайка АМ20х1,5-6Н.1 ГОСТ 9064-75</t>
-  </si>
-  <si>
     <t>Болт М24x2-6gx55 ГОСТ 7798-70</t>
   </si>
   <si>
-    <t>Гайка АМ24-6Н.09Г2С (оцинк.) ГОСТ 9064-75</t>
+    <t>Герметик силиконовый универс. белый 310мл</t>
   </si>
   <si>
     <t>Герметик "Макрофлекс"  силик. универс. белый 290мл</t>
   </si>
   <si>
-    <t>Герметик силиконовый универс. белый 310мл</t>
+    <t>Лист S=6 ГОСТ19903-74/20Х13 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист ПВЛ 506 09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
+  </si>
+  <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-15 IP65 2ExеdIIСТ6</t>
+  </si>
+  <si>
+    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
+  </si>
+  <si>
+    <t>Прокладка 1-1-150-63-08кп ГОСТ Р 53561-2009</t>
+  </si>
+  <si>
+    <t>Прокладка 1-1-80-63-08кп ГОСТ Р 53561-2009</t>
+  </si>
+  <si>
+    <t>Прокладка 1-1-50-63-08кп ГОСТ Р 53561-2009</t>
+  </si>
+  <si>
+    <t>Прокладка Б-150-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-16-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-25-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-80-16-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-80-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Гайка М20.7H.09Г2С.019 ОСТ 26-2041-96</t>
+  </si>
+  <si>
+    <t>Гайка М30.7Н.09Г2С ОСТ 26-2041-96</t>
   </si>
 </sst>
 </file>
@@ -1484,13 +1643,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F289"/>
+  <dimension ref="A1:F344"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
@@ -1632,7 +1791,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="5">
-        <v>800</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>18</v>
@@ -1650,10 +1809,10 @@
         <v>19</v>
       </c>
       <c r="D9" s="5">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>16</v>
@@ -1665,13 +1824,13 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="D10" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>16</v>
@@ -1683,13 +1842,13 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>16</v>
@@ -1701,13 +1860,13 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="D12" s="5">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>16</v>
@@ -1719,13 +1878,13 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D13" s="5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>16</v>
@@ -1737,13 +1896,13 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D14" s="5">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>16</v>
@@ -1755,13 +1914,13 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>16</v>
@@ -1773,214 +1932,214 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D16" s="5">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="D17" s="5">
-        <v>10</v>
+        <v>342</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>27</v>
+        <v>170</v>
       </c>
       <c r="D18" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" s="5">
+        <v>56</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="5">
-        <v>4</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>30</v>
+        <v>172</v>
       </c>
       <c r="D20" s="5">
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>31</v>
+        <v>173</v>
       </c>
       <c r="D21" s="5">
-        <v>10</v>
+        <v>28.5</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="D22" s="5">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="D23" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="D24" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="D25" s="5">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
       <c r="D26" s="5">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="D27" s="5">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1989,13 +2148,13 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="D28" s="5">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>29</v>
@@ -2007,16 +2166,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="D29" s="5">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2025,16 +2184,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="D30" s="5">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2043,16 +2202,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>44</v>
+        <v>183</v>
       </c>
       <c r="D31" s="5">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2061,52 +2220,52 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="D32" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>46</v>
+        <v>185</v>
       </c>
       <c r="D33" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>47</v>
+        <v>186</v>
       </c>
       <c r="D34" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2115,16 +2274,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D35" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2133,16 +2292,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="D36" s="5">
-        <v>2</v>
+        <v>396.5</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2151,16 +2310,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>52</v>
+        <v>188</v>
       </c>
       <c r="D37" s="5">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2169,16 +2328,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="D38" s="5">
-        <v>5</v>
+        <v>320</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2187,16 +2346,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="D39" s="5">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2205,34 +2364,34 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="D40" s="5">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>58</v>
+        <v>192</v>
       </c>
       <c r="D41" s="5">
-        <v>6</v>
+        <v>989</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2241,16 +2400,16 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" s="7">
-        <v>30000</v>
+        <v>193</v>
+      </c>
+      <c r="D42" s="5">
+        <v>288</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2259,34 +2418,34 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="D43" s="5">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="D44" s="5">
-        <v>3</v>
+        <v>861.2</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2295,16 +2454,16 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>64</v>
+        <v>196</v>
       </c>
       <c r="D45" s="5">
         <v>30</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2313,16 +2472,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="D46" s="5">
-        <v>224</v>
+        <v>10</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2331,16 +2490,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" s="7">
-        <v>1456</v>
+        <v>198</v>
+      </c>
+      <c r="D47" s="5">
+        <v>40</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2349,16 +2508,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="D48" s="5">
-        <v>24</v>
+        <v>16.8</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2367,16 +2526,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="D49" s="5">
-        <v>0.24</v>
+        <v>602.20000000000005</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2385,16 +2544,16 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D50" s="5">
-        <v>6</v>
+        <v>201</v>
+      </c>
+      <c r="D50" s="7">
+        <v>1040</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2403,142 +2562,142 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="D51" s="5">
-        <v>12</v>
+        <v>259</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="D52" s="5">
-        <v>12</v>
+        <v>274.8</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>52</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="D53" s="5">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D54" s="5">
-        <v>24</v>
+        <v>205</v>
+      </c>
+      <c r="D54" s="7">
+        <v>1199</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>54</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="D55" s="5">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="D56" s="5">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>56</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="D57" s="5">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>57</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="D58" s="5">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2547,88 +2706,88 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="D59" s="5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>59</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="D60" s="5">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>60</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="D61" s="5">
-        <v>193</v>
+        <v>100.8</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>61</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="D62" s="5">
-        <v>28.5</v>
+        <v>88</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="D63" s="5">
-        <v>342</v>
+        <v>16</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2637,16 +2796,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="D64" s="5">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2655,70 +2814,70 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="D65" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="D66" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>66</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>146</v>
+        <v>216</v>
       </c>
       <c r="D67" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="D68" s="5">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2727,16 +2886,16 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="D69" s="5">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2745,43 +2904,43 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="D70" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>70</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D71" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>71</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="D72" s="5">
         <v>10</v>
@@ -2790,61 +2949,61 @@
         <v>7</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>152</v>
+        <v>222</v>
       </c>
       <c r="D73" s="5">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="D74" s="5">
-        <v>5</v>
+        <v>192</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>74</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>154</v>
+        <v>224</v>
       </c>
       <c r="D75" s="5">
-        <v>18</v>
+        <v>560</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2853,16 +3012,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="D76" s="5">
-        <v>112</v>
+        <v>400</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2871,16 +3030,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="D77" s="5">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2889,16 +3048,16 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="D78" s="5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2907,16 +3066,16 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="D79" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2925,16 +3084,16 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>159</v>
+        <v>229</v>
       </c>
       <c r="D80" s="5">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2943,16 +3102,16 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="D81" s="5">
-        <v>192</v>
+        <v>32</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2961,16 +3120,16 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="D82" s="5">
-        <v>560</v>
+        <v>42</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2979,34 +3138,34 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>162</v>
+        <v>38</v>
       </c>
       <c r="D83" s="5">
-        <v>400</v>
+        <v>153</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>163</v>
+        <v>39</v>
       </c>
       <c r="D84" s="5">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3015,16 +3174,16 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="D85" s="5">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3033,16 +3192,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>165</v>
+        <v>41</v>
       </c>
       <c r="D86" s="5">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3051,7 +3210,7 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="D87" s="5">
         <v>8</v>
@@ -3060,7 +3219,7 @@
         <v>7</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3069,16 +3228,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="D88" s="5">
-        <v>5</v>
+        <v>900</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3087,16 +3246,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="D89" s="5">
-        <v>8</v>
+        <v>422</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3105,16 +3264,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="D90" s="5">
-        <v>32</v>
+        <v>298</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3123,16 +3282,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>71</v>
+        <v>235</v>
       </c>
       <c r="D91" s="5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3141,7 +3300,7 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>170</v>
+        <v>236</v>
       </c>
       <c r="D92" s="5">
         <v>8</v>
@@ -3150,7 +3309,7 @@
         <v>7</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3159,7 +3318,7 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="D93" s="5">
         <v>8</v>
@@ -3168,7 +3327,7 @@
         <v>7</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3177,16 +3336,16 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="D94" s="5">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3195,16 +3354,16 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="D95" s="5">
-        <v>298</v>
+        <v>56</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3213,16 +3372,16 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="D96" s="5">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3231,16 +3390,16 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D97" s="5">
-        <v>422</v>
+        <v>8</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3249,16 +3408,16 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="D98" s="5">
-        <v>900</v>
+        <v>8</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3267,7 +3426,7 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="D99" s="5">
         <v>8</v>
@@ -3276,25 +3435,25 @@
         <v>7</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="D100" s="5">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3303,16 +3462,16 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="D101" s="5">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3321,7 +3480,7 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="D102" s="5">
         <v>64</v>
@@ -3330,7 +3489,7 @@
         <v>7</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3339,34 +3498,34 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="D103" s="5">
-        <v>240</v>
+        <v>32</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="D104" s="5">
-        <v>48</v>
+        <v>0.4</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3375,628 +3534,628 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>73</v>
+        <v>249</v>
       </c>
       <c r="D105" s="5">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>74</v>
+        <v>250</v>
       </c>
       <c r="D106" s="5">
-        <v>160</v>
+        <v>4.5750000000000002</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>106</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>75</v>
+        <v>251</v>
       </c>
       <c r="D107" s="5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>107</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="D108" s="5">
-        <v>144</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>108</v>
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D109" s="5">
-        <v>32</v>
+        <v>252</v>
+      </c>
+      <c r="D109" s="7">
+        <v>1371.68</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="D110" s="5">
-        <v>6</v>
+        <v>15.95</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>110</v>
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="D111" s="5">
-        <v>48</v>
+        <v>2.35</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>111</v>
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>185</v>
+        <v>255</v>
       </c>
       <c r="D112" s="5">
-        <v>396.5</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="D113" s="5">
-        <v>3</v>
+        <v>25.47</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>186</v>
+        <v>257</v>
       </c>
       <c r="D114" s="5">
-        <v>88</v>
+        <v>27.45</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="D115" s="5">
-        <v>989</v>
+        <v>67.98</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="D116" s="5">
-        <v>320</v>
+        <v>15.95</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="D117" s="5">
-        <v>16</v>
+        <v>13.76</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="D118" s="5">
-        <v>0.6</v>
+        <v>183</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>118</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>191</v>
+        <v>261</v>
       </c>
       <c r="D119" s="5">
-        <v>288</v>
+        <v>1.68</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>119</v>
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="D120" s="5">
-        <v>98</v>
+        <v>15.44</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>120</v>
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="D121" s="5">
-        <v>861.2</v>
+        <v>803.05</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>121</v>
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="D122" s="5">
-        <v>30</v>
+        <v>13.28</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>122</v>
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="D123" s="5">
-        <v>10</v>
+        <v>26.67</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>123</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="D124" s="5">
-        <v>40</v>
+        <v>266</v>
+      </c>
+      <c r="D124" s="7">
+        <v>2077.35</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>124</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="D125" s="5">
-        <v>16.8</v>
+        <v>11.36</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>125</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="D126" s="5">
-        <v>602.20000000000005</v>
+        <v>5.52</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D127" s="7">
-        <v>1040</v>
+        <v>269</v>
+      </c>
+      <c r="D127" s="5">
+        <v>31.76</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>127</v>
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D128" s="5">
-        <v>259</v>
+        <v>270</v>
+      </c>
+      <c r="D128" s="7">
+        <v>3123.56</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>128</v>
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D129" s="5">
-        <v>48</v>
+        <v>271</v>
+      </c>
+      <c r="D129" s="7">
+        <v>2549.337</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="D130" s="5">
-        <v>274.8</v>
+        <v>11.84</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>130</v>
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="D131" s="5">
-        <v>56</v>
+        <v>47.52</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D132" s="7">
-        <v>1199</v>
+        <v>274</v>
+      </c>
+      <c r="D132" s="5">
+        <v>8</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>132</v>
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="D133" s="5">
-        <v>100.8</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>133</v>
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D134" s="5">
-        <v>16</v>
+        <v>276</v>
+      </c>
+      <c r="D134" s="7">
+        <v>1284.922</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>206</v>
+        <v>277</v>
       </c>
       <c r="D135" s="5">
-        <v>40</v>
+        <v>29.1</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>207</v>
+        <v>278</v>
       </c>
       <c r="D136" s="5">
-        <v>32</v>
+        <v>94.4</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>136</v>
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="D137" s="5">
-        <v>64</v>
+        <v>82.14</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>137</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="D138" s="5">
-        <v>57</v>
+        <v>97.2</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>138</v>
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="D139" s="5">
-        <v>144</v>
+        <v>832.5</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4005,16 +4164,16 @@
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D140" s="5">
-        <v>0.4</v>
+        <v>281</v>
+      </c>
+      <c r="D140" s="7">
+        <v>1711.45</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4023,16 +4182,16 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D141" s="5">
-        <v>12</v>
+        <v>103.04</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4041,7 +4200,7 @@
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>213</v>
+        <v>283</v>
       </c>
       <c r="D142" s="5">
         <v>6</v>
@@ -4050,7 +4209,7 @@
         <v>7</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4059,16 +4218,16 @@
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="D143" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E143" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4077,16 +4236,16 @@
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="D144" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4095,16 +4254,16 @@
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>85</v>
+        <v>286</v>
       </c>
       <c r="D145" s="5">
-        <v>8.9700000000000006</v>
+        <v>6</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4113,16 +4272,16 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="D146" s="5">
-        <v>15.95</v>
+        <v>13.4</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4131,16 +4290,16 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>87</v>
+        <v>287</v>
       </c>
       <c r="D147" s="5">
-        <v>832.5</v>
+        <v>41</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4149,16 +4308,16 @@
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="D148" s="5">
-        <v>103.04</v>
+        <v>209</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4167,16 +4326,16 @@
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D149" s="5">
-        <v>15.44</v>
+        <v>289</v>
+      </c>
+      <c r="D149" s="7">
+        <v>3613.62</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4185,16 +4344,16 @@
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="8" t="s">
-        <v>218</v>
+        <v>290</v>
       </c>
       <c r="D150" s="5">
-        <v>97.2</v>
+        <v>6.48</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4203,16 +4362,16 @@
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>219</v>
+        <v>291</v>
       </c>
       <c r="D151" s="5">
-        <v>82.14</v>
+        <v>16.2</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4221,16 +4380,16 @@
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="D152" s="5">
-        <v>94.4</v>
+        <v>168</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4239,16 +4398,16 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="D153" s="7">
-        <v>1711.45</v>
+        <v>2115.44</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4257,16 +4416,16 @@
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="8" t="s">
-        <v>222</v>
+        <v>294</v>
       </c>
       <c r="D154" s="5">
-        <v>29.1</v>
+        <v>55.56</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4275,16 +4434,16 @@
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D155" s="7">
-        <v>1284.922</v>
+        <v>295</v>
+      </c>
+      <c r="D155" s="5">
+        <v>774.47</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4293,16 +4452,16 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="D156" s="5">
-        <v>8.5500000000000007</v>
+        <v>226.24</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4311,16 +4470,16 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D157" s="5">
-        <v>8</v>
+        <v>297</v>
+      </c>
+      <c r="D157" s="7">
+        <v>2471.12</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4329,16 +4488,16 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="D158" s="5">
-        <v>47.52</v>
+        <v>298</v>
+      </c>
+      <c r="D158" s="7">
+        <v>1084.0150000000001</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4347,16 +4506,16 @@
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="D159" s="5">
-        <v>11.84</v>
+        <v>431.68</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4365,16 +4524,16 @@
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="D160" s="7">
-        <v>2549.337</v>
+        <v>300</v>
+      </c>
+      <c r="D160" s="5">
+        <v>57.52</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4383,16 +4542,16 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="D161" s="7">
-        <v>3123.56</v>
+        <v>6015.74</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4401,16 +4560,16 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>230</v>
+        <v>302</v>
       </c>
       <c r="D162" s="5">
-        <v>31.76</v>
+        <v>789.92</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4419,16 +4578,16 @@
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D163" s="5">
-        <v>5.52</v>
+        <v>303</v>
+      </c>
+      <c r="D163" s="7">
+        <v>9355.9599999999991</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4437,16 +4596,16 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>232</v>
+        <v>304</v>
       </c>
       <c r="D164" s="5">
-        <v>11.36</v>
+        <v>114</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4455,16 +4614,16 @@
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="D165" s="7">
-        <v>2077.35</v>
+        <v>305</v>
+      </c>
+      <c r="D165" s="5">
+        <v>2.4500000000000002</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4473,16 +4632,16 @@
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="8" t="s">
-        <v>234</v>
+        <v>306</v>
       </c>
       <c r="D166" s="5">
-        <v>26.67</v>
+        <v>3.44</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4491,16 +4650,16 @@
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>235</v>
+        <v>307</v>
       </c>
       <c r="D167" s="5">
-        <v>13.28</v>
+        <v>1.2</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4509,16 +4668,16 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>236</v>
+        <v>308</v>
       </c>
       <c r="D168" s="5">
-        <v>803.05</v>
+        <v>39</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4527,16 +4686,16 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>237</v>
+        <v>309</v>
       </c>
       <c r="D169" s="5">
-        <v>1.68</v>
+        <v>55</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4545,16 +4704,16 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D170" s="5">
-        <v>183</v>
+        <v>5</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4563,16 +4722,16 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="D171" s="5">
-        <v>13.76</v>
+        <v>20</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4581,16 +4740,16 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D172" s="7">
-        <v>1371.68</v>
+        <v>311</v>
+      </c>
+      <c r="D172" s="5">
+        <v>6</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4599,16 +4758,16 @@
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>241</v>
+        <v>312</v>
       </c>
       <c r="D173" s="5">
-        <v>15.95</v>
+        <v>3</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4617,16 +4776,16 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="D174" s="5">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4635,16 +4794,16 @@
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="8" t="s">
-        <v>243</v>
+        <v>314</v>
       </c>
       <c r="D175" s="5">
-        <v>17.760000000000002</v>
+        <v>3</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4653,16 +4812,16 @@
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="8" t="s">
-        <v>244</v>
+        <v>315</v>
       </c>
       <c r="D176" s="5">
-        <v>25.47</v>
+        <v>100</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4671,16 +4830,16 @@
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="8" t="s">
-        <v>245</v>
+        <v>316</v>
       </c>
       <c r="D177" s="5">
-        <v>27.45</v>
+        <v>25</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4689,16 +4848,16 @@
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="8" t="s">
-        <v>246</v>
+        <v>317</v>
       </c>
       <c r="D178" s="5">
-        <v>67.98</v>
+        <v>33</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4707,16 +4866,16 @@
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="8" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
       <c r="D179" s="5">
-        <v>4.5750000000000002</v>
+        <v>318</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4725,16 +4884,16 @@
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="8" t="s">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="D180" s="5">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4743,16 +4902,16 @@
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="8" t="s">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="D181" s="5">
-        <v>6</v>
+        <v>303</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4761,16 +4920,16 @@
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="8" t="s">
-        <v>250</v>
+        <v>321</v>
       </c>
       <c r="D182" s="5">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4779,196 +4938,196 @@
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="8" t="s">
-        <v>251</v>
+        <v>322</v>
       </c>
       <c r="D183" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E183" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
         <v>183</v>
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="8" t="s">
-        <v>252</v>
+        <v>54</v>
       </c>
       <c r="D184" s="5">
-        <v>6.48</v>
+        <v>1</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="3">
         <v>184</v>
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="8" t="s">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="D185" s="5">
-        <v>16.2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
         <v>185</v>
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="8" t="s">
-        <v>254</v>
+        <v>324</v>
       </c>
       <c r="D186" s="5">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="3">
         <v>186</v>
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="D187" s="7">
-        <v>2115.44</v>
+        <v>325</v>
+      </c>
+      <c r="D187" s="5">
+        <v>1</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
         <v>187</v>
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="8" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
       <c r="D188" s="5">
-        <v>55.56</v>
+        <v>1</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="3">
         <v>188</v>
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="8" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
       <c r="D189" s="5">
-        <v>774.47</v>
+        <v>2</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>189</v>
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="8" t="s">
-        <v>258</v>
+        <v>59</v>
       </c>
       <c r="D190" s="5">
-        <v>226.24</v>
+        <v>15</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="3">
         <v>190</v>
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="D191" s="7">
-        <v>2471.12</v>
+        <v>60</v>
+      </c>
+      <c r="D191" s="5">
+        <v>5</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
         <v>191</v>
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="D192" s="7">
-        <v>1084.0150000000001</v>
+        <v>61</v>
+      </c>
+      <c r="D192" s="5">
+        <v>60</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="3">
         <v>192</v>
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="8" t="s">
-        <v>261</v>
+        <v>63</v>
       </c>
       <c r="D193" s="5">
-        <v>431.68</v>
+        <v>20</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4977,16 +5136,16 @@
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="D194" s="5">
-        <v>57.52</v>
+        <v>65</v>
+      </c>
+      <c r="D194" s="7">
+        <v>30000</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4995,34 +5154,34 @@
       </c>
       <c r="B195" s="4"/>
       <c r="C195" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="D195" s="7">
-        <v>6015.74</v>
+        <v>66</v>
+      </c>
+      <c r="D195" s="5">
+        <v>3</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>195</v>
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="8" t="s">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="D196" s="5">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5031,34 +5190,34 @@
       </c>
       <c r="B197" s="4"/>
       <c r="C197" s="8" t="s">
-        <v>265</v>
+        <v>68</v>
       </c>
       <c r="D197" s="5">
-        <v>789.92</v>
+        <v>6</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>197</v>
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="8" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="D198" s="5">
-        <v>13.4</v>
+        <v>4</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5067,16 +5226,16 @@
       </c>
       <c r="B199" s="4"/>
       <c r="C199" s="8" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="D199" s="5">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5085,16 +5244,16 @@
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="8" t="s">
-        <v>267</v>
+        <v>328</v>
       </c>
       <c r="D200" s="5">
-        <v>209</v>
+        <v>2</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5103,16 +5262,16 @@
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="D201" s="7">
-        <v>3613.62</v>
+        <v>329</v>
+      </c>
+      <c r="D201" s="5">
+        <v>96</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5121,16 +5280,16 @@
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D202" s="7">
-        <v>9355.9599999999991</v>
+        <v>330</v>
+      </c>
+      <c r="D202" s="5">
+        <v>48</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5139,16 +5298,16 @@
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="8" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="D203" s="5">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5157,16 +5316,16 @@
       </c>
       <c r="B204" s="4"/>
       <c r="C204" s="8" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="D204" s="5">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5175,16 +5334,16 @@
       </c>
       <c r="B205" s="4"/>
       <c r="C205" s="8" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
       <c r="D205" s="5">
-        <v>2.4500000000000002</v>
+        <v>8</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5193,16 +5352,16 @@
       </c>
       <c r="B206" s="4"/>
       <c r="C206" s="8" t="s">
-        <v>273</v>
+        <v>334</v>
       </c>
       <c r="D206" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5211,16 +5370,16 @@
       </c>
       <c r="B207" s="4"/>
       <c r="C207" s="8" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="D207" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E207" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5229,16 +5388,16 @@
       </c>
       <c r="B208" s="4"/>
       <c r="C208" s="8" t="s">
-        <v>275</v>
+        <v>336</v>
       </c>
       <c r="D208" s="5">
-        <v>303</v>
+        <v>32</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5247,16 +5406,16 @@
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="8" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="D209" s="5">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="E209" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5265,16 +5424,16 @@
       </c>
       <c r="B210" s="4"/>
       <c r="C210" s="8" t="s">
-        <v>277</v>
+        <v>338</v>
       </c>
       <c r="D210" s="5">
-        <v>318</v>
+        <v>10</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5283,16 +5442,16 @@
       </c>
       <c r="B211" s="4"/>
       <c r="C211" s="8" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="D211" s="5">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E211" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5301,16 +5460,16 @@
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="8" t="s">
-        <v>279</v>
+        <v>340</v>
       </c>
       <c r="D212" s="5">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5319,16 +5478,16 @@
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="8" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="D213" s="5">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E213" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5337,16 +5496,16 @@
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="8" t="s">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="D214" s="5">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5355,16 +5514,16 @@
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="8" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="D215" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E215" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5373,16 +5532,16 @@
       </c>
       <c r="B216" s="4"/>
       <c r="C216" s="8" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="D216" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5391,16 +5550,16 @@
       </c>
       <c r="B217" s="4"/>
       <c r="C217" s="8" t="s">
-        <v>284</v>
+        <v>345</v>
       </c>
       <c r="D217" s="5">
-        <v>6</v>
+        <v>376</v>
       </c>
       <c r="E217" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5409,16 +5568,16 @@
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="8" t="s">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="D218" s="5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5427,16 +5586,16 @@
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="8" t="s">
-        <v>286</v>
+        <v>347</v>
       </c>
       <c r="D219" s="5">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E219" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5445,16 +5604,16 @@
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="8" t="s">
-        <v>287</v>
+        <v>348</v>
       </c>
       <c r="D220" s="5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5463,34 +5622,34 @@
       </c>
       <c r="B221" s="4"/>
       <c r="C221" s="8" t="s">
-        <v>214</v>
+        <v>349</v>
       </c>
       <c r="D221" s="5">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="E221" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="3">
         <v>221</v>
       </c>
       <c r="B222" s="4"/>
       <c r="C222" s="8" t="s">
-        <v>93</v>
+        <v>350</v>
       </c>
       <c r="D222" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5499,16 +5658,16 @@
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="8" t="s">
-        <v>288</v>
+        <v>351</v>
       </c>
       <c r="D223" s="5">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="E223" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5517,7 +5676,7 @@
       </c>
       <c r="B224" s="4"/>
       <c r="C224" s="8" t="s">
-        <v>289</v>
+        <v>352</v>
       </c>
       <c r="D224" s="5">
         <v>32</v>
@@ -5526,7 +5685,7 @@
         <v>7</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5535,16 +5694,16 @@
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D225" s="5">
-        <v>24</v>
+        <v>353</v>
+      </c>
+      <c r="D225" s="7">
+        <v>1392</v>
       </c>
       <c r="E225" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5553,16 +5712,16 @@
       </c>
       <c r="B226" s="4"/>
       <c r="C226" s="8" t="s">
-        <v>97</v>
+        <v>354</v>
       </c>
       <c r="D226" s="5">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5571,7 +5730,7 @@
       </c>
       <c r="B227" s="4"/>
       <c r="C227" s="8" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="D227" s="5">
         <v>16</v>
@@ -5580,7 +5739,7 @@
         <v>7</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5589,7 +5748,7 @@
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="8" t="s">
-        <v>292</v>
+        <v>356</v>
       </c>
       <c r="D228" s="5">
         <v>16</v>
@@ -5598,7 +5757,7 @@
         <v>7</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5607,16 +5766,16 @@
       </c>
       <c r="B229" s="4"/>
       <c r="C229" s="8" t="s">
-        <v>293</v>
+        <v>72</v>
       </c>
       <c r="D229" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E229" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5625,16 +5784,16 @@
       </c>
       <c r="B230" s="4"/>
       <c r="C230" s="8" t="s">
-        <v>294</v>
+        <v>357</v>
       </c>
       <c r="D230" s="5">
-        <v>376</v>
+        <v>24</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5643,16 +5802,16 @@
       </c>
       <c r="B231" s="4"/>
       <c r="C231" s="8" t="s">
-        <v>295</v>
+        <v>358</v>
       </c>
       <c r="D231" s="5">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E231" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5661,16 +5820,16 @@
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="8" t="s">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="D232" s="5">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5679,16 +5838,16 @@
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="8" t="s">
-        <v>125</v>
+        <v>360</v>
       </c>
       <c r="D233" s="5">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="E233" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5697,16 +5856,16 @@
       </c>
       <c r="B234" s="4"/>
       <c r="C234" s="8" t="s">
-        <v>297</v>
+        <v>361</v>
       </c>
       <c r="D234" s="5">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5715,16 +5874,16 @@
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="8" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="D235" s="5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E235" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5733,16 +5892,16 @@
       </c>
       <c r="B236" s="4"/>
       <c r="C236" s="8" t="s">
-        <v>299</v>
+        <v>363</v>
       </c>
       <c r="D236" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5751,16 +5910,16 @@
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="8" t="s">
-        <v>300</v>
+        <v>364</v>
       </c>
       <c r="D237" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E237" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5769,16 +5928,16 @@
       </c>
       <c r="B238" s="4"/>
       <c r="C238" s="8" t="s">
-        <v>301</v>
+        <v>365</v>
       </c>
       <c r="D238" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5787,16 +5946,16 @@
       </c>
       <c r="B239" s="4"/>
       <c r="C239" s="8" t="s">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="D239" s="5">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E239" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5805,16 +5964,16 @@
       </c>
       <c r="B240" s="4"/>
       <c r="C240" s="8" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D240" s="5">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="241" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5823,16 +5982,16 @@
       </c>
       <c r="B241" s="4"/>
       <c r="C241" s="8" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="D241" s="5">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E241" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5841,142 +6000,142 @@
       </c>
       <c r="B242" s="4"/>
       <c r="C242" s="8" t="s">
-        <v>305</v>
+        <v>369</v>
       </c>
       <c r="D242" s="5">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="3">
         <v>242</v>
       </c>
       <c r="B243" s="4"/>
       <c r="C243" s="8" t="s">
-        <v>306</v>
+        <v>73</v>
       </c>
       <c r="D243" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="3">
         <v>243</v>
       </c>
       <c r="B244" s="4"/>
       <c r="C244" s="8" t="s">
-        <v>307</v>
+        <v>370</v>
       </c>
       <c r="D244" s="5">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="3">
         <v>244</v>
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="8" t="s">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="D245" s="5">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="E245" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>245</v>
       </c>
       <c r="B246" s="4"/>
       <c r="C246" s="8" t="s">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="D246" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="3">
         <v>246</v>
       </c>
       <c r="B247" s="4"/>
       <c r="C247" s="8" t="s">
-        <v>310</v>
+        <v>78</v>
       </c>
       <c r="D247" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E247" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>247</v>
       </c>
       <c r="B248" s="4"/>
       <c r="C248" s="8" t="s">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="D248" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="3">
         <v>248</v>
       </c>
       <c r="B249" s="4"/>
       <c r="C249" s="8" t="s">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="D249" s="5">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="250" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5985,34 +6144,34 @@
       </c>
       <c r="B250" s="4"/>
       <c r="C250" s="8" t="s">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="D250" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="3">
         <v>250</v>
       </c>
       <c r="B251" s="4"/>
       <c r="C251" s="8" t="s">
-        <v>314</v>
+        <v>85</v>
       </c>
       <c r="D251" s="5">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="252" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6021,16 +6180,16 @@
       </c>
       <c r="B252" s="4"/>
       <c r="C252" s="8" t="s">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="D252" s="5">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6039,16 +6198,16 @@
       </c>
       <c r="B253" s="4"/>
       <c r="C253" s="8" t="s">
-        <v>316</v>
+        <v>373</v>
       </c>
       <c r="D253" s="5">
-        <v>60</v>
+        <v>448</v>
       </c>
       <c r="E253" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6057,16 +6216,16 @@
       </c>
       <c r="B254" s="4"/>
       <c r="C254" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="D254" s="5">
-        <v>160</v>
+        <v>374</v>
+      </c>
+      <c r="D254" s="7">
+        <v>2688</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6075,16 +6234,16 @@
       </c>
       <c r="B255" s="4"/>
       <c r="C255" s="8" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="D255" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E255" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="256" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6093,16 +6252,16 @@
       </c>
       <c r="B256" s="4"/>
       <c r="C256" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="D256" s="5">
-        <v>80</v>
+        <v>87</v>
+      </c>
+      <c r="D256" s="7">
+        <v>23748.799999999999</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="257" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6111,16 +6270,16 @@
       </c>
       <c r="B257" s="4"/>
       <c r="C257" s="8" t="s">
-        <v>320</v>
+        <v>376</v>
       </c>
       <c r="D257" s="5">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E257" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="258" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6129,16 +6288,16 @@
       </c>
       <c r="B258" s="4"/>
       <c r="C258" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="D258" s="7">
-        <v>1392</v>
+        <v>377</v>
+      </c>
+      <c r="D258" s="5">
+        <v>1</v>
       </c>
       <c r="E258" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="259" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6147,16 +6306,16 @@
       </c>
       <c r="B259" s="4"/>
       <c r="C259" s="8" t="s">
-        <v>322</v>
+        <v>200</v>
       </c>
       <c r="D259" s="5">
-        <v>92</v>
+        <v>16.8</v>
       </c>
       <c r="E259" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6165,16 +6324,16 @@
       </c>
       <c r="B260" s="4"/>
       <c r="C260" s="8" t="s">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="D260" s="5">
-        <v>48</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="261" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6183,16 +6342,16 @@
       </c>
       <c r="B261" s="4"/>
       <c r="C261" s="8" t="s">
-        <v>324</v>
+        <v>91</v>
       </c>
       <c r="D261" s="5">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E261" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="262" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6201,16 +6360,16 @@
       </c>
       <c r="B262" s="4"/>
       <c r="C262" s="8" t="s">
-        <v>325</v>
+        <v>93</v>
       </c>
       <c r="D262" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E262" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="263" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6219,16 +6378,16 @@
       </c>
       <c r="B263" s="4"/>
       <c r="C263" s="8" t="s">
-        <v>326</v>
+        <v>94</v>
       </c>
       <c r="D263" s="5">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="E263" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="264" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6237,16 +6396,16 @@
       </c>
       <c r="B264" s="4"/>
       <c r="C264" s="8" t="s">
-        <v>327</v>
+        <v>95</v>
       </c>
       <c r="D264" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E264" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="265" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6255,16 +6414,16 @@
       </c>
       <c r="B265" s="4"/>
       <c r="C265" s="8" t="s">
-        <v>328</v>
+        <v>96</v>
       </c>
       <c r="D265" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E265" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="266" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6273,16 +6432,16 @@
       </c>
       <c r="B266" s="4"/>
       <c r="C266" s="8" t="s">
-        <v>329</v>
+        <v>97</v>
       </c>
       <c r="D266" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="267" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6291,73 +6450,73 @@
       </c>
       <c r="B267" s="4"/>
       <c r="C267" s="8" t="s">
-        <v>330</v>
+        <v>99</v>
       </c>
       <c r="D267" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="268" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="3">
         <v>267</v>
       </c>
       <c r="B268" s="4"/>
       <c r="C268" s="8" t="s">
-        <v>331</v>
+        <v>100</v>
       </c>
       <c r="D268" s="5">
-        <v>0.12</v>
+        <v>2</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="3">
         <v>268</v>
       </c>
       <c r="B269" s="4"/>
       <c r="C269" s="8" t="s">
-        <v>332</v>
+        <v>101</v>
       </c>
       <c r="D269" s="5">
-        <v>0.24</v>
+        <v>3</v>
       </c>
       <c r="E269" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="3">
         <v>269</v>
       </c>
       <c r="B270" s="4"/>
       <c r="C270" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D270" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="3">
         <v>270</v>
       </c>
@@ -6366,121 +6525,121 @@
         <v>103</v>
       </c>
       <c r="D271" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="3">
         <v>271</v>
       </c>
       <c r="B272" s="4"/>
       <c r="C272" s="8" t="s">
-        <v>105</v>
+        <v>379</v>
       </c>
       <c r="D272" s="5">
-        <v>5</v>
+        <v>700</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="3">
         <v>272</v>
       </c>
       <c r="B273" s="4"/>
       <c r="C273" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D273" s="5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="3">
         <v>273</v>
       </c>
       <c r="B274" s="4"/>
       <c r="C274" s="8" t="s">
-        <v>333</v>
+        <v>105</v>
       </c>
       <c r="D274" s="5">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="3">
         <v>274</v>
       </c>
       <c r="B275" s="4"/>
       <c r="C275" s="8" t="s">
-        <v>334</v>
+        <v>106</v>
       </c>
       <c r="D275" s="5">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="3">
         <v>275</v>
       </c>
       <c r="B276" s="4"/>
       <c r="C276" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D276" s="5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="3">
         <v>276</v>
       </c>
       <c r="B277" s="4"/>
       <c r="C277" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D277" s="5">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="278" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6489,34 +6648,34 @@
       </c>
       <c r="B278" s="4"/>
       <c r="C278" s="8" t="s">
-        <v>112</v>
+        <v>380</v>
       </c>
       <c r="D278" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="3">
         <v>278</v>
       </c>
       <c r="B279" s="4"/>
       <c r="C279" s="8" t="s">
-        <v>114</v>
+        <v>381</v>
       </c>
       <c r="D279" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E279" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="280" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6525,16 +6684,16 @@
       </c>
       <c r="B280" s="4"/>
       <c r="C280" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="D280" s="7">
-        <v>2688</v>
+        <v>382</v>
+      </c>
+      <c r="D280" s="5">
+        <v>4</v>
       </c>
       <c r="E280" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="281" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6543,16 +6702,16 @@
       </c>
       <c r="B281" s="4"/>
       <c r="C281" s="8" t="s">
-        <v>336</v>
+        <v>110</v>
       </c>
       <c r="D281" s="5">
-        <v>448</v>
+        <v>48</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="282" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6561,16 +6720,16 @@
       </c>
       <c r="B282" s="4"/>
       <c r="C282" s="8" t="s">
-        <v>337</v>
+        <v>112</v>
       </c>
       <c r="D282" s="5">
-        <v>4</v>
+        <v>480</v>
       </c>
       <c r="E282" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6579,16 +6738,16 @@
       </c>
       <c r="B283" s="4"/>
       <c r="C283" s="8" t="s">
-        <v>338</v>
+        <v>113</v>
       </c>
       <c r="D283" s="5">
-        <v>4</v>
+        <v>480</v>
       </c>
       <c r="E283" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="284" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6597,16 +6756,16 @@
       </c>
       <c r="B284" s="4"/>
       <c r="C284" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D284" s="5">
-        <v>267</v>
+        <v>48</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="285" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6615,34 +6774,34 @@
       </c>
       <c r="B285" s="4"/>
       <c r="C285" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D285" s="5">
-        <v>134</v>
+        <v>4</v>
       </c>
       <c r="E285" s="6" t="s">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="3">
         <v>285</v>
       </c>
       <c r="B286" s="4"/>
       <c r="C286" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D286" s="7">
-        <v>23748.799999999999</v>
+        <v>116</v>
+      </c>
+      <c r="D286" s="5">
+        <v>15</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="287" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6651,16 +6810,16 @@
       </c>
       <c r="B287" s="4"/>
       <c r="C287" s="8" t="s">
-        <v>198</v>
+        <v>117</v>
       </c>
       <c r="D287" s="5">
-        <v>16.8</v>
+        <v>2</v>
       </c>
       <c r="E287" s="6" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="288" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6669,16 +6828,16 @@
       </c>
       <c r="B288" s="4"/>
       <c r="C288" s="8" t="s">
-        <v>339</v>
+        <v>119</v>
       </c>
       <c r="D288" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E288" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="289" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6687,16 +6846,1006 @@
       </c>
       <c r="B289" s="4"/>
       <c r="C289" s="8" t="s">
-        <v>340</v>
+        <v>120</v>
       </c>
       <c r="D289" s="5">
         <v>1</v>
       </c>
       <c r="E289" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F289" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="3">
+        <v>289</v>
+      </c>
+      <c r="B290" s="4"/>
+      <c r="C290" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D290" s="5">
+        <v>1</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="3">
+        <v>290</v>
+      </c>
+      <c r="B291" s="4"/>
+      <c r="C291" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D291" s="5">
+        <v>1</v>
+      </c>
+      <c r="E291" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" s="3">
+        <v>291</v>
+      </c>
+      <c r="B292" s="4"/>
+      <c r="C292" s="8" t="s">
         <v>122</v>
+      </c>
+      <c r="D292" s="5">
+        <v>2</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="3">
+        <v>292</v>
+      </c>
+      <c r="B293" s="4"/>
+      <c r="C293" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D293" s="5">
+        <v>4</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" s="3">
+        <v>293</v>
+      </c>
+      <c r="B294" s="4"/>
+      <c r="C294" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D294" s="5">
+        <v>32</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="3">
+        <v>294</v>
+      </c>
+      <c r="B295" s="4"/>
+      <c r="C295" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D295" s="5">
+        <v>4</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="3">
+        <v>295</v>
+      </c>
+      <c r="B296" s="4"/>
+      <c r="C296" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="D296" s="5">
+        <v>26</v>
+      </c>
+      <c r="E296" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="3">
+        <v>296</v>
+      </c>
+      <c r="B297" s="4"/>
+      <c r="C297" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="D297" s="5">
+        <v>15</v>
+      </c>
+      <c r="E297" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="3">
+        <v>297</v>
+      </c>
+      <c r="B298" s="4"/>
+      <c r="C298" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="D298" s="5">
+        <v>26</v>
+      </c>
+      <c r="E298" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="3">
+        <v>298</v>
+      </c>
+      <c r="B299" s="4"/>
+      <c r="C299" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="D299" s="5">
+        <v>26</v>
+      </c>
+      <c r="E299" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="3">
+        <v>299</v>
+      </c>
+      <c r="B300" s="4"/>
+      <c r="C300" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="D300" s="5">
+        <v>15</v>
+      </c>
+      <c r="E300" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="3">
+        <v>300</v>
+      </c>
+      <c r="B301" s="4"/>
+      <c r="C301" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="D301" s="5">
+        <v>182</v>
+      </c>
+      <c r="E301" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="3">
+        <v>301</v>
+      </c>
+      <c r="B302" s="4"/>
+      <c r="C302" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="D302" s="5">
+        <v>512</v>
+      </c>
+      <c r="E302" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="3">
+        <v>302</v>
+      </c>
+      <c r="B303" s="4"/>
+      <c r="C303" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D303" s="7">
+        <v>3360</v>
+      </c>
+      <c r="E303" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" s="3">
+        <v>303</v>
+      </c>
+      <c r="B304" s="4"/>
+      <c r="C304" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D304" s="5">
+        <v>240</v>
+      </c>
+      <c r="E304" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="3">
+        <v>304</v>
+      </c>
+      <c r="B305" s="4"/>
+      <c r="C305" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D305" s="5">
+        <v>64</v>
+      </c>
+      <c r="E305" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="3">
+        <v>305</v>
+      </c>
+      <c r="B306" s="4"/>
+      <c r="C306" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D306" s="5">
+        <v>104</v>
+      </c>
+      <c r="E306" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="3">
+        <v>306</v>
+      </c>
+      <c r="B307" s="4"/>
+      <c r="C307" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D307" s="5">
+        <v>16</v>
+      </c>
+      <c r="E307" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="3">
+        <v>307</v>
+      </c>
+      <c r="B308" s="4"/>
+      <c r="C308" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D308" s="5">
+        <v>60</v>
+      </c>
+      <c r="E308" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309" s="3">
+        <v>308</v>
+      </c>
+      <c r="B309" s="4"/>
+      <c r="C309" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D309" s="5">
+        <v>32</v>
+      </c>
+      <c r="E309" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="3">
+        <v>309</v>
+      </c>
+      <c r="B310" s="4"/>
+      <c r="C310" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D310" s="5">
+        <v>256</v>
+      </c>
+      <c r="E310" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311" s="3">
+        <v>310</v>
+      </c>
+      <c r="B311" s="4"/>
+      <c r="C311" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D311" s="5">
+        <v>164</v>
+      </c>
+      <c r="E311" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A312" s="3">
+        <v>311</v>
+      </c>
+      <c r="B312" s="4"/>
+      <c r="C312" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D312" s="7">
+        <v>1456</v>
+      </c>
+      <c r="E312" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A313" s="3">
+        <v>312</v>
+      </c>
+      <c r="B313" s="4"/>
+      <c r="C313" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D313" s="5">
+        <v>1</v>
+      </c>
+      <c r="E313" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="3">
+        <v>313</v>
+      </c>
+      <c r="B314" s="4"/>
+      <c r="C314" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D314" s="5">
+        <v>1</v>
+      </c>
+      <c r="E314" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="3">
+        <v>314</v>
+      </c>
+      <c r="B315" s="4"/>
+      <c r="C315" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D315" s="5">
+        <v>1</v>
+      </c>
+      <c r="E315" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="3">
+        <v>315</v>
+      </c>
+      <c r="B316" s="4"/>
+      <c r="C316" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D316" s="5">
+        <v>4</v>
+      </c>
+      <c r="E316" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="3">
+        <v>316</v>
+      </c>
+      <c r="B317" s="4"/>
+      <c r="C317" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D317" s="5">
+        <v>3</v>
+      </c>
+      <c r="E317" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318" s="3">
+        <v>317</v>
+      </c>
+      <c r="B318" s="4"/>
+      <c r="C318" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D318" s="5">
+        <v>5</v>
+      </c>
+      <c r="E318" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="3">
+        <v>318</v>
+      </c>
+      <c r="B319" s="4"/>
+      <c r="C319" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D319" s="5">
+        <v>1</v>
+      </c>
+      <c r="E319" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A320" s="3">
+        <v>319</v>
+      </c>
+      <c r="B320" s="4"/>
+      <c r="C320" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D320" s="5">
+        <v>1</v>
+      </c>
+      <c r="E320" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="3">
+        <v>320</v>
+      </c>
+      <c r="B321" s="4"/>
+      <c r="C321" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D321" s="5">
+        <v>1</v>
+      </c>
+      <c r="E321" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="3">
+        <v>321</v>
+      </c>
+      <c r="B322" s="4"/>
+      <c r="C322" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D322" s="5">
+        <v>1</v>
+      </c>
+      <c r="E322" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="3">
+        <v>322</v>
+      </c>
+      <c r="B323" s="4"/>
+      <c r="C323" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D323" s="5">
+        <v>2</v>
+      </c>
+      <c r="E323" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A324" s="3">
+        <v>323</v>
+      </c>
+      <c r="B324" s="4"/>
+      <c r="C324" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D324" s="5">
+        <v>2</v>
+      </c>
+      <c r="E324" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="3">
+        <v>324</v>
+      </c>
+      <c r="B325" s="4"/>
+      <c r="C325" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D325" s="5">
+        <v>100</v>
+      </c>
+      <c r="E325" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326" s="3">
+        <v>325</v>
+      </c>
+      <c r="B326" s="4"/>
+      <c r="C326" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D326" s="5">
+        <v>1</v>
+      </c>
+      <c r="E326" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="3">
+        <v>326</v>
+      </c>
+      <c r="B327" s="4"/>
+      <c r="C327" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D327" s="5">
+        <v>1</v>
+      </c>
+      <c r="E327" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="3">
+        <v>327</v>
+      </c>
+      <c r="B328" s="4"/>
+      <c r="C328" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D328" s="5">
+        <v>2</v>
+      </c>
+      <c r="E328" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="3">
+        <v>328</v>
+      </c>
+      <c r="B329" s="4"/>
+      <c r="C329" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D329" s="5">
+        <v>5</v>
+      </c>
+      <c r="E329" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330" s="3">
+        <v>329</v>
+      </c>
+      <c r="B330" s="4"/>
+      <c r="C330" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D330" s="5">
+        <v>48</v>
+      </c>
+      <c r="E330" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331" s="3">
+        <v>330</v>
+      </c>
+      <c r="B331" s="4"/>
+      <c r="C331" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D331" s="5">
+        <v>1</v>
+      </c>
+      <c r="E331" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332" s="3">
+        <v>331</v>
+      </c>
+      <c r="B332" s="4"/>
+      <c r="C332" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D332" s="5">
+        <v>6</v>
+      </c>
+      <c r="E332" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="3">
+        <v>332</v>
+      </c>
+      <c r="B333" s="4"/>
+      <c r="C333" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D333" s="5">
+        <v>4</v>
+      </c>
+      <c r="E333" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="3">
+        <v>333</v>
+      </c>
+      <c r="B334" s="4"/>
+      <c r="C334" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D334" s="5">
+        <v>2</v>
+      </c>
+      <c r="E334" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A335" s="3">
+        <v>334</v>
+      </c>
+      <c r="B335" s="4"/>
+      <c r="C335" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D335" s="5">
+        <v>1</v>
+      </c>
+      <c r="E335" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A336" s="3">
+        <v>335</v>
+      </c>
+      <c r="B336" s="4"/>
+      <c r="C336" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D336" s="5">
+        <v>1</v>
+      </c>
+      <c r="E336" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A337" s="3">
+        <v>336</v>
+      </c>
+      <c r="B337" s="4"/>
+      <c r="C337" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D337" s="5">
+        <v>1</v>
+      </c>
+      <c r="E337" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338" s="3">
+        <v>337</v>
+      </c>
+      <c r="B338" s="4"/>
+      <c r="C338" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D338" s="5">
+        <v>1</v>
+      </c>
+      <c r="E338" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F338" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A339" s="3">
+        <v>338</v>
+      </c>
+      <c r="B339" s="4"/>
+      <c r="C339" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D339" s="5">
+        <v>2</v>
+      </c>
+      <c r="E339" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F339" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A340" s="3">
+        <v>339</v>
+      </c>
+      <c r="B340" s="4"/>
+      <c r="C340" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D340" s="5">
+        <v>6</v>
+      </c>
+      <c r="E340" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F340" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="3">
+        <v>340</v>
+      </c>
+      <c r="B341" s="4"/>
+      <c r="C341" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D341" s="5">
+        <v>1</v>
+      </c>
+      <c r="E341" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A342" s="3">
+        <v>341</v>
+      </c>
+      <c r="B342" s="4"/>
+      <c r="C342" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D342" s="5">
+        <v>1</v>
+      </c>
+      <c r="E342" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F342" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="3">
+        <v>342</v>
+      </c>
+      <c r="B343" s="4"/>
+      <c r="C343" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D343" s="5">
+        <v>30</v>
+      </c>
+      <c r="E343" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F343" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="3">
+        <v>343</v>
+      </c>
+      <c r="B344" s="4"/>
+      <c r="C344" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D344" s="5">
+        <v>1</v>
+      </c>
+      <c r="E344" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36433B96-F7A6-44A2-B7A2-E99BF8B9CA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9706ADB8-69C4-4A0E-AE49-941715F2D264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3570" yWindow="3180" windowWidth="23730" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="438">
   <si>
     <t>№ п/п</t>
   </si>
@@ -69,120 +69,117 @@
     <t>ЛГУП-6943</t>
   </si>
   <si>
+    <t>Ключ комбинированные омедненные 36</t>
+  </si>
+  <si>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>ЛГУП-7332</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 30</t>
+  </si>
+  <si>
+    <t>Ножницы по металлу</t>
+  </si>
+  <si>
     <t>Ключи обмедненные</t>
   </si>
   <si>
     <t>набор</t>
   </si>
   <si>
-    <t>ЛГУП-7332</t>
+    <t>Резак</t>
+  </si>
+  <si>
+    <t>Гайковерт</t>
+  </si>
+  <si>
+    <t>Ключ комбинированные омедненные 41</t>
   </si>
   <si>
     <t>Ключ комбинированные омедненные 24</t>
   </si>
   <si>
-    <t>шт.</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 30</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 36</t>
-  </si>
-  <si>
-    <t>Ключ комбинированные омедненные 41</t>
-  </si>
-  <si>
-    <t>Гайковерт</t>
+    <t>Трещетка ключ 1/2</t>
   </si>
   <si>
     <t>Кувалда 1 кг.</t>
   </si>
   <si>
-    <t>Резак</t>
-  </si>
-  <si>
-    <t>Ножницы по металлу</t>
-  </si>
-  <si>
-    <t>Трещетка ключ 1/2</t>
+    <t>ЛГУП-7653</t>
   </si>
   <si>
     <t>пог. м</t>
   </si>
   <si>
-    <t>ЛГУП-7653</t>
+    <t>м</t>
   </si>
   <si>
     <t>ЛГУП-7654</t>
   </si>
   <si>
+    <t>Пломба 1-6х10-АД-1М ГОСТ 18677-73</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
+  </si>
+  <si>
+    <t>Электроприв четвер.взры. ГЗ-ОФВ-300/28М 1х220 DN80PN63 L=452 УХЛ (исп. фл. J)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-20 У2 IP54 ЗЭТА</t>
+  </si>
+  <si>
+    <t>Лампа индикации ADDS D22 LED белая 220В AC/DC ЛK-22 IP55 25152DEK Dekraft</t>
+  </si>
+  <si>
+    <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт.CM030508</t>
+  </si>
+  <si>
+    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
+  </si>
+  <si>
+    <t>мм</t>
+  </si>
+  <si>
     <t>Комплект кабельной проходки МКС</t>
   </si>
   <si>
     <t>компл</t>
   </si>
   <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>мм</t>
-  </si>
-  <si>
     <t>г</t>
   </si>
   <si>
-    <t>Пломба 1-6х10-АД-1М ГОСТ 18677-73</t>
-  </si>
-  <si>
-    <t>Электроприв четвер.взры. ГЗ-ОФВ-300/28М 1х220 DN80PN63 L=452 УХЛ (исп. фл. J)</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-20 У2 IP54 ЗЭТА</t>
-  </si>
-  <si>
-    <t>Лампа индикации ADDS D22 LED белая 220В AC/DC ЛK-22 IP55 25152DEK Dekraft</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
-  </si>
-  <si>
-    <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт.CM030508</t>
-  </si>
-  <si>
-    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
-  </si>
-  <si>
     <t>ЛГУП-7657</t>
   </si>
   <si>
-    <t>ЛГУП-7661</t>
-  </si>
-  <si>
     <t>кг</t>
   </si>
   <si>
     <t>ЛГУП-7663</t>
   </si>
   <si>
+    <t>Труба D720х12 09Г2С ГОСТ 10705-80</t>
+  </si>
+  <si>
+    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
+  </si>
+  <si>
     <t>Труба D89х8 Ст. 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D720х12 09Г2С ГОСТ 10705-80</t>
-  </si>
-  <si>
     <t>ЛГУП-7664</t>
   </si>
   <si>
+    <t>ЛГУП-7665</t>
+  </si>
+  <si>
     <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.3сп ГОСТ 535-88</t>
   </si>
   <si>
-    <t>ЛГУП-7665</t>
-  </si>
-  <si>
     <t>ЛГУП-7666</t>
   </si>
   <si>
@@ -198,48 +195,45 @@
     <t>ЛГУП-7593</t>
   </si>
   <si>
+    <t>Борфреза твердосплавная F 1225/6</t>
+  </si>
+  <si>
+    <t>ЛГУП-7646</t>
+  </si>
+  <si>
+    <t>Борфреза твердосплавная сфероцилиндрическая C1225-M06</t>
+  </si>
+  <si>
     <t>Набор ударных торцовых головок Makita Impact Black 1/2", 9 шт. (арт. E-16564)</t>
   </si>
   <si>
-    <t>ЛГУП-7646</t>
-  </si>
-  <si>
-    <t>Борфреза твердосплавная F 1225/6</t>
-  </si>
-  <si>
-    <t>Борфреза твердосплавная сфероцилиндрическая C1225-M06</t>
-  </si>
-  <si>
     <t>Удостоверение по электробезопасности</t>
   </si>
   <si>
     <t>НТУП-018086</t>
   </si>
   <si>
+    <t>Кран шаровой ГАЛЛОП 11/4'' ,внутр/наружн резьба, рукоятка 11б27п1 Стандарт 221 (Код 41070227 "ВИ")</t>
+  </si>
+  <si>
+    <t>ЛГУП-7647</t>
+  </si>
+  <si>
+    <t>Гайка для циркуляционного насоса 11/4", черная AV Engineering AVE183010 (код. 27874394 "ВИ")</t>
+  </si>
+  <si>
+    <t>Кран ПП 32</t>
+  </si>
+  <si>
+    <t>Тройник ⌀32 x 25 x 32 мм полипропилен</t>
+  </si>
+  <si>
+    <t>Труба ПП армированная стекловолокном, ф 32</t>
+  </si>
+  <si>
     <t>Угол 90° ⌀25 мм полипропилен</t>
   </si>
   <si>
-    <t>ЛГУП-7647</t>
-  </si>
-  <si>
-    <t>Труба ПП армированная стекловолокном, ф 32</t>
-  </si>
-  <si>
-    <t>Гайка для циркуляционного насоса 11/4", черная AV Engineering AVE183010 (код. 27874394 "ВИ")</t>
-  </si>
-  <si>
-    <t>Тройник ⌀32 x 25 x 32 мм полипропилен</t>
-  </si>
-  <si>
-    <t>Кран шаровой ГАЛЛОП 11/4'' ,внутр/наружн резьба, рукоятка 11б27п1 Стандарт 221 (Код 41070227 "ВИ")</t>
-  </si>
-  <si>
-    <t>Кран ПП 32</t>
-  </si>
-  <si>
-    <t>ЛГУП-7671</t>
-  </si>
-  <si>
     <t>ЛГУП-7674</t>
   </si>
   <si>
@@ -264,135 +258,126 @@
     <t>Шкаф ПС и ОС АГЗУ 14-400 АО Оренбургнефтегаз</t>
   </si>
   <si>
+    <t>Профлист С-8(Желтый) 1,2*6м</t>
+  </si>
+  <si>
+    <t>НТУП-018112</t>
+  </si>
+  <si>
     <t>Саморез  кровельный 5,5х60 С пресс-шайбой со сверлом (мет/мет)</t>
   </si>
   <si>
     <t>100 шт</t>
   </si>
   <si>
-    <t>НТУП-018112</t>
-  </si>
-  <si>
-    <t>Профлист С-8(Желтый) 1,2*6м</t>
+    <t>Сегмент ПСМНТ.001.014.000</t>
+  </si>
+  <si>
+    <t>ЛГУП-7680</t>
   </si>
   <si>
     <t>Вал ПСМНТ.001.015.000 св.загот (нормализация "стоя" при темп-ре 350-400 град 30 мин и отпуск в печи)</t>
   </si>
   <si>
-    <t>ЛГУП-7680</t>
-  </si>
-  <si>
-    <t>Сегмент ПСМНТ.001.014.000</t>
-  </si>
-  <si>
     <t>ЛГУП-7683</t>
   </si>
   <si>
-    <t>Сетка армированная С1 диам. 12 мм размер яч. 200х200 мм</t>
-  </si>
-  <si>
-    <t>ЛГУП-7685</t>
-  </si>
-  <si>
     <t>ЛГ00-000043</t>
   </si>
   <si>
     <t>ЛГУП-7686</t>
   </si>
   <si>
+    <t>Кран шаровой фланцевый 11лс01 пф PN1,6 DN50 КОФ</t>
+  </si>
+  <si>
+    <t>ЛГУП-7687</t>
+  </si>
+  <si>
+    <t>Кран шаровой фланцевый 11лс01 пф PN63 DN50 КОФ</t>
+  </si>
+  <si>
     <t>Кран шаровой штуцерный 11лс01пп PN63 DN15 КОФ</t>
   </si>
   <si>
-    <t>ЛГУП-7687</t>
+    <t>Задвижка клиновая фланцевая с ручным приводом 30лс76нж PN63 DN150 КОФ с контр.протечек</t>
   </si>
   <si>
     <t>Задвижка клиновая фланцевая с руч. прив. 30лс76нж PN63 DN150 КОФ</t>
   </si>
   <si>
-    <t>Задвижка клиновая фланцевая с ручным приводом 30лс76нж PN63 DN150 КОФ с контр.протечек</t>
-  </si>
-  <si>
-    <t>Кран шаровой фланцевый 11лс01 пф PN1,6 DN50 КОФ</t>
-  </si>
-  <si>
-    <t>Кран шаровой фланцевый 11лс01 пф PN63 DN50 КОФ</t>
+    <t>ЛГУП-7688</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-6 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-4 ГОСТ 19903-74/09Г2С ГОСТ 5520-79</t>
+  </si>
+  <si>
+    <t>Круг 38-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-10 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг 28-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Круг 22-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-8 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-0-5,0 ГОСТ 19903-2015/ 09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Шестиграник 27-h12 ГОСТ 8560-78/(ст.13ХФА)</t>
   </si>
   <si>
     <t>Лист Б-ПН-0-10 ГОСТ 19903-74/09Г2С ГОСТ 19281-2014</t>
   </si>
   <si>
-    <t>ЛГУП-7688</t>
-  </si>
-  <si>
     <t>Круг 50-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
   </si>
   <si>
-    <t>Круг 38-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Круг 28-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-0-5,0 ГОСТ 19903-2015/ 09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Круг 22-В ГОСТ 2590-2006/ст.13ХФА ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-0-6 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-0-4 ГОСТ 19903-74/09Г2С ГОСТ 5520-79</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-0-10 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Шестиграник 27-h12 ГОСТ 8560-78/(ст.13ХФА)</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-0-8 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>ЛГУП-7689</t>
-  </si>
-  <si>
     <t>Гайка М36.7Н.09Г2С ОСТ 26-2041-96</t>
   </si>
   <si>
     <t>ЛГУП-7691</t>
   </si>
   <si>
+    <t>Шпильки 1-М36-8gx190.09Г2С.05 ОСТ 26-2038-96</t>
+  </si>
+  <si>
     <t>Гайка М30.7H.09Г2С.05 ОСТ 26-2038-96</t>
   </si>
   <si>
+    <t>Болт М14-6gx45.10Г2.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М10-6gx40.56.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
     <t>Шпильки 1-М30-8gx160.09Г2С.05 ОСТ 26-2038-96</t>
   </si>
   <si>
-    <t>Шпильки 1-М36-8gx190.09Г2С.05 ОСТ 26-2038-96</t>
-  </si>
-  <si>
-    <t>Болт М10-6gx40.56.019 ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Болт М14-6gx45.10Г2.019 ГОСТ 7798-70</t>
+    <t>Шуроповерт Макита</t>
+  </si>
+  <si>
+    <t>ЛГУП-7699</t>
   </si>
   <si>
     <t>Заклепочник (2,4 - 4,8мм)</t>
   </si>
   <si>
-    <t>ЛГУП-7699</t>
+    <t>Набор ключей ударных 17-55</t>
   </si>
   <si>
     <t>Сверло по металлу   5,0мм</t>
   </si>
   <si>
-    <t>Шуроповерт Макита</t>
-  </si>
-  <si>
-    <t>Набор ключей ударных 17-55</t>
-  </si>
-  <si>
     <t>Батарейка Camelion Plus Alkaline LR03-BP4, алкалиновая, LR03 AAA (4 шт.)</t>
   </si>
   <si>
@@ -405,610 +390,706 @@
     <t>ЛГУП-7705</t>
   </si>
   <si>
+    <t>Гайка М12.7Н.09Г2С.019 ОСТ 26-2041-96</t>
+  </si>
+  <si>
     <t>Гайка М16.7Н.09Г2С.019 ОСТ 26-2041-96</t>
   </si>
   <si>
-    <t>Гайка М12.7Н.09Г2С.019 ОСТ 26-2041-96</t>
-  </si>
-  <si>
     <t>Шпилька 1-М12-8gx60.09Г2С.019 ОСТ 26-2040-96</t>
   </si>
   <si>
+    <t>Шпилька 1-М16-8gx90.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М16-8g x100.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
     <t>Шпилька 1-М12-8gx80.09Г2С.019 ОСТ 26-2040-96</t>
   </si>
   <si>
+    <t>Шпилька 1-М20-8gx130.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
     <t>Шпилька 1-М16-8gx80.09Г2С.019 ОСТ 26-2040-96</t>
   </si>
   <si>
     <t>Шпилька 1-М30-8gx160.09Г2С.019 ОСТ 26-2040-96</t>
   </si>
   <si>
-    <t>Шпилька 1-М20-8gx130.09Г2С.019 ОСТ 26-2040-96</t>
-  </si>
-  <si>
-    <t>Шпилька 1-М16-8gx90.09Г2С.019 ОСТ 26-2040-96</t>
-  </si>
-  <si>
-    <t>Шпилька 1-М16-8g x100.09Г2С.019 ОСТ 26-2040-96</t>
+    <t>Затирка</t>
+  </si>
+  <si>
+    <t>ЛГУП-7707</t>
+  </si>
+  <si>
+    <t>Клей монтажный</t>
+  </si>
+  <si>
+    <t>Шпаклевка полимер. финишная VETONIT KR 20 кг</t>
+  </si>
+  <si>
+    <t>Шпатель 100мм</t>
+  </si>
+  <si>
+    <t>Шпатель 350мм, н/ж ст., пласт.ручка</t>
+  </si>
+  <si>
+    <t>Ведро 20л пластик.</t>
+  </si>
+  <si>
+    <t>Ведро 12л пластиковое</t>
+  </si>
+  <si>
+    <t>Гипсокартон</t>
+  </si>
+  <si>
+    <t>Профиль потолочный П28х27-3000 (3м) КНАУФ</t>
+  </si>
+  <si>
+    <t>Профиль потолочный 60х2 7мм 3м 0,6мм КНАУФ</t>
+  </si>
+  <si>
+    <t>Перчатки</t>
+  </si>
+  <si>
+    <t>Саморез по дереву 3,5*3,8х35 мм черный</t>
+  </si>
+  <si>
+    <t>Пескобетон М-300 (25 кг)</t>
+  </si>
+  <si>
+    <t>Крестики для кафеля 1,5 мм</t>
+  </si>
+  <si>
+    <t>Серпянка</t>
+  </si>
+  <si>
+    <t>Саморез полусфера-прессшайба со сверлом 4,2*19мм оцинк.</t>
+  </si>
+  <si>
+    <t>Перчатки  х/б двойной облив латексный зеленый 13кл</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
+    <t>Мешки п/п 50 кг 55*95</t>
+  </si>
+  <si>
+    <t>Клей для плитки 25 кг</t>
+  </si>
+  <si>
+    <t>Подвес прямой Knauf Шт</t>
+  </si>
+  <si>
+    <t>Дюбель+шуруп 6*40</t>
+  </si>
+  <si>
+    <t>Набор малярный валик и кювета</t>
+  </si>
+  <si>
+    <t>Набор малярный  для фасадных работ</t>
+  </si>
+  <si>
+    <t>Пленка BEGINIA 100 мкм 3x10 м прозрачный полиэтилен</t>
+  </si>
+  <si>
+    <t>Грунтовка глубокого проникновения Церезит CT17 10 л</t>
+  </si>
+  <si>
+    <t>Лист шлифовальный на бумажной основе DILWIS P180 93x230 мм, 5 шт.</t>
+  </si>
+  <si>
+    <t>Лист шлифовальный на бумажной основе DILWIS P120 230x280 мм</t>
+  </si>
+  <si>
+    <t>Лист шлифовальный на бумажной основе DILWIS P40 230x280 мм</t>
+  </si>
+  <si>
+    <t>Шпатель зубчатый Интек 10108-150-006 150 мм, нержавеющая сталь, зуб 6x6 мм</t>
+  </si>
+  <si>
+    <t>Шпатель зубчатый Интек 10108-350-010 350 мм, нержавеющая сталь, зуб 10x10 мм</t>
   </si>
   <si>
     <t>Крестики для кафеля 2мм</t>
   </si>
   <si>
-    <t>ЛГУП-7707</t>
-  </si>
-  <si>
-    <t>Шпатель зубчатый Интек 10108-350-010 350 мм, нержавеющая сталь, зуб 10x10 мм</t>
-  </si>
-  <si>
-    <t>Шпатель зубчатый Интек 10108-150-006 150 мм, нержавеющая сталь, зуб 6x6 мм</t>
-  </si>
-  <si>
-    <t>Перчатки  х/б двойной облив латексный зеленый 13кл</t>
-  </si>
-  <si>
-    <t>пар</t>
-  </si>
-  <si>
-    <t>Лист шлифовальный на бумажной основе DILWIS P40 230x280 мм</t>
-  </si>
-  <si>
-    <t>Лист шлифовальный на бумажной основе DILWIS P120 230x280 мм</t>
-  </si>
-  <si>
-    <t>Лист шлифовальный на бумажной основе DILWIS P180 93x230 мм, 5 шт.</t>
-  </si>
-  <si>
-    <t>Грунтовка глубокого проникновения Церезит CT17 10 л</t>
-  </si>
-  <si>
     <t>Набор малярный Dexter валик 100 мм и кисть 40 мм, ручка, кювета, скотч</t>
   </si>
   <si>
-    <t>Набор малярный  для фасадных работ</t>
-  </si>
-  <si>
-    <t>Серпянка</t>
-  </si>
-  <si>
-    <t>Набор малярный валик и кювета</t>
-  </si>
-  <si>
-    <t>Дюбель+шуруп 6*40</t>
-  </si>
-  <si>
-    <t>Пленка BEGINIA 100 мкм 3x10 м прозрачный полиэтилен</t>
-  </si>
-  <si>
-    <t>Крестики для кафеля 1,5 мм</t>
-  </si>
-  <si>
-    <t>Пескобетон М-300 (25 кг)</t>
-  </si>
-  <si>
-    <t>Перчатки</t>
-  </si>
-  <si>
-    <t>Саморез полусфера-прессшайба со сверлом 4,2*19мм оцинк.</t>
-  </si>
-  <si>
-    <t>Саморез по дереву 3,5*3,8х35 мм черный</t>
-  </si>
-  <si>
-    <t>Профиль потолочный 60х2 7мм 3м 0,6мм КНАУФ</t>
-  </si>
-  <si>
-    <t>Профиль потолочный П28х27-3000 (3м) КНАУФ</t>
-  </si>
-  <si>
-    <t>Гипсокартон</t>
-  </si>
-  <si>
-    <t>Ведро 12л пластиковое</t>
-  </si>
-  <si>
-    <t>Ведро 20л пластик.</t>
-  </si>
-  <si>
-    <t>Шпатель 350мм, н/ж ст., пласт.ручка</t>
-  </si>
-  <si>
-    <t>Шпатель 100мм</t>
-  </si>
-  <si>
-    <t>Шпаклевка полимер. финишная VETONIT KR 20 кг</t>
-  </si>
-  <si>
-    <t>Клей монтажный</t>
-  </si>
-  <si>
-    <t>Затирка</t>
-  </si>
-  <si>
-    <t>Клей для плитки 25 кг</t>
-  </si>
-  <si>
-    <t>Подвес прямой Knauf Шт</t>
-  </si>
-  <si>
-    <t>Мешки п/п 50 кг 55*95</t>
+    <t>ЛГУП-7711</t>
+  </si>
+  <si>
+    <t>ЛГУП-7715</t>
+  </si>
+  <si>
+    <t>ЛГУП-7716</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gx160.60.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>ЛГУП-7717</t>
+  </si>
+  <si>
+    <t>Штуцер Ш2.7038.001 (покрытие Хим.Фас)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7720</t>
+  </si>
+  <si>
+    <t>ЛГУП-7722</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2300х1000х80,  снаружи RAL 1021 / внутри RAL 9003</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2500х1000х80 RAL 1021 (желт) снаружи/ RAL 9003 (белый) внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2900х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 3100х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 3100х1000х100 9003/9003</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2900х1000х150 мм RAL 9003 (белый)</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2800х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>Панель стеновая ПТСМ 2600х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
+  </si>
+  <si>
+    <t>Лист профилированный С21-1000-0,7 L=1600мм RAL 1021 (желтый)</t>
+  </si>
+  <si>
+    <t>Лист профилированный С21-1000-0,7 L=1350мм RAL 1021 (желтый)</t>
   </si>
   <si>
     <t>Отлив нижний Лист Б-ПН-0-0,55 ГОСТ 19904-90 ОН-КР-1 ГОСТ 14918-80 RAL 7036 (платиново-серый)</t>
   </si>
   <si>
-    <t>Панель стеновая ПТСМ 2500х1000х80 RAL 1021 (желт) снаружи/ RAL 9003 (белый) внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2300х1000х80,  снаружи RAL 1021 / внутри RAL 9003</t>
-  </si>
-  <si>
-    <t>Лист профилированный С21-1000-0,7 L=1600мм RAL 1021 (желтый)</t>
-  </si>
-  <si>
-    <t>Лист профилированный С21-1000-0,7 L=1350мм RAL 1021 (желтый)</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2600х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 3100х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2800х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2900х1000х100 RAL 1021(желтый) снаружи/RAL 9003(белый)внутри</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 2900х1000х150 мм RAL 9003 (белый)</t>
-  </si>
-  <si>
-    <t>Панель стеновая ПТСМ 3100х1000х100 9003/9003</t>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(А)-FRLS 2*2*0,75</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 100х60</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
+  </si>
+  <si>
+    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS- 3х2,50</t>
+  </si>
+  <si>
+    <t>Трубка 3.31 ТВ-40 ГОСТ 19034-82</t>
+  </si>
+  <si>
+    <t>Провод НВМ 0,35 IV 500 ГОСТ 17515-72</t>
+  </si>
+  <si>
+    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
+  </si>
+  <si>
+    <t>Заглушка 10707 Legrand DPL 65х195</t>
+  </si>
+  <si>
+    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 40х40 мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
+  </si>
+  <si>
+    <t>Крышка (100х15х3000)</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 4.1.1</t>
+  </si>
+  <si>
+    <t>Пластина для заземления PTCE арт. 37501</t>
+  </si>
+  <si>
+    <t>Плата печатная ПСМ.11.00.01.01-02</t>
+  </si>
+  <si>
+    <t>Плата питания ПСМ.11.00.00.01-02</t>
+  </si>
+  <si>
+    <t>Геркон КЭМ-2</t>
+  </si>
+  <si>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
+  </si>
+  <si>
+    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
   </si>
   <si>
     <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
   </si>
   <si>
+    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
+  </si>
+  <si>
+    <t>Аварийное освещение Вега 60 2Ex Тех  IP65</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 120</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
+  </si>
+  <si>
+    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 4.1.1</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 2.1.1</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 2.1.1</t>
+  </si>
+  <si>
+    <t>Трубка для фильтра 1/4" Гейзер</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
+  </si>
+  <si>
+    <t>Профиль PSM (3000) арт. 34181</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
+  </si>
+  <si>
+    <t>Консоль с опорой ML 300мм (шт)</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
+  </si>
+  <si>
+    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка распаячная КМ41242 IP55</t>
+  </si>
+  <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
     <t>Крышка (50х15х3000)</t>
   </si>
   <si>
-    <t>Крышка (100х15х3000)</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
-    <t>Коробка распаячная КМ41242 IP55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
-  </si>
-  <si>
-    <t>Провод НВМ 0,35 IV 500 ГОСТ 17515-72</t>
-  </si>
-  <si>
-    <t>Трубка 3.31 ТВ-40 ГОСТ 19034-82</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(А)-FRLS 2*2*0,75</t>
-  </si>
-  <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 100х60</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 40х40 мм</t>
-  </si>
-  <si>
-    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
-  </si>
-  <si>
-    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
-  </si>
-  <si>
-    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
-  </si>
-  <si>
-    <t>Провод Rd8</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS- 3х2,50</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
-  </si>
-  <si>
-    <t>Трубка для фильтра 1/4" Гейзер</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
-  </si>
-  <si>
-    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
-  </si>
-  <si>
-    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
-  </si>
-  <si>
-    <t>Консоль с опорой ML 300мм (шт)</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
-  </si>
-  <si>
-    <t>Заглушка 10707 Legrand DPL 65х195</t>
-  </si>
-  <si>
-    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
-  </si>
-  <si>
-    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
-  </si>
-  <si>
-    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
-  </si>
-  <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>Геркон КЭМ-2</t>
-  </si>
-  <si>
-    <t>Выключатель двухклавишный IP55</t>
-  </si>
-  <si>
-    <t>Аварийное освещение Вега 60 2Ex Тех  IP65</t>
-  </si>
-  <si>
-    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Профиль PSM (3000) арт. 34181</t>
-  </si>
-  <si>
-    <t>Плата питания ПСМ.11.00.00.01-02</t>
-  </si>
-  <si>
-    <t>Плата печатная ПСМ.11.00.01.01-02</t>
-  </si>
-  <si>
-    <t>Пластина для заземления PTCE арт. 37501</t>
-  </si>
-  <si>
-    <t>Пластина анкерная 120</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 4.1.1</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 2.1.1</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 4.1.1</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 2.1.1</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
   </si>
   <si>
     <t>Металлический лоток, неперфорированный (100х50х3000)</t>
   </si>
   <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
     <t>Автолак акриловый бесцветный Auton спрей 520мл</t>
   </si>
   <si>
+    <t>Труба D1020х26 ст.09Г2С-К52 ГОСТ 20295-85</t>
+  </si>
+  <si>
+    <t>Труба D34х4 Ст.09Г2С ГОСТ8733-75</t>
+  </si>
+  <si>
+    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D32х3 Ст.09Г2С ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D34х3,5 Ст.09Г2С ГОСТ10705-80</t>
+  </si>
+  <si>
+    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D57х4 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
+  </si>
+  <si>
+    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D720х20 Ст.09Г2С-К50 ГОСТ 20295-85</t>
+  </si>
+  <si>
+    <t>Труба D83х12 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D93х4-В-20 ГОСТ32528</t>
+  </si>
+  <si>
+    <t>Труба D219х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
+  </si>
+  <si>
+    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>Труба D110х16 ГОСТ 8734-75/ Ст.20 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D14х2 09Г2С ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D152х5 09Г2С ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D159х14 ГОСТ 8732-78/ Ст.09Г2С-3 ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D219х12 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
+  </si>
+  <si>
+    <t>Труба D273х16 Ст.09Г2С-3 ГОСТ 8731-87</t>
+  </si>
+  <si>
+    <t>Труба D32х4 Ст.09Г2С ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 219х4-25 16ГС-3 ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 1020х26 09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 720х20-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Швеллер №20У ГОСТ 8240-97/ 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Труба профильная 25х25х1,5 ГОСТ 8639-82/ В 20 ГОСТ 13663-86</t>
+  </si>
+  <si>
+    <t>Швеллер №5П ГОСТ 8240-97/ Ст.09Г2С ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.3пс5-св ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Профиль 50х25х5 Ст3сп-ГОСТ 30245-2012 L=125мм</t>
+  </si>
+  <si>
+    <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Уголок 30х30х3-В ГОСТ 8509-93/ Ст.3сп3-1 ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Уголок 63х63х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Уголок 75х75х5 ГОСТ 8509-93/ 09Г2С 535-88</t>
+  </si>
+  <si>
+    <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
+  </si>
+  <si>
+    <t>Швеллер 16У ГОСТ 8240-97 / 09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Швеллер 20У ГОСТ 8240-97 / Ст3сп ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Швеллер 8П ГОСТ 8240-97/Ст3сп ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
+  </si>
+  <si>
+    <t>Уголок 40х40х3 ГОСТ 8509-93/ Ст3пс ГОСТ 535-88</t>
+  </si>
+  <si>
+    <t>Труба D20х5 БрКМц 3-1 ГОСТ 1208-2014</t>
+  </si>
+  <si>
+    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
+  </si>
+  <si>
+    <t>Труба ДКРПТ 8х1 М2 ГОСТ 617-90 (отгружать L кратно 2,5м, либо бухтами)</t>
+  </si>
+  <si>
     <t>Фланец 150-40-11-1-F-09Г2С ГОСТ 33259-2015</t>
   </si>
   <si>
-    <t>Труба D1020х26 ст.09Г2С-К52 ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>Труба D110х16 ГОСТ 8734-75/ Ст.20 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D426х50 Ст.20 ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D34х4 Ст.09Г2С ГОСТ8733-75</t>
-  </si>
-  <si>
-    <t>Труба D34х3,5 Ст.09Г2С ГОСТ10705-80</t>
-  </si>
-  <si>
-    <t>Труба D32х4 Ст.09Г2С ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D32х3 Ст.09Г2С ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D273х16 Ст.09Г2С-3 ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Труба D42х10 Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D480х16 10Г2 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D57х4 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
-  </si>
-  <si>
-    <t>Труба D65х14 Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D720х20 Ст.09Г2С-К50 ГОСТ 20295-85</t>
-  </si>
-  <si>
-    <t>Труба D73х9 Ст20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D83х12 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Труба D83х9 Ст.40Х ГОСТ 8731-87</t>
-  </si>
-  <si>
-    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D93х4-В-20 ГОСТ32528</t>
-  </si>
-  <si>
-    <t>Труба D114х28 ГОСТ 8732-78/ Ст.20 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D14х2 09Г2С ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D152х5 09Г2С ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>Труба D159х10 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D159х14 ГОСТ 8732-78/ Ст.09Г2С-3 ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D219х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
-  </si>
-  <si>
-    <t>Труба D219х12 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D219х18 Ст.09ГС ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D273х10 ГОСТ 8732-78/ 09Г2С ГОСТ 30564-98</t>
-  </si>
-  <si>
-    <t>Днище 1020х26 09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 219х4-25 16ГС-3 ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 720х20-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Профиль 50х25х5 Ст3сп-ГОСТ 30245-2012 L=125мм</t>
-  </si>
-  <si>
-    <t>Труба профильная 25х25х1,5 ГОСТ 8639-82/ В 20 ГОСТ 13663-86</t>
-  </si>
-  <si>
-    <t>Труба профильная 50х25х4 09Г2С ГОСТ 8645-68</t>
-  </si>
-  <si>
-    <t>Уголок 30х30х3-В ГОСТ 8509-93/ Ст.3сп3-1 ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Уголок 40х40х3 ГОСТ 8509-93/ Ст3пс ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х5 ГОСТ 8509-93/ Ст.3пс5-св ГОСТ 535-88</t>
-  </si>
-  <si>
-    <t>Уголок 63х63х5 ГОСТ 8509-93/ Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Уголок 75х75х5 ГОСТ 8509-93/ 09Г2С 535-88</t>
-  </si>
-  <si>
-    <t>Швеллер 16П ГОСТ 8240-97 / 09Г2С ГОСТ19281-2014</t>
-  </si>
-  <si>
-    <t>Швеллер 16У ГОСТ 8240-97 / 09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Швеллер 20У ГОСТ 8240-97 / Ст3сп ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Швеллер 8П ГОСТ 8240-97/Ст3сп ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Швеллер №20У ГОСТ 8240-97/ 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Швеллер №5П ГОСТ 8240-97/ Ст.09Г2С ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Труба профильная 80х80х5 ГОСТ 30245-2003/ 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Уголок 25х25х3 ГОСТ 8509-93/ Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Труба ДКРПТ 8х1 М2 ГОСТ 617-90 (отгружать L кратно 2,5м, либо бухтами)</t>
-  </si>
-  <si>
-    <t>Труба D83*10 Ст.12Х18Н10Т ГОСТ 5949-72</t>
-  </si>
-  <si>
-    <t>Труба D20х5 БрКМц 3-1 ГОСТ 1208-2014</t>
+    <t>Фланец 80-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 150-40-11-1-Е-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 3-250-63 Ст.09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Фланец 3-500-63 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 50-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 50-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-63-11-1-J-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец ANSI CL300-3'' Ду80 - заготовка поковка ст.09Г2С</t>
+  </si>
+  <si>
+    <t>Фланец х-50-63 ГОСТ 12821 (заготовка-поковка Ст.13ХФА гр.IV КП195 ГОСТ 8479-70)</t>
   </si>
   <si>
     <t>Фланец 150-63-11-1-J-09Г2С-IV ГОСТ 33259-2015</t>
   </si>
   <si>
-    <t>Фланец 150-40-11-1-Е-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
     <t>Фланец 200-63-11-1-J 09Г2С-IV ГОСТ 33259-2015</t>
   </si>
   <si>
-    <t>Фланец 3-250-63 Ст.09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
-    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Фланец 3-500-63 09Г2С ГОСТ 12821-80</t>
-  </si>
-  <si>
-    <t>Фланец 50-40-11-1-E-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 50-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
     <t>Фланец 50-63-11-1-J 09Г2С-IV ГОСТ 33259-2015</t>
   </si>
   <si>
-    <t>Фланец 80-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 80-40-11-1-F-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 80-63-11-1-J-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец ANSI CL300-3'' Ду80 - заготовка поковка ст.09Г2С</t>
-  </si>
-  <si>
-    <t>Фланец х-50-63 ГОСТ 12821 (заготовка-поковка Ст.13ХФА гр.IV КП195 ГОСТ 8479-70)</t>
+    <t>Картридж Standart TK-1170 7,2k 750</t>
+  </si>
+  <si>
+    <t>Кассета подачи бумаги в сборе CT-1150 для Kyocera</t>
+  </si>
+  <si>
+    <t>Печка FK-1150</t>
   </si>
   <si>
     <t>Узел барабана DК-1150 (c двухслойным ракелем) для Kyocera</t>
   </si>
   <si>
-    <t>Печка FK-1150</t>
-  </si>
-  <si>
-    <t>Кассета подачи бумаги в сборе CT-1150 для Kyocera</t>
-  </si>
-  <si>
-    <t>Картридж Standart TK-1170 7,2k 750</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+    <t>Шпилька АМ30-6gх160.60.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька М30-6gх160.30.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька М20х110 ГОСТ 9066-75 ст 40Х</t>
+  </si>
+  <si>
+    <t>Шпилька АМ20-6gx120.40. 20 IV.2. ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька А1М30-6gx180.09Г2С (оцинк.) ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька А1М20-6gх120.48.40Х.IV.1 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Гайка М16.5.019 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Саморез 4,2х19 оцинк. со сверлом</t>
+  </si>
+  <si>
+    <t>Болт М16-6gх110.58 ГОСТ 7805-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх16 56.35.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gх40.58 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Винт М4-6gх16.58.019 ГОСТ 17473-80</t>
+  </si>
+  <si>
+    <t>Винт М6-6gх16.58.019 ГОСТ 17475-80</t>
+  </si>
+  <si>
+    <t>Гайка АМ30-6Н.20.III.4.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка АМ36-6Н.20lll.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>Гайка М20 ГОСТ 9064 -75</t>
+  </si>
+  <si>
+    <t>Гайка М24 оцинк. ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Гвозди П1,6х25 ГОСТ 4028-63</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х10</t>
+  </si>
+  <si>
+    <t>Заклепка 4,8х8 оцинкованная</t>
+  </si>
+  <si>
+    <t>Заклепка вытяжная 3,2х8-NiCu/SSt ISO 16584</t>
+  </si>
+  <si>
+    <t>Заклепка вытяжная Al 4,0х8 din 7337</t>
+  </si>
+  <si>
+    <t>Шайба 12 65Г 06 ГОСТ 6402-70</t>
   </si>
   <si>
     <t>Шайба 12 ГОСТ 11371-78</t>
@@ -1035,108 +1116,33 @@
     <t>Шайба С.16.05.019 ГОСТ 11371-78</t>
   </si>
   <si>
-    <t>Шпилька А1М20-6gх120.48.40Х.IV.1 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шайба 12 65Г 06 ГОСТ 6402-70</t>
+    <t>Шпилька М24х130 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шпилька М20х130 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Гайка М30 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
+  </si>
+  <si>
+    <t>Шпилька АМ36-6gх190.48.35.III.4.019 ГОСТ 9066-75</t>
   </si>
   <si>
     <t>Шайба 10.02.019 ГОСТ 11371-78</t>
   </si>
   <si>
-    <t>Шпилька А1М30-6gx180.09Г2С (оцинк.) ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька АМ20-6gx120.40. 20 IV.2. ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька АМ36-6gх190.48.35.III.4.019 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Заклепка вытяжная Al 4,0х8 din 7337</t>
-  </si>
-  <si>
-    <t>Шпилька М16-6gх260.58.35Х.026 ГОСТ 22042-76</t>
-  </si>
-  <si>
-    <t>Заклепка вытяжная 3,2х8-NiCu/SSt ISO 16584</t>
-  </si>
-  <si>
-    <t>Шпилька М20х110 ГОСТ 9066-75 ст 40Х</t>
-  </si>
-  <si>
-    <t>Шпилька М20х130 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Заклепка 4,8х8 оцинкованная</t>
-  </si>
-  <si>
-    <t>Заклепка 4,8х10</t>
-  </si>
-  <si>
-    <t>Гвозди П1,6х25 ГОСТ 4028-63</t>
-  </si>
-  <si>
-    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Гайка М30 ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Гайка М24 оцинк. ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Гайка М20 ГОСТ 9064 -75</t>
-  </si>
-  <si>
-    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
-  </si>
-  <si>
-    <t>Шпилька М24х130 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька М30-6gх160.30.35.III.4.019 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шпилька АМ30-6gх160.60.1 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Гайка АМ30-6Н.20.III.4.019 ГОСТ 9064-75</t>
-  </si>
-  <si>
     <t>Гайка М48 ГОСТ 9064-75</t>
   </si>
   <si>
+    <t>Шпилька М48х260 ГОСТ 9064-75</t>
+  </si>
+  <si>
     <t>Шайба 48.1 ГОСТ 9065-75</t>
   </si>
   <si>
-    <t>Шпилька М48х260 ГОСТ 9064-75</t>
-  </si>
-  <si>
-    <t>Винт М6-6gх16.58.019 ГОСТ 17475-80</t>
-  </si>
-  <si>
-    <t>Винт М4-6gх16.58.019 ГОСТ 17473-80</t>
-  </si>
-  <si>
-    <t>Болт М8-6gх40.58 ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Болт М8-6gх16 56.35.019 ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Болт М16-6gх110.58 ГОСТ 7805-70</t>
-  </si>
-  <si>
-    <t>Саморез 4,2х19 оцинк. со сверлом</t>
-  </si>
-  <si>
-    <t>Гайка М16.5.019 ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Гайка АМ36-6Н.20lll.019 ГОСТ 9064-75</t>
-  </si>
-  <si>
     <t>Шкаф управления</t>
   </si>
   <si>
@@ -1146,15 +1152,15 @@
     <t>Гайка АМ24-6Н.09Г2С (оцинк.) ГОСТ 9064-75</t>
   </si>
   <si>
+    <t>Болт М24x2-6gx55 ГОСТ 7798-70</t>
+  </si>
+  <si>
     <t>Гайка АМ20х1,5-6Н.1 ГОСТ 9064-75</t>
   </si>
   <si>
     <t>Гайка АМ16-6Н.20.III.4 ГОСТ 9064-75</t>
   </si>
   <si>
-    <t>Болт М24x2-6gx55 ГОСТ 7798-70</t>
-  </si>
-  <si>
     <t>Герметик силиконовый универс. белый 310мл</t>
   </si>
   <si>
@@ -1167,46 +1173,172 @@
     <t>Лист ПВЛ 506 09Г2С ГОСТ 19281-2014</t>
   </si>
   <si>
-    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
-  </si>
-  <si>
-    <t>Пост кнопочный взрывозащищенный ПВК-15 IP65 2ExеdIIСТ6</t>
-  </si>
-  <si>
-    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
-  </si>
-  <si>
     <t>Прокладка 1-1-150-63-08кп ГОСТ Р 53561-2009</t>
   </si>
   <si>
     <t>Прокладка 1-1-80-63-08кп ГОСТ Р 53561-2009</t>
   </si>
   <si>
+    <t>Прокладка Б-150-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-16-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-25-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-80-16-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
+    <t>Прокладка Б-80-40-ПМБ ГОСТ 15180-86</t>
+  </si>
+  <si>
     <t>Прокладка 1-1-50-63-08кп ГОСТ Р 53561-2009</t>
   </si>
   <si>
-    <t>Прокладка Б-150-40-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>Прокладка Б-50-16-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>Прокладка Б-50-25-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>Прокладка Б-50-40-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>Прокладка Б-80-16-ПМБ ГОСТ 15180-86</t>
-  </si>
-  <si>
-    <t>Прокладка Б-80-40-ПМБ ГОСТ 15180-86</t>
+    <t>Гайка М30.7Н.09Г2С ОСТ 26-2041-96</t>
   </si>
   <si>
     <t>Гайка М20.7H.09Г2С.019 ОСТ 26-2041-96</t>
   </si>
   <si>
-    <t>Гайка М30.7Н.09Г2С ОСТ 26-2041-96</t>
+    <t>Круг D370 Ст.20 ГОСТ1050-88</t>
+  </si>
+  <si>
+    <t>Труба D159х10 Ст.20 ГОСТ 8732-78</t>
+  </si>
+  <si>
+    <t>Круг D60 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Кольцо 065-075-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-090-58 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 112-118-36 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Тройник 159х8 09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Отвод 60-89х6-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 45-89х8-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 45-89х6-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Заглушка 219х12 09Г2С ГОСТ 17379-01</t>
+  </si>
+  <si>
+    <t>Отвод 90-57х6 09Г2С ГОСТ 17375-01</t>
+  </si>
+  <si>
+    <t>Отвод 90-32х3,5 ст.09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 90-159х8 09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 90-159х10-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 90-108х8 ст.09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 90 89х6 ст.09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 60-89х8-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Заглушка 159х8 ст.09Г2С ГОСТ 17379-2001</t>
+  </si>
+  <si>
+    <t>Заглушка 159х10 ст.09Г2С ГОСТ 17379-01</t>
+  </si>
+  <si>
+    <t>Заглушка 108х8-09Г2С ГОСТ 17379-2001</t>
+  </si>
+  <si>
+    <t>Заглушка 2-250-63-09Г2С АТК 24.200.02-90</t>
+  </si>
+  <si>
+    <t>Заглушка 2-500-6,3 09Г2С АТК 24.200.0. 2-90</t>
+  </si>
+  <si>
+    <t>Отвод 90-219х12-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 90-89х6-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Тройник 57х5 09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Тройник 89х8 ст.09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Тройник 89х6 ст.09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Тройник 159х10 ст.09Г2С ГОСТ 17376-01</t>
+  </si>
+  <si>
+    <t>Тройник 114х9 ст.20 ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Переход 89х8-76х8 ст. 09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход 89х8-76х6 ст.09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход 89х6-76х6 ст.09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Отвод 90-89х8 Ст.09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Переход 89х6-57х6 ст.09Г2С ГОСТ 17378-2001</t>
+  </si>
+  <si>
+    <t>Переход 57х6-89х8 09Г2С ГОСТ 17378-2001</t>
+  </si>
+  <si>
+    <t>Переход 159х8-108х8 ст.09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход 159х10-89х8 ст 09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход 108х8-89х8 ст. 09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход 108х6-89х6 ст.09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Труба D250х0,5 мм спирально-замковая оцинк.</t>
+  </si>
+  <si>
+    <t>Решетка вентиляционная  не регулируемая 300 мм х 300 мм</t>
+  </si>
+  <si>
+    <t>Вставка гибкая ВГ 250</t>
+  </si>
+  <si>
+    <t>Вентилятор ВО 06-300 И1; №2,5; 0,37кВт; 1350 об/мин вз/защищ</t>
+  </si>
+  <si>
+    <t>Ниппель 250</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1775,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F344"/>
+  <dimension ref="A1:F387"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
@@ -1794,7 +1926,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>16</v>
@@ -1806,13 +1938,13 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="5">
         <v>10</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>16</v>
@@ -1824,13 +1956,13 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="5">
         <v>10</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>16</v>
@@ -1845,10 +1977,10 @@
         <v>21</v>
       </c>
       <c r="D11" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>16</v>
@@ -1866,7 +1998,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>16</v>
@@ -1881,10 +2013,10 @@
         <v>23</v>
       </c>
       <c r="D13" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>16</v>
@@ -1899,10 +2031,10 @@
         <v>24</v>
       </c>
       <c r="D14" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>16</v>
@@ -1920,7 +2052,7 @@
         <v>10</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>16</v>
@@ -1935,10 +2067,10 @@
         <v>26</v>
       </c>
       <c r="D16" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>16</v>
@@ -1950,16 +2082,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D17" s="5">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="E17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1968,7 +2100,7 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D18" s="5">
         <v>40</v>
@@ -1977,7 +2109,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1986,16 +2118,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D19" s="5">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2004,16 +2136,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D20" s="5">
-        <v>193</v>
+        <v>12</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2022,16 +2154,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D21" s="5">
-        <v>28.5</v>
+        <v>24</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2040,16 +2172,16 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D22" s="5">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2058,16 +2190,16 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D23" s="5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2076,16 +2208,16 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D24" s="5">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2094,16 +2226,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D25" s="5">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2112,16 +2244,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D26" s="5">
-        <v>56</v>
+        <v>28.5</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2130,16 +2262,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D27" s="5">
-        <v>24</v>
+        <v>342</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2148,16 +2280,16 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D28" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2166,16 +2298,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D29" s="5">
-        <v>144</v>
+        <v>861.2</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2184,16 +2316,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D30" s="5">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2202,16 +2334,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D31" s="5">
-        <v>75</v>
+        <v>288</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2220,52 +2352,52 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D32" s="5">
-        <v>8</v>
+        <v>100.8</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D33" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D34" s="5">
-        <v>10</v>
+        <v>189</v>
+      </c>
+      <c r="D34" s="7">
+        <v>1199</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2274,16 +2406,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" s="5">
+        <v>274.8</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="D35" s="5">
-        <v>3</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2292,16 +2424,16 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D36" s="5">
-        <v>396.5</v>
+        <v>16.8</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2310,16 +2442,16 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D37" s="5">
-        <v>48</v>
+        <v>602.20000000000005</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2328,16 +2460,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D38" s="5">
-        <v>320</v>
+        <v>259</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2346,16 +2478,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>190</v>
+        <v>31</v>
       </c>
       <c r="D39" s="5">
         <v>16</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2364,16 +2496,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D40" s="5">
-        <v>0.6</v>
+        <v>989</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2382,16 +2514,16 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D41" s="5">
-        <v>989</v>
+        <v>56</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2400,16 +2532,16 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D42" s="5">
-        <v>288</v>
+        <v>0.6</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2418,16 +2550,16 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D43" s="5">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2436,16 +2568,16 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D44" s="5">
-        <v>861.2</v>
+        <v>40</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2454,16 +2586,16 @@
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D45" s="5">
+        <v>10</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2472,16 +2604,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D46" s="5">
-        <v>10</v>
+        <v>200</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1040</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2490,16 +2622,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D47" s="5">
         <v>40</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2508,16 +2640,16 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D48" s="5">
-        <v>16.8</v>
+        <v>396.5</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2526,16 +2658,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D49" s="5">
-        <v>602.20000000000005</v>
+        <v>48</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2544,16 +2676,16 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D50" s="7">
-        <v>1040</v>
+        <v>204</v>
+      </c>
+      <c r="D50" s="5">
+        <v>16</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2562,16 +2694,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D51" s="5">
-        <v>259</v>
+        <v>76</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2580,16 +2712,16 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D52" s="5">
-        <v>274.8</v>
+        <v>560</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2598,34 +2730,34 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D53" s="5">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>53</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D54" s="7">
-        <v>1199</v>
+        <v>32</v>
+      </c>
+      <c r="D54" s="5">
+        <v>24</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2634,16 +2766,16 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D55" s="5">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2652,16 +2784,16 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D56" s="5">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2670,16 +2802,16 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D57" s="5">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2688,34 +2820,34 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D58" s="5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>58</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D59" s="5">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2724,16 +2856,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D60" s="5">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2742,16 +2874,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D61" s="5">
-        <v>100.8</v>
+        <v>32</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2760,16 +2892,16 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D62" s="5">
-        <v>88</v>
+        <v>400</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2778,16 +2910,16 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="D63" s="5">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2796,16 +2928,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D64" s="5">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2814,70 +2946,70 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="D65" s="5">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D66" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>66</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>216</v>
+        <v>33</v>
       </c>
       <c r="D67" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D68" s="5">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2886,16 +3018,16 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D69" s="5">
-        <v>112</v>
+        <v>900</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2904,16 +3036,16 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D70" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2922,16 +3054,16 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="D71" s="5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2940,16 +3072,16 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
       <c r="D72" s="5">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2958,16 +3090,16 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>222</v>
+        <v>36</v>
       </c>
       <c r="D73" s="5">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2976,16 +3108,16 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>223</v>
+        <v>37</v>
       </c>
       <c r="D74" s="5">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2994,16 +3126,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D75" s="5">
-        <v>560</v>
+        <v>144</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3012,16 +3144,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D76" s="5">
-        <v>400</v>
+        <v>8</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3030,16 +3162,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D77" s="5">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3048,7 +3180,7 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D78" s="5">
         <v>8</v>
@@ -3057,7 +3189,7 @@
         <v>7</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3066,16 +3198,16 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D79" s="5">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3084,16 +3216,16 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D80" s="5">
-        <v>8</v>
+        <v>320</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3102,16 +3234,16 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D81" s="5">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3120,16 +3252,16 @@
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>37</v>
+        <v>230</v>
       </c>
       <c r="D82" s="5">
-        <v>42</v>
+        <v>298</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3138,34 +3270,34 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>38</v>
+        <v>231</v>
       </c>
       <c r="D83" s="5">
-        <v>153</v>
+        <v>422</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>39</v>
+        <v>232</v>
       </c>
       <c r="D84" s="5">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3174,43 +3306,43 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>40</v>
+        <v>233</v>
       </c>
       <c r="D85" s="5">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>85</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>41</v>
+        <v>234</v>
       </c>
       <c r="D86" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>86</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D87" s="5">
         <v>8</v>
@@ -3219,7 +3351,7 @@
         <v>7</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3228,16 +3360,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>232</v>
+        <v>39</v>
       </c>
       <c r="D88" s="5">
-        <v>900</v>
+        <v>3</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3246,16 +3378,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D89" s="5">
-        <v>422</v>
+        <v>88</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3264,16 +3396,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D90" s="5">
-        <v>298</v>
+        <v>32</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3282,16 +3414,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D91" s="5">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3300,16 +3432,16 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D92" s="5">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3318,88 +3450,88 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D93" s="5">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D94" s="5">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>94</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D95" s="5">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D96" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D97" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3408,7 +3540,7 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D98" s="5">
         <v>8</v>
@@ -3417,7 +3549,7 @@
         <v>7</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3426,16 +3558,16 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D99" s="5">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3444,7 +3576,7 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D100" s="5">
         <v>144</v>
@@ -3453,7 +3585,7 @@
         <v>7</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3462,16 +3594,16 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D101" s="5">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3480,7 +3612,7 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D102" s="5">
         <v>64</v>
@@ -3489,7 +3621,7 @@
         <v>7</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3498,16 +3630,16 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D103" s="5">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3516,7 +3648,7 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D104" s="5">
         <v>0.4</v>
@@ -3534,16 +3666,16 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D105" s="5">
-        <v>10</v>
+        <v>4.5750000000000002</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3552,16 +3684,16 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D106" s="5">
-        <v>4.5750000000000002</v>
+        <v>2.35</v>
       </c>
       <c r="E106" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F106" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3570,16 +3702,16 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D107" s="5">
-        <v>14</v>
+        <v>15.95</v>
       </c>
       <c r="E107" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F107" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3588,16 +3720,16 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>46</v>
+        <v>255</v>
       </c>
       <c r="D108" s="5">
-        <v>8.9700000000000006</v>
+        <v>27.45</v>
       </c>
       <c r="E108" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3606,16 +3738,16 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="D109" s="7">
-        <v>1371.68</v>
+        <v>256</v>
+      </c>
+      <c r="D109" s="5">
+        <v>17.760000000000002</v>
       </c>
       <c r="E109" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F109" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3624,16 +3756,16 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D110" s="5">
-        <v>15.95</v>
+        <v>257</v>
+      </c>
+      <c r="D110" s="7">
+        <v>1371.68</v>
       </c>
       <c r="E110" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F110" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3642,16 +3774,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D111" s="5">
-        <v>2.35</v>
+        <v>183</v>
       </c>
       <c r="E111" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3660,16 +3792,16 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D112" s="5">
-        <v>17.760000000000002</v>
+        <v>1.68</v>
       </c>
       <c r="E112" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3678,16 +3810,16 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D113" s="5">
-        <v>25.47</v>
+        <v>803.05</v>
       </c>
       <c r="E113" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F113" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3696,16 +3828,16 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D114" s="5">
-        <v>27.45</v>
+        <v>13.28</v>
       </c>
       <c r="E114" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F114" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3714,16 +3846,16 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D115" s="5">
-        <v>67.98</v>
+        <v>26.67</v>
       </c>
       <c r="E115" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3732,16 +3864,16 @@
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D116" s="5">
-        <v>15.95</v>
+        <v>263</v>
+      </c>
+      <c r="D116" s="7">
+        <v>2077.35</v>
       </c>
       <c r="E116" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F116" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3750,16 +3882,16 @@
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D117" s="5">
-        <v>13.76</v>
+        <v>5.52</v>
       </c>
       <c r="E117" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3768,16 +3900,16 @@
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="D118" s="5">
-        <v>183</v>
+        <v>265</v>
+      </c>
+      <c r="D118" s="7">
+        <v>3123.56</v>
       </c>
       <c r="E118" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F118" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3786,16 +3918,16 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="D119" s="5">
-        <v>1.68</v>
+        <v>266</v>
+      </c>
+      <c r="D119" s="7">
+        <v>2549.337</v>
       </c>
       <c r="E119" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F119" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3804,16 +3936,16 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D120" s="5">
-        <v>15.44</v>
+        <v>11.84</v>
       </c>
       <c r="E120" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F120" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3822,16 +3954,16 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D121" s="5">
-        <v>803.05</v>
+        <v>94.4</v>
       </c>
       <c r="E121" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F121" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3840,16 +3972,16 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D122" s="5">
-        <v>13.28</v>
+        <v>97.2</v>
       </c>
       <c r="E122" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F122" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3858,16 +3990,16 @@
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D123" s="5">
-        <v>26.67</v>
+        <v>13.76</v>
       </c>
       <c r="E123" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F123" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3876,16 +4008,16 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="D124" s="7">
-        <v>2077.35</v>
+        <v>271</v>
+      </c>
+      <c r="D124" s="5">
+        <v>11.36</v>
       </c>
       <c r="E124" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F124" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3894,16 +4026,16 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D125" s="5">
-        <v>11.36</v>
+        <v>31.76</v>
       </c>
       <c r="E125" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F125" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3912,16 +4044,16 @@
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>268</v>
+        <v>45</v>
       </c>
       <c r="D126" s="5">
-        <v>5.52</v>
+        <v>832.5</v>
       </c>
       <c r="E126" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F126" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3930,16 +4062,16 @@
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>269</v>
+        <v>46</v>
       </c>
       <c r="D127" s="5">
-        <v>31.76</v>
+        <v>15.95</v>
       </c>
       <c r="E127" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F127" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3948,16 +4080,16 @@
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="D128" s="7">
-        <v>3123.56</v>
+        <v>47</v>
+      </c>
+      <c r="D128" s="5">
+        <v>8.9700000000000006</v>
       </c>
       <c r="E128" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F128" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3966,16 +4098,16 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D129" s="7">
-        <v>2549.337</v>
+        <v>273</v>
+      </c>
+      <c r="D129" s="5">
+        <v>14</v>
       </c>
       <c r="E129" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F129" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3984,16 +4116,16 @@
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D130" s="5">
-        <v>11.84</v>
+        <v>47.52</v>
       </c>
       <c r="E130" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F130" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4002,16 +4134,16 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D131" s="5">
-        <v>47.52</v>
+        <v>8</v>
       </c>
       <c r="E131" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F131" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4020,16 +4152,16 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D132" s="5">
-        <v>8</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="E132" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F132" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4038,16 +4170,16 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="D133" s="5">
-        <v>8.5500000000000007</v>
+        <v>277</v>
+      </c>
+      <c r="D133" s="7">
+        <v>1284.922</v>
       </c>
       <c r="E133" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F133" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F133" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4056,16 +4188,16 @@
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="D134" s="7">
-        <v>1284.922</v>
+        <v>278</v>
+      </c>
+      <c r="D134" s="5">
+        <v>29.1</v>
       </c>
       <c r="E134" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F134" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4074,16 +4206,16 @@
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="D135" s="5">
-        <v>29.1</v>
+        <v>279</v>
+      </c>
+      <c r="D135" s="7">
+        <v>1711.45</v>
       </c>
       <c r="E135" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F135" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F135" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4092,16 +4224,16 @@
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D136" s="5">
-        <v>94.4</v>
+        <v>82.14</v>
       </c>
       <c r="E136" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F136" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F136" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4110,16 +4242,16 @@
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D137" s="5">
-        <v>82.14</v>
+        <v>15.44</v>
       </c>
       <c r="E137" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F137" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4128,16 +4260,16 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D138" s="5">
-        <v>97.2</v>
+        <v>103.04</v>
       </c>
       <c r="E138" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F138" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4146,16 +4278,16 @@
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>48</v>
+        <v>283</v>
       </c>
       <c r="D139" s="5">
-        <v>832.5</v>
+        <v>67.98</v>
       </c>
       <c r="E139" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F139" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4164,16 +4296,16 @@
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D140" s="7">
-        <v>1711.45</v>
+        <v>284</v>
+      </c>
+      <c r="D140" s="5">
+        <v>25.47</v>
       </c>
       <c r="E140" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F140" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4182,16 +4314,16 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D141" s="5">
-        <v>103.04</v>
+        <v>10</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4200,7 +4332,7 @@
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D142" s="5">
         <v>6</v>
@@ -4209,7 +4341,7 @@
         <v>7</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4218,7 +4350,7 @@
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D143" s="5">
         <v>6</v>
@@ -4227,7 +4359,7 @@
         <v>7</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4236,16 +4368,16 @@
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D144" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4254,13 +4386,13 @@
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D145" s="5">
-        <v>6</v>
+        <v>289</v>
+      </c>
+      <c r="D145" s="7">
+        <v>6015.74</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>49</v>
@@ -4272,16 +4404,16 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="D146" s="5">
-        <v>13.4</v>
+        <v>209</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4290,16 +4422,16 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D147" s="5">
-        <v>41</v>
+        <v>789.92</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4308,16 +4440,16 @@
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D148" s="5">
-        <v>209</v>
+        <v>55.56</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4326,16 +4458,16 @@
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="D149" s="7">
-        <v>3613.62</v>
+        <v>50</v>
+      </c>
+      <c r="D149" s="5">
+        <v>13.4</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4344,16 +4476,16 @@
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D150" s="5">
-        <v>6.48</v>
+        <v>41</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4362,16 +4494,16 @@
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D151" s="5">
-        <v>16.2</v>
+        <v>294</v>
+      </c>
+      <c r="D151" s="7">
+        <v>9355.9599999999991</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4380,16 +4512,16 @@
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D152" s="5">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4398,16 +4530,16 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D153" s="7">
-        <v>2115.44</v>
+        <v>296</v>
+      </c>
+      <c r="D153" s="5">
+        <v>6.48</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4416,16 +4548,16 @@
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D154" s="5">
-        <v>55.56</v>
+        <v>168</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4434,16 +4566,16 @@
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="D155" s="5">
-        <v>774.47</v>
+        <v>298</v>
+      </c>
+      <c r="D155" s="7">
+        <v>2115.44</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4452,16 +4584,16 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D156" s="5">
-        <v>226.24</v>
+        <v>774.47</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4470,16 +4602,16 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="D157" s="7">
-        <v>2471.12</v>
+        <v>300</v>
+      </c>
+      <c r="D157" s="5">
+        <v>226.24</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4488,16 +4620,16 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D158" s="7">
-        <v>1084.0150000000001</v>
+        <v>2471.12</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4506,16 +4638,16 @@
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="D159" s="5">
-        <v>431.68</v>
+        <v>302</v>
+      </c>
+      <c r="D159" s="7">
+        <v>1084.0150000000001</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4524,16 +4656,16 @@
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D160" s="5">
-        <v>57.52</v>
+        <v>431.68</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4542,16 +4674,16 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D161" s="7">
-        <v>6015.74</v>
+        <v>304</v>
+      </c>
+      <c r="D161" s="5">
+        <v>57.52</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4560,16 +4692,16 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="D162" s="5">
-        <v>789.92</v>
+        <v>305</v>
+      </c>
+      <c r="D162" s="7">
+        <v>3613.62</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4578,16 +4710,16 @@
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="D163" s="7">
-        <v>9355.9599999999991</v>
+        <v>306</v>
+      </c>
+      <c r="D163" s="5">
+        <v>16.2</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4596,13 +4728,13 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D164" s="5">
-        <v>114</v>
+        <v>1.2</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>51</v>
@@ -4614,16 +4746,16 @@
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D165" s="5">
-        <v>2.4500000000000002</v>
+        <v>3.44</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4632,16 +4764,16 @@
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D166" s="5">
-        <v>3.44</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4650,13 +4782,13 @@
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D167" s="5">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>52</v>
@@ -4668,16 +4800,16 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D168" s="5">
-        <v>39</v>
+        <v>318</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4686,7 +4818,7 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D169" s="5">
         <v>55</v>
@@ -4695,7 +4827,7 @@
         <v>7</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4704,16 +4836,16 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
       <c r="D170" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4722,16 +4854,16 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D171" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E171" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4740,16 +4872,16 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="8" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D172" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4758,7 +4890,7 @@
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D173" s="5">
         <v>3</v>
@@ -4767,7 +4899,7 @@
         <v>7</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4776,16 +4908,16 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D174" s="5">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4794,16 +4926,16 @@
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="8" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D175" s="5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E175" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4812,16 +4944,16 @@
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="8" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D176" s="5">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4830,16 +4962,16 @@
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="8" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D177" s="5">
-        <v>25</v>
+        <v>303</v>
       </c>
       <c r="E177" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4848,16 +4980,16 @@
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="8" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D178" s="5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4866,16 +4998,16 @@
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="8" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D179" s="5">
-        <v>318</v>
+        <v>18</v>
       </c>
       <c r="E179" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4884,16 +5016,16 @@
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="8" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D180" s="5">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4902,16 +5034,16 @@
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="8" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D181" s="5">
-        <v>303</v>
+        <v>6</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4920,34 +5052,34 @@
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="8" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D182" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="3">
         <v>182</v>
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="8" t="s">
-        <v>322</v>
+        <v>53</v>
       </c>
       <c r="D183" s="5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E183" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4956,7 +5088,7 @@
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="8" t="s">
-        <v>54</v>
+        <v>326</v>
       </c>
       <c r="D184" s="5">
         <v>1</v>
@@ -4974,7 +5106,7 @@
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="8" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D185" s="5">
         <v>1</v>
@@ -4983,7 +5115,7 @@
         <v>7</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4992,7 +5124,7 @@
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="8" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D186" s="5">
         <v>1</v>
@@ -5001,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5010,7 +5142,7 @@
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D187" s="5">
         <v>1</v>
@@ -5019,7 +5151,7 @@
         <v>7</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5028,16 +5160,16 @@
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="8" t="s">
-        <v>326</v>
+        <v>56</v>
       </c>
       <c r="D188" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5046,16 +5178,16 @@
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D189" s="5">
+        <v>5</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F189" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="D189" s="5">
-        <v>2</v>
-      </c>
-      <c r="E189" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F189" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5067,13 +5199,13 @@
         <v>59</v>
       </c>
       <c r="D190" s="5">
+        <v>2</v>
+      </c>
+      <c r="E190" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E190" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="F190" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5085,52 +5217,52 @@
         <v>60</v>
       </c>
       <c r="D191" s="5">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
         <v>191</v>
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D192" s="5">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="3">
         <v>192</v>
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D193" s="5">
+        <v>3</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F193" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D193" s="5">
-        <v>20</v>
-      </c>
-      <c r="E193" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="194" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -5138,17 +5270,17 @@
       <c r="C194" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D194" s="7">
-        <v>30000</v>
+      <c r="D194" s="5">
+        <v>4</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -5157,16 +5289,16 @@
         <v>66</v>
       </c>
       <c r="D195" s="5">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -5174,17 +5306,17 @@
       <c r="C196" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D196" s="5">
-        <v>30</v>
+      <c r="D196" s="7">
+        <v>30000</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="3">
         <v>196</v>
       </c>
@@ -5193,31 +5325,31 @@
         <v>68</v>
       </c>
       <c r="D197" s="5">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>197</v>
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D198" s="5">
+        <v>24</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F198" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D198" s="5">
-        <v>4</v>
-      </c>
-      <c r="E198" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F198" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5226,16 +5358,16 @@
       </c>
       <c r="B199" s="4"/>
       <c r="C199" s="8" t="s">
-        <v>327</v>
+        <v>70</v>
       </c>
       <c r="D199" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E199" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5244,16 +5376,16 @@
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D200" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5262,16 +5394,16 @@
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D201" s="5">
-        <v>96</v>
+        <v>376</v>
       </c>
       <c r="E201" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5280,16 +5412,16 @@
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D202" s="5">
-        <v>48</v>
+        <v>288</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5298,16 +5430,16 @@
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D203" s="5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E203" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5316,16 +5448,16 @@
       </c>
       <c r="B204" s="4"/>
       <c r="C204" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D204" s="5">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5334,16 +5466,16 @@
       </c>
       <c r="B205" s="4"/>
       <c r="C205" s="8" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D205" s="5">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E205" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5352,16 +5484,16 @@
       </c>
       <c r="B206" s="4"/>
       <c r="C206" s="8" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D206" s="5">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5370,16 +5502,16 @@
       </c>
       <c r="B207" s="4"/>
       <c r="C207" s="8" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D207" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E207" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5388,16 +5520,16 @@
       </c>
       <c r="B208" s="4"/>
       <c r="C208" s="8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D208" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5406,16 +5538,16 @@
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="8" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D209" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E209" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5424,16 +5556,16 @@
       </c>
       <c r="B210" s="4"/>
       <c r="C210" s="8" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D210" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5442,16 +5574,16 @@
       </c>
       <c r="B211" s="4"/>
       <c r="C211" s="8" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D211" s="5">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E211" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5460,16 +5592,16 @@
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D212" s="5">
-        <v>288</v>
+        <v>48</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5478,16 +5610,16 @@
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D213" s="5">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E213" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5496,16 +5628,16 @@
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D214" s="5">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5514,16 +5646,16 @@
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="D215" s="5">
-        <v>4</v>
+        <v>346</v>
+      </c>
+      <c r="D215" s="7">
+        <v>1392</v>
       </c>
       <c r="E215" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5532,16 +5664,16 @@
       </c>
       <c r="B216" s="4"/>
       <c r="C216" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D216" s="5">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5550,16 +5682,16 @@
       </c>
       <c r="B217" s="4"/>
       <c r="C217" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D217" s="5">
-        <v>376</v>
+        <v>10</v>
       </c>
       <c r="E217" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5568,16 +5700,16 @@
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="8" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D218" s="5">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5586,7 +5718,7 @@
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D219" s="5">
         <v>60</v>
@@ -5595,7 +5727,7 @@
         <v>7</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5604,7 +5736,7 @@
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="8" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D220" s="5">
         <v>60</v>
@@ -5613,7 +5745,7 @@
         <v>7</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5622,16 +5754,16 @@
       </c>
       <c r="B221" s="4"/>
       <c r="C221" s="8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D221" s="5">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="E221" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5640,16 +5772,16 @@
       </c>
       <c r="B222" s="4"/>
       <c r="C222" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D222" s="5">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5658,16 +5790,16 @@
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D223" s="5">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E223" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5676,16 +5808,16 @@
       </c>
       <c r="B224" s="4"/>
       <c r="C224" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D224" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5694,16 +5826,16 @@
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="D225" s="7">
-        <v>1392</v>
+        <v>356</v>
+      </c>
+      <c r="D225" s="5">
+        <v>96</v>
       </c>
       <c r="E225" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5712,16 +5844,16 @@
       </c>
       <c r="B226" s="4"/>
       <c r="C226" s="8" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D226" s="5">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5730,16 +5862,16 @@
       </c>
       <c r="B227" s="4"/>
       <c r="C227" s="8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D227" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E227" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5748,16 +5880,16 @@
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D228" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5766,16 +5898,16 @@
       </c>
       <c r="B229" s="4"/>
       <c r="C229" s="8" t="s">
-        <v>72</v>
+        <v>360</v>
       </c>
       <c r="D229" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E229" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5784,16 +5916,16 @@
       </c>
       <c r="B230" s="4"/>
       <c r="C230" s="8" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D230" s="5">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5802,16 +5934,16 @@
       </c>
       <c r="B231" s="4"/>
       <c r="C231" s="8" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D231" s="5">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="E231" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5820,16 +5952,16 @@
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="8" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D232" s="5">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5838,16 +5970,16 @@
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="8" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D233" s="5">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E233" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5856,16 +5988,16 @@
       </c>
       <c r="B234" s="4"/>
       <c r="C234" s="8" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D234" s="5">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5874,16 +6006,16 @@
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="8" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D235" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E235" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5892,16 +6024,16 @@
       </c>
       <c r="B236" s="4"/>
       <c r="C236" s="8" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D236" s="5">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5910,16 +6042,16 @@
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="8" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D237" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E237" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5928,16 +6060,16 @@
       </c>
       <c r="B238" s="4"/>
       <c r="C238" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D238" s="5">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5946,16 +6078,16 @@
       </c>
       <c r="B239" s="4"/>
       <c r="C239" s="8" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D239" s="5">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E239" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5964,52 +6096,52 @@
       </c>
       <c r="B240" s="4"/>
       <c r="C240" s="8" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D240" s="5">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="3">
         <v>240</v>
       </c>
       <c r="B241" s="4"/>
       <c r="C241" s="8" t="s">
-        <v>368</v>
+        <v>71</v>
       </c>
       <c r="D241" s="5">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="3">
         <v>241</v>
       </c>
       <c r="B242" s="4"/>
       <c r="C242" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D242" s="5">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6018,16 +6150,16 @@
       </c>
       <c r="B243" s="4"/>
       <c r="C243" s="8" t="s">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="D243" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E243" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F243" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="F243" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6036,16 +6168,16 @@
       </c>
       <c r="B244" s="4"/>
       <c r="C244" s="8" t="s">
-        <v>370</v>
+        <v>75</v>
       </c>
       <c r="D244" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6054,16 +6186,16 @@
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="8" t="s">
-        <v>371</v>
+        <v>76</v>
       </c>
       <c r="D245" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E245" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="246" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6075,13 +6207,13 @@
         <v>77</v>
       </c>
       <c r="D246" s="5">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6090,16 +6222,16 @@
       </c>
       <c r="B247" s="4"/>
       <c r="C247" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D247" s="5">
+        <v>15</v>
+      </c>
+      <c r="E247" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F247" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="D247" s="5">
-        <v>5</v>
-      </c>
-      <c r="E247" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F247" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6108,34 +6240,34 @@
       </c>
       <c r="B248" s="4"/>
       <c r="C248" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D248" s="5">
+        <v>10</v>
+      </c>
+      <c r="E248" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E248" s="6" t="s">
-        <v>80</v>
-      </c>
       <c r="F248" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="3">
         <v>248</v>
       </c>
       <c r="B249" s="4"/>
       <c r="C249" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D249" s="5">
+        <v>10</v>
+      </c>
+      <c r="E249" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F249" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="D249" s="5">
-        <v>46</v>
-      </c>
-      <c r="E249" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F249" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="250" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6144,31 +6276,31 @@
       </c>
       <c r="B250" s="4"/>
       <c r="C250" s="8" t="s">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="D250" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="3">
         <v>250</v>
       </c>
       <c r="B251" s="4"/>
       <c r="C251" s="8" t="s">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="D251" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F251" s="4" t="s">
         <v>84</v>
@@ -6180,16 +6312,16 @@
       </c>
       <c r="B252" s="4"/>
       <c r="C252" s="8" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D252" s="5">
-        <v>4</v>
+        <v>448</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -6198,16 +6330,16 @@
       </c>
       <c r="B253" s="4"/>
       <c r="C253" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="D253" s="5">
-        <v>448</v>
+        <v>377</v>
+      </c>
+ 